--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran.sharepoint.com/sites/PlaneacinyGestinInstitucional-REFORMACURRICULAR/Documentos compartidos/REFORMA CURRICULAR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12502" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA951688-5E9F-4565-BC9E-EA2D00CEF1D9}"/>
+  <xr:revisionPtr revIDLastSave="12508" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7223A297-0BD9-445D-B510-CF5A32594A04}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -26,9 +26,9 @@
     <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Borrador!$C$10:$BL$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Borrador!$C$10:$BL$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -68,83 +68,83 @@
   <commentList>
     <comment ref="J9" authorId="0" shapeId="0" xr:uid="{4909E1DA-D04D-459F-A755-C874E2A2376C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Maria Isabel</t>
       </text>
     </comment>
     <comment ref="S9" authorId="1" shapeId="0" xr:uid="{C5EACC81-0278-4BD6-BE1C-328BE6CEF044}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
     <comment ref="T9" authorId="2" shapeId="0" xr:uid="{07A9C90F-C4AF-4058-8369-82DC7D82B304}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Lina Giraldo</t>
       </text>
     </comment>
     <comment ref="U9" authorId="3" shapeId="0" xr:uid="{33379761-7408-47CA-A73F-96920D166F6F}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero
 </t>
       </text>
     </comment>
     <comment ref="AA9" authorId="4" shapeId="0" xr:uid="{DA888406-B3C3-47EB-94C0-AD38A44E0A0E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Hector</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="5" shapeId="0" xr:uid="{AB292E73-2881-46CA-A2EC-13F131DCF115}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Luis Martín / Jonathan Camilo</t>
       </text>
     </comment>
     <comment ref="AR9" authorId="6" shapeId="0" xr:uid="{469532B5-891A-4F4C-925C-AFAB7020C3BF}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Yady fernanda
 </t>
       </text>
     </comment>
     <comment ref="BD9" authorId="7" shapeId="0" xr:uid="{4F4D565E-CBAD-4B43-8202-B4F4327A7F61}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Ivonne</t>
       </text>
     </comment>
     <comment ref="BQ9" authorId="8" shapeId="0" xr:uid="{7492BF5A-A8EA-4806-BFAF-95DE22CE85C5}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Laura Barrera</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="9" shapeId="0" xr:uid="{EBC3B04C-562F-4E8D-B1E3-F992E17EAF0F}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Aprobación interna </t>
       </text>
     </comment>
@@ -174,124 +174,124 @@
   <commentList>
     <comment ref="J9" authorId="0" shapeId="0" xr:uid="{80B52061-08F6-47ED-A848-F47BBBD771FF}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Maria Isabel</t>
       </text>
     </comment>
     <comment ref="R9" authorId="1" shapeId="0" xr:uid="{D8DA1F30-A300-40F4-B476-925996CD8443}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
     <comment ref="S9" authorId="2" shapeId="0" xr:uid="{7505DC0C-967B-426C-BC16-554113003C7D}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Lina Giraldo</t>
       </text>
     </comment>
     <comment ref="T9" authorId="3" shapeId="0" xr:uid="{E461B7D9-0641-45C6-B1E3-DC5A9AAB3A7F}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero
 </t>
       </text>
     </comment>
     <comment ref="V9" authorId="4" shapeId="0" xr:uid="{3C05002E-BD16-4D38-A66E-AF06581FFA22}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Hector</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="5" shapeId="0" xr:uid="{3AD9E8E6-50E3-4D5D-95F5-5ADA3E45292E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Luis Martín / Jonathan Camilo</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="6" shapeId="0" xr:uid="{A8DE3515-C1E1-49EA-AFBF-F0B22E7FF84F}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Yady fernanda
 </t>
       </text>
     </comment>
     <comment ref="AT9" authorId="7" shapeId="0" xr:uid="{08ACDCC1-6649-4D0D-A86B-69B7D4B48783}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Ivonne</t>
       </text>
     </comment>
     <comment ref="BC9" authorId="8" shapeId="0" xr:uid="{A8FB029E-3F6A-4304-877C-1A3D4AB675EB}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Laura Barrera</t>
       </text>
     </comment>
     <comment ref="R10" authorId="9" shapeId="0" xr:uid="{411F6E4D-EB04-444D-97BB-743F5F223921}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
     <comment ref="S10" authorId="10" shapeId="0" xr:uid="{9429D19F-F6E1-4D65-96A4-BBC6C65BA555}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Lina Giraldo</t>
       </text>
     </comment>
     <comment ref="T10" authorId="11" shapeId="0" xr:uid="{229B08B3-705D-48B7-A5B3-05517A327727}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero
 </t>
       </text>
     </comment>
     <comment ref="Y10" authorId="12" shapeId="0" xr:uid="{98402C78-9325-4277-98CE-1DE573CC177E}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Aprobación interna </t>
       </text>
     </comment>
     <comment ref="AK54" authorId="13" shapeId="0" xr:uid="{60A29768-0473-460C-80A7-6B195BBBC9AA}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Módulos que se hicieron antes de establecer el cronograma de la reforma.</t>
       </text>
     </comment>
     <comment ref="AK56" authorId="14" shapeId="0" xr:uid="{D36016F3-8B56-4D59-B47D-9F6A1EA5603E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Módulos que se hicieron antes de establecer el cronograma de la reforma.</t>
       </text>
     </comment>
@@ -319,108 +319,108 @@
   <commentList>
     <comment ref="J9" authorId="0" shapeId="0" xr:uid="{AB1486C7-AA92-4748-891B-886743035FDC}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Maria Isabel</t>
       </text>
     </comment>
     <comment ref="R9" authorId="1" shapeId="0" xr:uid="{5E2A0871-3C6A-43AF-B856-9A20F44C0E24}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
     <comment ref="S9" authorId="2" shapeId="0" xr:uid="{D2E187A2-AF3B-4B43-AD8A-5A22A99E567B}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Lina Giraldo</t>
       </text>
     </comment>
     <comment ref="T9" authorId="3" shapeId="0" xr:uid="{ED914BC0-A9AD-4460-B4AD-64B21C38754F}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero
 </t>
       </text>
     </comment>
     <comment ref="V9" authorId="4" shapeId="0" xr:uid="{AC196D12-BAF7-4D77-BB76-8DDDB1D1AAED}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Hector</t>
       </text>
     </comment>
     <comment ref="AC9" authorId="5" shapeId="0" xr:uid="{B5416B51-2416-4442-87A8-60557435D0C6}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Luis Martín / Jonathan Camilo</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="6" shapeId="0" xr:uid="{AF20519C-A4E1-4A0C-9814-C243E278D15B}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Yady fernanda
 </t>
       </text>
     </comment>
     <comment ref="AO9" authorId="7" shapeId="0" xr:uid="{6A140D46-EDD4-4F6C-AA4F-2CBC120DF7BC}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Ivonne</t>
       </text>
     </comment>
     <comment ref="AS9" authorId="8" shapeId="0" xr:uid="{1D6AE7E6-0283-49B1-9DFE-C7D5B111CED2}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Laura Barrera</t>
       </text>
     </comment>
     <comment ref="R10" authorId="9" shapeId="0" xr:uid="{E74F1B1E-CE79-46D3-807A-5DC12A7AF859}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
     <comment ref="S10" authorId="10" shapeId="0" xr:uid="{AA67B0D4-AF29-4510-BBF9-3D69C706909F}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Lina Giraldo</t>
       </text>
     </comment>
     <comment ref="T10" authorId="11" shapeId="0" xr:uid="{E23E8F9A-23D4-451D-B6DF-68EA924C4E68}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero
 </t>
       </text>
     </comment>
     <comment ref="Y10" authorId="12" shapeId="0" xr:uid="{0C99F784-E3FA-43BC-809B-1404E6FC59EA}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Aprobación interna </t>
       </text>
     </comment>
@@ -437,17 +437,17 @@
   <commentList>
     <comment ref="C3" authorId="0" shapeId="0" xr:uid="{3D8D95EC-E3AE-4A32-8BE6-752AA4DE3B2A}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
     <comment ref="B14" authorId="1" shapeId="0" xr:uid="{6CD20443-83D8-4BD3-A822-701BF3EC7215}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
@@ -463,9 +463,9 @@
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{243354BE-D8F0-45DF-A6E5-F55CAC4D8EC2}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Diligencia Diana Baquero</t>
       </text>
     </comment>
@@ -474,7 +474,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4631" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4633" uniqueCount="410">
   <si>
     <t>RC</t>
   </si>
@@ -1753,6 +1753,9 @@
   <si>
     <t>Todas las modalidades</t>
   </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
 </sst>
 </file>
 
@@ -1761,7 +1764,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="82" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3702,6 +3705,72 @@
     <xf numFmtId="0" fontId="58" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="60" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -3720,85 +3789,22 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3810,9 +3816,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3820,6 +3823,294 @@
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="86">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEEFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFDC2626"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD97706"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16A34A"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4511,7 +4802,7 @@
         <name val="Nunito Sans"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="d/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -4552,7 +4843,7 @@
         <name val="Nunito Sans"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="d/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -4861,294 +5152,6 @@
         </top>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEEFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFDC2626"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF16A34A"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -5200,8 +5203,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="378278" y="2313214"/>
-          <a:ext cx="2360840" cy="1202871"/>
+          <a:off x="380999" y="2351314"/>
+          <a:ext cx="2427515" cy="1208314"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1121230"/>
         </a:xfrm>
@@ -5408,8 +5411,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5799363" y="2364923"/>
-          <a:ext cx="1985284" cy="1172936"/>
+          <a:off x="5954484" y="2405744"/>
+          <a:ext cx="2013859" cy="1175658"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1090927"/>
         </a:xfrm>
@@ -5642,8 +5645,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2978602" y="2324100"/>
-          <a:ext cx="2690134" cy="1170215"/>
+          <a:off x="3047998" y="2362200"/>
+          <a:ext cx="2775859" cy="1175658"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1090927"/>
         </a:xfrm>
@@ -5867,8 +5870,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7882617" y="2324100"/>
-          <a:ext cx="2087337" cy="1170215"/>
+          <a:off x="8066313" y="2362200"/>
+          <a:ext cx="2144487" cy="1175658"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1090927"/>
         </a:xfrm>
@@ -6105,8 +6108,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10100581" y="2313214"/>
-          <a:ext cx="2087337" cy="1239611"/>
+          <a:off x="10341427" y="2351314"/>
+          <a:ext cx="2144487" cy="1251857"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1262646"/>
         </a:xfrm>
@@ -6333,8 +6336,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12340318" y="2313214"/>
-          <a:ext cx="2087337" cy="1239611"/>
+          <a:off x="12638314" y="2351314"/>
+          <a:ext cx="2144487" cy="1251857"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1262646"/>
         </a:xfrm>
@@ -6615,8 +6618,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="247649" y="4980212"/>
-          <a:ext cx="2013859" cy="1439636"/>
+          <a:off x="250370" y="5018312"/>
+          <a:ext cx="2013859" cy="1447801"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -7960,8 +7963,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14159592" y="4558389"/>
-          <a:ext cx="2822122" cy="1932218"/>
+          <a:off x="14162313" y="4599210"/>
+          <a:ext cx="2822122" cy="1943104"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -8284,57 +8287,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2702B81F-42B0-42CE-8024-EAD267A2A087}" name="Tabla2" displayName="Tabla2" ref="C10:AY70" totalsRowShown="0" tableBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2702B81F-42B0-42CE-8024-EAD267A2A087}" name="Tabla2" displayName="Tabla2" ref="C10:AY70" totalsRowShown="0" tableBorderDxfId="85">
   <autoFilter ref="C10:AY70" xr:uid="{2702B81F-42B0-42CE-8024-EAD267A2A087}"/>
   <tableColumns count="49">
-    <tableColumn id="1" xr3:uid="{20A3EBC3-3DAF-4FB8-9EE8-783061139F75}" name="FACULTAD " dataDxfId="45" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{D028144E-8876-4666-A616-748ECA8EBAB7}" name="ESCUELA " dataDxfId="44" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{20A3EBC3-3DAF-4FB8-9EE8-783061139F75}" name="FACULTAD " dataDxfId="84" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{D028144E-8876-4666-A616-748ECA8EBAB7}" name="ESCUELA " dataDxfId="83" dataCellStyle="Normal 2"/>
     <tableColumn id="3" xr3:uid="{1CE9EC88-A183-42EA-9C04-AC26BBC97E8E}" name="NOMBRE DEL PROGRAMA"/>
-    <tableColumn id="4" xr3:uid="{2EFAD5DC-BB89-46D3-9FC8-3F55A7936A46}" name="MODALIDAD " dataDxfId="43" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{A82C0495-17CD-4853-BC2D-598A9BE98ED9}" name="NIVEL " dataDxfId="42" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{A2734990-A055-4FF8-9E05-D65BDDFB9F2B}" name="SEDE" dataDxfId="41" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{67253687-A94A-42D1-9697-5091A9F94BFF}" name="SNIES VIGENTE " dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{88E2041F-6B31-4A2C-9E79-2B4471FFD8C0}" name="Formato creación de programas Banner" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{135B0583-9D8C-42AB-A884-47E97945D128}" name="Instrumento de verificación curricular" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{3559F58B-EC8A-4DB3-BC40-DAD5A32EAF3E}" name="LA REFORMA CUMPLE CON LA POLITICA CURRICULAR " dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{DEBBC1F6-CF16-424A-B06D-D886277D783E}" name="Formato RA_x000a_Escuelas" dataDxfId="36" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{108600FC-3626-4D1E-B130-742350B73E0C}" name="Formato RA_x000a_Aseguramiento de la Calidad" dataDxfId="35" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{2E1205FE-0F61-4D78-A5A0-856853FED427}" name="Acta de consejo de facultad" dataDxfId="34"/>
-    <tableColumn id="14" xr3:uid="{025EF1F8-8700-400A-90D5-DFCC902BE8D8}" name="SYLLABUS COMPLETOS" dataDxfId="33"/>
-    <tableColumn id="15" xr3:uid="{9508264F-6B88-4B3B-B65E-534F07C62BE1}" name="PLAN DE VIRTUALIZACIÓN " dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{04F16A62-66FE-4DBB-B66D-4AF86EF8CCAE}" name="Formato de proyecciones académicas y financieras" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{F3436AC1-2E2F-4B61-9E0D-2AB50B94DED3}" name="CONCEPTO SECRETARIA ACADÉMICA Y DOCENCIA" dataDxfId="30"/>
-    <tableColumn id="18" xr3:uid="{44A8096A-56AA-470C-A2CB-DB4EFC61105E}" name="CONCEPTO FINANCIERO" dataDxfId="29"/>
-    <tableColumn id="19" xr3:uid="{A7FB8043-DDB2-4E69-BC0F-A7B528CE1694}" name="APROBACIÓN IMPLEMENTACIÓN " dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{B1398148-35F8-4BB3-9DE1-6A13BBEF5C82}" name="Tipo de trámite de aseguramiento de la calidad " dataDxfId="27"/>
-    <tableColumn id="21" xr3:uid="{19E9529F-5B79-49D2-87E4-E3FE0F3B19DA}" name="Estado del trámite" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{2EFAD5DC-BB89-46D3-9FC8-3F55A7936A46}" name="MODALIDAD " dataDxfId="82" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{A82C0495-17CD-4853-BC2D-598A9BE98ED9}" name="NIVEL " dataDxfId="81" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{A2734990-A055-4FF8-9E05-D65BDDFB9F2B}" name="SEDE" dataDxfId="80" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{67253687-A94A-42D1-9697-5091A9F94BFF}" name="SNIES VIGENTE " dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{88E2041F-6B31-4A2C-9E79-2B4471FFD8C0}" name="Formato creación de programas Banner" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{135B0583-9D8C-42AB-A884-47E97945D128}" name="Instrumento de verificación curricular" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{3559F58B-EC8A-4DB3-BC40-DAD5A32EAF3E}" name="LA REFORMA CUMPLE CON LA POLITICA CURRICULAR " dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{DEBBC1F6-CF16-424A-B06D-D886277D783E}" name="Formato RA_x000a_Escuelas" dataDxfId="75" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{108600FC-3626-4D1E-B130-742350B73E0C}" name="Formato RA_x000a_Aseguramiento de la Calidad" dataDxfId="74" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{2E1205FE-0F61-4D78-A5A0-856853FED427}" name="Acta de consejo de facultad" dataDxfId="73"/>
+    <tableColumn id="14" xr3:uid="{025EF1F8-8700-400A-90D5-DFCC902BE8D8}" name="SYLLABUS COMPLETOS" dataDxfId="72"/>
+    <tableColumn id="15" xr3:uid="{9508264F-6B88-4B3B-B65E-534F07C62BE1}" name="PLAN DE VIRTUALIZACIÓN " dataDxfId="71"/>
+    <tableColumn id="16" xr3:uid="{04F16A62-66FE-4DBB-B66D-4AF86EF8CCAE}" name="Formato de proyecciones académicas y financieras" dataDxfId="70"/>
+    <tableColumn id="17" xr3:uid="{F3436AC1-2E2F-4B61-9E0D-2AB50B94DED3}" name="CONCEPTO SECRETARIA ACADÉMICA Y DOCENCIA" dataDxfId="69"/>
+    <tableColumn id="18" xr3:uid="{44A8096A-56AA-470C-A2CB-DB4EFC61105E}" name="CONCEPTO FINANCIERO" dataDxfId="68"/>
+    <tableColumn id="19" xr3:uid="{A7FB8043-DDB2-4E69-BC0F-A7B528CE1694}" name="APROBACIÓN IMPLEMENTACIÓN " dataDxfId="67"/>
+    <tableColumn id="20" xr3:uid="{B1398148-35F8-4BB3-9DE1-6A13BBEF5C82}" name="Tipo de trámite de aseguramiento de la calidad " dataDxfId="66"/>
+    <tableColumn id="21" xr3:uid="{19E9529F-5B79-49D2-87E4-E3FE0F3B19DA}" name="Estado del trámite" dataDxfId="65"/>
     <tableColumn id="22" xr3:uid="{9879528A-2063-414A-9C84-3D5118CCE759}" name="Fecha de_x000a_Documentos de notificación MEN"/>
-    <tableColumn id="23" xr3:uid="{38EF0233-764B-4258-8441-86A2C6F0F4B2}" name="APROBACIÓN CONSEJO DE DELEGADOS _x000a_# acta " dataDxfId="25"/>
-    <tableColumn id="24" xr3:uid="{28033A7F-E299-497F-A943-88B7B2BE006F}" name="¿Requiere aprobación ministerial?" dataDxfId="24"/>
-    <tableColumn id="25" xr3:uid="{C601BE83-FBA5-4DE0-A7C8-197A9A9BBDA8}" name="APROBACIÓN MINISTERIO DE EDUCACIÓN _x000a_# resolución" dataDxfId="23"/>
-    <tableColumn id="26" xr3:uid="{82E7A889-3964-4CEC-ACFF-3251F08D0FE9}" name="CORREO PARA IMPLEMENTACIÓN" dataDxfId="22"/>
-    <tableColumn id="27" xr3:uid="{FAD6E183-0DF2-4A25-92B0-E9326F93564C}" name="NÚMERO DE MÓDULOS NUEVOS" dataDxfId="21"/>
-    <tableColumn id="28" xr3:uid="{D1CFD773-52B1-4852-B832-CA6CDAA79B4D}" name="NÚMERO DE MÓDULOS POR ACTUALIZAR" dataDxfId="20"/>
-    <tableColumn id="29" xr3:uid="{000AF496-27CC-45D2-8C1B-857B4DE51652}" name="TOTAL  MÓDULOS CON CAMBIOS " dataDxfId="19"/>
-    <tableColumn id="30" xr3:uid="{C36E1F6A-C3C0-4870-86EF-305211A45DA4}" name="FECHA INICIO " dataDxfId="18"/>
-    <tableColumn id="31" xr3:uid="{41D62A19-F97B-4BA4-BF9C-5B71556988C3}" name="FECHA FIN " dataDxfId="17"/>
-    <tableColumn id="32" xr3:uid="{3D26E35C-F690-4210-A23A-4E295F10D24D}" name="% avance contenidos virtuales" dataDxfId="16"/>
-    <tableColumn id="33" xr3:uid="{C225E0FD-F933-49AC-B529-8332BEACB093}" name="Acta de homologación" dataDxfId="15"/>
-    <tableColumn id="34" xr3:uid="{B4F8DB9D-103A-453D-8F35-FDB42CF04974}" name="Ruta sugerida programa homologación/articulación convenio" dataDxfId="14"/>
-    <tableColumn id="35" xr3:uid="{882827BF-CE49-4742-BBAE-2A3BBF70BC6C}" name="Formato reconocimiento de competencias o resultados de aprendizaje para homologación" dataDxfId="13"/>
-    <tableColumn id="36" xr3:uid="{24C494D9-7310-4F8F-B11D-B61C217EFD83}" name="Formato acta currículo articulación SENA" dataDxfId="12"/>
-    <tableColumn id="37" xr3:uid="{4DB9B283-387E-4A50-8048-240EC0E21F54}" name="Formato acta currículo homologación/convenios" dataDxfId="11"/>
-    <tableColumn id="38" xr3:uid="{732FB30C-6247-4B14-A83B-0E0D80C2443E}" name="% avance " dataDxfId="10"/>
-    <tableColumn id="39" xr3:uid="{4A533727-9626-41DC-B313-0FCF46692090}" name="Aulas  máster nueva" dataDxfId="9"/>
-    <tableColumn id="40" xr3:uid="{60ADFF34-9529-4BBF-B0C5-AFECCD10BB30}" name="Aulas máster actualizada" dataDxfId="8"/>
-    <tableColumn id="41" xr3:uid="{1219C52E-02FA-472A-A844-E113611D5AEC}" name="Parametrizar y configurar actividades evaluativas" dataDxfId="7"/>
-    <tableColumn id="42" xr3:uid="{B3DBC2C2-A0DA-4250-8BA9-3CEF5DE2EA2C}" name="Configurar plan de estudios en Banner" dataDxfId="6"/>
-    <tableColumn id="43" xr3:uid="{F36AFE5D-35EC-41EE-ADB2-5F5DC7C049FD}" name="Elaborar plan de estudios pdf" dataDxfId="5"/>
-    <tableColumn id="44" xr3:uid="{DD8360D4-BF89-410A-944E-2A075CEA0F01}" name="Publicar plan de estudios en Web" dataDxfId="4"/>
-    <tableColumn id="45" xr3:uid="{ACCBB2F6-8E5C-4057-8E03-BF0DCC1CF869}" name="Planeación la formación a los equipos comerciales y de servicio " dataDxfId="3"/>
-    <tableColumn id="46" xr3:uid="{9B4E7DCB-AFEB-4AA8-A8E9-1F8234A38E68}" name="FECHA DE CREACIÓN OFERTA" dataDxfId="2"/>
-    <tableColumn id="47" xr3:uid="{72FB1ED5-BBF7-4217-B10E-803EA1349111}" name="FECHA INICIO MATRÍCULAS" dataDxfId="1"/>
-    <tableColumn id="48" xr3:uid="{DDC9E6BB-9AB9-4E7F-B2DA-E1A674E44FE0}" name="PERIODO DE IMPLEMENTACIÓN " dataDxfId="0" dataCellStyle="Normal 2"/>
+    <tableColumn id="23" xr3:uid="{38EF0233-764B-4258-8441-86A2C6F0F4B2}" name="APROBACIÓN CONSEJO DE DELEGADOS _x000a_# acta " dataDxfId="64"/>
+    <tableColumn id="24" xr3:uid="{28033A7F-E299-497F-A943-88B7B2BE006F}" name="¿Requiere aprobación ministerial?" dataDxfId="63"/>
+    <tableColumn id="25" xr3:uid="{C601BE83-FBA5-4DE0-A7C8-197A9A9BBDA8}" name="APROBACIÓN MINISTERIO DE EDUCACIÓN _x000a_# resolución" dataDxfId="62"/>
+    <tableColumn id="26" xr3:uid="{82E7A889-3964-4CEC-ACFF-3251F08D0FE9}" name="CORREO PARA IMPLEMENTACIÓN" dataDxfId="61"/>
+    <tableColumn id="27" xr3:uid="{FAD6E183-0DF2-4A25-92B0-E9326F93564C}" name="NÚMERO DE MÓDULOS NUEVOS" dataDxfId="60"/>
+    <tableColumn id="28" xr3:uid="{D1CFD773-52B1-4852-B832-CA6CDAA79B4D}" name="NÚMERO DE MÓDULOS POR ACTUALIZAR" dataDxfId="59"/>
+    <tableColumn id="29" xr3:uid="{000AF496-27CC-45D2-8C1B-857B4DE51652}" name="TOTAL  MÓDULOS CON CAMBIOS " dataDxfId="58"/>
+    <tableColumn id="30" xr3:uid="{C36E1F6A-C3C0-4870-86EF-305211A45DA4}" name="FECHA INICIO " dataDxfId="57"/>
+    <tableColumn id="31" xr3:uid="{41D62A19-F97B-4BA4-BF9C-5B71556988C3}" name="FECHA FIN " dataDxfId="56"/>
+    <tableColumn id="32" xr3:uid="{3D26E35C-F690-4210-A23A-4E295F10D24D}" name="% avance contenidos virtuales" dataDxfId="55"/>
+    <tableColumn id="33" xr3:uid="{C225E0FD-F933-49AC-B529-8332BEACB093}" name="Acta de homologación" dataDxfId="54"/>
+    <tableColumn id="34" xr3:uid="{B4F8DB9D-103A-453D-8F35-FDB42CF04974}" name="Ruta sugerida programa homologación/articulación convenio" dataDxfId="53"/>
+    <tableColumn id="35" xr3:uid="{882827BF-CE49-4742-BBAE-2A3BBF70BC6C}" name="Formato reconocimiento de competencias o resultados de aprendizaje para homologación" dataDxfId="52"/>
+    <tableColumn id="36" xr3:uid="{24C494D9-7310-4F8F-B11D-B61C217EFD83}" name="Formato acta currículo articulación SENA" dataDxfId="51"/>
+    <tableColumn id="37" xr3:uid="{4DB9B283-387E-4A50-8048-240EC0E21F54}" name="Formato acta currículo homologación/convenios" dataDxfId="50"/>
+    <tableColumn id="38" xr3:uid="{732FB30C-6247-4B14-A83B-0E0D80C2443E}" name="% avance " dataDxfId="49"/>
+    <tableColumn id="39" xr3:uid="{4A533727-9626-41DC-B313-0FCF46692090}" name="Aulas  máster nueva" dataDxfId="48"/>
+    <tableColumn id="40" xr3:uid="{60ADFF34-9529-4BBF-B0C5-AFECCD10BB30}" name="Aulas máster actualizada" dataDxfId="47"/>
+    <tableColumn id="41" xr3:uid="{1219C52E-02FA-472A-A844-E113611D5AEC}" name="Parametrizar y configurar actividades evaluativas" dataDxfId="46"/>
+    <tableColumn id="42" xr3:uid="{B3DBC2C2-A0DA-4250-8BA9-3CEF5DE2EA2C}" name="Configurar plan de estudios en Banner" dataDxfId="45"/>
+    <tableColumn id="43" xr3:uid="{F36AFE5D-35EC-41EE-ADB2-5F5DC7C049FD}" name="Elaborar plan de estudios pdf" dataDxfId="44"/>
+    <tableColumn id="44" xr3:uid="{DD8360D4-BF89-410A-944E-2A075CEA0F01}" name="Publicar plan de estudios en Web" dataDxfId="43"/>
+    <tableColumn id="45" xr3:uid="{ACCBB2F6-8E5C-4057-8E03-BF0DCC1CF869}" name="Planeación la formación a los equipos comerciales y de servicio " dataDxfId="42"/>
+    <tableColumn id="46" xr3:uid="{9B4E7DCB-AFEB-4AA8-A8E9-1F8234A38E68}" name="FECHA DE CREACIÓN OFERTA" dataDxfId="41"/>
+    <tableColumn id="47" xr3:uid="{72FB1ED5-BBF7-4217-B10E-803EA1349111}" name="FECHA INICIO MATRÍCULAS" dataDxfId="40"/>
+    <tableColumn id="48" xr3:uid="{DDC9E6BB-9AB9-4E7F-B2DA-E1A674E44FE0}" name="PERIODO DE IMPLEMENTACIÓN " dataDxfId="39" dataCellStyle="Normal 2"/>
     <tableColumn id="49" xr3:uid="{59BAC39A-835C-4395-9DB7-0AD7DB2CD3A3}" name="ESTADO GENERAL DE LA REFORMA "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -8845,14 +8848,14 @@
     <tabColor rgb="FF0E2841"/>
   </sheetPr>
   <dimension ref="A1:Q179"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" customWidth="1"/>
-    <col min="3" max="16" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="16" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21">
+    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="200"/>
       <c r="B1" s="207" t="s">
         <v>0</v>
@@ -8878,7 +8881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="21">
+    <row r="2" spans="1:17" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="200"/>
       <c r="B2" s="207"/>
       <c r="C2" s="208"/>
@@ -8898,7 +8901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="288" customFormat="1" ht="40.9" customHeight="1">
+    <row r="3" spans="1:17" s="288" customFormat="1" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="284"/>
       <c r="B3" s="285" t="s">
         <v>5</v>
@@ -8907,11 +8910,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="284"/>
-      <c r="E3" s="315" t="s">
+      <c r="E3" s="337" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="316"/>
-      <c r="G3" s="317"/>
+      <c r="F3" s="338"/>
+      <c r="G3" s="339"/>
       <c r="H3" s="282" t="s">
         <v>8</v>
       </c>
@@ -8932,12 +8935,12 @@
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P4" s="289" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="21">
+    <row r="5" spans="1:17" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="200"/>
       <c r="B5" s="207"/>
       <c r="C5" s="208"/>
@@ -8954,12 +8957,12 @@
       <c r="N5" s="200"/>
       <c r="O5" s="209"/>
     </row>
-    <row r="6" spans="1:17" ht="37.9" customHeight="1">
+    <row r="6" spans="1:17" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P6" s="289" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="22.15" customHeight="1">
+    <row r="7" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="201"/>
       <c r="B7" s="272" t="s">
         <v>11</v>
@@ -8983,12 +8986,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="7.9" customHeight="1">
+    <row r="8" spans="1:17" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P8" s="289" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="289" customFormat="1" ht="67.900000000000006" customHeight="1">
+    <row r="9" spans="1:17" s="289" customFormat="1" ht="67.95" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A9" s="303"/>
       <c r="B9" s="304" cm="1">
         <f t="array" ref="B9">SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))</f>
@@ -9024,7 +9027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="289" customFormat="1" ht="28.15" customHeight="1">
+    <row r="10" spans="1:17" s="289" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="303"/>
       <c r="B10" s="302"/>
       <c r="C10" s="302"/>
@@ -9042,7 +9045,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="28.15" customHeight="1">
+    <row r="11" spans="1:17" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="247"/>
       <c r="B11" s="305"/>
       <c r="C11" s="305"/>
@@ -9057,8 +9060,8 @@
       <c r="L11" s="305"/>
       <c r="M11" s="305"/>
     </row>
-    <row r="12" spans="1:17" ht="28.15" customHeight="1"/>
-    <row r="13" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="12" spans="1:17" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="203"/>
       <c r="B13" s="275" t="s">
         <v>17</v>
@@ -9077,14 +9080,14 @@
       <c r="N13" s="273"/>
       <c r="O13" s="273"/>
     </row>
-    <row r="14" spans="1:17" ht="22.15" customHeight="1">
+    <row r="14" spans="1:17" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="203"/>
       <c r="B14" s="311" t="str" cm="1">
         <f t="array" ref="B14">CONCATENATE("AVANCE POR ETAPA  —  8 procesos según hoja Estructura  ·  ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))),"0")," programas")</f>
         <v>AVANCE POR ETAPA  —  8 procesos según hoja Estructura  ·  2 programas</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="36.6" customHeight="1">
+    <row r="15" spans="1:17" ht="36.6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="203"/>
       <c r="B15" s="239" t="s">
         <v>18</v>
@@ -9119,7 +9122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="67.900000000000006" customHeight="1">
+    <row r="16" spans="1:17" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="203"/>
       <c r="B16" s="312"/>
       <c r="C16" s="202"/>
@@ -9134,7 +9137,7 @@
       <c r="L16" s="202"/>
       <c r="M16" s="238"/>
     </row>
-    <row r="17" spans="1:15" ht="24" customHeight="1">
+    <row r="17" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="203"/>
       <c r="B17" s="310" t="str" cm="1">
         <f t="array" ref="B17">CONCATENATE("✔ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("finalizado",Maestro!J11:J70))*1),"0"),"  Final.     ◑ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("en proceso",Maestro!J11:J70))*1),"0"),"  En proc.     ○ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("finalizado",Maestro!J11:J70))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("en proceso",Maestro!J11:J70))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!J11:J70))*1),"0"),"  Sin inic.     — ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!J11:J70))*1),"0"),"  N/A")</f>
@@ -9161,7 +9164,7 @@
       <c r="L17" s="202"/>
       <c r="M17" s="238"/>
     </row>
-    <row r="18" spans="1:15" ht="24" customHeight="1">
+    <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="203"/>
       <c r="B18" s="204"/>
       <c r="C18" s="204"/>
@@ -9176,7 +9179,7 @@
       <c r="L18" s="206"/>
       <c r="M18" s="206"/>
     </row>
-    <row r="19" spans="1:15" ht="24" customHeight="1">
+    <row r="19" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="203"/>
       <c r="B19" s="243" t="s">
         <v>22</v>
@@ -9211,7 +9214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="24" customHeight="1">
+    <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="203"/>
       <c r="B20" s="313"/>
       <c r="C20" s="202"/>
@@ -9226,7 +9229,7 @@
       <c r="L20" s="202"/>
       <c r="M20" s="238"/>
     </row>
-    <row r="21" spans="1:15" ht="24" customHeight="1">
+    <row r="21" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="203"/>
       <c r="B21" s="310" t="str" cm="1">
         <f t="array" ref="B21">CONCATENATE("✔ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))*1),"0"),"  Final.     ◑ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1))*1),"0"),"  En proc.     ○ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AQ11:AQ70))*1),"0"),"  Sin inic.     — ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AQ11:AQ70))*1),"0"),"  N/A")</f>
@@ -9253,7 +9256,7 @@
       <c r="L21" s="202"/>
       <c r="M21" s="238"/>
     </row>
-    <row r="22" spans="1:15" ht="24" customHeight="1">
+    <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="203"/>
       <c r="B22" s="206"/>
       <c r="C22" s="206"/>
@@ -9268,8 +9271,8 @@
       <c r="L22" s="206"/>
       <c r="M22" s="206"/>
     </row>
-    <row r="23" spans="1:15" ht="24" customHeight="1"/>
-    <row r="24" spans="1:15" ht="24" customHeight="1">
+    <row r="23" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="205"/>
       <c r="B24" s="275" t="s">
         <v>26</v>
@@ -9290,10 +9293,10 @@
       <c r="N24" s="273"/>
       <c r="O24" s="273"/>
     </row>
-    <row r="25" spans="1:15" ht="10.15" customHeight="1">
+    <row r="25" spans="1:15" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="205"/>
     </row>
-    <row r="26" spans="1:15" ht="22.15" customHeight="1">
+    <row r="26" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="205"/>
       <c r="B26" s="212" t="s">
         <v>28</v>
@@ -9325,7 +9328,7 @@
       </c>
       <c r="O26" s="200"/>
     </row>
-    <row r="27" spans="1:15" ht="24" customHeight="1">
+    <row r="27" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="205"/>
       <c r="B27" s="248" t="s">
         <v>36</v>
@@ -9357,7 +9360,7 @@
       </c>
       <c r="O27" s="216"/>
     </row>
-    <row r="28" spans="1:15" ht="24" customHeight="1">
+    <row r="28" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="205"/>
       <c r="B28" s="257" t="s">
         <v>39</v>
@@ -9389,7 +9392,7 @@
       </c>
       <c r="O28" s="202"/>
     </row>
-    <row r="29" spans="1:15" ht="24" customHeight="1">
+    <row r="29" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="205"/>
       <c r="B29" s="262" t="s">
         <v>42</v>
@@ -9421,7 +9424,7 @@
       </c>
       <c r="O29" s="213"/>
     </row>
-    <row r="30" spans="1:15" ht="10.15" customHeight="1">
+    <row r="30" spans="1:15" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="205"/>
       <c r="B30" s="267" t="s">
         <v>45</v>
@@ -9453,7 +9456,7 @@
       </c>
       <c r="O30" s="202"/>
     </row>
-    <row r="31" spans="1:15" ht="22.15" customHeight="1">
+    <row r="31" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="268" t="s">
         <v>48</v>
@@ -9485,7 +9488,7 @@
       </c>
       <c r="O31" s="213"/>
     </row>
-    <row r="32" spans="1:15" ht="22.15" customHeight="1">
+    <row r="32" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="205"/>
       <c r="B32" s="269" t="s">
         <v>50</v>
@@ -9517,7 +9520,7 @@
       </c>
       <c r="O32" s="202"/>
     </row>
-    <row r="33" spans="1:15" ht="22.15" customHeight="1">
+    <row r="33" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="205"/>
       <c r="B33" s="270" t="s">
         <v>52</v>
@@ -9549,7 +9552,7 @@
       </c>
       <c r="O33" s="213"/>
     </row>
-    <row r="34" spans="1:15" ht="22.15" customHeight="1">
+    <row r="34" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="205"/>
       <c r="B34" s="271" t="s">
         <v>54</v>
@@ -9581,7 +9584,7 @@
       </c>
       <c r="O34" s="202"/>
     </row>
-    <row r="35" spans="1:15" ht="22.15" customHeight="1">
+    <row r="35" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="205"/>
       <c r="H35" s="219" t="s">
         <v>56</v>
@@ -9598,11 +9601,11 @@
       </c>
       <c r="O35" s="213"/>
     </row>
-    <row r="36" spans="1:15" ht="22.15" customHeight="1">
+    <row r="36" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="205"/>
       <c r="M36" s="298"/>
     </row>
-    <row r="37" spans="1:15" ht="18" customHeight="1">
+    <row r="37" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="205"/>
       <c r="H37" s="218" t="s">
         <v>57</v>
@@ -9619,7 +9622,7 @@
       </c>
       <c r="O37" s="216"/>
     </row>
-    <row r="38" spans="1:15" ht="22.15" customHeight="1">
+    <row r="38" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="205"/>
       <c r="H38" s="211" t="s">
         <v>59</v>
@@ -9636,7 +9639,7 @@
       </c>
       <c r="O38" s="202"/>
     </row>
-    <row r="39" spans="1:15" ht="22.15" customHeight="1">
+    <row r="39" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="205"/>
       <c r="H39" s="219" t="s">
         <v>60</v>
@@ -9653,7 +9656,7 @@
       </c>
       <c r="O39" s="213"/>
     </row>
-    <row r="40" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="40" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="205"/>
       <c r="H40" s="211" t="s">
         <v>61</v>
@@ -9670,7 +9673,7 @@
       </c>
       <c r="O40" s="202"/>
     </row>
-    <row r="41" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="41" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="205"/>
       <c r="H41" s="219" t="s">
         <v>62</v>
@@ -9687,7 +9690,7 @@
       </c>
       <c r="O41" s="213"/>
     </row>
-    <row r="42" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="42" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="205"/>
       <c r="H42" s="211" t="s">
         <v>63</v>
@@ -9704,7 +9707,7 @@
       </c>
       <c r="O42" s="202"/>
     </row>
-    <row r="43" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="43" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="205"/>
       <c r="H43" s="219" t="s">
         <v>64</v>
@@ -9721,11 +9724,11 @@
       </c>
       <c r="O43" s="213"/>
     </row>
-    <row r="44" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="44" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="205"/>
       <c r="M44" s="298"/>
     </row>
-    <row r="45" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="45" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="205"/>
       <c r="H45" s="218" t="s">
         <v>65</v>
@@ -9742,7 +9745,7 @@
       </c>
       <c r="O45" s="216"/>
     </row>
-    <row r="46" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="46" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H46" s="211" t="s">
         <v>66</v>
       </c>
@@ -9758,7 +9761,7 @@
       </c>
       <c r="O46" s="202"/>
     </row>
-    <row r="47" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="47" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H47" s="219" t="s">
         <v>67</v>
       </c>
@@ -9774,7 +9777,7 @@
       </c>
       <c r="O47" s="213"/>
     </row>
-    <row r="48" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="48" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H48" s="211" t="s">
         <v>68</v>
       </c>
@@ -9790,7 +9793,7 @@
       </c>
       <c r="O48" s="202"/>
     </row>
-    <row r="49" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="49" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H49" s="219" t="s">
         <v>69</v>
       </c>
@@ -9806,7 +9809,7 @@
       </c>
       <c r="O49" s="213"/>
     </row>
-    <row r="50" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="50" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H50" s="211" t="s">
         <v>70</v>
       </c>
@@ -9822,8 +9825,8 @@
       </c>
       <c r="O50" s="202"/>
     </row>
-    <row r="51" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="52" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="51" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="201"/>
       <c r="B52" s="210" t="s">
         <v>71</v>
@@ -9842,7 +9845,7 @@
       <c r="N52" s="201"/>
       <c r="O52" s="201"/>
     </row>
-    <row r="53" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="53" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="220" t="s">
         <v>72</v>
       </c>
@@ -9886,7 +9889,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="54" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="221" t="s">
         <v>40</v>
       </c>
@@ -9930,7 +9933,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="55" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="227" t="s">
         <v>93</v>
       </c>
@@ -9974,7 +9977,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="56" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="221" t="s">
         <v>46</v>
       </c>
@@ -10018,7 +10021,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="57" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="227" t="s">
         <v>98</v>
       </c>
@@ -10062,7 +10065,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="58" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="221" t="s">
         <v>102</v>
       </c>
@@ -10106,7 +10109,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="59" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="227" t="s">
         <v>104</v>
       </c>
@@ -10150,7 +10153,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="60" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="221" t="s">
         <v>107</v>
       </c>
@@ -10194,7 +10197,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="61" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="227" t="s">
         <v>108</v>
       </c>
@@ -10238,7 +10241,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="62" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="221" t="s">
         <v>109</v>
       </c>
@@ -10282,7 +10285,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="63" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="227" t="s">
         <v>110</v>
       </c>
@@ -10326,7 +10329,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="64" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="221" t="s">
         <v>111</v>
       </c>
@@ -10370,7 +10373,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="65" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="227" t="s">
         <v>114</v>
       </c>
@@ -10414,7 +10417,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="66" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="221" t="s">
         <v>68</v>
       </c>
@@ -10458,7 +10461,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="67" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="67" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="227" t="s">
         <v>116</v>
       </c>
@@ -10502,7 +10505,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="68" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="68" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="221" t="s">
         <v>118</v>
       </c>
@@ -10546,7 +10549,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="69" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="227" t="s">
         <v>59</v>
       </c>
@@ -10590,7 +10593,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="70" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="70" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="221" t="s">
         <v>60</v>
       </c>
@@ -10634,7 +10637,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="71" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="227" t="s">
         <v>122</v>
       </c>
@@ -10678,7 +10681,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="72" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="72" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="221" t="s">
         <v>62</v>
       </c>
@@ -10722,7 +10725,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="73" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="73" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="227" t="s">
         <v>61</v>
       </c>
@@ -10766,7 +10769,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="74" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="74" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="221" t="s">
         <v>124</v>
       </c>
@@ -10810,7 +10813,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="75" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="75" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="227" t="s">
         <v>126</v>
       </c>
@@ -10854,7 +10857,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="76" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="76" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="221" t="s">
         <v>127</v>
       </c>
@@ -10898,7 +10901,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="77" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="227" t="s">
         <v>128</v>
       </c>
@@ -10942,7 +10945,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="78" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="78" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="221" t="s">
         <v>63</v>
       </c>
@@ -10986,7 +10989,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="79" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="79" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="227" t="s">
         <v>129</v>
       </c>
@@ -11030,7 +11033,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="80" spans="2:15" ht="19.899999999999999" customHeight="1">
+    <row r="80" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="221" t="s">
         <v>130</v>
       </c>
@@ -11074,7 +11077,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="81" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="227" t="s">
         <v>131</v>
       </c>
@@ -11118,7 +11121,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="82" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="221" t="s">
         <v>132</v>
       </c>
@@ -11162,7 +11165,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="83" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="227" t="s">
         <v>133</v>
       </c>
@@ -11206,7 +11209,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="19.899999999999999" customHeight="1">
+    <row r="84" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="213"/>
       <c r="B84" s="233" t="s">
         <v>134</v>
@@ -11233,24 +11236,24 @@
       <c r="N84" s="213"/>
       <c r="O84" s="213"/>
     </row>
-    <row r="85" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="86" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="87" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="88" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="89" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="90" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="91" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="92" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="93" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="94" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="95" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="96" spans="1:15" ht="19.899999999999999" customHeight="1"/>
-    <row r="97" ht="19.899999999999999" customHeight="1"/>
-    <row r="98" ht="19.899999999999999" customHeight="1"/>
-    <row r="99" ht="19.899999999999999" customHeight="1"/>
-    <row r="100" ht="18" customHeight="1"/>
-    <row r="173" spans="1:16" ht="68.45" customHeight="1"/>
-    <row r="175" spans="1:16" s="169" customFormat="1" ht="58.9" customHeight="1">
+    <row r="85" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="1:16" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="1:16" s="169" customFormat="1" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175"/>
       <c r="B175"/>
       <c r="C175"/>
@@ -11268,137 +11271,105 @@
       <c r="O175"/>
       <c r="P175"/>
     </row>
-    <row r="177" ht="64.900000000000006" customHeight="1"/>
-    <row r="179" ht="84.6" customHeight="1"/>
+    <row r="177" ht="64.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="84.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="85" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="greaterThanOrEqual">
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="84" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="between">
       <formula>40</formula>
       <formula>70</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="3" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="83" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" dxfId="35" priority="13" operator="greaterThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="14" operator="between">
+      <formula>40</formula>
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="15" operator="lessThan">
       <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15">
-    <cfRule type="cellIs" dxfId="82" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="greaterThanOrEqual">
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="cellIs" dxfId="81" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="between">
       <formula>40</formula>
       <formula>70</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="cellIs" dxfId="80" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="G19">
+    <cfRule type="cellIs" dxfId="29" priority="16" operator="greaterThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="17" operator="between">
+      <formula>40</formula>
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="18" operator="lessThan">
       <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="cellIs" dxfId="79" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThanOrEqual">
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="cellIs" dxfId="78" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="25" priority="8" operator="between">
       <formula>40</formula>
       <formula>70</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="9" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="cellIs" dxfId="77" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="J19">
+    <cfRule type="cellIs" dxfId="23" priority="19" operator="greaterThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="between">
+      <formula>40</formula>
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="lessThan">
       <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
-    <cfRule type="cellIs" dxfId="76" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="greaterThanOrEqual">
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M15">
-    <cfRule type="cellIs" dxfId="75" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="between">
       <formula>40</formula>
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M15">
-    <cfRule type="cellIs" dxfId="74" priority="12" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="cellIs" dxfId="73" priority="13" operator="greaterThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="cellIs" dxfId="72" priority="14" operator="between">
-      <formula>40</formula>
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="cellIs" dxfId="71" priority="15" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="cellIs" dxfId="70" priority="16" operator="greaterThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="cellIs" dxfId="69" priority="17" operator="between">
-      <formula>40</formula>
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="cellIs" dxfId="68" priority="18" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19">
-    <cfRule type="cellIs" dxfId="67" priority="19" operator="greaterThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19">
-    <cfRule type="cellIs" dxfId="66" priority="20" operator="between">
-      <formula>40</formula>
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19">
-    <cfRule type="cellIs" dxfId="65" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="12" operator="lessThan">
       <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19">
-    <cfRule type="cellIs" dxfId="64" priority="22" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="22" operator="greaterThanOrEqual">
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M19">
-    <cfRule type="cellIs" dxfId="63" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="16" priority="23" operator="between">
       <formula>40</formula>
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M19">
-    <cfRule type="cellIs" dxfId="62" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="24" operator="lessThan">
       <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11421,28 +11392,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB500005-09F1-4E6A-9C5B-5530F5C9D660}">
   <dimension ref="B1:N230"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="32" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
       <c r="J1"/>
     </row>
-    <row r="2" spans="2:14" ht="19.899999999999999">
+    <row r="2" spans="2:14" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B2" s="114" t="s">
         <v>139</v>
       </c>
@@ -11459,14 +11430,14 @@
       <c r="M2" s="113"/>
       <c r="N2" s="113"/>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="115" t="s">
         <v>140</v>
       </c>
@@ -11489,14 +11460,14 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="2:14">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
     </row>
-    <row r="6" spans="2:14" ht="15.6">
+    <row r="6" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="120" t="s">
         <v>146</v>
       </c>
@@ -11511,7 +11482,7 @@
       <c r="K6" s="119"/>
       <c r="L6" s="119"/>
     </row>
-    <row r="7" spans="2:14" ht="24.6">
+    <row r="7" spans="2:14" ht="24.6" x14ac:dyDescent="0.3">
       <c r="B7" s="122" t="s">
         <v>147</v>
       </c>
@@ -11546,7 +11517,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="124" t="s">
         <v>157</v>
       </c>
@@ -11591,7 +11562,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="9" spans="2:14">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="135" t="s">
         <v>158</v>
       </c>
@@ -11636,7 +11607,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="123" t="s">
         <v>159</v>
       </c>
@@ -11681,7 +11652,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="11" spans="2:14">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="134" t="s">
         <v>160</v>
       </c>
@@ -11726,7 +11697,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="12" spans="2:14">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="123" t="s">
         <v>161</v>
       </c>
@@ -11771,7 +11742,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="13" spans="2:14">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>162</v>
       </c>
@@ -11816,7 +11787,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="14" spans="2:14">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="123" t="s">
         <v>163</v>
       </c>
@@ -11861,7 +11832,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="134" t="s">
         <v>164</v>
       </c>
@@ -11906,7 +11877,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="16" spans="2:14">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="123" t="s">
         <v>165</v>
       </c>
@@ -11951,14 +11922,14 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="17" spans="2:14">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="2:14" ht="15.6">
+    <row r="18" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18" s="120" t="s">
         <v>166</v>
       </c>
@@ -11975,34 +11946,34 @@
       <c r="M18" s="119"/>
       <c r="N18" s="119"/>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C20" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="318" t="s">
+      <c r="D20" s="340" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="318"/>
-      <c r="F20" s="318"/>
-      <c r="G20" s="319" t="s">
+      <c r="E20" s="340"/>
+      <c r="F20" s="340"/>
+      <c r="G20" s="341" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="319"/>
-      <c r="I20" s="319"/>
-      <c r="J20" s="320" t="s">
+      <c r="H20" s="341"/>
+      <c r="I20" s="341"/>
+      <c r="J20" s="342" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="320"/>
-      <c r="L20" s="320"/>
-    </row>
-    <row r="21" spans="2:14">
+      <c r="K20" s="342"/>
+      <c r="L20" s="342"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C21" s="146"/>
       <c r="D21" s="147" t="s">
         <v>167</v>
@@ -12032,7 +12003,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>170</v>
       </c>
@@ -12076,7 +12047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C23" s="135" t="s">
         <v>172</v>
       </c>
@@ -12117,7 +12088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C24" s="123" t="s">
         <v>173</v>
       </c>
@@ -12158,7 +12129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C25" s="134" t="s">
         <v>174</v>
       </c>
@@ -12199,7 +12170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C26" s="123" t="s">
         <v>175</v>
       </c>
@@ -12240,7 +12211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C27" s="134" t="s">
         <v>162</v>
       </c>
@@ -12281,7 +12252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:14">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C28" s="123" t="s">
         <v>176</v>
       </c>
@@ -12322,7 +12293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C29" s="134" t="s">
         <v>177</v>
       </c>
@@ -12363,7 +12334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:14">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C30" s="123" t="s">
         <v>178</v>
       </c>
@@ -12404,21 +12375,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="2:14">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F31"/>
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="2:14">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F32"/>
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32"/>
     </row>
-    <row r="33" spans="2:14" ht="15.6">
+    <row r="33" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33" s="120" t="s">
         <v>179</v>
       </c>
@@ -12437,7 +12408,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="2:14">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="122" t="s">
         <v>181</v>
       </c>
@@ -12472,7 +12443,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="35" spans="2:14">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" s="165">
         <f>IF(Maestro!I11="","",Maestro!I11)</f>
         <v>108274</v>
@@ -12518,7 +12489,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="36" spans="2:14">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B36" s="166">
         <f>IF(Maestro!I12="","",Maestro!I12)</f>
         <v>111231</v>
@@ -12564,7 +12535,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="37" spans="2:14">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B37" s="165">
         <f>IF(Maestro!I13="","",Maestro!I13)</f>
         <v>101647</v>
@@ -12610,7 +12581,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="38" spans="2:14">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B38" s="166">
         <f>IF(Maestro!I14="","",Maestro!I14)</f>
         <v>102464</v>
@@ -12656,7 +12627,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="39" spans="2:14">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B39" s="165">
         <f>IF(Maestro!I15="","",Maestro!I15)</f>
         <v>107733</v>
@@ -12702,7 +12673,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="40" spans="2:14">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B40" s="166">
         <f>IF(Maestro!I16="","",Maestro!I16)</f>
         <v>101525</v>
@@ -12748,7 +12719,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="41" spans="2:14">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B41" s="165">
         <f>IF(Maestro!I17="","",Maestro!I17)</f>
         <v>111116</v>
@@ -12794,7 +12765,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="42" spans="2:14">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B42" s="166">
         <f>IF(Maestro!I18="","",Maestro!I18)</f>
         <v>101388</v>
@@ -12840,7 +12811,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="43" spans="2:14">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B43" s="165">
         <f>IF(Maestro!I19="","",Maestro!I19)</f>
         <v>54534</v>
@@ -12886,7 +12857,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="44" spans="2:14">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B44" s="166">
         <f>IF(Maestro!I20="","",Maestro!I20)</f>
         <v>102743</v>
@@ -12932,7 +12903,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="45" spans="2:14">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B45" s="165">
         <f>IF(Maestro!I21="","",Maestro!I21)</f>
         <v>10561</v>
@@ -12978,7 +12949,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="46" spans="2:14">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B46" s="166">
         <f>IF(Maestro!I22="","",Maestro!I22)</f>
         <v>102473</v>
@@ -13024,7 +12995,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="47" spans="2:14">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B47" s="165">
         <f>IF(Maestro!I23="","",Maestro!I23)</f>
         <v>101389</v>
@@ -13070,7 +13041,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="48" spans="2:14">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B48" s="166">
         <f>IF(Maestro!I24="","",Maestro!I24)</f>
         <v>4078</v>
@@ -13116,7 +13087,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="49" spans="2:12">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="165">
         <f>IF(Maestro!I25="","",Maestro!I25)</f>
         <v>53835</v>
@@ -13162,7 +13133,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="50" spans="2:12">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="166">
         <f>IF(Maestro!I26="","",Maestro!I26)</f>
         <v>105309</v>
@@ -13208,7 +13179,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="51" spans="2:12">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="165">
         <f>IF(Maestro!I27="","",Maestro!I27)</f>
         <v>7470</v>
@@ -13254,7 +13225,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="52" spans="2:12">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="166">
         <f>IF(Maestro!I28="","",Maestro!I28)</f>
         <v>101492</v>
@@ -13300,7 +13271,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="53" spans="2:12">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="165">
         <f>IF(Maestro!I29="","",Maestro!I29)</f>
         <v>105591</v>
@@ -13346,7 +13317,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="54" spans="2:12">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="166">
         <f>IF(Maestro!I30="","",Maestro!I30)</f>
         <v>3638</v>
@@ -13392,7 +13363,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="55" spans="2:12">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="165">
         <f>IF(Maestro!I31="","",Maestro!I31)</f>
         <v>111399</v>
@@ -13438,7 +13409,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="56" spans="2:12">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="166">
         <f>IF(Maestro!I32="","",Maestro!I32)</f>
         <v>111178</v>
@@ -13484,7 +13455,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="57" spans="2:12">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="165">
         <f>IF(Maestro!I33="","",Maestro!I33)</f>
         <v>1892</v>
@@ -13530,7 +13501,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="58" spans="2:12">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="166">
         <f>IF(Maestro!I34="","",Maestro!I34)</f>
         <v>107647</v>
@@ -13576,7 +13547,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="59" spans="2:12">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="165">
         <f>IF(Maestro!I35="","",Maestro!I35)</f>
         <v>1895</v>
@@ -13622,7 +13593,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="60" spans="2:12">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="166">
         <f>IF(Maestro!I36="","",Maestro!I36)</f>
         <v>103090</v>
@@ -13668,7 +13639,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="61" spans="2:12">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="165">
         <f>IF(Maestro!I37="","",Maestro!I37)</f>
         <v>102847</v>
@@ -13714,7 +13685,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="62" spans="2:12">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="166">
         <f>IF(Maestro!I38="","",Maestro!I38)</f>
         <v>101382</v>
@@ -13760,7 +13731,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="63" spans="2:12">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="165">
         <f>IF(Maestro!I39="","",Maestro!I39)</f>
         <v>53140</v>
@@ -13806,7 +13777,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="64" spans="2:12">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="166">
         <f>IF(Maestro!I40="","",Maestro!I40)</f>
         <v>103799</v>
@@ -13852,7 +13823,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="65" spans="2:12">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="165">
         <f>IF(Maestro!I41="","",Maestro!I41)</f>
         <v>91360</v>
@@ -13898,7 +13869,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="66" spans="2:12">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="166">
         <f>IF(Maestro!I42="","",Maestro!I42)</f>
         <v>54726</v>
@@ -13944,7 +13915,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="67" spans="2:12">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="165">
         <f>IF(Maestro!I43="","",Maestro!I43)</f>
         <v>110697</v>
@@ -13990,7 +13961,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="68" spans="2:12">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="166">
         <f>IF(Maestro!I44="","",Maestro!I44)</f>
         <v>103640</v>
@@ -14036,7 +14007,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="69" spans="2:12">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="165">
         <f>IF(Maestro!I45="","",Maestro!I45)</f>
         <v>3209</v>
@@ -14082,7 +14053,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="70" spans="2:12">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="166">
         <f>IF(Maestro!I46="","",Maestro!I46)</f>
         <v>1894</v>
@@ -14128,7 +14099,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="71" spans="2:12">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="165">
         <f>IF(Maestro!I47="","",Maestro!I47)</f>
         <v>53632</v>
@@ -14174,7 +14145,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="72" spans="2:12">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="166">
         <f>IF(Maestro!I48="","",Maestro!I48)</f>
         <v>110267</v>
@@ -14220,7 +14191,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="73" spans="2:12">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="165">
         <f>IF(Maestro!I49="","",Maestro!I49)</f>
         <v>102633</v>
@@ -14266,7 +14237,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="74" spans="2:12">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="166">
         <f>IF(Maestro!I50="","",Maestro!I50)</f>
         <v>102632</v>
@@ -14312,7 +14283,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="75" spans="2:12">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="165">
         <f>IF(Maestro!I51="","",Maestro!I51)</f>
         <v>110043</v>
@@ -14358,7 +14329,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="76" spans="2:12">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="166">
         <f>IF(Maestro!I52="","",Maestro!I52)</f>
         <v>16017</v>
@@ -14404,7 +14375,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="77" spans="2:12">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="165">
         <f>IF(Maestro!I53="","",Maestro!I53)</f>
         <v>103752</v>
@@ -14450,7 +14421,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="78" spans="2:12">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="166">
         <f>IF(Maestro!I54="","",Maestro!I54)</f>
         <v>110286</v>
@@ -14496,7 +14467,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="79" spans="2:12">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="165">
         <f>IF(Maestro!I55="","",Maestro!I55)</f>
         <v>53237</v>
@@ -14542,7 +14513,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="80" spans="2:12">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="166">
         <f>IF(Maestro!I56="","",Maestro!I56)</f>
         <v>116661</v>
@@ -14588,7 +14559,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="81" spans="2:12">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="165">
         <f>IF(Maestro!I57="","",Maestro!I57)</f>
         <v>91501</v>
@@ -14634,7 +14605,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="82" spans="2:12">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="166">
         <f>IF(Maestro!I58="","",Maestro!I58)</f>
         <v>101288</v>
@@ -14680,7 +14651,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="83" spans="2:12">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="165">
         <f>IF(Maestro!I59="","",Maestro!I59)</f>
         <v>91502</v>
@@ -14726,7 +14697,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="84" spans="2:12">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="166">
         <f>IF(Maestro!I60="","",Maestro!I60)</f>
         <v>107852</v>
@@ -14772,7 +14743,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="85" spans="2:12">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="165">
         <f>IF(Maestro!I61="","",Maestro!I61)</f>
         <v>102630</v>
@@ -14818,7 +14789,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="86" spans="2:12">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="166">
         <f>IF(Maestro!I62="","",Maestro!I62)</f>
         <v>109274</v>
@@ -14864,7 +14835,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="87" spans="2:12">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="165">
         <f>IF(Maestro!I63="","",Maestro!I63)</f>
         <v>111589</v>
@@ -14910,7 +14881,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="88" spans="2:12">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="166">
         <f>IF(Maestro!I64="","",Maestro!I64)</f>
         <v>101660</v>
@@ -14956,7 +14927,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="89" spans="2:12">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="165">
         <f>IF(Maestro!I65="","",Maestro!I65)</f>
         <v>110642</v>
@@ -15002,7 +14973,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="90" spans="2:12">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="166">
         <f>IF(Maestro!I66="","",Maestro!I66)</f>
         <v>3208</v>
@@ -15048,7 +15019,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="91" spans="2:12">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="165">
         <f>IF(Maestro!I67="","",Maestro!I67)</f>
         <v>103681</v>
@@ -15094,7 +15065,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="92" spans="2:12">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="166">
         <f>IF(Maestro!I68="","",Maestro!I68)</f>
         <v>3207</v>
@@ -15140,7 +15111,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="93" spans="2:12">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="165">
         <f>IF(Maestro!I69="","",Maestro!I69)</f>
         <v>110425</v>
@@ -15186,7 +15157,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="94" spans="2:12">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="166">
         <f>IF(Maestro!I70="","",Maestro!I70)</f>
         <v>54768</v>
@@ -15232,154 +15203,154 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="95" spans="2:12">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="F95"/>
       <c r="G95"/>
       <c r="H95"/>
       <c r="I95"/>
       <c r="J95"/>
     </row>
-    <row r="96" spans="2:12">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="F96"/>
       <c r="G96"/>
       <c r="H96"/>
       <c r="I96"/>
       <c r="J96"/>
     </row>
-    <row r="97" customFormat="1"/>
-    <row r="98" customFormat="1"/>
-    <row r="99" customFormat="1"/>
-    <row r="100" customFormat="1"/>
-    <row r="101" customFormat="1"/>
-    <row r="102" customFormat="1"/>
-    <row r="103" customFormat="1"/>
-    <row r="104" customFormat="1"/>
-    <row r="105" customFormat="1"/>
-    <row r="106" customFormat="1"/>
-    <row r="107" customFormat="1"/>
-    <row r="108" customFormat="1"/>
-    <row r="109" customFormat="1"/>
-    <row r="110" customFormat="1"/>
-    <row r="111" customFormat="1"/>
-    <row r="112" customFormat="1"/>
-    <row r="113" customFormat="1"/>
-    <row r="114" customFormat="1"/>
-    <row r="115" customFormat="1"/>
-    <row r="116" customFormat="1"/>
-    <row r="117" customFormat="1"/>
-    <row r="118" customFormat="1"/>
-    <row r="119" customFormat="1"/>
-    <row r="120" customFormat="1"/>
-    <row r="121" customFormat="1"/>
-    <row r="122" customFormat="1"/>
-    <row r="123" customFormat="1"/>
-    <row r="124" customFormat="1"/>
-    <row r="125" customFormat="1"/>
-    <row r="126" customFormat="1"/>
-    <row r="127" customFormat="1"/>
-    <row r="128" customFormat="1"/>
-    <row r="129" customFormat="1"/>
-    <row r="130" customFormat="1"/>
-    <row r="131" customFormat="1"/>
-    <row r="132" customFormat="1"/>
-    <row r="133" customFormat="1"/>
-    <row r="134" customFormat="1"/>
-    <row r="135" customFormat="1"/>
-    <row r="136" customFormat="1"/>
-    <row r="137" customFormat="1"/>
-    <row r="138" customFormat="1"/>
-    <row r="139" customFormat="1"/>
-    <row r="140" customFormat="1"/>
-    <row r="141" customFormat="1"/>
-    <row r="142" customFormat="1"/>
-    <row r="143" customFormat="1"/>
-    <row r="144" customFormat="1"/>
-    <row r="145" customFormat="1"/>
-    <row r="146" customFormat="1"/>
-    <row r="147" customFormat="1"/>
-    <row r="148" customFormat="1"/>
-    <row r="149" customFormat="1"/>
-    <row r="150" customFormat="1"/>
-    <row r="151" customFormat="1"/>
-    <row r="152" customFormat="1"/>
-    <row r="153" customFormat="1"/>
-    <row r="154" customFormat="1"/>
-    <row r="155" customFormat="1"/>
-    <row r="156" customFormat="1"/>
-    <row r="157" customFormat="1"/>
-    <row r="158" customFormat="1"/>
-    <row r="159" customFormat="1"/>
-    <row r="160" customFormat="1"/>
-    <row r="161" customFormat="1"/>
-    <row r="162" customFormat="1"/>
-    <row r="163" customFormat="1"/>
-    <row r="164" customFormat="1"/>
-    <row r="165" customFormat="1"/>
-    <row r="166" customFormat="1"/>
-    <row r="167" customFormat="1"/>
-    <row r="168" customFormat="1"/>
-    <row r="169" customFormat="1"/>
-    <row r="170" customFormat="1"/>
-    <row r="171" customFormat="1"/>
-    <row r="172" customFormat="1"/>
-    <row r="173" customFormat="1"/>
-    <row r="174" customFormat="1"/>
-    <row r="175" customFormat="1"/>
-    <row r="176" customFormat="1"/>
-    <row r="177" customFormat="1"/>
-    <row r="178" customFormat="1"/>
-    <row r="179" customFormat="1"/>
-    <row r="180" customFormat="1"/>
-    <row r="181" customFormat="1"/>
-    <row r="182" customFormat="1"/>
-    <row r="183" customFormat="1"/>
-    <row r="184" customFormat="1"/>
-    <row r="185" customFormat="1"/>
-    <row r="186" customFormat="1"/>
-    <row r="187" customFormat="1"/>
-    <row r="188" customFormat="1"/>
-    <row r="189" customFormat="1"/>
-    <row r="190" customFormat="1"/>
-    <row r="191" customFormat="1"/>
-    <row r="192" customFormat="1"/>
-    <row r="193" customFormat="1"/>
-    <row r="194" customFormat="1"/>
-    <row r="195" customFormat="1"/>
-    <row r="196" customFormat="1"/>
-    <row r="197" customFormat="1"/>
-    <row r="198" customFormat="1"/>
-    <row r="199" customFormat="1"/>
-    <row r="200" customFormat="1"/>
-    <row r="201" customFormat="1"/>
-    <row r="202" customFormat="1"/>
-    <row r="203" customFormat="1"/>
-    <row r="204" customFormat="1"/>
-    <row r="205" customFormat="1"/>
-    <row r="206" customFormat="1"/>
-    <row r="207" customFormat="1"/>
-    <row r="208" customFormat="1"/>
-    <row r="209" customFormat="1"/>
-    <row r="210" customFormat="1"/>
-    <row r="211" customFormat="1"/>
-    <row r="212" customFormat="1"/>
-    <row r="213" customFormat="1"/>
-    <row r="214" customFormat="1"/>
-    <row r="215" customFormat="1"/>
-    <row r="216" customFormat="1"/>
-    <row r="217" customFormat="1"/>
-    <row r="218" customFormat="1"/>
-    <row r="219" customFormat="1"/>
-    <row r="220" customFormat="1"/>
-    <row r="221" customFormat="1"/>
-    <row r="222" customFormat="1"/>
-    <row r="223" customFormat="1"/>
-    <row r="224" customFormat="1"/>
-    <row r="225" customFormat="1"/>
-    <row r="226" customFormat="1"/>
-    <row r="227" customFormat="1"/>
-    <row r="228" customFormat="1"/>
-    <row r="229" customFormat="1"/>
-    <row r="230" customFormat="1"/>
+    <row r="97" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="98" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="99" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="100" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="101" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="102" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="103" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="104" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="105" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="106" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="107" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="108" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="109" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="110" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="111" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="112" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="113" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="114" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="115" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="116" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="117" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="118" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="119" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="120" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="121" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="122" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="123" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="124" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="125" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="126" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="127" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="128" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="129" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="130" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="131" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="132" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="133" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="134" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="135" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="136" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="137" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="138" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="139" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="140" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="141" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="142" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="143" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="144" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="145" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="146" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="147" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="148" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="149" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="150" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="151" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="152" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="153" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="154" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="155" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="156" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="157" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="158" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="159" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="160" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="161" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="162" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="163" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="164" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="165" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="166" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="167" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="168" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="169" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="170" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="171" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="172" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="173" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="174" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="175" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="176" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="177" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="178" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="179" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="180" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="181" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="182" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="183" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="184" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="185" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="186" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="187" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="188" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="189" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="190" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="191" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="192" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="193" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="194" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="195" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="196" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="197" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="198" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="199" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="200" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="201" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="202" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="203" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="204" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="205" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="206" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="207" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="208" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="209" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="210" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="211" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="212" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="213" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="214" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="215" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="216" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="217" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="218" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="219" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="220" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="221" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="222" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="223" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="224" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="225" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="226" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="227" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="228" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="229" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="230" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D20:F20"/>
@@ -15387,24 +15358,24 @@
     <mergeCell ref="J20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="F35:K94">
-    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="Finalizado">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Finalizado">
       <formula>NOT(ISERROR(SEARCH("Finalizado",F35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="En proceso">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="En proceso">
       <formula>NOT(ISERROR(SEARCH("En proceso",F35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Sin iniciar">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Sin iniciar">
       <formula>NOT(ISERROR(SEARCH("Sin iniciar",F35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35:L94">
-    <cfRule type="containsText" dxfId="58" priority="4" operator="containsText" text="Completo">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Completo">
       <formula>NOT(ISERROR(SEARCH("Completo",L35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="⏳">
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="⏳">
       <formula>NOT(ISERROR(SEARCH("⏳",L35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="Pendiente">
+    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Pendiente">
       <formula>NOT(ISERROR(SEARCH("Pendiente",L35)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15415,83 +15386,83 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}">
   <dimension ref="C3:BZ83"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="78" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="15.7109375" style="1" customWidth="1"/>
-    <col min="19" max="28" width="18.42578125" customWidth="1"/>
-    <col min="29" max="40" width="17.28515625" customWidth="1"/>
-    <col min="41" max="41" width="9.7109375" customWidth="1"/>
-    <col min="42" max="42" width="8.5703125" customWidth="1"/>
-    <col min="43" max="43" width="17.28515625" customWidth="1"/>
-    <col min="44" max="44" width="13.7109375" customWidth="1"/>
-    <col min="45" max="45" width="19.7109375" customWidth="1"/>
-    <col min="46" max="46" width="25.5703125" customWidth="1"/>
-    <col min="47" max="47" width="17.28515625" customWidth="1"/>
-    <col min="48" max="51" width="14.5703125" customWidth="1"/>
-    <col min="52" max="55" width="21.7109375" customWidth="1"/>
-    <col min="71" max="71" width="18.7109375" customWidth="1"/>
-    <col min="72" max="72" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="78" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="15.6640625" style="1" customWidth="1"/>
+    <col min="19" max="28" width="18.44140625" customWidth="1"/>
+    <col min="29" max="40" width="17.33203125" customWidth="1"/>
+    <col min="41" max="41" width="9.6640625" customWidth="1"/>
+    <col min="42" max="42" width="8.5546875" customWidth="1"/>
+    <col min="43" max="43" width="17.33203125" customWidth="1"/>
+    <col min="44" max="44" width="13.6640625" customWidth="1"/>
+    <col min="45" max="45" width="19.6640625" customWidth="1"/>
+    <col min="46" max="46" width="25.5546875" customWidth="1"/>
+    <col min="47" max="47" width="17.33203125" customWidth="1"/>
+    <col min="48" max="51" width="14.5546875" customWidth="1"/>
+    <col min="52" max="55" width="21.6640625" customWidth="1"/>
+    <col min="71" max="71" width="18.6640625" customWidth="1"/>
+    <col min="72" max="72" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:78" ht="32.65" customHeight="1">
-      <c r="O3" s="334" t="s">
+    <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="332" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="334"/>
-      <c r="Q3" s="334"/>
-      <c r="R3" s="334"/>
-      <c r="S3" s="334"/>
-      <c r="T3" s="334"/>
-      <c r="U3" s="334"/>
-      <c r="V3" s="334"/>
-      <c r="W3" s="334"/>
-      <c r="X3" s="334"/>
-      <c r="Y3" s="334"/>
-      <c r="Z3" s="334"/>
-      <c r="AA3" s="334"/>
-      <c r="AB3" s="334"/>
-      <c r="AC3" s="334"/>
-    </row>
-    <row r="4" spans="3:78">
+      <c r="P3" s="332"/>
+      <c r="Q3" s="332"/>
+      <c r="R3" s="332"/>
+      <c r="S3" s="332"/>
+      <c r="T3" s="332"/>
+      <c r="U3" s="332"/>
+      <c r="V3" s="332"/>
+      <c r="W3" s="332"/>
+      <c r="X3" s="332"/>
+      <c r="Y3" s="332"/>
+      <c r="Z3" s="332"/>
+      <c r="AA3" s="332"/>
+      <c r="AB3" s="332"/>
+      <c r="AC3" s="332"/>
+    </row>
+    <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="334"/>
-      <c r="P4" s="334"/>
-      <c r="Q4" s="334"/>
-      <c r="R4" s="334"/>
-      <c r="S4" s="334"/>
-      <c r="T4" s="334"/>
-      <c r="U4" s="334"/>
-      <c r="V4" s="334"/>
-      <c r="W4" s="334"/>
-      <c r="X4" s="334"/>
-      <c r="Y4" s="334"/>
-      <c r="Z4" s="334"/>
-      <c r="AA4" s="334"/>
-      <c r="AB4" s="334"/>
-      <c r="AC4" s="334"/>
-    </row>
-    <row r="5" spans="3:78">
+      <c r="O4" s="332"/>
+      <c r="P4" s="332"/>
+      <c r="Q4" s="332"/>
+      <c r="R4" s="332"/>
+      <c r="S4" s="332"/>
+      <c r="T4" s="332"/>
+      <c r="U4" s="332"/>
+      <c r="V4" s="332"/>
+      <c r="W4" s="332"/>
+      <c r="X4" s="332"/>
+      <c r="Y4" s="332"/>
+      <c r="Z4" s="332"/>
+      <c r="AA4" s="332"/>
+      <c r="AB4" s="332"/>
+      <c r="AC4" s="332"/>
+    </row>
+    <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="3:78">
+    <row r="6" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J6" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="3:78" ht="14.65" customHeight="1">
+    <row r="7" spans="3:78" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -15500,7 +15471,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="77"/>
     </row>
-    <row r="8" spans="3:78" ht="43.5" customHeight="1">
+    <row r="8" spans="3:78" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -15508,17 +15479,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="330" t="s">
+      <c r="J8" s="323" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="330"/>
-      <c r="L8" s="330"/>
-      <c r="M8" s="330"/>
-      <c r="N8" s="330"/>
-      <c r="O8" s="330"/>
-      <c r="P8" s="330"/>
-      <c r="Q8" s="330"/>
-      <c r="R8" s="330"/>
+      <c r="K8" s="323"/>
+      <c r="L8" s="323"/>
+      <c r="M8" s="323"/>
+      <c r="N8" s="323"/>
+      <c r="O8" s="323"/>
+      <c r="P8" s="323"/>
+      <c r="Q8" s="323"/>
+      <c r="R8" s="323"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -15533,27 +15504,27 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="335" t="s">
+      <c r="AC8" s="324" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="336"/>
-      <c r="AE8" s="336"/>
-      <c r="AF8" s="336"/>
-      <c r="AG8" s="336"/>
-      <c r="AH8" s="337"/>
-      <c r="AI8" s="338" t="s">
+      <c r="AD8" s="325"/>
+      <c r="AE8" s="325"/>
+      <c r="AF8" s="325"/>
+      <c r="AG8" s="325"/>
+      <c r="AH8" s="326"/>
+      <c r="AI8" s="333" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="340" t="s">
+      <c r="AL8" s="335" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="341"/>
-      <c r="AN8" s="341"/>
-      <c r="AO8" s="341"/>
-      <c r="AP8" s="341"/>
-      <c r="AQ8" s="341"/>
+      <c r="AM8" s="336"/>
+      <c r="AN8" s="336"/>
+      <c r="AO8" s="336"/>
+      <c r="AP8" s="336"/>
+      <c r="AQ8" s="336"/>
       <c r="AR8" s="327" t="s">
         <v>201</v>
       </c>
@@ -15568,89 +15539,89 @@
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="323" t="s">
+      <c r="BD8" s="320" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="323"/>
-      <c r="BF8" s="323"/>
-      <c r="BG8" s="323"/>
-      <c r="BH8" s="323"/>
-      <c r="BI8" s="323"/>
-      <c r="BJ8" s="323"/>
-      <c r="BK8" s="323"/>
-      <c r="BL8" s="323"/>
-      <c r="BM8" s="323"/>
-      <c r="BN8" s="323"/>
-      <c r="BO8" s="323"/>
-      <c r="BP8" s="323"/>
-      <c r="BQ8" s="324" t="s">
+      <c r="BE8" s="320"/>
+      <c r="BF8" s="320"/>
+      <c r="BG8" s="320"/>
+      <c r="BH8" s="320"/>
+      <c r="BI8" s="320"/>
+      <c r="BJ8" s="320"/>
+      <c r="BK8" s="320"/>
+      <c r="BL8" s="320"/>
+      <c r="BM8" s="320"/>
+      <c r="BN8" s="320"/>
+      <c r="BO8" s="320"/>
+      <c r="BP8" s="320"/>
+      <c r="BQ8" s="321" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="324"/>
-      <c r="BS8" s="324"/>
+      <c r="BR8" s="321"/>
+      <c r="BS8" s="321"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
-    <row r="9" spans="3:78" s="2" customFormat="1" ht="58.15" customHeight="1">
-      <c r="C9" s="329" t="s">
+    <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="322" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="329"/>
-      <c r="E9" s="329"/>
-      <c r="F9" s="329"/>
-      <c r="G9" s="329"/>
-      <c r="H9" s="329"/>
-      <c r="I9" s="329"/>
-      <c r="J9" s="330" t="s">
+      <c r="D9" s="322"/>
+      <c r="E9" s="322"/>
+      <c r="F9" s="322"/>
+      <c r="G9" s="322"/>
+      <c r="H9" s="322"/>
+      <c r="I9" s="322"/>
+      <c r="J9" s="323" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="330"/>
-      <c r="L9" s="330"/>
-      <c r="M9" s="330"/>
-      <c r="N9" s="330"/>
-      <c r="O9" s="330"/>
-      <c r="P9" s="330"/>
-      <c r="Q9" s="330"/>
-      <c r="R9" s="330"/>
-      <c r="S9" s="331" t="s">
+      <c r="K9" s="323"/>
+      <c r="L9" s="323"/>
+      <c r="M9" s="323"/>
+      <c r="N9" s="323"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="323"/>
+      <c r="R9" s="323"/>
+      <c r="S9" s="346" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="332" t="s">
+      <c r="T9" s="343" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="332" t="s">
+      <c r="U9" s="343" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="332" t="s">
+      <c r="V9" s="343" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="199"/>
       <c r="X9" s="199"/>
       <c r="Y9" s="199"/>
       <c r="Z9" s="199"/>
-      <c r="AA9" s="335" t="s">
+      <c r="AA9" s="324" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="336"/>
-      <c r="AC9" s="336"/>
-      <c r="AD9" s="336"/>
-      <c r="AE9" s="336"/>
-      <c r="AF9" s="336"/>
-      <c r="AG9" s="336"/>
-      <c r="AH9" s="337"/>
-      <c r="AI9" s="339"/>
+      <c r="AB9" s="325"/>
+      <c r="AC9" s="325"/>
+      <c r="AD9" s="325"/>
+      <c r="AE9" s="325"/>
+      <c r="AF9" s="325"/>
+      <c r="AG9" s="325"/>
+      <c r="AH9" s="326"/>
+      <c r="AI9" s="334"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="342" t="s">
+      <c r="AL9" s="345" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="342"/>
-      <c r="AN9" s="342"/>
-      <c r="AO9" s="342"/>
-      <c r="AP9" s="342"/>
-      <c r="AQ9" s="342"/>
+      <c r="AM9" s="345"/>
+      <c r="AN9" s="345"/>
+      <c r="AO9" s="345"/>
+      <c r="AP9" s="345"/>
+      <c r="AQ9" s="345"/>
       <c r="AR9" s="328" t="s">
         <v>201</v>
       </c>
@@ -15665,43 +15636,43 @@
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="325" t="s">
+      <c r="BD9" s="316" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="325"/>
-      <c r="BF9" s="325"/>
-      <c r="BG9" s="325"/>
-      <c r="BH9" s="325"/>
-      <c r="BI9" s="325"/>
-      <c r="BJ9" s="325"/>
-      <c r="BK9" s="325"/>
-      <c r="BL9" s="325"/>
-      <c r="BM9" s="325"/>
-      <c r="BN9" s="325"/>
-      <c r="BO9" s="325"/>
-      <c r="BP9" s="325"/>
-      <c r="BQ9" s="326" t="s">
+      <c r="BE9" s="316"/>
+      <c r="BF9" s="316"/>
+      <c r="BG9" s="316"/>
+      <c r="BH9" s="316"/>
+      <c r="BI9" s="316"/>
+      <c r="BJ9" s="316"/>
+      <c r="BK9" s="316"/>
+      <c r="BL9" s="316"/>
+      <c r="BM9" s="316"/>
+      <c r="BN9" s="316"/>
+      <c r="BO9" s="316"/>
+      <c r="BP9" s="316"/>
+      <c r="BQ9" s="319" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="326"/>
-      <c r="BS9" s="326"/>
-      <c r="BT9" s="321" t="s">
+      <c r="BR9" s="319"/>
+      <c r="BS9" s="319"/>
+      <c r="BT9" s="347" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="321" t="s">
+      <c r="BU9" s="347" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="321" t="s">
+      <c r="BV9" s="347" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="322" t="s">
+      <c r="BW9" s="348" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="3:78" ht="62.65" customHeight="1">
+    <row r="10" spans="3:78" ht="62.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
         <v>217</v>
       </c>
@@ -15750,10 +15721,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="331"/>
-      <c r="T10" s="333"/>
-      <c r="U10" s="333"/>
-      <c r="V10" s="333"/>
+      <c r="S10" s="346"/>
+      <c r="T10" s="344"/>
+      <c r="U10" s="344"/>
+      <c r="V10" s="344"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -15879,12 +15850,12 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="321"/>
-      <c r="BU10" s="321"/>
-      <c r="BV10" s="321"/>
-      <c r="BW10" s="322"/>
-    </row>
-    <row r="11" spans="3:78" ht="52.15">
+      <c r="BT10" s="347"/>
+      <c r="BU10" s="347"/>
+      <c r="BV10" s="347"/>
+      <c r="BW10" s="348"/>
+    </row>
+    <row r="11" spans="3:78" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -16110,7 +16081,7 @@
       </c>
       <c r="BW11" s="12"/>
     </row>
-    <row r="12" spans="3:78" ht="52.15">
+    <row r="12" spans="3:78" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
@@ -16336,7 +16307,7 @@
       </c>
       <c r="BW12" s="12"/>
     </row>
-    <row r="13" spans="3:78" ht="52.15">
+    <row r="13" spans="3:78" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="s">
         <v>4</v>
       </c>
@@ -16562,7 +16533,7 @@
       </c>
       <c r="BW13" s="12"/>
     </row>
-    <row r="14" spans="3:78" ht="52.15">
+    <row r="14" spans="3:78" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -16788,7 +16759,7 @@
       </c>
       <c r="BW14" s="12"/>
     </row>
-    <row r="15" spans="3:78" ht="87">
+    <row r="15" spans="3:78" ht="87" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -17014,7 +16985,7 @@
       </c>
       <c r="BW15" s="12"/>
     </row>
-    <row r="16" spans="3:78" ht="87">
+    <row r="16" spans="3:78" ht="87" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -17240,7 +17211,7 @@
       </c>
       <c r="BW16" s="12"/>
     </row>
-    <row r="17" spans="3:75" ht="52.15">
+    <row r="17" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -17466,7 +17437,7 @@
       </c>
       <c r="BW17" s="12"/>
     </row>
-    <row r="18" spans="3:75" ht="57.6">
+    <row r="18" spans="3:75" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -17692,7 +17663,7 @@
       </c>
       <c r="BW18" s="12"/>
     </row>
-    <row r="19" spans="3:75" ht="52.15">
+    <row r="19" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -17918,7 +17889,7 @@
       </c>
       <c r="BW19" s="12"/>
     </row>
-    <row r="20" spans="3:75" ht="69.599999999999994">
+    <row r="20" spans="3:75" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -18145,7 +18116,7 @@
       </c>
       <c r="BW20" s="12"/>
     </row>
-    <row r="21" spans="3:75" ht="52.15">
+    <row r="21" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -18371,7 +18342,7 @@
       </c>
       <c r="BW21" s="12"/>
     </row>
-    <row r="22" spans="3:75" ht="52.15">
+    <row r="22" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -18597,7 +18568,7 @@
       </c>
       <c r="BW22" s="12"/>
     </row>
-    <row r="23" spans="3:75" ht="87">
+    <row r="23" spans="3:75" ht="87" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -18823,7 +18794,7 @@
       </c>
       <c r="BW23" s="12"/>
     </row>
-    <row r="24" spans="3:75" ht="52.15">
+    <row r="24" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -19049,7 +19020,7 @@
       </c>
       <c r="BW24" s="12"/>
     </row>
-    <row r="25" spans="3:75" ht="69.599999999999994">
+    <row r="25" spans="3:75" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -19275,7 +19246,7 @@
       </c>
       <c r="BW25" s="12"/>
     </row>
-    <row r="26" spans="3:75" ht="52.15">
+    <row r="26" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -19501,7 +19472,7 @@
       </c>
       <c r="BW26" s="12"/>
     </row>
-    <row r="27" spans="3:75" ht="52.15">
+    <row r="27" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -19727,7 +19698,7 @@
       </c>
       <c r="BW27" s="12"/>
     </row>
-    <row r="28" spans="3:75" ht="57.6">
+    <row r="28" spans="3:75" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -19953,7 +19924,7 @@
       </c>
       <c r="BW28" s="12"/>
     </row>
-    <row r="29" spans="3:75" ht="69.599999999999994">
+    <row r="29" spans="3:75" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C29" s="23" t="s">
         <v>10</v>
       </c>
@@ -20179,7 +20150,7 @@
       </c>
       <c r="BW29" s="12"/>
     </row>
-    <row r="30" spans="3:75" ht="52.15">
+    <row r="30" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -20405,7 +20376,7 @@
       </c>
       <c r="BW30" s="12"/>
     </row>
-    <row r="31" spans="3:75" ht="52.15">
+    <row r="31" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C31" s="22" t="s">
         <v>4</v>
       </c>
@@ -20631,7 +20602,7 @@
       </c>
       <c r="BW31" s="12"/>
     </row>
-    <row r="32" spans="3:75" ht="52.15">
+    <row r="32" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C32" s="22" t="s">
         <v>4</v>
       </c>
@@ -20858,7 +20829,7 @@
       </c>
       <c r="BW32" s="12"/>
     </row>
-    <row r="33" spans="3:75" ht="52.15">
+    <row r="33" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -21085,7 +21056,7 @@
       </c>
       <c r="BW33" s="12"/>
     </row>
-    <row r="34" spans="3:75" ht="69.599999999999994">
+    <row r="34" spans="3:75" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -21312,7 +21283,7 @@
       </c>
       <c r="BW34" s="12"/>
     </row>
-    <row r="35" spans="3:75" ht="69.599999999999994">
+    <row r="35" spans="3:75" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -21539,7 +21510,7 @@
       </c>
       <c r="BW35" s="12"/>
     </row>
-    <row r="36" spans="3:75" ht="52.15">
+    <row r="36" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C36" s="24" t="s">
         <v>7</v>
       </c>
@@ -21766,7 +21737,7 @@
       </c>
       <c r="BW36" s="12"/>
     </row>
-    <row r="37" spans="3:75" ht="52.15">
+    <row r="37" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C37" s="24" t="s">
         <v>7</v>
       </c>
@@ -21992,7 +21963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:75" ht="52.15">
+    <row r="38" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -22218,7 +22189,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:75" ht="52.15">
+    <row r="39" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -22444,7 +22415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:75" ht="69.599999999999994">
+    <row r="40" spans="3:75" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C40" s="22" t="s">
         <v>4</v>
       </c>
@@ -22670,7 +22641,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:75" ht="52.15">
+    <row r="41" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -22895,7 +22866,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:75" ht="52.15">
+    <row r="42" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -23121,7 +23092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="3:75" ht="52.15">
+    <row r="43" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C43" s="23" t="s">
         <v>10</v>
       </c>
@@ -23347,7 +23318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:75" ht="52.15">
+    <row r="44" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -23573,7 +23544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:75" ht="52.15">
+    <row r="45" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -23798,7 +23769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:75" ht="52.15">
+    <row r="46" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -24023,7 +23994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:75" ht="52.15">
+    <row r="47" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C47" s="24" t="s">
         <v>7</v>
       </c>
@@ -24248,7 +24219,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:75" ht="52.15">
+    <row r="48" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -24473,7 +24444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:74" ht="52.15">
+    <row r="49" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -24698,7 +24669,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:74" ht="52.15">
+    <row r="50" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -24923,7 +24894,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:74" ht="52.15">
+    <row r="51" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C51" s="24" t="s">
         <v>7</v>
       </c>
@@ -25148,7 +25119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:74" ht="69.599999999999994">
+    <row r="52" spans="3:74" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -25373,7 +25344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:74" ht="69.599999999999994">
+    <row r="53" spans="3:74" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -25598,7 +25569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:74" ht="69.599999999999994">
+    <row r="54" spans="3:74" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -25823,7 +25794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:74" ht="52.15">
+    <row r="55" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -26048,7 +26019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:74" ht="52.15">
+    <row r="56" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -26273,7 +26244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:74" ht="52.15">
+    <row r="57" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -26498,7 +26469,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:74" ht="69.599999999999994">
+    <row r="58" spans="3:74" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -26723,7 +26694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:74" ht="52.15">
+    <row r="59" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -26948,7 +26919,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:74" ht="52.15">
+    <row r="60" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -27173,7 +27144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:74" ht="52.15">
+    <row r="61" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -27398,7 +27369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:74" ht="52.15">
+    <row r="62" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -27623,7 +27594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:74" ht="52.15">
+    <row r="63" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -27848,7 +27819,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:74" ht="52.15">
+    <row r="64" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -28073,7 +28044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:74" ht="69.599999999999994">
+    <row r="65" spans="3:74" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -28298,7 +28269,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:74" ht="52.15">
+    <row r="66" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -28523,7 +28494,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:74" ht="69.599999999999994">
+    <row r="67" spans="3:74" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -28748,7 +28719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:74" ht="52.15">
+    <row r="68" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -28973,7 +28944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:74" ht="52.15">
+    <row r="69" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -29199,7 +29170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:74" ht="52.15">
+    <row r="70" spans="3:74" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -29424,47 +29395,62 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="3:74">
+    <row r="71" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB71" s="12"/>
     </row>
-    <row r="72" spans="3:74">
+    <row r="72" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB72" s="12"/>
     </row>
-    <row r="73" spans="3:74">
+    <row r="73" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB73" s="12"/>
     </row>
-    <row r="74" spans="3:74">
+    <row r="74" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB74" s="12"/>
     </row>
-    <row r="75" spans="3:74">
+    <row r="75" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB75" s="12"/>
     </row>
-    <row r="76" spans="3:74">
+    <row r="76" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB76" s="12"/>
     </row>
-    <row r="77" spans="3:74">
+    <row r="77" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB77" s="12"/>
     </row>
-    <row r="78" spans="3:74">
+    <row r="78" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB78" s="12"/>
     </row>
-    <row r="79" spans="3:74">
+    <row r="79" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB79" s="12"/>
     </row>
-    <row r="80" spans="3:74">
+    <row r="80" spans="3:74" x14ac:dyDescent="0.3">
       <c r="AB80" s="12"/>
     </row>
-    <row r="81" spans="28:28">
+    <row r="81" spans="28:28" x14ac:dyDescent="0.3">
       <c r="AB81" s="12"/>
     </row>
-    <row r="82" spans="28:28">
+    <row r="82" spans="28:28" x14ac:dyDescent="0.3">
       <c r="AB82" s="12"/>
     </row>
-    <row r="83" spans="28:28">
+    <row r="83" spans="28:28" x14ac:dyDescent="0.3">
       <c r="AB83" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -29473,30 +29459,15 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
-    <cfRule type="containsText" dxfId="55" priority="1" operator="containsText" text="En Proceso">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
       <formula>NOT(ISERROR(SEARCH("En Proceso",M11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="2" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",M11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="3" operator="containsText" text="SI">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH("SI",M11)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29524,76 +29495,76 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-  <dimension ref="C3:BL83"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="C3:BM83"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="78" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="15.7109375" style="1" customWidth="1"/>
-    <col min="18" max="23" width="18.42578125" customWidth="1"/>
-    <col min="24" max="34" width="17.28515625" customWidth="1"/>
-    <col min="35" max="35" width="9.7109375" customWidth="1"/>
-    <col min="36" max="36" width="8.5703125" customWidth="1"/>
-    <col min="37" max="37" width="17.28515625" customWidth="1"/>
-    <col min="38" max="38" width="13.7109375" customWidth="1"/>
-    <col min="39" max="39" width="19.7109375" customWidth="1"/>
-    <col min="40" max="40" width="25.5703125" customWidth="1"/>
-    <col min="41" max="41" width="17.28515625" customWidth="1"/>
-    <col min="42" max="44" width="14.5703125" customWidth="1"/>
-    <col min="45" max="45" width="21.7109375" customWidth="1"/>
-    <col min="48" max="49" width="11.42578125" style="78"/>
-    <col min="54" max="54" width="11.42578125" style="78"/>
-    <col min="60" max="60" width="18.7109375" customWidth="1"/>
-    <col min="61" max="61" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="78" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="15.6640625" style="1" customWidth="1"/>
+    <col min="18" max="23" width="18.44140625" customWidth="1"/>
+    <col min="24" max="34" width="17.33203125" customWidth="1"/>
+    <col min="35" max="35" width="9.6640625" customWidth="1"/>
+    <col min="36" max="36" width="8.5546875" customWidth="1"/>
+    <col min="37" max="37" width="17.33203125" customWidth="1"/>
+    <col min="38" max="38" width="13.6640625" customWidth="1"/>
+    <col min="39" max="39" width="19.6640625" customWidth="1"/>
+    <col min="40" max="40" width="25.5546875" customWidth="1"/>
+    <col min="41" max="41" width="17.33203125" customWidth="1"/>
+    <col min="42" max="44" width="14.5546875" customWidth="1"/>
+    <col min="45" max="45" width="21.6640625" customWidth="1"/>
+    <col min="48" max="49" width="11.44140625" style="78"/>
+    <col min="54" max="54" width="11.44140625" style="78"/>
+    <col min="60" max="60" width="18.6640625" customWidth="1"/>
+    <col min="61" max="61" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:64" ht="32.65" customHeight="1">
-      <c r="O3" s="334" t="s">
+    <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="332" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="334"/>
-      <c r="Q3" s="334"/>
-      <c r="R3" s="334"/>
-      <c r="S3" s="334"/>
-      <c r="T3" s="334"/>
-      <c r="U3" s="334"/>
-      <c r="V3" s="334"/>
-      <c r="W3" s="334"/>
-      <c r="X3" s="334"/>
-    </row>
-    <row r="4" spans="3:64" ht="14.45">
+      <c r="P3" s="332"/>
+      <c r="Q3" s="332"/>
+      <c r="R3" s="332"/>
+      <c r="S3" s="332"/>
+      <c r="T3" s="332"/>
+      <c r="U3" s="332"/>
+      <c r="V3" s="332"/>
+      <c r="W3" s="332"/>
+      <c r="X3" s="332"/>
+    </row>
+    <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="334"/>
-      <c r="P4" s="334"/>
-      <c r="Q4" s="334"/>
-      <c r="R4" s="334"/>
-      <c r="S4" s="334"/>
-      <c r="T4" s="334"/>
-      <c r="U4" s="334"/>
-      <c r="V4" s="334"/>
-      <c r="W4" s="334"/>
-      <c r="X4" s="334"/>
-    </row>
-    <row r="5" spans="3:64" ht="14.45">
+      <c r="O4" s="332"/>
+      <c r="P4" s="332"/>
+      <c r="Q4" s="332"/>
+      <c r="R4" s="332"/>
+      <c r="S4" s="332"/>
+      <c r="T4" s="332"/>
+      <c r="U4" s="332"/>
+      <c r="V4" s="332"/>
+      <c r="W4" s="332"/>
+      <c r="X4" s="332"/>
+    </row>
+    <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="3:64" ht="14.45">
+    <row r="6" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J6" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="3:64" ht="14.65" customHeight="1">
+    <row r="7" spans="3:65" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -29602,7 +29573,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="77"/>
     </row>
-    <row r="8" spans="3:64" ht="43.5" customHeight="1">
+    <row r="8" spans="3:65" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -29610,16 +29581,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="330" t="s">
+      <c r="J8" s="323" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="330"/>
-      <c r="L8" s="330"/>
-      <c r="M8" s="330"/>
-      <c r="N8" s="330"/>
-      <c r="O8" s="330"/>
-      <c r="P8" s="330"/>
-      <c r="Q8" s="330"/>
+      <c r="K8" s="323"/>
+      <c r="L8" s="323"/>
+      <c r="M8" s="323"/>
+      <c r="N8" s="323"/>
+      <c r="O8" s="323"/>
+      <c r="P8" s="323"/>
+      <c r="Q8" s="323"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -29630,26 +29601,26 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="335" t="s">
+      <c r="X8" s="324" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="336"/>
-      <c r="Z8" s="336"/>
-      <c r="AA8" s="336"/>
-      <c r="AB8" s="337"/>
-      <c r="AC8" s="338" t="s">
+      <c r="Y8" s="325"/>
+      <c r="Z8" s="325"/>
+      <c r="AA8" s="325"/>
+      <c r="AB8" s="326"/>
+      <c r="AC8" s="333" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="340" t="s">
+      <c r="AF8" s="335" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="341"/>
-      <c r="AH8" s="341"/>
-      <c r="AI8" s="341"/>
-      <c r="AJ8" s="341"/>
-      <c r="AK8" s="341"/>
+      <c r="AG8" s="336"/>
+      <c r="AH8" s="336"/>
+      <c r="AI8" s="336"/>
+      <c r="AJ8" s="336"/>
+      <c r="AK8" s="336"/>
       <c r="AL8" s="327" t="s">
         <v>201</v>
       </c>
@@ -29660,74 +29631,74 @@
       <c r="AQ8" s="327"/>
       <c r="AR8" s="327"/>
       <c r="AS8" s="327"/>
-      <c r="AT8" s="323" t="s">
+      <c r="AT8" s="320" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="323"/>
-      <c r="AV8" s="323"/>
-      <c r="AW8" s="323"/>
-      <c r="AX8" s="323"/>
-      <c r="AY8" s="323"/>
-      <c r="AZ8" s="323"/>
-      <c r="BA8" s="323"/>
-      <c r="BB8" s="323"/>
-      <c r="BC8" s="324" t="s">
+      <c r="AU8" s="320"/>
+      <c r="AV8" s="320"/>
+      <c r="AW8" s="320"/>
+      <c r="AX8" s="320"/>
+      <c r="AY8" s="320"/>
+      <c r="AZ8" s="320"/>
+      <c r="BA8" s="320"/>
+      <c r="BB8" s="320"/>
+      <c r="BC8" s="321" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="324"/>
-      <c r="BE8" s="324"/>
-      <c r="BF8" s="324"/>
-      <c r="BG8" s="324"/>
-      <c r="BH8" s="324"/>
+      <c r="BD8" s="321"/>
+      <c r="BE8" s="321"/>
+      <c r="BF8" s="321"/>
+      <c r="BG8" s="321"/>
+      <c r="BH8" s="321"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
-    <row r="9" spans="3:64" s="2" customFormat="1" ht="58.15" customHeight="1">
-      <c r="C9" s="329" t="s">
+    <row r="9" spans="3:65" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="322" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="329"/>
-      <c r="E9" s="329"/>
-      <c r="F9" s="329"/>
-      <c r="G9" s="329"/>
-      <c r="H9" s="329"/>
-      <c r="I9" s="329"/>
-      <c r="J9" s="330" t="s">
+      <c r="D9" s="322"/>
+      <c r="E9" s="322"/>
+      <c r="F9" s="322"/>
+      <c r="G9" s="322"/>
+      <c r="H9" s="322"/>
+      <c r="I9" s="322"/>
+      <c r="J9" s="323" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="330"/>
-      <c r="L9" s="330"/>
-      <c r="M9" s="330"/>
-      <c r="N9" s="330"/>
-      <c r="O9" s="330"/>
-      <c r="P9" s="330"/>
-      <c r="Q9" s="330"/>
+      <c r="K9" s="323"/>
+      <c r="L9" s="323"/>
+      <c r="M9" s="323"/>
+      <c r="N9" s="323"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="323"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="335" t="s">
+      <c r="V9" s="324" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="336"/>
-      <c r="X9" s="336"/>
-      <c r="Y9" s="336"/>
-      <c r="Z9" s="336"/>
-      <c r="AA9" s="336"/>
-      <c r="AB9" s="337"/>
-      <c r="AC9" s="339"/>
-      <c r="AD9" s="345" t="s">
+      <c r="W9" s="325"/>
+      <c r="X9" s="325"/>
+      <c r="Y9" s="325"/>
+      <c r="Z9" s="325"/>
+      <c r="AA9" s="325"/>
+      <c r="AB9" s="326"/>
+      <c r="AC9" s="334"/>
+      <c r="AD9" s="329" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="346"/>
-      <c r="AF9" s="346"/>
-      <c r="AG9" s="346"/>
-      <c r="AH9" s="346"/>
-      <c r="AI9" s="346"/>
-      <c r="AJ9" s="346"/>
-      <c r="AK9" s="347"/>
+      <c r="AE9" s="330"/>
+      <c r="AF9" s="330"/>
+      <c r="AG9" s="330"/>
+      <c r="AH9" s="330"/>
+      <c r="AI9" s="330"/>
+      <c r="AJ9" s="330"/>
+      <c r="AK9" s="331"/>
       <c r="AL9" s="328" t="s">
         <v>201</v>
       </c>
@@ -29738,25 +29709,25 @@
       <c r="AQ9" s="328"/>
       <c r="AR9" s="328"/>
       <c r="AS9" s="328"/>
-      <c r="AT9" s="325" t="s">
+      <c r="AT9" s="316" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="325"/>
-      <c r="AV9" s="325"/>
-      <c r="AW9" s="325"/>
-      <c r="AX9" s="325"/>
-      <c r="AY9" s="343"/>
-      <c r="AZ9" s="343"/>
-      <c r="BA9" s="343"/>
-      <c r="BB9" s="343"/>
-      <c r="BC9" s="344" t="s">
+      <c r="AU9" s="316"/>
+      <c r="AV9" s="316"/>
+      <c r="AW9" s="316"/>
+      <c r="AX9" s="316"/>
+      <c r="AY9" s="317"/>
+      <c r="AZ9" s="317"/>
+      <c r="BA9" s="317"/>
+      <c r="BB9" s="317"/>
+      <c r="BC9" s="318" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="326"/>
-      <c r="BE9" s="326"/>
-      <c r="BF9" s="326"/>
-      <c r="BG9" s="326"/>
-      <c r="BH9" s="326"/>
+      <c r="BD9" s="319"/>
+      <c r="BE9" s="319"/>
+      <c r="BF9" s="319"/>
+      <c r="BG9" s="319"/>
+      <c r="BH9" s="319"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -29770,7 +29741,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="3:64" ht="62.65" customHeight="1">
+    <row r="10" spans="3:65" ht="62.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
         <v>217</v>
       </c>
@@ -29957,8 +29928,11 @@
       <c r="BL10" s="84" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="11" spans="3:64" ht="52.15">
+      <c r="BM10" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -30002,7 +29976,7 @@
         <v>193</v>
       </c>
       <c r="S11" s="12"/>
-      <c r="T11" s="351" t="s">
+      <c r="T11" s="315" t="s">
         <v>194</v>
       </c>
       <c r="U11" s="12"/>
@@ -30103,7 +30077,7 @@
       </c>
       <c r="BL11" s="12"/>
     </row>
-    <row r="12" spans="3:64" ht="52.15">
+    <row r="12" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
@@ -30255,7 +30229,7 @@
       </c>
       <c r="BL12" s="12"/>
     </row>
-    <row r="13" spans="3:64" ht="52.15">
+    <row r="13" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="s">
         <v>4</v>
       </c>
@@ -30303,7 +30277,7 @@
         <v>193</v>
       </c>
       <c r="S13" s="12"/>
-      <c r="T13" s="351" t="s">
+      <c r="T13" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U13" s="12"/>
@@ -30411,7 +30385,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:64" ht="52.15">
+    <row r="14" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -30551,7 +30525,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:64" ht="87">
+    <row r="15" spans="3:65" ht="121.8" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -30687,11 +30661,14 @@
       <c r="BI15" s="13"/>
       <c r="BJ15" s="13"/>
       <c r="BK15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="BL15" s="12"/>
+      <c r="BM15" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="BL15" s="12"/>
-    </row>
-    <row r="16" spans="3:64" ht="55.15">
+    </row>
+    <row r="16" spans="3:65" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -30737,7 +30714,7 @@
         <v>193</v>
       </c>
       <c r="S16" s="12"/>
-      <c r="T16" s="351" t="s">
+      <c r="T16" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U16" s="12"/>
@@ -30828,7 +30805,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" ht="52.15">
+    <row r="17" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -30874,7 +30851,7 @@
         <v>193</v>
       </c>
       <c r="S17" s="12"/>
-      <c r="T17" s="351" t="s">
+      <c r="T17" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U17" s="12"/>
@@ -30955,7 +30932,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" ht="55.15">
+    <row r="18" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -31003,7 +30980,7 @@
         <v>193</v>
       </c>
       <c r="S18" s="12"/>
-      <c r="T18" s="351" t="s">
+      <c r="T18" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U18" s="12"/>
@@ -31109,7 +31086,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" ht="52.15">
+    <row r="19" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -31155,7 +31132,7 @@
         <v>193</v>
       </c>
       <c r="S19" s="12"/>
-      <c r="T19" s="351" t="s">
+      <c r="T19" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U19" s="12"/>
@@ -31248,7 +31225,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" ht="69.599999999999994">
+    <row r="20" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -31294,7 +31271,7 @@
         <v>193</v>
       </c>
       <c r="S20" s="12"/>
-      <c r="T20" s="351" t="s">
+      <c r="T20" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U20" s="12"/>
@@ -31387,7 +31364,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" ht="52.15">
+    <row r="21" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -31433,7 +31410,7 @@
         <v>193</v>
       </c>
       <c r="S21" s="12"/>
-      <c r="T21" s="351" t="s">
+      <c r="T21" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U21" s="12"/>
@@ -31526,7 +31503,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" ht="52.15">
+    <row r="22" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -31572,7 +31549,7 @@
         <v>193</v>
       </c>
       <c r="S22" s="12"/>
-      <c r="T22" s="351" t="s">
+      <c r="T22" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U22" s="12"/>
@@ -31665,7 +31642,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" ht="55.15">
+    <row r="23" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -31713,7 +31690,7 @@
         <v>193</v>
       </c>
       <c r="S23" s="12"/>
-      <c r="T23" s="351" t="s">
+      <c r="T23" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U23" s="12"/>
@@ -31819,7 +31796,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" ht="52.15">
+    <row r="24" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -31949,7 +31926,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" ht="69.599999999999994">
+    <row r="25" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -32088,7 +32065,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" ht="52.15">
+    <row r="26" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -32230,7 +32207,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" ht="52.15">
+    <row r="27" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -32369,7 +32346,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" ht="55.15">
+    <row r="28" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -32417,7 +32394,7 @@
         <v>193</v>
       </c>
       <c r="S28" s="12"/>
-      <c r="T28" s="351" t="s">
+      <c r="T28" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U28" s="12"/>
@@ -32523,7 +32500,7 @@
       </c>
       <c r="BL28" s="12"/>
     </row>
-    <row r="29" spans="3:64" ht="69.599999999999994">
+    <row r="29" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C29" s="23" t="s">
         <v>10</v>
       </c>
@@ -32571,7 +32548,7 @@
         <v>193</v>
       </c>
       <c r="S29" s="12"/>
-      <c r="T29" s="351" t="s">
+      <c r="T29" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U29" s="12"/>
@@ -32677,7 +32654,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" ht="52.15">
+    <row r="30" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -32804,7 +32781,7 @@
       </c>
       <c r="BL30" s="12"/>
     </row>
-    <row r="31" spans="3:64" ht="52.15">
+    <row r="31" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C31" s="22" t="s">
         <v>4</v>
       </c>
@@ -32962,7 +32939,7 @@
       </c>
       <c r="BL31" s="12"/>
     </row>
-    <row r="32" spans="3:64" ht="52.15">
+    <row r="32" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C32" s="22" t="s">
         <v>4</v>
       </c>
@@ -33120,7 +33097,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" ht="52.15">
+    <row r="33" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -33166,7 +33143,7 @@
         <v>193</v>
       </c>
       <c r="S33" s="12"/>
-      <c r="T33" s="351" t="s">
+      <c r="T33" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U33" s="12"/>
@@ -33259,7 +33236,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" ht="69.599999999999994">
+    <row r="34" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -33305,7 +33282,7 @@
         <v>193</v>
       </c>
       <c r="S34" s="12"/>
-      <c r="T34" s="351" t="s">
+      <c r="T34" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U34" s="12"/>
@@ -33386,7 +33363,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" ht="69.599999999999994">
+    <row r="35" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -33432,7 +33409,7 @@
         <v>193</v>
       </c>
       <c r="S35" s="12"/>
-      <c r="T35" s="351" t="s">
+      <c r="T35" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U35" s="12"/>
@@ -33525,7 +33502,7 @@
       </c>
       <c r="BL35" s="12"/>
     </row>
-    <row r="36" spans="3:64" ht="52.15">
+    <row r="36" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C36" s="24" t="s">
         <v>7</v>
       </c>
@@ -33677,7 +33654,7 @@
       </c>
       <c r="BL36" s="12"/>
     </row>
-    <row r="37" spans="3:64" ht="52.15">
+    <row r="37" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C37" s="24" t="s">
         <v>7</v>
       </c>
@@ -33814,7 +33791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:64" ht="52.15">
+    <row r="38" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -33948,7 +33925,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" ht="52.15">
+    <row r="39" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -34101,7 +34078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:64" ht="87">
+    <row r="40" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C40" s="22" t="s">
         <v>4</v>
       </c>
@@ -34254,7 +34231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" ht="52.15">
+    <row r="41" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -34302,7 +34279,7 @@
         <v>193</v>
       </c>
       <c r="S41" s="12"/>
-      <c r="T41" s="351" t="s">
+      <c r="T41" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U41" s="12"/>
@@ -34407,7 +34384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" ht="52.15">
+    <row r="42" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -34453,7 +34430,7 @@
         <v>193</v>
       </c>
       <c r="S42" s="12"/>
-      <c r="T42" s="351" t="s">
+      <c r="T42" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U42" s="12"/>
@@ -34543,7 +34520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="3:64" ht="52.15">
+    <row r="43" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C43" s="23" t="s">
         <v>10</v>
       </c>
@@ -34591,7 +34568,7 @@
         <v>193</v>
       </c>
       <c r="S43" s="12"/>
-      <c r="T43" s="351" t="s">
+      <c r="T43" s="315" t="s">
         <v>192</v>
       </c>
       <c r="U43" s="12"/>
@@ -34696,7 +34673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" ht="52.15">
+    <row r="44" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -34847,7 +34824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" ht="52.15">
+    <row r="45" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -34971,7 +34948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:64" ht="52.15">
+    <row r="46" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -35107,7 +35084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:64" ht="52.15">
+    <row r="47" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C47" s="24" t="s">
         <v>7</v>
       </c>
@@ -35155,7 +35132,7 @@
         <v>193</v>
       </c>
       <c r="S47" s="12"/>
-      <c r="T47" s="351" t="s">
+      <c r="T47" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U47" s="12"/>
@@ -35260,7 +35237,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" ht="52.15">
+    <row r="48" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -35411,7 +35388,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" ht="52.15">
+    <row r="49" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -35457,7 +35434,7 @@
         <v>193</v>
       </c>
       <c r="S49" s="12"/>
-      <c r="T49" s="351" t="s">
+      <c r="T49" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U49" s="12"/>
@@ -35535,7 +35512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" ht="52.15">
+    <row r="50" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -35581,7 +35558,7 @@
         <v>193</v>
       </c>
       <c r="S50" s="12"/>
-      <c r="T50" s="351" t="s">
+      <c r="T50" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U50" s="12"/>
@@ -35671,7 +35648,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:63" ht="52.15">
+    <row r="51" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C51" s="24" t="s">
         <v>7</v>
       </c>
@@ -35824,7 +35801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" ht="69.599999999999994">
+    <row r="52" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -35960,7 +35937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" ht="69.599999999999994">
+    <row r="53" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -36096,7 +36073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" ht="87">
+    <row r="54" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -36241,7 +36218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" ht="52.15">
+    <row r="55" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -36365,7 +36342,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" ht="52.15">
+    <row r="56" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -36413,7 +36390,7 @@
         <v>193</v>
       </c>
       <c r="S56" s="12"/>
-      <c r="T56" s="351" t="s">
+      <c r="T56" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U56" s="12"/>
@@ -36508,7 +36485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" ht="52.15">
+    <row r="57" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -36556,7 +36533,7 @@
         <v>193</v>
       </c>
       <c r="S57" s="12"/>
-      <c r="T57" s="351" t="s">
+      <c r="T57" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U57" s="12"/>
@@ -36659,7 +36636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" ht="69.599999999999994">
+    <row r="58" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -36783,7 +36760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" ht="52.15">
+    <row r="59" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -36907,7 +36884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" ht="52.15">
+    <row r="60" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -37031,7 +37008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" ht="52.15">
+    <row r="61" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -37167,7 +37144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" ht="52.15">
+    <row r="62" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -37215,7 +37192,7 @@
         <v>193</v>
       </c>
       <c r="S62" s="12"/>
-      <c r="T62" s="351" t="s">
+      <c r="T62" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U62" s="12"/>
@@ -37318,7 +37295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" ht="52.15">
+    <row r="63" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -37442,7 +37419,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="52.15">
+    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -37490,7 +37467,7 @@
         <v>193</v>
       </c>
       <c r="S64" s="12"/>
-      <c r="T64" s="351" t="s">
+      <c r="T64" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U64" s="12"/>
@@ -37599,7 +37576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" ht="87">
+    <row r="65" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -37647,7 +37624,7 @@
         <v>193</v>
       </c>
       <c r="S65" s="12"/>
-      <c r="T65" s="351" t="s">
+      <c r="T65" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U65" s="12"/>
@@ -37750,7 +37727,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" ht="52.15">
+    <row r="66" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -37874,7 +37851,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" ht="69.599999999999994">
+    <row r="67" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -37920,7 +37897,7 @@
         <v>193</v>
       </c>
       <c r="S67" s="12"/>
-      <c r="T67" s="351" t="s">
+      <c r="T67" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U67" s="12"/>
@@ -37998,7 +37975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" ht="52.15">
+    <row r="68" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -38044,7 +38021,7 @@
         <v>193</v>
       </c>
       <c r="S68" s="12"/>
-      <c r="T68" s="351" t="s">
+      <c r="T68" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U68" s="12"/>
@@ -38122,7 +38099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" ht="52.15">
+    <row r="69" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -38277,7 +38254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:63" ht="52.15">
+    <row r="70" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -38325,7 +38302,7 @@
         <v>193</v>
       </c>
       <c r="S70" s="12"/>
-      <c r="T70" s="351" t="s">
+      <c r="T70" s="315" t="s">
         <v>193</v>
       </c>
       <c r="U70" s="12"/>
@@ -38432,22 +38409,26 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="3:63" ht="14.45"/>
-    <row r="72" spans="3:63" ht="14.45"/>
-    <row r="73" spans="3:63" ht="14.45"/>
-    <row r="74" spans="3:63" ht="14.45"/>
-    <row r="75" spans="3:63" ht="14.45"/>
-    <row r="76" spans="3:63" ht="14.45"/>
-    <row r="77" spans="3:63" ht="14.45"/>
-    <row r="78" spans="3:63" ht="14.45"/>
-    <row r="79" spans="3:63" ht="14.45"/>
-    <row r="80" spans="3:63" ht="14.45"/>
-    <row r="81" ht="14.45"/>
-    <row r="82" ht="14.45"/>
-    <row r="83" ht="14.45"/>
+    <row r="71" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="C10:BL10" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}"/>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -38458,20 +38439,15 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
-    <cfRule type="containsText" dxfId="52" priority="1" operator="containsText" text="En Proceso">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
       <formula>NOT(ISERROR(SEARCH("En Proceso",M11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="2" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",M11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="3" operator="containsText" text="SI">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH("SI",M11)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38497,96 +38473,96 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E45BE9-C0E2-407D-BCEF-D4C7A244596E}">
   <dimension ref="C3:BB83"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="78" customWidth="1"/>
-    <col min="10" max="10" width="35.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="34.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="48.28515625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="15.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="26.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="78" customWidth="1"/>
+    <col min="10" max="10" width="35.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="48.33203125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="15.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="26.33203125" style="1" customWidth="1"/>
     <col min="16" max="16" width="23" style="1" customWidth="1"/>
-    <col min="17" max="17" width="25.28515625" style="1" customWidth="1"/>
-    <col min="18" max="19" width="45.7109375" customWidth="1"/>
+    <col min="17" max="17" width="25.33203125" style="1" customWidth="1"/>
+    <col min="18" max="19" width="45.6640625" customWidth="1"/>
     <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="31.28515625" customWidth="1"/>
-    <col min="22" max="22" width="49.7109375" customWidth="1"/>
-    <col min="23" max="23" width="20.7109375" customWidth="1"/>
-    <col min="24" max="25" width="17.28515625" customWidth="1"/>
-    <col min="26" max="26" width="36.5703125" customWidth="1"/>
-    <col min="27" max="27" width="17.28515625" customWidth="1"/>
-    <col min="28" max="28" width="37.85546875" customWidth="1"/>
-    <col min="29" max="29" width="30.42578125" customWidth="1"/>
-    <col min="30" max="30" width="37.7109375" customWidth="1"/>
-    <col min="31" max="31" width="31.28515625" customWidth="1"/>
-    <col min="32" max="32" width="15.28515625" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" customWidth="1"/>
-    <col min="34" max="34" width="28.7109375" customWidth="1"/>
-    <col min="35" max="35" width="21.7109375" customWidth="1"/>
-    <col min="36" max="36" width="54.28515625" customWidth="1"/>
-    <col min="37" max="37" width="78.85546875" customWidth="1"/>
+    <col min="21" max="21" width="31.33203125" customWidth="1"/>
+    <col min="22" max="22" width="49.6640625" customWidth="1"/>
+    <col min="23" max="23" width="20.6640625" customWidth="1"/>
+    <col min="24" max="25" width="17.33203125" customWidth="1"/>
+    <col min="26" max="26" width="36.5546875" customWidth="1"/>
+    <col min="27" max="27" width="17.33203125" customWidth="1"/>
+    <col min="28" max="28" width="37.88671875" customWidth="1"/>
+    <col min="29" max="29" width="30.44140625" customWidth="1"/>
+    <col min="30" max="30" width="37.6640625" customWidth="1"/>
+    <col min="31" max="31" width="31.33203125" customWidth="1"/>
+    <col min="32" max="32" width="15.33203125" customWidth="1"/>
+    <col min="33" max="33" width="12.33203125" customWidth="1"/>
+    <col min="34" max="34" width="28.6640625" customWidth="1"/>
+    <col min="35" max="35" width="21.6640625" customWidth="1"/>
+    <col min="36" max="36" width="54.33203125" customWidth="1"/>
+    <col min="37" max="37" width="78.88671875" customWidth="1"/>
     <col min="38" max="38" width="37" customWidth="1"/>
     <col min="39" max="39" width="44" customWidth="1"/>
-    <col min="40" max="40" width="21.7109375" customWidth="1"/>
-    <col min="41" max="41" width="19.85546875" customWidth="1"/>
-    <col min="42" max="42" width="23.7109375" customWidth="1"/>
-    <col min="43" max="43" width="43.7109375" customWidth="1"/>
-    <col min="44" max="44" width="35.28515625" customWidth="1"/>
-    <col min="45" max="45" width="27.7109375" customWidth="1"/>
-    <col min="46" max="46" width="31.28515625" customWidth="1"/>
-    <col min="47" max="47" width="56.7109375" customWidth="1"/>
-    <col min="48" max="48" width="29.28515625" customWidth="1"/>
+    <col min="40" max="40" width="21.6640625" customWidth="1"/>
+    <col min="41" max="41" width="19.88671875" customWidth="1"/>
+    <col min="42" max="42" width="23.6640625" customWidth="1"/>
+    <col min="43" max="43" width="43.6640625" customWidth="1"/>
+    <col min="44" max="44" width="35.33203125" customWidth="1"/>
+    <col min="45" max="45" width="27.6640625" customWidth="1"/>
+    <col min="46" max="46" width="31.33203125" customWidth="1"/>
+    <col min="47" max="47" width="56.6640625" customWidth="1"/>
+    <col min="48" max="48" width="29.33203125" customWidth="1"/>
     <col min="49" max="49" width="27" customWidth="1"/>
-    <col min="50" max="50" width="30.42578125" customWidth="1"/>
-    <col min="51" max="51" width="32.28515625" customWidth="1"/>
+    <col min="50" max="50" width="30.44140625" customWidth="1"/>
+    <col min="51" max="51" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:54" ht="32.65" customHeight="1">
-      <c r="O3" s="334" t="s">
+    <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="332" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="334"/>
-      <c r="Q3" s="334"/>
-      <c r="R3" s="334"/>
-      <c r="S3" s="334"/>
-      <c r="T3" s="334"/>
-      <c r="U3" s="334"/>
-      <c r="V3" s="334"/>
-      <c r="W3" s="334"/>
-      <c r="X3" s="334"/>
-    </row>
-    <row r="4" spans="3:54">
+      <c r="P3" s="332"/>
+      <c r="Q3" s="332"/>
+      <c r="R3" s="332"/>
+      <c r="S3" s="332"/>
+      <c r="T3" s="332"/>
+      <c r="U3" s="332"/>
+      <c r="V3" s="332"/>
+      <c r="W3" s="332"/>
+      <c r="X3" s="332"/>
+    </row>
+    <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="334"/>
-      <c r="P4" s="334"/>
-      <c r="Q4" s="334"/>
-      <c r="R4" s="334"/>
-      <c r="S4" s="334"/>
-      <c r="T4" s="334"/>
-      <c r="U4" s="334"/>
-      <c r="V4" s="334"/>
-      <c r="W4" s="334"/>
-      <c r="X4" s="334"/>
-    </row>
-    <row r="5" spans="3:54">
+      <c r="O4" s="332"/>
+      <c r="P4" s="332"/>
+      <c r="Q4" s="332"/>
+      <c r="R4" s="332"/>
+      <c r="S4" s="332"/>
+      <c r="T4" s="332"/>
+      <c r="U4" s="332"/>
+      <c r="V4" s="332"/>
+      <c r="W4" s="332"/>
+      <c r="X4" s="332"/>
+    </row>
+    <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="3:54">
+    <row r="6" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J6" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="3:54" ht="14.65" customHeight="1">
+    <row r="7" spans="3:54" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -38595,7 +38571,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="77"/>
     </row>
-    <row r="8" spans="3:54" ht="43.5" customHeight="1">
+    <row r="8" spans="3:54" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -38603,16 +38579,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="330" t="s">
+      <c r="J8" s="323" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="330"/>
-      <c r="L8" s="330"/>
-      <c r="M8" s="330"/>
-      <c r="N8" s="330"/>
-      <c r="O8" s="330"/>
-      <c r="P8" s="330"/>
-      <c r="Q8" s="330"/>
+      <c r="K8" s="323"/>
+      <c r="L8" s="323"/>
+      <c r="M8" s="323"/>
+      <c r="N8" s="323"/>
+      <c r="O8" s="323"/>
+      <c r="P8" s="323"/>
+      <c r="Q8" s="323"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -38623,23 +38599,23 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="335" t="s">
+      <c r="X8" s="324" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="336"/>
-      <c r="Z8" s="336"/>
-      <c r="AA8" s="337"/>
-      <c r="AB8" s="338" t="s">
+      <c r="Y8" s="325"/>
+      <c r="Z8" s="325"/>
+      <c r="AA8" s="326"/>
+      <c r="AB8" s="333" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="340" t="s">
+      <c r="AC8" s="335" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="341"/>
-      <c r="AE8" s="341"/>
-      <c r="AF8" s="341"/>
-      <c r="AG8" s="341"/>
-      <c r="AH8" s="341"/>
+      <c r="AD8" s="336"/>
+      <c r="AE8" s="336"/>
+      <c r="AF8" s="336"/>
+      <c r="AG8" s="336"/>
+      <c r="AH8" s="336"/>
       <c r="AI8" s="327" t="s">
         <v>201</v>
       </c>
@@ -38648,63 +38624,63 @@
       <c r="AL8" s="327"/>
       <c r="AM8" s="327"/>
       <c r="AN8" s="327"/>
-      <c r="AO8" s="323" t="s">
+      <c r="AO8" s="320" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="323"/>
-      <c r="AQ8" s="323"/>
-      <c r="AR8" s="323"/>
-      <c r="AS8" s="324" t="s">
+      <c r="AP8" s="320"/>
+      <c r="AQ8" s="320"/>
+      <c r="AR8" s="320"/>
+      <c r="AS8" s="321" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="324"/>
-      <c r="AU8" s="324"/>
+      <c r="AT8" s="321"/>
+      <c r="AU8" s="321"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
-    <row r="9" spans="3:54" s="2" customFormat="1" ht="58.15" customHeight="1">
-      <c r="C9" s="329" t="s">
+    <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="322" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="329"/>
-      <c r="E9" s="329"/>
-      <c r="F9" s="329"/>
-      <c r="G9" s="329"/>
-      <c r="H9" s="329"/>
-      <c r="I9" s="329"/>
-      <c r="J9" s="330" t="s">
+      <c r="D9" s="322"/>
+      <c r="E9" s="322"/>
+      <c r="F9" s="322"/>
+      <c r="G9" s="322"/>
+      <c r="H9" s="322"/>
+      <c r="I9" s="322"/>
+      <c r="J9" s="323" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="330"/>
-      <c r="L9" s="330"/>
-      <c r="M9" s="330"/>
-      <c r="N9" s="330"/>
-      <c r="O9" s="330"/>
-      <c r="P9" s="330"/>
-      <c r="Q9" s="330"/>
+      <c r="K9" s="323"/>
+      <c r="L9" s="323"/>
+      <c r="M9" s="323"/>
+      <c r="N9" s="323"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="323"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="335" t="s">
+      <c r="V9" s="324" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="336"/>
-      <c r="X9" s="336"/>
-      <c r="Y9" s="336"/>
-      <c r="Z9" s="336"/>
-      <c r="AA9" s="337"/>
-      <c r="AB9" s="339"/>
-      <c r="AC9" s="342" t="s">
+      <c r="W9" s="325"/>
+      <c r="X9" s="325"/>
+      <c r="Y9" s="325"/>
+      <c r="Z9" s="325"/>
+      <c r="AA9" s="326"/>
+      <c r="AB9" s="334"/>
+      <c r="AC9" s="345" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="342"/>
-      <c r="AE9" s="342"/>
-      <c r="AF9" s="342"/>
-      <c r="AG9" s="342"/>
-      <c r="AH9" s="342"/>
+      <c r="AD9" s="345"/>
+      <c r="AE9" s="345"/>
+      <c r="AF9" s="345"/>
+      <c r="AG9" s="345"/>
+      <c r="AH9" s="345"/>
       <c r="AI9" s="328" t="s">
         <v>201</v>
       </c>
@@ -38713,17 +38689,17 @@
       <c r="AL9" s="328"/>
       <c r="AM9" s="328"/>
       <c r="AN9" s="328"/>
-      <c r="AO9" s="325" t="s">
+      <c r="AO9" s="316" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="325"/>
-      <c r="AQ9" s="325"/>
-      <c r="AR9" s="325"/>
-      <c r="AS9" s="326" t="s">
+      <c r="AP9" s="316"/>
+      <c r="AQ9" s="316"/>
+      <c r="AR9" s="316"/>
+      <c r="AS9" s="319" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="326"/>
-      <c r="AU9" s="326"/>
+      <c r="AT9" s="319"/>
+      <c r="AU9" s="319"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -38740,7 +38716,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="3:54" ht="62.65" customHeight="1">
+    <row r="10" spans="3:54" ht="62.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="93" t="s">
         <v>217</v>
       </c>
@@ -38889,7 +38865,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="3:54" ht="52.15">
+    <row r="11" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="90" t="s">
         <v>4</v>
       </c>
@@ -38990,7 +38966,7 @@
       </c>
       <c r="AY11" s="12"/>
     </row>
-    <row r="12" spans="3:54" ht="52.15">
+    <row r="12" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C12" s="90" t="s">
         <v>4</v>
       </c>
@@ -39103,7 +39079,7 @@
       </c>
       <c r="AY12" s="12"/>
     </row>
-    <row r="13" spans="3:54" ht="52.15">
+    <row r="13" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C13" s="90" t="s">
         <v>4</v>
       </c>
@@ -39204,7 +39180,7 @@
       </c>
       <c r="AY13" s="12"/>
     </row>
-    <row r="14" spans="3:54" ht="52.15">
+    <row r="14" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="90" t="s">
         <v>4</v>
       </c>
@@ -39303,7 +39279,7 @@
       </c>
       <c r="AY14" s="12"/>
     </row>
-    <row r="15" spans="3:54" ht="52.15">
+    <row r="15" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C15" s="91" t="s">
         <v>10</v>
       </c>
@@ -39404,7 +39380,7 @@
       </c>
       <c r="AY15" s="12"/>
     </row>
-    <row r="16" spans="3:54" ht="87">
+    <row r="16" spans="3:54" ht="87" x14ac:dyDescent="0.3">
       <c r="C16" s="91" t="s">
         <v>10</v>
       </c>
@@ -39501,7 +39477,7 @@
       </c>
       <c r="AY16" s="12"/>
     </row>
-    <row r="17" spans="3:51" ht="52.15">
+    <row r="17" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="91" t="s">
         <v>10</v>
       </c>
@@ -39588,7 +39564,7 @@
       </c>
       <c r="AY17" s="12"/>
     </row>
-    <row r="18" spans="3:51" ht="52.15">
+    <row r="18" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C18" s="91" t="s">
         <v>10</v>
       </c>
@@ -39701,7 +39677,7 @@
       </c>
       <c r="AY18" s="12"/>
     </row>
-    <row r="19" spans="3:51" ht="52.15">
+    <row r="19" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="91" t="s">
         <v>10</v>
       </c>
@@ -39800,7 +39776,7 @@
       </c>
       <c r="AY19" s="12"/>
     </row>
-    <row r="20" spans="3:51" ht="69.599999999999994">
+    <row r="20" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="91" t="s">
         <v>10</v>
       </c>
@@ -39899,7 +39875,7 @@
       </c>
       <c r="AY20" s="12"/>
     </row>
-    <row r="21" spans="3:51" ht="52.15">
+    <row r="21" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="91" t="s">
         <v>10</v>
       </c>
@@ -39998,7 +39974,7 @@
       </c>
       <c r="AY21" s="12"/>
     </row>
-    <row r="22" spans="3:51" ht="52.15">
+    <row r="22" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="91" t="s">
         <v>10</v>
       </c>
@@ -40095,7 +40071,7 @@
       </c>
       <c r="AY22" s="12"/>
     </row>
-    <row r="23" spans="3:51" ht="87">
+    <row r="23" spans="3:51" ht="87" x14ac:dyDescent="0.3">
       <c r="C23" s="91" t="s">
         <v>10</v>
       </c>
@@ -40210,7 +40186,7 @@
       </c>
       <c r="AY23" s="12"/>
     </row>
-    <row r="24" spans="3:51" ht="52.15">
+    <row r="24" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="91" t="s">
         <v>10</v>
       </c>
@@ -40301,7 +40277,7 @@
       </c>
       <c r="AY24" s="12"/>
     </row>
-    <row r="25" spans="3:51" ht="69.599999999999994">
+    <row r="25" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="91" t="s">
         <v>10</v>
       </c>
@@ -40400,7 +40376,7 @@
       </c>
       <c r="AY25" s="12"/>
     </row>
-    <row r="26" spans="3:51" ht="52.15">
+    <row r="26" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="92" t="s">
         <v>7</v>
       </c>
@@ -40503,7 +40479,7 @@
       </c>
       <c r="AY26" s="12"/>
     </row>
-    <row r="27" spans="3:51" ht="52.15">
+    <row r="27" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="92" t="s">
         <v>7</v>
       </c>
@@ -40602,7 +40578,7 @@
       </c>
       <c r="AY27" s="12"/>
     </row>
-    <row r="28" spans="3:51" ht="52.15">
+    <row r="28" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C28" s="92" t="s">
         <v>7</v>
       </c>
@@ -40715,7 +40691,7 @@
       </c>
       <c r="AY28" s="12"/>
     </row>
-    <row r="29" spans="3:51" ht="69.599999999999994">
+    <row r="29" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C29" s="91" t="s">
         <v>10</v>
       </c>
@@ -40830,7 +40806,7 @@
       </c>
       <c r="AY29" s="12"/>
     </row>
-    <row r="30" spans="3:51" ht="52.15">
+    <row r="30" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="90" t="s">
         <v>4</v>
       </c>
@@ -40917,7 +40893,7 @@
       </c>
       <c r="AY30" s="12"/>
     </row>
-    <row r="31" spans="3:51" ht="52.15">
+    <row r="31" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C31" s="90" t="s">
         <v>4</v>
       </c>
@@ -41032,7 +41008,7 @@
       </c>
       <c r="AY31" s="12"/>
     </row>
-    <row r="32" spans="3:51" ht="52.15">
+    <row r="32" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C32" s="90" t="s">
         <v>4</v>
       </c>
@@ -41147,7 +41123,7 @@
       </c>
       <c r="AY32" s="12"/>
     </row>
-    <row r="33" spans="3:51" ht="52.15">
+    <row r="33" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="90" t="s">
         <v>4</v>
       </c>
@@ -41246,7 +41222,7 @@
       </c>
       <c r="AY33" s="12"/>
     </row>
-    <row r="34" spans="3:51" ht="69.599999999999994">
+    <row r="34" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="91" t="s">
         <v>10</v>
       </c>
@@ -41333,7 +41309,7 @@
       </c>
       <c r="AY34" s="12"/>
     </row>
-    <row r="35" spans="3:51" ht="69.599999999999994">
+    <row r="35" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="91" t="s">
         <v>10</v>
       </c>
@@ -41432,7 +41408,7 @@
       </c>
       <c r="AY35" s="12"/>
     </row>
-    <row r="36" spans="3:51" ht="52.15">
+    <row r="36" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C36" s="92" t="s">
         <v>7</v>
       </c>
@@ -41535,7 +41511,7 @@
       </c>
       <c r="AY36" s="12"/>
     </row>
-    <row r="37" spans="3:51" ht="52.15">
+    <row r="37" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C37" s="92" t="s">
         <v>7</v>
       </c>
@@ -41635,7 +41611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:51" ht="52.15">
+    <row r="38" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C38" s="92" t="s">
         <v>7</v>
       </c>
@@ -41729,7 +41705,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:51" ht="52.15">
+    <row r="39" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="92" t="s">
         <v>7</v>
       </c>
@@ -41843,7 +41819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:51" ht="69.599999999999994">
+    <row r="40" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C40" s="90" t="s">
         <v>4</v>
       </c>
@@ -41957,7 +41933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:51" ht="57.6">
+    <row r="41" spans="3:51" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C41" s="90" t="s">
         <v>4</v>
       </c>
@@ -42057,7 +42033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:51" ht="52.15">
+    <row r="42" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="91" t="s">
         <v>10</v>
       </c>
@@ -42155,7 +42131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="3:51" ht="52.15">
+    <row r="43" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C43" s="91" t="s">
         <v>10</v>
       </c>
@@ -42269,7 +42245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:51" ht="52.15">
+    <row r="44" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="90" t="s">
         <v>4</v>
       </c>
@@ -42369,7 +42345,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:51" ht="52.15">
+    <row r="45" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="92" t="s">
         <v>7</v>
       </c>
@@ -42455,7 +42431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:51" ht="52.15">
+    <row r="46" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C46" s="92" t="s">
         <v>7</v>
       </c>
@@ -42553,7 +42529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:51" ht="52.15">
+    <row r="47" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C47" s="92" t="s">
         <v>7</v>
       </c>
@@ -42667,7 +42643,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:51" ht="52.15">
+    <row r="48" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="92" t="s">
         <v>7</v>
       </c>
@@ -42767,7 +42743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:50" ht="52.15">
+    <row r="49" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="90" t="s">
         <v>4</v>
       </c>
@@ -42851,7 +42827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:50" ht="52.15">
+    <row r="50" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="90" t="s">
         <v>4</v>
       </c>
@@ -42947,7 +42923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:50" ht="52.15">
+    <row r="51" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C51" s="92" t="s">
         <v>7</v>
       </c>
@@ -43059,7 +43035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:50" ht="69.599999999999994">
+    <row r="52" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="90" t="s">
         <v>4</v>
       </c>
@@ -43155,7 +43131,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:50" ht="69.599999999999994">
+    <row r="53" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="90" t="s">
         <v>4</v>
       </c>
@@ -43251,7 +43227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:50" ht="69.599999999999994">
+    <row r="54" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="90" t="s">
         <v>4</v>
       </c>
@@ -43357,7 +43333,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:50" ht="52.15">
+    <row r="55" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="92" t="s">
         <v>7</v>
       </c>
@@ -43441,7 +43417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:50" ht="52.15">
+    <row r="56" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="91" t="s">
         <v>10</v>
       </c>
@@ -43535,7 +43511,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:50" ht="52.15">
+    <row r="57" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="91" t="s">
         <v>10</v>
       </c>
@@ -43635,7 +43611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:50" ht="69.599999999999994">
+    <row r="58" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="91" t="s">
         <v>10</v>
       </c>
@@ -43719,7 +43695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:50" ht="52.15">
+    <row r="59" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="92" t="s">
         <v>7</v>
       </c>
@@ -43803,7 +43779,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:50" ht="52.15">
+    <row r="60" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="92" t="s">
         <v>7</v>
       </c>
@@ -43887,7 +43863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:50" ht="52.15">
+    <row r="61" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="92" t="s">
         <v>7</v>
       </c>
@@ -43983,7 +43959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:50" ht="52.15">
+    <row r="62" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="90" t="s">
         <v>4</v>
       </c>
@@ -44083,7 +44059,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:50" ht="52.15">
+    <row r="63" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="90" t="s">
         <v>4</v>
       </c>
@@ -44167,7 +44143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:50" ht="52.15">
+    <row r="64" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="90" t="s">
         <v>4</v>
       </c>
@@ -44279,7 +44255,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:50" ht="69.599999999999994">
+    <row r="65" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="90" t="s">
         <v>4</v>
       </c>
@@ -44379,7 +44355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:50" ht="52.15">
+    <row r="66" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="92" t="s">
         <v>7</v>
       </c>
@@ -44463,7 +44439,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:50" ht="69.599999999999994">
+    <row r="67" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="90" t="s">
         <v>4</v>
       </c>
@@ -44545,7 +44521,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:50" ht="52.15">
+    <row r="68" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="90" t="s">
         <v>4</v>
       </c>
@@ -44629,7 +44605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:50" ht="52.15">
+    <row r="69" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="90" t="s">
         <v>4</v>
       </c>
@@ -44729,7 +44705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:50" ht="52.15">
+    <row r="70" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="90" t="s">
         <v>4</v>
       </c>
@@ -44829,52 +44805,47 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="3:50">
+    <row r="71" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W71" s="12"/>
     </row>
-    <row r="72" spans="3:50">
+    <row r="72" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W72" s="12"/>
     </row>
-    <row r="73" spans="3:50">
+    <row r="73" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W73" s="12"/>
     </row>
-    <row r="74" spans="3:50">
+    <row r="74" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W74" s="12"/>
     </row>
-    <row r="75" spans="3:50">
+    <row r="75" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W75" s="12"/>
     </row>
-    <row r="76" spans="3:50">
+    <row r="76" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W76" s="12"/>
     </row>
-    <row r="77" spans="3:50">
+    <row r="77" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W77" s="12"/>
     </row>
-    <row r="78" spans="3:50">
+    <row r="78" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W78" s="12"/>
     </row>
-    <row r="79" spans="3:50">
+    <row r="79" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W79" s="12"/>
     </row>
-    <row r="80" spans="3:50">
+    <row r="80" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W80" s="12"/>
     </row>
-    <row r="81" spans="23:23">
+    <row r="81" spans="23:23" x14ac:dyDescent="0.3">
       <c r="W81" s="12"/>
     </row>
-    <row r="82" spans="23:23">
+    <row r="82" spans="23:23" x14ac:dyDescent="0.3">
       <c r="W82" s="12"/>
     </row>
-    <row r="83" spans="23:23">
+    <row r="83" spans="23:23" x14ac:dyDescent="0.3">
       <c r="W83" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -44885,15 +44856,20 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
-    <cfRule type="containsText" dxfId="49" priority="1" operator="containsText" text="En Proceso">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
       <formula>NOT(ISERROR(SEARCH("En Proceso",M11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="2" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",M11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="3" operator="containsText" text="SI">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH("SI",M11)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44925,55 +44901,55 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06CB0E3-701B-45AE-AB79-3AAE71B2CA0C}">
   <dimension ref="A2:T31"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="72">
-      <c r="A2" s="349" t="s">
+    <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="350" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
+      <c r="B2" s="350"/>
+      <c r="C2" s="350"/>
       <c r="D2" t="s">
         <v>381</v>
       </c>
-      <c r="E2" s="349" t="s">
+      <c r="E2" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="F2" s="349"/>
+      <c r="F2" s="350"/>
       <c r="G2" s="182" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="348" t="s">
+      <c r="H2" s="349" t="s">
         <v>383</v>
       </c>
-      <c r="I2" s="348"/>
-      <c r="J2" s="348"/>
-      <c r="K2" s="348" t="s">
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="349"/>
-      <c r="M2" s="349"/>
-      <c r="N2" s="348" t="s">
+      <c r="L2" s="350"/>
+      <c r="M2" s="350"/>
+      <c r="N2" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="O2" s="349"/>
-      <c r="P2" s="349"/>
-      <c r="Q2" s="350"/>
-      <c r="R2" s="348" t="s">
+      <c r="O2" s="350"/>
+      <c r="P2" s="350"/>
+      <c r="Q2" s="351"/>
+      <c r="R2" s="349" t="s">
         <v>211</v>
       </c>
-      <c r="S2" s="349"/>
-    </row>
-    <row r="3" spans="1:20" ht="86.45">
+      <c r="S2" s="350"/>
+    </row>
+    <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="85" t="s">
         <v>224</v>
       </c>
@@ -45035,22 +45011,22 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="196" t="s">
         <v>380</v>
       </c>
@@ -45058,7 +45034,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="28.9">
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="196" t="s">
         <v>380</v>
       </c>
@@ -45066,7 +45042,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="28.9">
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="196" t="s">
         <v>380</v>
       </c>
@@ -45074,7 +45050,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="78" t="s">
         <v>381</v>
       </c>
@@ -45082,7 +45058,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="196" t="s">
         <v>382</v>
       </c>
@@ -45090,7 +45066,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="196" t="s">
         <v>382</v>
       </c>
@@ -45098,7 +45074,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="28.9">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="171" t="s">
         <v>199</v>
       </c>
@@ -45106,7 +45082,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="196" t="s">
         <v>383</v>
       </c>
@@ -45114,7 +45090,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="196" t="s">
         <v>383</v>
       </c>
@@ -45122,7 +45098,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="196" t="s">
         <v>383</v>
       </c>
@@ -45130,7 +45106,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="78" t="s">
         <v>23</v>
       </c>
@@ -45138,7 +45114,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="28.9">
+    <row r="23" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="78" t="s">
         <v>23</v>
       </c>
@@ -45146,7 +45122,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="78" t="s">
         <v>23</v>
       </c>
@@ -45154,7 +45130,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="78" t="s">
         <v>384</v>
       </c>
@@ -45162,7 +45138,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="78" t="s">
         <v>384</v>
       </c>
@@ -45170,7 +45146,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="78" t="s">
         <v>384</v>
       </c>
@@ -45178,7 +45154,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="78" t="s">
         <v>384</v>
       </c>
@@ -45186,7 +45162,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>211</v>
       </c>
@@ -45194,7 +45170,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>211</v>
       </c>
@@ -45202,7 +45178,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>211</v>
       </c>
@@ -45227,18 +45203,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E3B875-7ADC-4741-BE27-E237F70F3A60}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="197" t="s">
         <v>388</v>
       </c>
@@ -45246,7 +45222,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="196" t="s">
         <v>380</v>
       </c>
@@ -45254,7 +45230,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="196" t="s">
         <v>380</v>
       </c>
@@ -45262,7 +45238,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="196" t="s">
         <v>380</v>
       </c>
@@ -45273,7 +45249,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="196" t="s">
         <v>391</v>
       </c>
@@ -45284,7 +45260,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="196" t="s">
         <v>393</v>
       </c>
@@ -45295,7 +45271,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="196" t="s">
         <v>393</v>
       </c>
@@ -45303,7 +45279,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.9">
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="196" t="s">
         <v>394</v>
       </c>
@@ -45311,7 +45287,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="196" t="s">
         <v>396</v>
       </c>
@@ -45319,7 +45295,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="196" t="s">
         <v>396</v>
       </c>
@@ -45327,7 +45303,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="196" t="s">
         <v>396</v>
       </c>
@@ -45335,7 +45311,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="196" t="s">
         <v>398</v>
       </c>
@@ -45343,7 +45319,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.9">
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="196" t="s">
         <v>398</v>
       </c>
@@ -45351,7 +45327,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="196" t="s">
         <v>398</v>
       </c>
@@ -45359,7 +45335,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="196" t="s">
         <v>399</v>
       </c>
@@ -45367,7 +45343,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="196" t="s">
         <v>399</v>
       </c>
@@ -45375,7 +45351,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="196" t="s">
         <v>399</v>
       </c>
@@ -45383,7 +45359,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="196" t="s">
         <v>399</v>
       </c>
@@ -45391,7 +45367,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="196" t="s">
         <v>404</v>
       </c>
@@ -45399,7 +45375,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="196" t="s">
         <v>404</v>
       </c>
@@ -45407,7 +45383,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="196" t="s">
         <v>404</v>
       </c>
@@ -45424,9 +45400,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BABA1AD-5F60-4CF2-9381-F579E93FA4C9}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>408</v>
       </c>
@@ -45437,7 +45413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -45448,7 +45424,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -45459,7 +45435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -45470,7 +45446,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -45481,21 +45457,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -45633,14 +45594,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12508" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7223A297-0BD9-445D-B510-CF5A32594A04}"/>
+  <xr:revisionPtr revIDLastSave="12520" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7CA6FB6-73D6-4D63-99F5-9C6E6DD713EA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Borrador!$C$10:$BL$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Borrador!$C$10:$BM$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$70</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="BW14" s="12"/>
     </row>
-    <row r="15" spans="3:78" ht="87" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:78" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -16981,7 +16981,7 @@
       <c r="BT15" s="13"/>
       <c r="BU15" s="13"/>
       <c r="BV15" s="20" t="s">
-        <v>265</v>
+        <v>15</v>
       </c>
       <c r="BW15" s="12"/>
     </row>
@@ -45457,6 +45457,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -45594,22 +45603,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -45627,19 +45635,11 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12853" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{329DD59B-529A-44C8-9611-F83955782D7C}"/>
+  <xr:revisionPtr revIDLastSave="12883" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7264511E-D687-423D-BDD4-B3022074C40D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Ejecutivo" sheetId="9" state="hidden" r:id="rId1"/>
@@ -3727,11 +3727,47 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3754,43 +3790,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15611,43 +15611,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="322" t="s">
+      <c r="O3" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="322"/>
-      <c r="Q3" s="322"/>
-      <c r="R3" s="322"/>
-      <c r="S3" s="322"/>
-      <c r="T3" s="322"/>
-      <c r="U3" s="322"/>
-      <c r="V3" s="322"/>
-      <c r="W3" s="322"/>
-      <c r="X3" s="322"/>
-      <c r="Y3" s="322"/>
-      <c r="Z3" s="322"/>
-      <c r="AA3" s="322"/>
-      <c r="AB3" s="322"/>
-      <c r="AC3" s="322"/>
+      <c r="P3" s="335"/>
+      <c r="Q3" s="335"/>
+      <c r="R3" s="335"/>
+      <c r="S3" s="335"/>
+      <c r="T3" s="335"/>
+      <c r="U3" s="335"/>
+      <c r="V3" s="335"/>
+      <c r="W3" s="335"/>
+      <c r="X3" s="335"/>
+      <c r="Y3" s="335"/>
+      <c r="Z3" s="335"/>
+      <c r="AA3" s="335"/>
+      <c r="AB3" s="335"/>
+      <c r="AC3" s="335"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="322"/>
-      <c r="P4" s="322"/>
-      <c r="Q4" s="322"/>
-      <c r="R4" s="322"/>
-      <c r="S4" s="322"/>
-      <c r="T4" s="322"/>
-      <c r="U4" s="322"/>
-      <c r="V4" s="322"/>
-      <c r="W4" s="322"/>
-      <c r="X4" s="322"/>
-      <c r="Y4" s="322"/>
-      <c r="Z4" s="322"/>
-      <c r="AA4" s="322"/>
-      <c r="AB4" s="322"/>
-      <c r="AC4" s="322"/>
+      <c r="O4" s="335"/>
+      <c r="P4" s="335"/>
+      <c r="Q4" s="335"/>
+      <c r="R4" s="335"/>
+      <c r="S4" s="335"/>
+      <c r="T4" s="335"/>
+      <c r="U4" s="335"/>
+      <c r="V4" s="335"/>
+      <c r="W4" s="335"/>
+      <c r="X4" s="335"/>
+      <c r="Y4" s="335"/>
+      <c r="Z4" s="335"/>
+      <c r="AA4" s="335"/>
+      <c r="AB4" s="335"/>
+      <c r="AC4" s="335"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -15676,17 +15676,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="323" t="s">
+      <c r="J8" s="331" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="323"/>
-      <c r="L8" s="323"/>
-      <c r="M8" s="323"/>
-      <c r="N8" s="323"/>
-      <c r="O8" s="323"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
-      <c r="R8" s="323"/>
+      <c r="K8" s="331"/>
+      <c r="L8" s="331"/>
+      <c r="M8" s="331"/>
+      <c r="N8" s="331"/>
+      <c r="O8" s="331"/>
+      <c r="P8" s="331"/>
+      <c r="Q8" s="331"/>
+      <c r="R8" s="331"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -15701,168 +15701,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="324" t="s">
+      <c r="AC8" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
-      <c r="AG8" s="325"/>
-      <c r="AH8" s="326"/>
-      <c r="AI8" s="327" t="s">
+      <c r="AD8" s="337"/>
+      <c r="AE8" s="337"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="337"/>
+      <c r="AH8" s="338"/>
+      <c r="AI8" s="339" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="329" t="s">
+      <c r="AL8" s="341" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="330"/>
-      <c r="AN8" s="330"/>
-      <c r="AO8" s="330"/>
-      <c r="AP8" s="330"/>
-      <c r="AQ8" s="330"/>
-      <c r="AR8" s="334" t="s">
+      <c r="AM8" s="342"/>
+      <c r="AN8" s="342"/>
+      <c r="AO8" s="342"/>
+      <c r="AP8" s="342"/>
+      <c r="AQ8" s="342"/>
+      <c r="AR8" s="328" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="334"/>
-      <c r="AT8" s="334"/>
-      <c r="AU8" s="334"/>
-      <c r="AV8" s="334"/>
-      <c r="AW8" s="334"/>
-      <c r="AX8" s="334"/>
-      <c r="AY8" s="334"/>
-      <c r="AZ8" s="334"/>
+      <c r="AS8" s="328"/>
+      <c r="AT8" s="328"/>
+      <c r="AU8" s="328"/>
+      <c r="AV8" s="328"/>
+      <c r="AW8" s="328"/>
+      <c r="AX8" s="328"/>
+      <c r="AY8" s="328"/>
+      <c r="AZ8" s="328"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="340" t="s">
+      <c r="BD8" s="324" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="340"/>
-      <c r="BF8" s="340"/>
-      <c r="BG8" s="340"/>
-      <c r="BH8" s="340"/>
-      <c r="BI8" s="340"/>
-      <c r="BJ8" s="340"/>
-      <c r="BK8" s="340"/>
-      <c r="BL8" s="340"/>
-      <c r="BM8" s="340"/>
-      <c r="BN8" s="340"/>
-      <c r="BO8" s="340"/>
-      <c r="BP8" s="340"/>
-      <c r="BQ8" s="341" t="s">
+      <c r="BE8" s="324"/>
+      <c r="BF8" s="324"/>
+      <c r="BG8" s="324"/>
+      <c r="BH8" s="324"/>
+      <c r="BI8" s="324"/>
+      <c r="BJ8" s="324"/>
+      <c r="BK8" s="324"/>
+      <c r="BL8" s="324"/>
+      <c r="BM8" s="324"/>
+      <c r="BN8" s="324"/>
+      <c r="BO8" s="324"/>
+      <c r="BP8" s="324"/>
+      <c r="BQ8" s="325" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="341"/>
-      <c r="BS8" s="341"/>
+      <c r="BR8" s="325"/>
+      <c r="BS8" s="325"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="336" t="s">
+      <c r="C9" s="330" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
-      <c r="F9" s="336"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
-      <c r="J9" s="323" t="s">
+      <c r="D9" s="330"/>
+      <c r="E9" s="330"/>
+      <c r="F9" s="330"/>
+      <c r="G9" s="330"/>
+      <c r="H9" s="330"/>
+      <c r="I9" s="330"/>
+      <c r="J9" s="331" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="323"/>
-      <c r="L9" s="323"/>
-      <c r="M9" s="323"/>
-      <c r="N9" s="323"/>
-      <c r="O9" s="323"/>
-      <c r="P9" s="323"/>
-      <c r="Q9" s="323"/>
-      <c r="R9" s="323"/>
-      <c r="S9" s="337" t="s">
+      <c r="K9" s="331"/>
+      <c r="L9" s="331"/>
+      <c r="M9" s="331"/>
+      <c r="N9" s="331"/>
+      <c r="O9" s="331"/>
+      <c r="P9" s="331"/>
+      <c r="Q9" s="331"/>
+      <c r="R9" s="331"/>
+      <c r="S9" s="332" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="331" t="s">
+      <c r="T9" s="333" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="331" t="s">
+      <c r="U9" s="333" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="331" t="s">
+      <c r="V9" s="333" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="199"/>
       <c r="X9" s="199"/>
       <c r="Y9" s="199"/>
       <c r="Z9" s="199"/>
-      <c r="AA9" s="324" t="s">
+      <c r="AA9" s="336" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="325"/>
-      <c r="AC9" s="325"/>
-      <c r="AD9" s="325"/>
-      <c r="AE9" s="325"/>
-      <c r="AF9" s="325"/>
-      <c r="AG9" s="325"/>
-      <c r="AH9" s="326"/>
-      <c r="AI9" s="328"/>
+      <c r="AB9" s="337"/>
+      <c r="AC9" s="337"/>
+      <c r="AD9" s="337"/>
+      <c r="AE9" s="337"/>
+      <c r="AF9" s="337"/>
+      <c r="AG9" s="337"/>
+      <c r="AH9" s="338"/>
+      <c r="AI9" s="340"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="333" t="s">
+      <c r="AL9" s="343" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="333"/>
-      <c r="AN9" s="333"/>
-      <c r="AO9" s="333"/>
-      <c r="AP9" s="333"/>
-      <c r="AQ9" s="333"/>
-      <c r="AR9" s="335" t="s">
+      <c r="AM9" s="343"/>
+      <c r="AN9" s="343"/>
+      <c r="AO9" s="343"/>
+      <c r="AP9" s="343"/>
+      <c r="AQ9" s="343"/>
+      <c r="AR9" s="329" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="335"/>
-      <c r="AT9" s="335"/>
-      <c r="AU9" s="335"/>
-      <c r="AV9" s="335"/>
-      <c r="AW9" s="335"/>
-      <c r="AX9" s="335"/>
-      <c r="AY9" s="335"/>
-      <c r="AZ9" s="335"/>
+      <c r="AS9" s="329"/>
+      <c r="AT9" s="329"/>
+      <c r="AU9" s="329"/>
+      <c r="AV9" s="329"/>
+      <c r="AW9" s="329"/>
+      <c r="AX9" s="329"/>
+      <c r="AY9" s="329"/>
+      <c r="AZ9" s="329"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="342" t="s">
+      <c r="BD9" s="326" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="342"/>
-      <c r="BF9" s="342"/>
-      <c r="BG9" s="342"/>
-      <c r="BH9" s="342"/>
-      <c r="BI9" s="342"/>
-      <c r="BJ9" s="342"/>
-      <c r="BK9" s="342"/>
-      <c r="BL9" s="342"/>
-      <c r="BM9" s="342"/>
-      <c r="BN9" s="342"/>
-      <c r="BO9" s="342"/>
-      <c r="BP9" s="342"/>
-      <c r="BQ9" s="343" t="s">
+      <c r="BE9" s="326"/>
+      <c r="BF9" s="326"/>
+      <c r="BG9" s="326"/>
+      <c r="BH9" s="326"/>
+      <c r="BI9" s="326"/>
+      <c r="BJ9" s="326"/>
+      <c r="BK9" s="326"/>
+      <c r="BL9" s="326"/>
+      <c r="BM9" s="326"/>
+      <c r="BN9" s="326"/>
+      <c r="BO9" s="326"/>
+      <c r="BP9" s="326"/>
+      <c r="BQ9" s="327" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="343"/>
-      <c r="BS9" s="343"/>
-      <c r="BT9" s="338" t="s">
+      <c r="BR9" s="327"/>
+      <c r="BS9" s="327"/>
+      <c r="BT9" s="322" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="338" t="s">
+      <c r="BU9" s="322" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="338" t="s">
+      <c r="BV9" s="322" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="339" t="s">
+      <c r="BW9" s="323" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -15918,10 +15918,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="337"/>
-      <c r="T10" s="332"/>
-      <c r="U10" s="332"/>
-      <c r="V10" s="332"/>
+      <c r="S10" s="332"/>
+      <c r="T10" s="334"/>
+      <c r="U10" s="334"/>
+      <c r="V10" s="334"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16047,10 +16047,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="338"/>
-      <c r="BU10" s="338"/>
-      <c r="BV10" s="338"/>
-      <c r="BW10" s="339"/>
+      <c r="BT10" s="322"/>
+      <c r="BU10" s="322"/>
+      <c r="BV10" s="322"/>
+      <c r="BW10" s="323"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33090,6 +33090,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33098,21 +33113,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33232,33 +33232,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="322" t="s">
+      <c r="O3" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="322"/>
-      <c r="Q3" s="322"/>
-      <c r="R3" s="322"/>
-      <c r="S3" s="322"/>
-      <c r="T3" s="322"/>
-      <c r="U3" s="322"/>
-      <c r="V3" s="322"/>
-      <c r="W3" s="322"/>
-      <c r="X3" s="322"/>
+      <c r="P3" s="335"/>
+      <c r="Q3" s="335"/>
+      <c r="R3" s="335"/>
+      <c r="S3" s="335"/>
+      <c r="T3" s="335"/>
+      <c r="U3" s="335"/>
+      <c r="V3" s="335"/>
+      <c r="W3" s="335"/>
+      <c r="X3" s="335"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="322"/>
-      <c r="P4" s="322"/>
-      <c r="Q4" s="322"/>
-      <c r="R4" s="322"/>
-      <c r="S4" s="322"/>
-      <c r="T4" s="322"/>
-      <c r="U4" s="322"/>
-      <c r="V4" s="322"/>
-      <c r="W4" s="322"/>
-      <c r="X4" s="322"/>
+      <c r="O4" s="335"/>
+      <c r="P4" s="335"/>
+      <c r="Q4" s="335"/>
+      <c r="R4" s="335"/>
+      <c r="S4" s="335"/>
+      <c r="T4" s="335"/>
+      <c r="U4" s="335"/>
+      <c r="V4" s="335"/>
+      <c r="W4" s="335"/>
+      <c r="X4" s="335"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -33287,16 +33287,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="323" t="s">
+      <c r="J8" s="331" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="323"/>
-      <c r="L8" s="323"/>
-      <c r="M8" s="323"/>
-      <c r="N8" s="323"/>
-      <c r="O8" s="323"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
+      <c r="K8" s="331"/>
+      <c r="L8" s="331"/>
+      <c r="M8" s="331"/>
+      <c r="N8" s="331"/>
+      <c r="O8" s="331"/>
+      <c r="P8" s="331"/>
+      <c r="Q8" s="331"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33307,94 +33307,94 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="324" t="s">
+      <c r="X8" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="325"/>
-      <c r="Z8" s="325"/>
-      <c r="AA8" s="325"/>
-      <c r="AB8" s="326"/>
-      <c r="AC8" s="327" t="s">
+      <c r="Y8" s="337"/>
+      <c r="Z8" s="337"/>
+      <c r="AA8" s="337"/>
+      <c r="AB8" s="338"/>
+      <c r="AC8" s="339" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="329" t="s">
+      <c r="AF8" s="341" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="330"/>
-      <c r="AH8" s="330"/>
-      <c r="AI8" s="330"/>
-      <c r="AJ8" s="330"/>
-      <c r="AK8" s="330"/>
-      <c r="AL8" s="334" t="s">
+      <c r="AG8" s="342"/>
+      <c r="AH8" s="342"/>
+      <c r="AI8" s="342"/>
+      <c r="AJ8" s="342"/>
+      <c r="AK8" s="342"/>
+      <c r="AL8" s="328" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="334"/>
-      <c r="AN8" s="334"/>
-      <c r="AO8" s="334"/>
-      <c r="AP8" s="334"/>
-      <c r="AQ8" s="334"/>
-      <c r="AR8" s="334"/>
-      <c r="AS8" s="334"/>
-      <c r="AT8" s="340" t="s">
+      <c r="AM8" s="328"/>
+      <c r="AN8" s="328"/>
+      <c r="AO8" s="328"/>
+      <c r="AP8" s="328"/>
+      <c r="AQ8" s="328"/>
+      <c r="AR8" s="328"/>
+      <c r="AS8" s="328"/>
+      <c r="AT8" s="324" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="340"/>
-      <c r="AV8" s="340"/>
-      <c r="AW8" s="340"/>
-      <c r="AX8" s="340"/>
-      <c r="AY8" s="340"/>
-      <c r="AZ8" s="340"/>
-      <c r="BA8" s="340"/>
-      <c r="BB8" s="340"/>
-      <c r="BC8" s="341" t="s">
+      <c r="AU8" s="324"/>
+      <c r="AV8" s="324"/>
+      <c r="AW8" s="324"/>
+      <c r="AX8" s="324"/>
+      <c r="AY8" s="324"/>
+      <c r="AZ8" s="324"/>
+      <c r="BA8" s="324"/>
+      <c r="BB8" s="324"/>
+      <c r="BC8" s="325" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="341"/>
-      <c r="BE8" s="341"/>
-      <c r="BF8" s="341"/>
-      <c r="BG8" s="341"/>
-      <c r="BH8" s="341"/>
+      <c r="BD8" s="325"/>
+      <c r="BE8" s="325"/>
+      <c r="BF8" s="325"/>
+      <c r="BG8" s="325"/>
+      <c r="BH8" s="325"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="336" t="s">
+      <c r="C9" s="330" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
-      <c r="F9" s="336"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
-      <c r="J9" s="323" t="s">
+      <c r="D9" s="330"/>
+      <c r="E9" s="330"/>
+      <c r="F9" s="330"/>
+      <c r="G9" s="330"/>
+      <c r="H9" s="330"/>
+      <c r="I9" s="330"/>
+      <c r="J9" s="331" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="323"/>
-      <c r="L9" s="323"/>
-      <c r="M9" s="323"/>
-      <c r="N9" s="323"/>
-      <c r="O9" s="323"/>
-      <c r="P9" s="323"/>
-      <c r="Q9" s="323"/>
+      <c r="K9" s="331"/>
+      <c r="L9" s="331"/>
+      <c r="M9" s="331"/>
+      <c r="N9" s="331"/>
+      <c r="O9" s="331"/>
+      <c r="P9" s="331"/>
+      <c r="Q9" s="331"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="324" t="s">
+      <c r="V9" s="336" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="325"/>
-      <c r="X9" s="325"/>
-      <c r="Y9" s="325"/>
-      <c r="Z9" s="325"/>
-      <c r="AA9" s="325"/>
-      <c r="AB9" s="326"/>
-      <c r="AC9" s="328"/>
+      <c r="W9" s="337"/>
+      <c r="X9" s="337"/>
+      <c r="Y9" s="337"/>
+      <c r="Z9" s="337"/>
+      <c r="AA9" s="337"/>
+      <c r="AB9" s="338"/>
+      <c r="AC9" s="340"/>
       <c r="AD9" s="346" t="s">
         <v>209</v>
       </c>
@@ -33405,23 +33405,23 @@
       <c r="AI9" s="347"/>
       <c r="AJ9" s="347"/>
       <c r="AK9" s="348"/>
-      <c r="AL9" s="335" t="s">
+      <c r="AL9" s="329" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="335"/>
-      <c r="AN9" s="335"/>
-      <c r="AO9" s="335"/>
-      <c r="AP9" s="335"/>
-      <c r="AQ9" s="335"/>
-      <c r="AR9" s="335"/>
-      <c r="AS9" s="335"/>
-      <c r="AT9" s="342" t="s">
+      <c r="AM9" s="329"/>
+      <c r="AN9" s="329"/>
+      <c r="AO9" s="329"/>
+      <c r="AP9" s="329"/>
+      <c r="AQ9" s="329"/>
+      <c r="AR9" s="329"/>
+      <c r="AS9" s="329"/>
+      <c r="AT9" s="326" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="342"/>
-      <c r="AV9" s="342"/>
-      <c r="AW9" s="342"/>
-      <c r="AX9" s="342"/>
+      <c r="AU9" s="326"/>
+      <c r="AV9" s="326"/>
+      <c r="AW9" s="326"/>
+      <c r="AX9" s="326"/>
       <c r="AY9" s="344"/>
       <c r="AZ9" s="344"/>
       <c r="BA9" s="344"/>
@@ -33429,11 +33429,11 @@
       <c r="BC9" s="345" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="343"/>
-      <c r="BE9" s="343"/>
-      <c r="BF9" s="343"/>
-      <c r="BG9" s="343"/>
-      <c r="BH9" s="343"/>
+      <c r="BD9" s="327"/>
+      <c r="BE9" s="327"/>
+      <c r="BF9" s="327"/>
+      <c r="BG9" s="327"/>
+      <c r="BH9" s="327"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -42133,11 +42133,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -42148,6 +42143,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -42233,33 +42233,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="322" t="s">
+      <c r="O3" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="322"/>
-      <c r="Q3" s="322"/>
-      <c r="R3" s="322"/>
-      <c r="S3" s="322"/>
-      <c r="T3" s="322"/>
-      <c r="U3" s="322"/>
-      <c r="V3" s="322"/>
-      <c r="W3" s="322"/>
-      <c r="X3" s="322"/>
+      <c r="P3" s="335"/>
+      <c r="Q3" s="335"/>
+      <c r="R3" s="335"/>
+      <c r="S3" s="335"/>
+      <c r="T3" s="335"/>
+      <c r="U3" s="335"/>
+      <c r="V3" s="335"/>
+      <c r="W3" s="335"/>
+      <c r="X3" s="335"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="322"/>
-      <c r="P4" s="322"/>
-      <c r="Q4" s="322"/>
-      <c r="R4" s="322"/>
-      <c r="S4" s="322"/>
-      <c r="T4" s="322"/>
-      <c r="U4" s="322"/>
-      <c r="V4" s="322"/>
-      <c r="W4" s="322"/>
-      <c r="X4" s="322"/>
+      <c r="O4" s="335"/>
+      <c r="P4" s="335"/>
+      <c r="Q4" s="335"/>
+      <c r="R4" s="335"/>
+      <c r="S4" s="335"/>
+      <c r="T4" s="335"/>
+      <c r="U4" s="335"/>
+      <c r="V4" s="335"/>
+      <c r="W4" s="335"/>
+      <c r="X4" s="335"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -42288,16 +42288,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="323" t="s">
+      <c r="J8" s="331" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="323"/>
-      <c r="L8" s="323"/>
-      <c r="M8" s="323"/>
-      <c r="N8" s="323"/>
-      <c r="O8" s="323"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
+      <c r="K8" s="331"/>
+      <c r="L8" s="331"/>
+      <c r="M8" s="331"/>
+      <c r="N8" s="331"/>
+      <c r="O8" s="331"/>
+      <c r="P8" s="331"/>
+      <c r="Q8" s="331"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -42308,107 +42308,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="324" t="s">
+      <c r="X8" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="325"/>
-      <c r="Z8" s="325"/>
-      <c r="AA8" s="326"/>
-      <c r="AB8" s="327" t="s">
+      <c r="Y8" s="337"/>
+      <c r="Z8" s="337"/>
+      <c r="AA8" s="338"/>
+      <c r="AB8" s="339" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="329" t="s">
+      <c r="AC8" s="341" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="330"/>
-      <c r="AE8" s="330"/>
-      <c r="AF8" s="330"/>
-      <c r="AG8" s="330"/>
-      <c r="AH8" s="330"/>
-      <c r="AI8" s="334" t="s">
+      <c r="AD8" s="342"/>
+      <c r="AE8" s="342"/>
+      <c r="AF8" s="342"/>
+      <c r="AG8" s="342"/>
+      <c r="AH8" s="342"/>
+      <c r="AI8" s="328" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="334"/>
-      <c r="AK8" s="334"/>
-      <c r="AL8" s="334"/>
-      <c r="AM8" s="334"/>
-      <c r="AN8" s="334"/>
-      <c r="AO8" s="340" t="s">
+      <c r="AJ8" s="328"/>
+      <c r="AK8" s="328"/>
+      <c r="AL8" s="328"/>
+      <c r="AM8" s="328"/>
+      <c r="AN8" s="328"/>
+      <c r="AO8" s="324" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="340"/>
-      <c r="AQ8" s="340"/>
-      <c r="AR8" s="340"/>
-      <c r="AS8" s="341" t="s">
+      <c r="AP8" s="324"/>
+      <c r="AQ8" s="324"/>
+      <c r="AR8" s="324"/>
+      <c r="AS8" s="325" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="341"/>
-      <c r="AU8" s="341"/>
+      <c r="AT8" s="325"/>
+      <c r="AU8" s="325"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="336" t="s">
+      <c r="C9" s="330" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
-      <c r="F9" s="336"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
-      <c r="J9" s="323" t="s">
+      <c r="D9" s="330"/>
+      <c r="E9" s="330"/>
+      <c r="F9" s="330"/>
+      <c r="G9" s="330"/>
+      <c r="H9" s="330"/>
+      <c r="I9" s="330"/>
+      <c r="J9" s="331" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="323"/>
-      <c r="L9" s="323"/>
-      <c r="M9" s="323"/>
-      <c r="N9" s="323"/>
-      <c r="O9" s="323"/>
-      <c r="P9" s="323"/>
-      <c r="Q9" s="323"/>
+      <c r="K9" s="331"/>
+      <c r="L9" s="331"/>
+      <c r="M9" s="331"/>
+      <c r="N9" s="331"/>
+      <c r="O9" s="331"/>
+      <c r="P9" s="331"/>
+      <c r="Q9" s="331"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="324" t="s">
+      <c r="V9" s="336" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="325"/>
-      <c r="X9" s="325"/>
-      <c r="Y9" s="325"/>
-      <c r="Z9" s="325"/>
-      <c r="AA9" s="326"/>
-      <c r="AB9" s="328"/>
-      <c r="AC9" s="333" t="s">
+      <c r="W9" s="337"/>
+      <c r="X9" s="337"/>
+      <c r="Y9" s="337"/>
+      <c r="Z9" s="337"/>
+      <c r="AA9" s="338"/>
+      <c r="AB9" s="340"/>
+      <c r="AC9" s="343" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="333"/>
-      <c r="AE9" s="333"/>
-      <c r="AF9" s="333"/>
-      <c r="AG9" s="333"/>
-      <c r="AH9" s="333"/>
-      <c r="AI9" s="335" t="s">
+      <c r="AD9" s="343"/>
+      <c r="AE9" s="343"/>
+      <c r="AF9" s="343"/>
+      <c r="AG9" s="343"/>
+      <c r="AH9" s="343"/>
+      <c r="AI9" s="329" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="335"/>
-      <c r="AK9" s="335"/>
-      <c r="AL9" s="335"/>
-      <c r="AM9" s="335"/>
-      <c r="AN9" s="335"/>
-      <c r="AO9" s="342" t="s">
+      <c r="AJ9" s="329"/>
+      <c r="AK9" s="329"/>
+      <c r="AL9" s="329"/>
+      <c r="AM9" s="329"/>
+      <c r="AN9" s="329"/>
+      <c r="AO9" s="326" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="342"/>
-      <c r="AQ9" s="342"/>
-      <c r="AR9" s="342"/>
-      <c r="AS9" s="343" t="s">
+      <c r="AP9" s="326"/>
+      <c r="AQ9" s="326"/>
+      <c r="AR9" s="326"/>
+      <c r="AS9" s="327" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="343"/>
-      <c r="AU9" s="343"/>
+      <c r="AT9" s="327"/>
+      <c r="AU9" s="327"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -48555,6 +48555,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -48565,11 +48570,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -49166,6 +49166,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -49303,35 +49318,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -49353,9 +49343,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12883" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7264511E-D687-423D-BDD4-B3022074C40D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{112CFA50-3194-417D-B4BC-6D8321F8E0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="410">
   <si>
     <t>RC</t>
   </si>
@@ -2926,7 +2926,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3709,6 +3709,72 @@
     <xf numFmtId="0" fontId="0" fillId="49" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -3727,85 +3793,22 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -9107,11 +9110,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="284"/>
-      <c r="E3" s="316" t="s">
+      <c r="E3" s="338" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="317"/>
-      <c r="G3" s="318"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="340"/>
       <c r="H3" s="282" t="s">
         <v>8</v>
       </c>
@@ -11863,19 +11866,19 @@
       </c>
       <c r="E11" s="141">
         <f>COUNTIFS(Maestro!AQ11:AQ70,"&gt;0",Maestro!AQ11:AQ70,"&lt;1")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="142">
         <f t="shared" si="1"/>
-        <v>3.3333333333333333E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="G11" s="143">
         <f>COUNTIF(Maestro!AQ11:AQ70,0)</f>
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H11" s="144">
         <f t="shared" si="2"/>
-        <v>0.96666666666666667</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="I11" s="145">
         <f t="shared" si="3"/>
@@ -12154,21 +12157,21 @@
       <c r="C20" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="319" t="s">
+      <c r="D20" s="341" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="319"/>
-      <c r="F20" s="319"/>
-      <c r="G20" s="320" t="s">
+      <c r="E20" s="341"/>
+      <c r="F20" s="341"/>
+      <c r="G20" s="342" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="320"/>
-      <c r="I20" s="320"/>
-      <c r="J20" s="321" t="s">
+      <c r="H20" s="342"/>
+      <c r="I20" s="342"/>
+      <c r="J20" s="343" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="321"/>
-      <c r="L20" s="321"/>
+      <c r="K20" s="343"/>
+      <c r="L20" s="343"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C21" s="146"/>
@@ -12336,11 +12339,11 @@
       </c>
       <c r="E25" s="154">
         <f>COUNTIFS(Maestro!F11:F70,"Presencial",Maestro!AQ11:AQ70,"&gt;0",Maestro!AQ11:AQ70,"&lt;1")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="155">
         <f>COUNTIFS(Maestro!F11:F70,"Presencial",Maestro!AQ11:AQ70,0)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="153">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!AQ11:AQ70,"&gt;=1")</f>
@@ -12348,11 +12351,11 @@
       </c>
       <c r="H25" s="154">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!AQ11:AQ70,"&gt;0",Maestro!AQ11:AQ70,"&lt;1")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" s="155">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!AQ11:AQ70,0)</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J25" s="153">
         <f>COUNTIFS(Maestro!F11:F70,"Híbrido",Maestro!AQ11:AQ70,"&gt;=1")</f>
@@ -13587,7 +13590,7 @@
       </c>
       <c r="H55" s="157" t="str">
         <f>IF(B55="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B55,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>10%</v>
       </c>
       <c r="I55" s="157" t="str">
         <f>IF(B55="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B55,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14231,7 +14234,7 @@
       </c>
       <c r="H69" s="157" t="str">
         <f>IF(B69="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B69,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>10%</v>
       </c>
       <c r="I69" s="157" t="str">
         <f>IF(B69="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B69,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14277,7 +14280,7 @@
       </c>
       <c r="H70" s="137" t="str">
         <f>IF(B70="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B70,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>10%</v>
       </c>
       <c r="I70" s="137" t="str">
         <f>IF(B70="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B70,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15611,43 +15614,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="335" t="s">
+      <c r="O3" s="333" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="335"/>
-      <c r="Q3" s="335"/>
-      <c r="R3" s="335"/>
-      <c r="S3" s="335"/>
-      <c r="T3" s="335"/>
-      <c r="U3" s="335"/>
-      <c r="V3" s="335"/>
-      <c r="W3" s="335"/>
-      <c r="X3" s="335"/>
-      <c r="Y3" s="335"/>
-      <c r="Z3" s="335"/>
-      <c r="AA3" s="335"/>
-      <c r="AB3" s="335"/>
-      <c r="AC3" s="335"/>
+      <c r="P3" s="333"/>
+      <c r="Q3" s="333"/>
+      <c r="R3" s="333"/>
+      <c r="S3" s="333"/>
+      <c r="T3" s="333"/>
+      <c r="U3" s="333"/>
+      <c r="V3" s="333"/>
+      <c r="W3" s="333"/>
+      <c r="X3" s="333"/>
+      <c r="Y3" s="333"/>
+      <c r="Z3" s="333"/>
+      <c r="AA3" s="333"/>
+      <c r="AB3" s="333"/>
+      <c r="AC3" s="333"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="335"/>
-      <c r="P4" s="335"/>
-      <c r="Q4" s="335"/>
-      <c r="R4" s="335"/>
-      <c r="S4" s="335"/>
-      <c r="T4" s="335"/>
-      <c r="U4" s="335"/>
-      <c r="V4" s="335"/>
-      <c r="W4" s="335"/>
-      <c r="X4" s="335"/>
-      <c r="Y4" s="335"/>
-      <c r="Z4" s="335"/>
-      <c r="AA4" s="335"/>
-      <c r="AB4" s="335"/>
-      <c r="AC4" s="335"/>
+      <c r="O4" s="333"/>
+      <c r="P4" s="333"/>
+      <c r="Q4" s="333"/>
+      <c r="R4" s="333"/>
+      <c r="S4" s="333"/>
+      <c r="T4" s="333"/>
+      <c r="U4" s="333"/>
+      <c r="V4" s="333"/>
+      <c r="W4" s="333"/>
+      <c r="X4" s="333"/>
+      <c r="Y4" s="333"/>
+      <c r="Z4" s="333"/>
+      <c r="AA4" s="333"/>
+      <c r="AB4" s="333"/>
+      <c r="AC4" s="333"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -15676,17 +15679,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="331" t="s">
+      <c r="J8" s="324" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="331"/>
-      <c r="L8" s="331"/>
-      <c r="M8" s="331"/>
-      <c r="N8" s="331"/>
-      <c r="O8" s="331"/>
-      <c r="P8" s="331"/>
-      <c r="Q8" s="331"/>
-      <c r="R8" s="331"/>
+      <c r="K8" s="324"/>
+      <c r="L8" s="324"/>
+      <c r="M8" s="324"/>
+      <c r="N8" s="324"/>
+      <c r="O8" s="324"/>
+      <c r="P8" s="324"/>
+      <c r="Q8" s="324"/>
+      <c r="R8" s="324"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -15701,27 +15704,27 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="336" t="s">
+      <c r="AC8" s="325" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="337"/>
-      <c r="AE8" s="337"/>
-      <c r="AF8" s="337"/>
-      <c r="AG8" s="337"/>
-      <c r="AH8" s="338"/>
-      <c r="AI8" s="339" t="s">
+      <c r="AD8" s="326"/>
+      <c r="AE8" s="326"/>
+      <c r="AF8" s="326"/>
+      <c r="AG8" s="326"/>
+      <c r="AH8" s="327"/>
+      <c r="AI8" s="334" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="341" t="s">
+      <c r="AL8" s="336" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="342"/>
-      <c r="AN8" s="342"/>
-      <c r="AO8" s="342"/>
-      <c r="AP8" s="342"/>
-      <c r="AQ8" s="342"/>
+      <c r="AM8" s="337"/>
+      <c r="AN8" s="337"/>
+      <c r="AO8" s="337"/>
+      <c r="AP8" s="337"/>
+      <c r="AQ8" s="337"/>
       <c r="AR8" s="328" t="s">
         <v>201</v>
       </c>
@@ -15736,89 +15739,89 @@
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="324" t="s">
+      <c r="BD8" s="321" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="324"/>
-      <c r="BF8" s="324"/>
-      <c r="BG8" s="324"/>
-      <c r="BH8" s="324"/>
-      <c r="BI8" s="324"/>
-      <c r="BJ8" s="324"/>
-      <c r="BK8" s="324"/>
-      <c r="BL8" s="324"/>
-      <c r="BM8" s="324"/>
-      <c r="BN8" s="324"/>
-      <c r="BO8" s="324"/>
-      <c r="BP8" s="324"/>
-      <c r="BQ8" s="325" t="s">
+      <c r="BE8" s="321"/>
+      <c r="BF8" s="321"/>
+      <c r="BG8" s="321"/>
+      <c r="BH8" s="321"/>
+      <c r="BI8" s="321"/>
+      <c r="BJ8" s="321"/>
+      <c r="BK8" s="321"/>
+      <c r="BL8" s="321"/>
+      <c r="BM8" s="321"/>
+      <c r="BN8" s="321"/>
+      <c r="BO8" s="321"/>
+      <c r="BP8" s="321"/>
+      <c r="BQ8" s="322" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="325"/>
-      <c r="BS8" s="325"/>
+      <c r="BR8" s="322"/>
+      <c r="BS8" s="322"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="330" t="s">
+      <c r="C9" s="323" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
-      <c r="G9" s="330"/>
-      <c r="H9" s="330"/>
-      <c r="I9" s="330"/>
-      <c r="J9" s="331" t="s">
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="331"/>
-      <c r="L9" s="331"/>
-      <c r="M9" s="331"/>
-      <c r="N9" s="331"/>
-      <c r="O9" s="331"/>
-      <c r="P9" s="331"/>
-      <c r="Q9" s="331"/>
-      <c r="R9" s="331"/>
-      <c r="S9" s="332" t="s">
+      <c r="K9" s="324"/>
+      <c r="L9" s="324"/>
+      <c r="M9" s="324"/>
+      <c r="N9" s="324"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
+      <c r="R9" s="324"/>
+      <c r="S9" s="347" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="333" t="s">
+      <c r="T9" s="344" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="333" t="s">
+      <c r="U9" s="344" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="333" t="s">
+      <c r="V9" s="344" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="199"/>
       <c r="X9" s="199"/>
       <c r="Y9" s="199"/>
       <c r="Z9" s="199"/>
-      <c r="AA9" s="336" t="s">
+      <c r="AA9" s="325" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="337"/>
-      <c r="AC9" s="337"/>
-      <c r="AD9" s="337"/>
-      <c r="AE9" s="337"/>
-      <c r="AF9" s="337"/>
-      <c r="AG9" s="337"/>
-      <c r="AH9" s="338"/>
-      <c r="AI9" s="340"/>
+      <c r="AB9" s="326"/>
+      <c r="AC9" s="326"/>
+      <c r="AD9" s="326"/>
+      <c r="AE9" s="326"/>
+      <c r="AF9" s="326"/>
+      <c r="AG9" s="326"/>
+      <c r="AH9" s="327"/>
+      <c r="AI9" s="335"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="343" t="s">
+      <c r="AL9" s="346" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="343"/>
-      <c r="AN9" s="343"/>
-      <c r="AO9" s="343"/>
-      <c r="AP9" s="343"/>
-      <c r="AQ9" s="343"/>
+      <c r="AM9" s="346"/>
+      <c r="AN9" s="346"/>
+      <c r="AO9" s="346"/>
+      <c r="AP9" s="346"/>
+      <c r="AQ9" s="346"/>
       <c r="AR9" s="329" t="s">
         <v>201</v>
       </c>
@@ -15833,36 +15836,36 @@
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="326" t="s">
+      <c r="BD9" s="317" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="326"/>
-      <c r="BF9" s="326"/>
-      <c r="BG9" s="326"/>
-      <c r="BH9" s="326"/>
-      <c r="BI9" s="326"/>
-      <c r="BJ9" s="326"/>
-      <c r="BK9" s="326"/>
-      <c r="BL9" s="326"/>
-      <c r="BM9" s="326"/>
-      <c r="BN9" s="326"/>
-      <c r="BO9" s="326"/>
-      <c r="BP9" s="326"/>
-      <c r="BQ9" s="327" t="s">
+      <c r="BE9" s="317"/>
+      <c r="BF9" s="317"/>
+      <c r="BG9" s="317"/>
+      <c r="BH9" s="317"/>
+      <c r="BI9" s="317"/>
+      <c r="BJ9" s="317"/>
+      <c r="BK9" s="317"/>
+      <c r="BL9" s="317"/>
+      <c r="BM9" s="317"/>
+      <c r="BN9" s="317"/>
+      <c r="BO9" s="317"/>
+      <c r="BP9" s="317"/>
+      <c r="BQ9" s="320" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="327"/>
-      <c r="BS9" s="327"/>
-      <c r="BT9" s="322" t="s">
+      <c r="BR9" s="320"/>
+      <c r="BS9" s="320"/>
+      <c r="BT9" s="348" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="322" t="s">
+      <c r="BU9" s="348" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="322" t="s">
+      <c r="BV9" s="348" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="323" t="s">
+      <c r="BW9" s="349" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -15918,10 +15921,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="332"/>
-      <c r="T10" s="334"/>
-      <c r="U10" s="334"/>
-      <c r="V10" s="334"/>
+      <c r="S10" s="347"/>
+      <c r="T10" s="345"/>
+      <c r="U10" s="345"/>
+      <c r="V10" s="345"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16047,10 +16050,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="322"/>
-      <c r="BU10" s="322"/>
-      <c r="BV10" s="322"/>
-      <c r="BW10" s="323"/>
+      <c r="BT10" s="348"/>
+      <c r="BU10" s="348"/>
+      <c r="BV10" s="348"/>
+      <c r="BW10" s="349"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -16455,7 +16458,7 @@
       </c>
       <c r="AG12" s="12" t="str" cm="1">
         <f t="array" ref="AG12">IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AG$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v>No</v>
       </c>
       <c r="AH12" s="12" t="str" cm="1">
         <f t="array" ref="AH12">IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AH$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -16739,7 +16742,7 @@
       </c>
       <c r="AG13" s="12" t="str" cm="1">
         <f t="array" ref="AG13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AG$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Si</v>
+        <v>Sí</v>
       </c>
       <c r="AH13" s="12" t="str" cm="1">
         <f t="array" ref="AH13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AH$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -16849,7 +16852,7 @@
       </c>
       <c r="BJ13" s="12" t="str" cm="1">
         <f t="array" ref="BJ13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Validar datos de Aulas Master</v>
+        <v>No aplica</v>
       </c>
       <c r="BK13" s="12" cm="1">
         <f t="array" ref="BK13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BK$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17133,7 +17136,7 @@
       </c>
       <c r="BJ14" s="12" t="str" cm="1">
         <f t="array" ref="BJ14">IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Validar datos de Aulas Master</v>
+        <v>No aplica</v>
       </c>
       <c r="BK14" s="12" cm="1">
         <f t="array" ref="BK14">IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BK$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19690,7 +19693,7 @@
       </c>
       <c r="BJ23" s="12" t="str" cm="1">
         <f t="array" ref="BJ23">IFERROR(_xlfn.XLOOKUP($I23,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Validar datos de Aulas Master</v>
+        <v>No aplica</v>
       </c>
       <c r="BK23" s="12" cm="1">
         <f t="array" ref="BK23">IFERROR(_xlfn.XLOOKUP($I23,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BK$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20258,7 +20261,7 @@
       </c>
       <c r="BJ25" s="12" t="str" cm="1">
         <f t="array" ref="BJ25">IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Validar datos de Aulas Master</v>
+        <v>No aplica</v>
       </c>
       <c r="BK25" s="12" cm="1">
         <f t="array" ref="BK25">IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BK$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21614,15 +21617,15 @@
       </c>
       <c r="AT30" s="12" t="str" cm="1">
         <f t="array" ref="AT30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AT$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AU30" s="12" t="str" cm="1">
         <f t="array" ref="AU30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AU$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AV30" s="12" t="str" cm="1">
         <f t="array" ref="AV30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AV$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AW30" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,Borrador!$AQ$11:$AQ$70,""),"")</f>
@@ -21887,7 +21890,7 @@
       </c>
       <c r="AQ31" s="11" cm="1">
         <f t="array" ref="AQ31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR31" s="12" t="str" cm="1">
         <f t="array" ref="AR31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21919,11 +21922,11 @@
       </c>
       <c r="AY31" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AZ31" s="11" cm="1">
         <f t="array" ref="AZ31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA31" s="11" cm="1">
         <f t="array" ref="BA31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23388,7 +23391,7 @@
       </c>
       <c r="BJ36" s="12" t="str" cm="1">
         <f t="array" ref="BJ36">IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Validar datos de Aulas Master</v>
+        <v>No aplica</v>
       </c>
       <c r="BK36" s="12" cm="1">
         <f t="array" ref="BK36">IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BK$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25874,7 +25877,7 @@
       </c>
       <c r="AQ45" s="11" cm="1">
         <f t="array" ref="AQ45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR45" s="12" t="str" cm="1">
         <f t="array" ref="AR45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25886,15 +25889,15 @@
       </c>
       <c r="AT45" s="12" t="str" cm="1">
         <f t="array" ref="AT45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AT$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AU45" s="12" t="str" cm="1">
         <f t="array" ref="AU45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AU$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AV45" s="12" t="str" cm="1">
         <f t="array" ref="AV45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AV$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AW45" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,Borrador!$AQ$11:$AQ$70,""),"")</f>
@@ -25906,11 +25909,11 @@
       </c>
       <c r="AY45" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AZ45" s="11" cm="1">
         <f t="array" ref="AZ45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA45" s="11" t="str" cm="1">
         <f t="array" ref="BA45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26158,7 +26161,7 @@
       </c>
       <c r="AQ46" s="11" cm="1">
         <f t="array" ref="AQ46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR46" s="12" t="str" cm="1">
         <f t="array" ref="AR46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26170,15 +26173,15 @@
       </c>
       <c r="AT46" s="12" t="str" cm="1">
         <f t="array" ref="AT46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AT$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AU46" s="12" t="str" cm="1">
         <f t="array" ref="AU46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AU$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AV46" s="12" t="str" cm="1">
         <f t="array" ref="AV46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AV$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>sin iniciar</v>
+        <v>en proceso</v>
       </c>
       <c r="AW46" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,Borrador!$AQ$11:$AQ$70,""),"")</f>
@@ -26190,11 +26193,11 @@
       </c>
       <c r="AY46" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AZ46" s="11" cm="1">
         <f t="array" ref="AZ46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA46" s="11" cm="1">
         <f t="array" ref="BA46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28222,7 +28225,7 @@
       </c>
       <c r="BJ53" s="12" t="str" cm="1">
         <f t="array" ref="BJ53">IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Validar datos de Aulas Master</v>
+        <v>No aplica</v>
       </c>
       <c r="BK53" s="12" cm="1">
         <f t="array" ref="BK53">IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BK$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28680,7 +28683,7 @@
       </c>
       <c r="AG55" s="12" t="str" cm="1">
         <f t="array" ref="AG55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AG$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v>No</v>
       </c>
       <c r="AH55" s="12" t="str" cm="1">
         <f t="array" ref="AH55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AH$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28788,9 +28791,9 @@
         <f t="array" ref="BI55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BI$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>sin iniciar</v>
       </c>
-      <c r="BJ55" s="12" t="str" cm="1">
+      <c r="BJ55" s="12" cm="1">
         <f t="array" ref="BJ55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Validar datos de Aulas Master</v>
+        <v>1</v>
       </c>
       <c r="BK55" s="12" cm="1">
         <f t="array" ref="BK55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BK$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31236,7 +31239,7 @@
       </c>
       <c r="AG64" s="12" t="str" cm="1">
         <f t="array" ref="AG64">IFERROR(_xlfn.XLOOKUP($I64,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AG$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v>No</v>
       </c>
       <c r="AH64" s="12" t="str" cm="1">
         <f t="array" ref="AH64">IFERROR(_xlfn.XLOOKUP($I64,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AH$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -33090,6 +33093,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33098,21 +33116,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33232,33 +33235,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="335" t="s">
+      <c r="O3" s="333" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="335"/>
-      <c r="Q3" s="335"/>
-      <c r="R3" s="335"/>
-      <c r="S3" s="335"/>
-      <c r="T3" s="335"/>
-      <c r="U3" s="335"/>
-      <c r="V3" s="335"/>
-      <c r="W3" s="335"/>
-      <c r="X3" s="335"/>
+      <c r="P3" s="333"/>
+      <c r="Q3" s="333"/>
+      <c r="R3" s="333"/>
+      <c r="S3" s="333"/>
+      <c r="T3" s="333"/>
+      <c r="U3" s="333"/>
+      <c r="V3" s="333"/>
+      <c r="W3" s="333"/>
+      <c r="X3" s="333"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="335"/>
-      <c r="P4" s="335"/>
-      <c r="Q4" s="335"/>
-      <c r="R4" s="335"/>
-      <c r="S4" s="335"/>
-      <c r="T4" s="335"/>
-      <c r="U4" s="335"/>
-      <c r="V4" s="335"/>
-      <c r="W4" s="335"/>
-      <c r="X4" s="335"/>
+      <c r="O4" s="333"/>
+      <c r="P4" s="333"/>
+      <c r="Q4" s="333"/>
+      <c r="R4" s="333"/>
+      <c r="S4" s="333"/>
+      <c r="T4" s="333"/>
+      <c r="U4" s="333"/>
+      <c r="V4" s="333"/>
+      <c r="W4" s="333"/>
+      <c r="X4" s="333"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -33287,16 +33290,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="331" t="s">
+      <c r="J8" s="324" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="331"/>
-      <c r="L8" s="331"/>
-      <c r="M8" s="331"/>
-      <c r="N8" s="331"/>
-      <c r="O8" s="331"/>
-      <c r="P8" s="331"/>
-      <c r="Q8" s="331"/>
+      <c r="K8" s="324"/>
+      <c r="L8" s="324"/>
+      <c r="M8" s="324"/>
+      <c r="N8" s="324"/>
+      <c r="O8" s="324"/>
+      <c r="P8" s="324"/>
+      <c r="Q8" s="324"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33307,26 +33310,26 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="336" t="s">
+      <c r="X8" s="325" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="337"/>
-      <c r="Z8" s="337"/>
-      <c r="AA8" s="337"/>
-      <c r="AB8" s="338"/>
-      <c r="AC8" s="339" t="s">
+      <c r="Y8" s="326"/>
+      <c r="Z8" s="326"/>
+      <c r="AA8" s="326"/>
+      <c r="AB8" s="327"/>
+      <c r="AC8" s="334" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="341" t="s">
+      <c r="AF8" s="336" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="342"/>
-      <c r="AH8" s="342"/>
-      <c r="AI8" s="342"/>
-      <c r="AJ8" s="342"/>
-      <c r="AK8" s="342"/>
+      <c r="AG8" s="337"/>
+      <c r="AH8" s="337"/>
+      <c r="AI8" s="337"/>
+      <c r="AJ8" s="337"/>
+      <c r="AK8" s="337"/>
       <c r="AL8" s="328" t="s">
         <v>201</v>
       </c>
@@ -33337,74 +33340,74 @@
       <c r="AQ8" s="328"/>
       <c r="AR8" s="328"/>
       <c r="AS8" s="328"/>
-      <c r="AT8" s="324" t="s">
+      <c r="AT8" s="321" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="324"/>
-      <c r="AV8" s="324"/>
-      <c r="AW8" s="324"/>
-      <c r="AX8" s="324"/>
-      <c r="AY8" s="324"/>
-      <c r="AZ8" s="324"/>
-      <c r="BA8" s="324"/>
-      <c r="BB8" s="324"/>
-      <c r="BC8" s="325" t="s">
+      <c r="AU8" s="321"/>
+      <c r="AV8" s="321"/>
+      <c r="AW8" s="321"/>
+      <c r="AX8" s="321"/>
+      <c r="AY8" s="321"/>
+      <c r="AZ8" s="321"/>
+      <c r="BA8" s="321"/>
+      <c r="BB8" s="321"/>
+      <c r="BC8" s="322" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="325"/>
-      <c r="BE8" s="325"/>
-      <c r="BF8" s="325"/>
-      <c r="BG8" s="325"/>
-      <c r="BH8" s="325"/>
+      <c r="BD8" s="322"/>
+      <c r="BE8" s="322"/>
+      <c r="BF8" s="322"/>
+      <c r="BG8" s="322"/>
+      <c r="BH8" s="322"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="330" t="s">
+      <c r="C9" s="323" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
-      <c r="G9" s="330"/>
-      <c r="H9" s="330"/>
-      <c r="I9" s="330"/>
-      <c r="J9" s="331" t="s">
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="331"/>
-      <c r="L9" s="331"/>
-      <c r="M9" s="331"/>
-      <c r="N9" s="331"/>
-      <c r="O9" s="331"/>
-      <c r="P9" s="331"/>
-      <c r="Q9" s="331"/>
+      <c r="K9" s="324"/>
+      <c r="L9" s="324"/>
+      <c r="M9" s="324"/>
+      <c r="N9" s="324"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="336" t="s">
+      <c r="V9" s="325" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="337"/>
-      <c r="X9" s="337"/>
-      <c r="Y9" s="337"/>
-      <c r="Z9" s="337"/>
-      <c r="AA9" s="337"/>
-      <c r="AB9" s="338"/>
-      <c r="AC9" s="340"/>
-      <c r="AD9" s="346" t="s">
+      <c r="W9" s="326"/>
+      <c r="X9" s="326"/>
+      <c r="Y9" s="326"/>
+      <c r="Z9" s="326"/>
+      <c r="AA9" s="326"/>
+      <c r="AB9" s="327"/>
+      <c r="AC9" s="335"/>
+      <c r="AD9" s="330" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="347"/>
-      <c r="AF9" s="347"/>
-      <c r="AG9" s="347"/>
-      <c r="AH9" s="347"/>
-      <c r="AI9" s="347"/>
-      <c r="AJ9" s="347"/>
-      <c r="AK9" s="348"/>
+      <c r="AE9" s="331"/>
+      <c r="AF9" s="331"/>
+      <c r="AG9" s="331"/>
+      <c r="AH9" s="331"/>
+      <c r="AI9" s="331"/>
+      <c r="AJ9" s="331"/>
+      <c r="AK9" s="332"/>
       <c r="AL9" s="329" t="s">
         <v>201</v>
       </c>
@@ -33415,25 +33418,25 @@
       <c r="AQ9" s="329"/>
       <c r="AR9" s="329"/>
       <c r="AS9" s="329"/>
-      <c r="AT9" s="326" t="s">
+      <c r="AT9" s="317" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="326"/>
-      <c r="AV9" s="326"/>
-      <c r="AW9" s="326"/>
-      <c r="AX9" s="326"/>
-      <c r="AY9" s="344"/>
-      <c r="AZ9" s="344"/>
-      <c r="BA9" s="344"/>
-      <c r="BB9" s="344"/>
-      <c r="BC9" s="345" t="s">
+      <c r="AU9" s="317"/>
+      <c r="AV9" s="317"/>
+      <c r="AW9" s="317"/>
+      <c r="AX9" s="317"/>
+      <c r="AY9" s="318"/>
+      <c r="AZ9" s="318"/>
+      <c r="BA9" s="318"/>
+      <c r="BB9" s="318"/>
+      <c r="BC9" s="319" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="327"/>
-      <c r="BE9" s="327"/>
-      <c r="BF9" s="327"/>
-      <c r="BG9" s="327"/>
-      <c r="BH9" s="327"/>
+      <c r="BD9" s="320"/>
+      <c r="BE9" s="320"/>
+      <c r="BF9" s="320"/>
+      <c r="BG9" s="320"/>
+      <c r="BH9" s="320"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -34006,7 +34009,7 @@
         <v>312</v>
       </c>
       <c r="AA13" s="190" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AB13" s="190" t="s">
         <v>312</v>
@@ -34158,7 +34161,7 @@
         <v>317</v>
       </c>
       <c r="AA14" s="190" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AB14" s="190" t="s">
         <v>318</v>
@@ -34217,9 +34220,8 @@
       </c>
       <c r="AZ14" s="12"/>
       <c r="BA14" s="12"/>
-      <c r="BB14" s="185" t="str">
-        <f>IFERROR(AW14/AV14,"Validar datos de Aulas Master")</f>
-        <v>Validar datos de Aulas Master</v>
+      <c r="BB14" s="185" t="s">
+        <v>312</v>
       </c>
       <c r="BC14" s="12"/>
       <c r="BD14" s="177"/>
@@ -34357,9 +34359,8 @@
       </c>
       <c r="AZ15" s="12"/>
       <c r="BA15" s="12"/>
-      <c r="BB15" s="185" t="str">
-        <f>IFERROR(AW15/AV15,"Validar datos de Aulas Master")</f>
-        <v>Validar datos de Aulas Master</v>
+      <c r="BB15" s="185" t="s">
+        <v>312</v>
       </c>
       <c r="BC15" s="12"/>
       <c r="BD15" s="177"/>
@@ -35618,9 +35619,8 @@
       </c>
       <c r="AZ24" s="12"/>
       <c r="BA24" s="12"/>
-      <c r="BB24" s="185" t="str">
-        <f>IFERROR(AW24/AV24,"Validar datos de Aulas Master")</f>
-        <v>Validar datos de Aulas Master</v>
+      <c r="BB24" s="185" t="s">
+        <v>312</v>
       </c>
       <c r="BC24" s="12"/>
       <c r="BD24" s="177"/>
@@ -35899,9 +35899,8 @@
       </c>
       <c r="AZ26" s="12"/>
       <c r="BA26" s="12"/>
-      <c r="BB26" s="185" t="str">
-        <f>IFERROR(AW26/AV26,"Validar datos de Aulas Master")</f>
-        <v>Validar datos de Aulas Master</v>
+      <c r="BB26" s="185" t="s">
+        <v>312</v>
       </c>
       <c r="BC26" s="12"/>
       <c r="BD26" s="177"/>
@@ -36597,13 +36596,13 @@
         <v>194</v>
       </c>
       <c r="AN31" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AO31" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AP31" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AQ31" s="12"/>
       <c r="AR31" s="12"/>
@@ -36765,8 +36764,8 @@
       </c>
       <c r="AQ32" s="12"/>
       <c r="AR32" s="12"/>
-      <c r="AS32" s="11">
-        <v>0</v>
+      <c r="AS32" s="70">
+        <v>0.1</v>
       </c>
       <c r="AT32" s="12" t="s">
         <v>194</v>
@@ -37435,7 +37434,9 @@
       <c r="AC37" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD37" s="12"/>
+      <c r="AD37" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE37" s="12"/>
       <c r="AF37" s="11"/>
       <c r="AG37" s="11"/>
@@ -37484,9 +37485,8 @@
       </c>
       <c r="AZ37" s="12"/>
       <c r="BA37" s="12"/>
-      <c r="BB37" s="185" t="str">
-        <f>IFERROR(AW37/AV37,"Validar datos de Aulas Master")</f>
-        <v>Validar datos de Aulas Master</v>
+      <c r="BB37" s="185" t="s">
+        <v>312</v>
       </c>
       <c r="BC37" s="12"/>
       <c r="BD37" s="177"/>
@@ -37574,7 +37574,9 @@
       <c r="AC38" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD38" s="12"/>
+      <c r="AD38" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE38" s="12"/>
       <c r="AF38" s="11" t="s">
         <v>312</v>
@@ -38167,7 +38169,9 @@
       <c r="AC42" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD42" s="12"/>
+      <c r="AD42" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE42" s="12"/>
       <c r="AF42" s="11" t="s">
         <v>312</v>
@@ -38607,7 +38611,9 @@
       <c r="AC45" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD45" s="12"/>
+      <c r="AD45" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE45" s="12"/>
       <c r="AF45" s="11" t="s">
         <v>312</v>
@@ -38731,7 +38737,9 @@
       <c r="AC46" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD46" s="12"/>
+      <c r="AD46" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE46" s="12"/>
       <c r="AF46" s="11" t="s">
         <v>312</v>
@@ -38754,18 +38762,18 @@
         <v>194</v>
       </c>
       <c r="AN46" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AO46" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AP46" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AQ46" s="12"/>
       <c r="AR46" s="12"/>
       <c r="AS46" s="70">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AT46" s="12"/>
       <c r="AU46" s="12"/>
@@ -38896,18 +38904,18 @@
         <v>194</v>
       </c>
       <c r="AN47" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AO47" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AP47" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AQ47" s="12"/>
       <c r="AR47" s="12"/>
       <c r="AS47" s="70">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AT47" s="12" t="s">
         <v>194</v>
@@ -39171,7 +39179,9 @@
       <c r="AC49" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD49" s="12"/>
+      <c r="AD49" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE49" s="12"/>
       <c r="AF49" s="11" t="s">
         <v>312</v>
@@ -39295,7 +39305,9 @@
       <c r="AC50" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD50" s="12"/>
+      <c r="AD50" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE50" s="12"/>
       <c r="AF50" s="11" t="s">
         <v>312</v>
@@ -39584,7 +39596,9 @@
       <c r="AC52" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD52" s="12"/>
+      <c r="AD52" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE52" s="12"/>
       <c r="AF52" s="11" t="s">
         <v>312</v>
@@ -39720,7 +39734,9 @@
       <c r="AC53" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD53" s="12"/>
+      <c r="AD53" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE53" s="12"/>
       <c r="AF53" s="11" t="s">
         <v>312</v>
@@ -39897,7 +39913,7 @@
         <v>194</v>
       </c>
       <c r="AV54" s="79">
-        <f t="shared" si="1"/>
+        <f>AH54</f>
         <v>0</v>
       </c>
       <c r="AW54" s="184">
@@ -39911,9 +39927,8 @@
       </c>
       <c r="AZ54" s="12"/>
       <c r="BA54" s="12"/>
-      <c r="BB54" s="185" t="str">
-        <f>IFERROR(AW54/AV54,"Validar datos de Aulas Master")</f>
-        <v>Validar datos de Aulas Master</v>
+      <c r="BB54" s="185" t="s">
+        <v>312</v>
       </c>
       <c r="BC54" s="12"/>
       <c r="BD54" s="177"/>
@@ -40001,7 +40016,9 @@
       <c r="AC55" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD55" s="12"/>
+      <c r="AD55" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE55" s="12"/>
       <c r="AF55" s="11" t="s">
         <v>312</v>
@@ -40119,7 +40136,7 @@
         <v>312</v>
       </c>
       <c r="AA56" s="190" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AB56" s="190" t="s">
         <v>312</v>
@@ -40178,9 +40195,8 @@
       </c>
       <c r="AZ56" s="12"/>
       <c r="BA56" s="12"/>
-      <c r="BB56" s="185" t="str">
-        <f>IFERROR(AW56/AV56,"Validar datos de Aulas Master")</f>
-        <v>Validar datos de Aulas Master</v>
+      <c r="BB56" s="185">
+        <v>1</v>
       </c>
       <c r="BC56" s="12"/>
       <c r="BD56" s="177"/>
@@ -40419,7 +40435,9 @@
       <c r="AC58" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD58" s="12"/>
+      <c r="AD58" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE58" s="12"/>
       <c r="AF58" s="11" t="s">
         <v>312</v>
@@ -40543,7 +40561,9 @@
       <c r="AC59" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD59" s="12"/>
+      <c r="AD59" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE59" s="12"/>
       <c r="AF59" s="11" t="s">
         <v>312</v>
@@ -40667,7 +40687,9 @@
       <c r="AC60" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD60" s="12"/>
+      <c r="AD60" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE60" s="12"/>
       <c r="AF60" s="11" t="s">
         <v>312</v>
@@ -40791,7 +40813,9 @@
       <c r="AC61" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD61" s="12"/>
+      <c r="AD61" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE61" s="12"/>
       <c r="AF61" s="11" t="s">
         <v>312</v>
@@ -41078,7 +41102,9 @@
       <c r="AC63" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD63" s="12"/>
+      <c r="AD63" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE63" s="12"/>
       <c r="AF63" s="11" t="s">
         <v>312</v>
@@ -41353,7 +41379,7 @@
         <v>312</v>
       </c>
       <c r="AA65" s="190" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AB65" s="190" t="s">
         <v>312</v>
@@ -41510,7 +41536,9 @@
       <c r="AC66" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD66" s="12"/>
+      <c r="AD66" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE66" s="12"/>
       <c r="AF66" s="11" t="s">
         <v>312</v>
@@ -41634,7 +41662,9 @@
       <c r="AC67" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD67" s="12"/>
+      <c r="AD67" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE67" s="12"/>
       <c r="AF67" s="11" t="s">
         <v>312</v>
@@ -41758,7 +41788,9 @@
       <c r="AC68" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="AD68" s="12"/>
+      <c r="AD68" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="AE68" s="12"/>
       <c r="AF68" s="11" t="s">
         <v>312</v>
@@ -42118,7 +42150,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="3:63" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="BB71" s="316"/>
+    </row>
     <row r="72" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="73" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="74" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
@@ -42133,6 +42167,11 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -42143,11 +42182,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -42233,33 +42267,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="335" t="s">
+      <c r="O3" s="333" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="335"/>
-      <c r="Q3" s="335"/>
-      <c r="R3" s="335"/>
-      <c r="S3" s="335"/>
-      <c r="T3" s="335"/>
-      <c r="U3" s="335"/>
-      <c r="V3" s="335"/>
-      <c r="W3" s="335"/>
-      <c r="X3" s="335"/>
+      <c r="P3" s="333"/>
+      <c r="Q3" s="333"/>
+      <c r="R3" s="333"/>
+      <c r="S3" s="333"/>
+      <c r="T3" s="333"/>
+      <c r="U3" s="333"/>
+      <c r="V3" s="333"/>
+      <c r="W3" s="333"/>
+      <c r="X3" s="333"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="335"/>
-      <c r="P4" s="335"/>
-      <c r="Q4" s="335"/>
-      <c r="R4" s="335"/>
-      <c r="S4" s="335"/>
-      <c r="T4" s="335"/>
-      <c r="U4" s="335"/>
-      <c r="V4" s="335"/>
-      <c r="W4" s="335"/>
-      <c r="X4" s="335"/>
+      <c r="O4" s="333"/>
+      <c r="P4" s="333"/>
+      <c r="Q4" s="333"/>
+      <c r="R4" s="333"/>
+      <c r="S4" s="333"/>
+      <c r="T4" s="333"/>
+      <c r="U4" s="333"/>
+      <c r="V4" s="333"/>
+      <c r="W4" s="333"/>
+      <c r="X4" s="333"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -42288,16 +42322,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="331" t="s">
+      <c r="J8" s="324" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="331"/>
-      <c r="L8" s="331"/>
-      <c r="M8" s="331"/>
-      <c r="N8" s="331"/>
-      <c r="O8" s="331"/>
-      <c r="P8" s="331"/>
-      <c r="Q8" s="331"/>
+      <c r="K8" s="324"/>
+      <c r="L8" s="324"/>
+      <c r="M8" s="324"/>
+      <c r="N8" s="324"/>
+      <c r="O8" s="324"/>
+      <c r="P8" s="324"/>
+      <c r="Q8" s="324"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -42308,23 +42342,23 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="336" t="s">
+      <c r="X8" s="325" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="337"/>
-      <c r="Z8" s="337"/>
-      <c r="AA8" s="338"/>
-      <c r="AB8" s="339" t="s">
+      <c r="Y8" s="326"/>
+      <c r="Z8" s="326"/>
+      <c r="AA8" s="327"/>
+      <c r="AB8" s="334" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="341" t="s">
+      <c r="AC8" s="336" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="342"/>
-      <c r="AE8" s="342"/>
-      <c r="AF8" s="342"/>
-      <c r="AG8" s="342"/>
-      <c r="AH8" s="342"/>
+      <c r="AD8" s="337"/>
+      <c r="AE8" s="337"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="337"/>
+      <c r="AH8" s="337"/>
       <c r="AI8" s="328" t="s">
         <v>201</v>
       </c>
@@ -42333,63 +42367,63 @@
       <c r="AL8" s="328"/>
       <c r="AM8" s="328"/>
       <c r="AN8" s="328"/>
-      <c r="AO8" s="324" t="s">
+      <c r="AO8" s="321" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="324"/>
-      <c r="AQ8" s="324"/>
-      <c r="AR8" s="324"/>
-      <c r="AS8" s="325" t="s">
+      <c r="AP8" s="321"/>
+      <c r="AQ8" s="321"/>
+      <c r="AR8" s="321"/>
+      <c r="AS8" s="322" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="325"/>
-      <c r="AU8" s="325"/>
+      <c r="AT8" s="322"/>
+      <c r="AU8" s="322"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="330" t="s">
+      <c r="C9" s="323" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
-      <c r="G9" s="330"/>
-      <c r="H9" s="330"/>
-      <c r="I9" s="330"/>
-      <c r="J9" s="331" t="s">
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="331"/>
-      <c r="L9" s="331"/>
-      <c r="M9" s="331"/>
-      <c r="N9" s="331"/>
-      <c r="O9" s="331"/>
-      <c r="P9" s="331"/>
-      <c r="Q9" s="331"/>
+      <c r="K9" s="324"/>
+      <c r="L9" s="324"/>
+      <c r="M9" s="324"/>
+      <c r="N9" s="324"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="336" t="s">
+      <c r="V9" s="325" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="337"/>
-      <c r="X9" s="337"/>
-      <c r="Y9" s="337"/>
-      <c r="Z9" s="337"/>
-      <c r="AA9" s="338"/>
-      <c r="AB9" s="340"/>
-      <c r="AC9" s="343" t="s">
+      <c r="W9" s="326"/>
+      <c r="X9" s="326"/>
+      <c r="Y9" s="326"/>
+      <c r="Z9" s="326"/>
+      <c r="AA9" s="327"/>
+      <c r="AB9" s="335"/>
+      <c r="AC9" s="346" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="343"/>
-      <c r="AE9" s="343"/>
-      <c r="AF9" s="343"/>
-      <c r="AG9" s="343"/>
-      <c r="AH9" s="343"/>
+      <c r="AD9" s="346"/>
+      <c r="AE9" s="346"/>
+      <c r="AF9" s="346"/>
+      <c r="AG9" s="346"/>
+      <c r="AH9" s="346"/>
       <c r="AI9" s="329" t="s">
         <v>201</v>
       </c>
@@ -42398,17 +42432,17 @@
       <c r="AL9" s="329"/>
       <c r="AM9" s="329"/>
       <c r="AN9" s="329"/>
-      <c r="AO9" s="326" t="s">
+      <c r="AO9" s="317" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="326"/>
-      <c r="AQ9" s="326"/>
-      <c r="AR9" s="326"/>
-      <c r="AS9" s="327" t="s">
+      <c r="AP9" s="317"/>
+      <c r="AQ9" s="317"/>
+      <c r="AR9" s="317"/>
+      <c r="AS9" s="320" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="327"/>
-      <c r="AU9" s="327"/>
+      <c r="AT9" s="320"/>
+      <c r="AU9" s="320"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -48555,11 +48589,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -48570,6 +48599,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -48622,41 +48656,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="351" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
+      <c r="B2" s="351"/>
+      <c r="C2" s="351"/>
       <c r="D2" t="s">
         <v>381</v>
       </c>
-      <c r="E2" s="350" t="s">
+      <c r="E2" s="351" t="s">
         <v>382</v>
       </c>
-      <c r="F2" s="350"/>
+      <c r="F2" s="351"/>
       <c r="G2" s="182" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="349" t="s">
+      <c r="H2" s="350" t="s">
         <v>383</v>
       </c>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349" t="s">
+      <c r="I2" s="350"/>
+      <c r="J2" s="350"/>
+      <c r="K2" s="350" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="350"/>
-      <c r="M2" s="350"/>
-      <c r="N2" s="349" t="s">
+      <c r="L2" s="351"/>
+      <c r="M2" s="351"/>
+      <c r="N2" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="O2" s="350"/>
-      <c r="P2" s="350"/>
-      <c r="Q2" s="351"/>
-      <c r="R2" s="349" t="s">
+      <c r="O2" s="351"/>
+      <c r="P2" s="351"/>
+      <c r="Q2" s="352"/>
+      <c r="R2" s="350" t="s">
         <v>211</v>
       </c>
-      <c r="S2" s="350"/>
+      <c r="S2" s="351"/>
     </row>
     <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="85" t="s">
@@ -49166,18 +49200,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49319,25 +49353,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{112CFA50-3194-417D-B4BC-6D8321F8E0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{112CFA50-3194-417D-B4BC-6D8321F8E0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB3C08E2-BB5E-4514-81CB-995412ADDA10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3712,6 +3712,33 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3733,18 +3760,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3759,21 +3774,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3793,6 +3793,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3800,15 +3809,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -15614,43 +15614,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="333" t="s">
+      <c r="O3" s="317" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="333"/>
-      <c r="Q3" s="333"/>
-      <c r="R3" s="333"/>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
-      <c r="Y3" s="333"/>
-      <c r="Z3" s="333"/>
-      <c r="AA3" s="333"/>
-      <c r="AB3" s="333"/>
-      <c r="AC3" s="333"/>
+      <c r="P3" s="317"/>
+      <c r="Q3" s="317"/>
+      <c r="R3" s="317"/>
+      <c r="S3" s="317"/>
+      <c r="T3" s="317"/>
+      <c r="U3" s="317"/>
+      <c r="V3" s="317"/>
+      <c r="W3" s="317"/>
+      <c r="X3" s="317"/>
+      <c r="Y3" s="317"/>
+      <c r="Z3" s="317"/>
+      <c r="AA3" s="317"/>
+      <c r="AB3" s="317"/>
+      <c r="AC3" s="317"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="333"/>
-      <c r="P4" s="333"/>
-      <c r="Q4" s="333"/>
-      <c r="R4" s="333"/>
-      <c r="S4" s="333"/>
-      <c r="T4" s="333"/>
-      <c r="U4" s="333"/>
-      <c r="V4" s="333"/>
-      <c r="W4" s="333"/>
-      <c r="X4" s="333"/>
-      <c r="Y4" s="333"/>
-      <c r="Z4" s="333"/>
-      <c r="AA4" s="333"/>
-      <c r="AB4" s="333"/>
-      <c r="AC4" s="333"/>
+      <c r="O4" s="317"/>
+      <c r="P4" s="317"/>
+      <c r="Q4" s="317"/>
+      <c r="R4" s="317"/>
+      <c r="S4" s="317"/>
+      <c r="T4" s="317"/>
+      <c r="U4" s="317"/>
+      <c r="V4" s="317"/>
+      <c r="W4" s="317"/>
+      <c r="X4" s="317"/>
+      <c r="Y4" s="317"/>
+      <c r="Z4" s="317"/>
+      <c r="AA4" s="317"/>
+      <c r="AB4" s="317"/>
+      <c r="AC4" s="317"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -15679,17 +15679,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="324" t="s">
+      <c r="J8" s="318" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="324"/>
-      <c r="L8" s="324"/>
-      <c r="M8" s="324"/>
-      <c r="N8" s="324"/>
-      <c r="O8" s="324"/>
-      <c r="P8" s="324"/>
-      <c r="Q8" s="324"/>
-      <c r="R8" s="324"/>
+      <c r="K8" s="318"/>
+      <c r="L8" s="318"/>
+      <c r="M8" s="318"/>
+      <c r="N8" s="318"/>
+      <c r="O8" s="318"/>
+      <c r="P8" s="318"/>
+      <c r="Q8" s="318"/>
+      <c r="R8" s="318"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -15704,168 +15704,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="325" t="s">
+      <c r="AC8" s="319" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="326"/>
-      <c r="AE8" s="326"/>
-      <c r="AF8" s="326"/>
-      <c r="AG8" s="326"/>
-      <c r="AH8" s="327"/>
-      <c r="AI8" s="334" t="s">
+      <c r="AD8" s="320"/>
+      <c r="AE8" s="320"/>
+      <c r="AF8" s="320"/>
+      <c r="AG8" s="320"/>
+      <c r="AH8" s="321"/>
+      <c r="AI8" s="322" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="336" t="s">
+      <c r="AL8" s="324" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="337"/>
-      <c r="AN8" s="337"/>
-      <c r="AO8" s="337"/>
-      <c r="AP8" s="337"/>
-      <c r="AQ8" s="337"/>
-      <c r="AR8" s="328" t="s">
+      <c r="AM8" s="325"/>
+      <c r="AN8" s="325"/>
+      <c r="AO8" s="325"/>
+      <c r="AP8" s="325"/>
+      <c r="AQ8" s="325"/>
+      <c r="AR8" s="333" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="328"/>
-      <c r="AT8" s="328"/>
-      <c r="AU8" s="328"/>
-      <c r="AV8" s="328"/>
-      <c r="AW8" s="328"/>
-      <c r="AX8" s="328"/>
-      <c r="AY8" s="328"/>
-      <c r="AZ8" s="328"/>
+      <c r="AS8" s="333"/>
+      <c r="AT8" s="333"/>
+      <c r="AU8" s="333"/>
+      <c r="AV8" s="333"/>
+      <c r="AW8" s="333"/>
+      <c r="AX8" s="333"/>
+      <c r="AY8" s="333"/>
+      <c r="AZ8" s="333"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="321" t="s">
+      <c r="BD8" s="330" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="321"/>
-      <c r="BF8" s="321"/>
-      <c r="BG8" s="321"/>
-      <c r="BH8" s="321"/>
-      <c r="BI8" s="321"/>
-      <c r="BJ8" s="321"/>
-      <c r="BK8" s="321"/>
-      <c r="BL8" s="321"/>
-      <c r="BM8" s="321"/>
-      <c r="BN8" s="321"/>
-      <c r="BO8" s="321"/>
-      <c r="BP8" s="321"/>
-      <c r="BQ8" s="322" t="s">
+      <c r="BE8" s="330"/>
+      <c r="BF8" s="330"/>
+      <c r="BG8" s="330"/>
+      <c r="BH8" s="330"/>
+      <c r="BI8" s="330"/>
+      <c r="BJ8" s="330"/>
+      <c r="BK8" s="330"/>
+      <c r="BL8" s="330"/>
+      <c r="BM8" s="330"/>
+      <c r="BN8" s="330"/>
+      <c r="BO8" s="330"/>
+      <c r="BP8" s="330"/>
+      <c r="BQ8" s="331" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="322"/>
-      <c r="BS8" s="322"/>
+      <c r="BR8" s="331"/>
+      <c r="BS8" s="331"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="323" t="s">
+      <c r="C9" s="332" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="323"/>
-      <c r="E9" s="323"/>
-      <c r="F9" s="323"/>
-      <c r="G9" s="323"/>
-      <c r="H9" s="323"/>
-      <c r="I9" s="323"/>
-      <c r="J9" s="324" t="s">
+      <c r="D9" s="332"/>
+      <c r="E9" s="332"/>
+      <c r="F9" s="332"/>
+      <c r="G9" s="332"/>
+      <c r="H9" s="332"/>
+      <c r="I9" s="332"/>
+      <c r="J9" s="318" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="324"/>
-      <c r="L9" s="324"/>
-      <c r="M9" s="324"/>
-      <c r="N9" s="324"/>
-      <c r="O9" s="324"/>
-      <c r="P9" s="324"/>
-      <c r="Q9" s="324"/>
-      <c r="R9" s="324"/>
-      <c r="S9" s="347" t="s">
+      <c r="K9" s="318"/>
+      <c r="L9" s="318"/>
+      <c r="M9" s="318"/>
+      <c r="N9" s="318"/>
+      <c r="O9" s="318"/>
+      <c r="P9" s="318"/>
+      <c r="Q9" s="318"/>
+      <c r="R9" s="318"/>
+      <c r="S9" s="346" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="344" t="s">
+      <c r="T9" s="347" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="344" t="s">
+      <c r="U9" s="347" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="344" t="s">
+      <c r="V9" s="347" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="199"/>
       <c r="X9" s="199"/>
       <c r="Y9" s="199"/>
       <c r="Z9" s="199"/>
-      <c r="AA9" s="325" t="s">
+      <c r="AA9" s="319" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="326"/>
-      <c r="AC9" s="326"/>
-      <c r="AD9" s="326"/>
-      <c r="AE9" s="326"/>
-      <c r="AF9" s="326"/>
-      <c r="AG9" s="326"/>
-      <c r="AH9" s="327"/>
-      <c r="AI9" s="335"/>
+      <c r="AB9" s="320"/>
+      <c r="AC9" s="320"/>
+      <c r="AD9" s="320"/>
+      <c r="AE9" s="320"/>
+      <c r="AF9" s="320"/>
+      <c r="AG9" s="320"/>
+      <c r="AH9" s="321"/>
+      <c r="AI9" s="323"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="346" t="s">
+      <c r="AL9" s="349" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="346"/>
-      <c r="AN9" s="346"/>
-      <c r="AO9" s="346"/>
-      <c r="AP9" s="346"/>
-      <c r="AQ9" s="346"/>
-      <c r="AR9" s="329" t="s">
+      <c r="AM9" s="349"/>
+      <c r="AN9" s="349"/>
+      <c r="AO9" s="349"/>
+      <c r="AP9" s="349"/>
+      <c r="AQ9" s="349"/>
+      <c r="AR9" s="334" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="329"/>
-      <c r="AT9" s="329"/>
-      <c r="AU9" s="329"/>
-      <c r="AV9" s="329"/>
-      <c r="AW9" s="329"/>
-      <c r="AX9" s="329"/>
-      <c r="AY9" s="329"/>
-      <c r="AZ9" s="329"/>
+      <c r="AS9" s="334"/>
+      <c r="AT9" s="334"/>
+      <c r="AU9" s="334"/>
+      <c r="AV9" s="334"/>
+      <c r="AW9" s="334"/>
+      <c r="AX9" s="334"/>
+      <c r="AY9" s="334"/>
+      <c r="AZ9" s="334"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="317" t="s">
+      <c r="BD9" s="326" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="317"/>
-      <c r="BF9" s="317"/>
-      <c r="BG9" s="317"/>
-      <c r="BH9" s="317"/>
-      <c r="BI9" s="317"/>
-      <c r="BJ9" s="317"/>
-      <c r="BK9" s="317"/>
-      <c r="BL9" s="317"/>
-      <c r="BM9" s="317"/>
-      <c r="BN9" s="317"/>
-      <c r="BO9" s="317"/>
-      <c r="BP9" s="317"/>
-      <c r="BQ9" s="320" t="s">
+      <c r="BE9" s="326"/>
+      <c r="BF9" s="326"/>
+      <c r="BG9" s="326"/>
+      <c r="BH9" s="326"/>
+      <c r="BI9" s="326"/>
+      <c r="BJ9" s="326"/>
+      <c r="BK9" s="326"/>
+      <c r="BL9" s="326"/>
+      <c r="BM9" s="326"/>
+      <c r="BN9" s="326"/>
+      <c r="BO9" s="326"/>
+      <c r="BP9" s="326"/>
+      <c r="BQ9" s="329" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="320"/>
-      <c r="BS9" s="320"/>
-      <c r="BT9" s="348" t="s">
+      <c r="BR9" s="329"/>
+      <c r="BS9" s="329"/>
+      <c r="BT9" s="344" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="348" t="s">
+      <c r="BU9" s="344" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="348" t="s">
+      <c r="BV9" s="344" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="349" t="s">
+      <c r="BW9" s="345" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -15921,10 +15921,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="347"/>
-      <c r="T10" s="345"/>
-      <c r="U10" s="345"/>
-      <c r="V10" s="345"/>
+      <c r="S10" s="346"/>
+      <c r="T10" s="348"/>
+      <c r="U10" s="348"/>
+      <c r="V10" s="348"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16050,10 +16050,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="348"/>
-      <c r="BU10" s="348"/>
-      <c r="BV10" s="348"/>
-      <c r="BW10" s="349"/>
+      <c r="BT10" s="344"/>
+      <c r="BU10" s="344"/>
+      <c r="BV10" s="344"/>
+      <c r="BW10" s="345"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33093,6 +33093,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33101,21 +33116,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33204,6 +33204,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="C3:BM83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -33235,33 +33236,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="333" t="s">
+      <c r="O3" s="317" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="333"/>
-      <c r="Q3" s="333"/>
-      <c r="R3" s="333"/>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
+      <c r="P3" s="317"/>
+      <c r="Q3" s="317"/>
+      <c r="R3" s="317"/>
+      <c r="S3" s="317"/>
+      <c r="T3" s="317"/>
+      <c r="U3" s="317"/>
+      <c r="V3" s="317"/>
+      <c r="W3" s="317"/>
+      <c r="X3" s="317"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="333"/>
-      <c r="P4" s="333"/>
-      <c r="Q4" s="333"/>
-      <c r="R4" s="333"/>
-      <c r="S4" s="333"/>
-      <c r="T4" s="333"/>
-      <c r="U4" s="333"/>
-      <c r="V4" s="333"/>
-      <c r="W4" s="333"/>
-      <c r="X4" s="333"/>
+      <c r="O4" s="317"/>
+      <c r="P4" s="317"/>
+      <c r="Q4" s="317"/>
+      <c r="R4" s="317"/>
+      <c r="S4" s="317"/>
+      <c r="T4" s="317"/>
+      <c r="U4" s="317"/>
+      <c r="V4" s="317"/>
+      <c r="W4" s="317"/>
+      <c r="X4" s="317"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -33290,16 +33291,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="324" t="s">
+      <c r="J8" s="318" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="324"/>
-      <c r="L8" s="324"/>
-      <c r="M8" s="324"/>
-      <c r="N8" s="324"/>
-      <c r="O8" s="324"/>
-      <c r="P8" s="324"/>
-      <c r="Q8" s="324"/>
+      <c r="K8" s="318"/>
+      <c r="L8" s="318"/>
+      <c r="M8" s="318"/>
+      <c r="N8" s="318"/>
+      <c r="O8" s="318"/>
+      <c r="P8" s="318"/>
+      <c r="Q8" s="318"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33310,133 +33311,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="325" t="s">
+      <c r="X8" s="319" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="326"/>
-      <c r="Z8" s="326"/>
-      <c r="AA8" s="326"/>
-      <c r="AB8" s="327"/>
-      <c r="AC8" s="334" t="s">
+      <c r="Y8" s="320"/>
+      <c r="Z8" s="320"/>
+      <c r="AA8" s="320"/>
+      <c r="AB8" s="321"/>
+      <c r="AC8" s="322" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="336" t="s">
+      <c r="AF8" s="324" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="337"/>
-      <c r="AH8" s="337"/>
-      <c r="AI8" s="337"/>
-      <c r="AJ8" s="337"/>
-      <c r="AK8" s="337"/>
-      <c r="AL8" s="328" t="s">
+      <c r="AG8" s="325"/>
+      <c r="AH8" s="325"/>
+      <c r="AI8" s="325"/>
+      <c r="AJ8" s="325"/>
+      <c r="AK8" s="325"/>
+      <c r="AL8" s="333" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="328"/>
-      <c r="AN8" s="328"/>
-      <c r="AO8" s="328"/>
-      <c r="AP8" s="328"/>
-      <c r="AQ8" s="328"/>
-      <c r="AR8" s="328"/>
-      <c r="AS8" s="328"/>
-      <c r="AT8" s="321" t="s">
+      <c r="AM8" s="333"/>
+      <c r="AN8" s="333"/>
+      <c r="AO8" s="333"/>
+      <c r="AP8" s="333"/>
+      <c r="AQ8" s="333"/>
+      <c r="AR8" s="333"/>
+      <c r="AS8" s="333"/>
+      <c r="AT8" s="330" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="321"/>
-      <c r="AV8" s="321"/>
-      <c r="AW8" s="321"/>
-      <c r="AX8" s="321"/>
-      <c r="AY8" s="321"/>
-      <c r="AZ8" s="321"/>
-      <c r="BA8" s="321"/>
-      <c r="BB8" s="321"/>
-      <c r="BC8" s="322" t="s">
+      <c r="AU8" s="330"/>
+      <c r="AV8" s="330"/>
+      <c r="AW8" s="330"/>
+      <c r="AX8" s="330"/>
+      <c r="AY8" s="330"/>
+      <c r="AZ8" s="330"/>
+      <c r="BA8" s="330"/>
+      <c r="BB8" s="330"/>
+      <c r="BC8" s="331" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="322"/>
-      <c r="BE8" s="322"/>
-      <c r="BF8" s="322"/>
-      <c r="BG8" s="322"/>
-      <c r="BH8" s="322"/>
+      <c r="BD8" s="331"/>
+      <c r="BE8" s="331"/>
+      <c r="BF8" s="331"/>
+      <c r="BG8" s="331"/>
+      <c r="BH8" s="331"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="323" t="s">
+      <c r="C9" s="332" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="323"/>
-      <c r="E9" s="323"/>
-      <c r="F9" s="323"/>
-      <c r="G9" s="323"/>
-      <c r="H9" s="323"/>
-      <c r="I9" s="323"/>
-      <c r="J9" s="324" t="s">
+      <c r="D9" s="332"/>
+      <c r="E9" s="332"/>
+      <c r="F9" s="332"/>
+      <c r="G9" s="332"/>
+      <c r="H9" s="332"/>
+      <c r="I9" s="332"/>
+      <c r="J9" s="318" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="324"/>
-      <c r="L9" s="324"/>
-      <c r="M9" s="324"/>
-      <c r="N9" s="324"/>
-      <c r="O9" s="324"/>
-      <c r="P9" s="324"/>
-      <c r="Q9" s="324"/>
+      <c r="K9" s="318"/>
+      <c r="L9" s="318"/>
+      <c r="M9" s="318"/>
+      <c r="N9" s="318"/>
+      <c r="O9" s="318"/>
+      <c r="P9" s="318"/>
+      <c r="Q9" s="318"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="325" t="s">
+      <c r="V9" s="319" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="326"/>
-      <c r="X9" s="326"/>
-      <c r="Y9" s="326"/>
-      <c r="Z9" s="326"/>
-      <c r="AA9" s="326"/>
-      <c r="AB9" s="327"/>
-      <c r="AC9" s="335"/>
-      <c r="AD9" s="330" t="s">
+      <c r="W9" s="320"/>
+      <c r="X9" s="320"/>
+      <c r="Y9" s="320"/>
+      <c r="Z9" s="320"/>
+      <c r="AA9" s="320"/>
+      <c r="AB9" s="321"/>
+      <c r="AC9" s="323"/>
+      <c r="AD9" s="335" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="331"/>
-      <c r="AF9" s="331"/>
-      <c r="AG9" s="331"/>
-      <c r="AH9" s="331"/>
-      <c r="AI9" s="331"/>
-      <c r="AJ9" s="331"/>
-      <c r="AK9" s="332"/>
-      <c r="AL9" s="329" t="s">
+      <c r="AE9" s="336"/>
+      <c r="AF9" s="336"/>
+      <c r="AG9" s="336"/>
+      <c r="AH9" s="336"/>
+      <c r="AI9" s="336"/>
+      <c r="AJ9" s="336"/>
+      <c r="AK9" s="337"/>
+      <c r="AL9" s="334" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="329"/>
-      <c r="AN9" s="329"/>
-      <c r="AO9" s="329"/>
-      <c r="AP9" s="329"/>
-      <c r="AQ9" s="329"/>
-      <c r="AR9" s="329"/>
-      <c r="AS9" s="329"/>
-      <c r="AT9" s="317" t="s">
+      <c r="AM9" s="334"/>
+      <c r="AN9" s="334"/>
+      <c r="AO9" s="334"/>
+      <c r="AP9" s="334"/>
+      <c r="AQ9" s="334"/>
+      <c r="AR9" s="334"/>
+      <c r="AS9" s="334"/>
+      <c r="AT9" s="326" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="317"/>
-      <c r="AV9" s="317"/>
-      <c r="AW9" s="317"/>
-      <c r="AX9" s="317"/>
-      <c r="AY9" s="318"/>
-      <c r="AZ9" s="318"/>
-      <c r="BA9" s="318"/>
-      <c r="BB9" s="318"/>
-      <c r="BC9" s="319" t="s">
+      <c r="AU9" s="326"/>
+      <c r="AV9" s="326"/>
+      <c r="AW9" s="326"/>
+      <c r="AX9" s="326"/>
+      <c r="AY9" s="327"/>
+      <c r="AZ9" s="327"/>
+      <c r="BA9" s="327"/>
+      <c r="BB9" s="327"/>
+      <c r="BC9" s="328" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="320"/>
-      <c r="BE9" s="320"/>
-      <c r="BF9" s="320"/>
-      <c r="BG9" s="320"/>
-      <c r="BH9" s="320"/>
+      <c r="BD9" s="329"/>
+      <c r="BE9" s="329"/>
+      <c r="BF9" s="329"/>
+      <c r="BG9" s="329"/>
+      <c r="BH9" s="329"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -33644,7 +33645,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="11" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -33789,7 +33790,7 @@
       </c>
       <c r="BL11" s="12"/>
     </row>
-    <row r="12" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
@@ -33941,7 +33942,7 @@
       </c>
       <c r="BL12" s="12"/>
     </row>
-    <row r="13" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="s">
         <v>4</v>
       </c>
@@ -34097,7 +34098,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -34236,7 +34237,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:65" ht="121.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:65" ht="121.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -34378,7 +34379,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="3:65" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:65" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -34515,7 +34516,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -34642,7 +34643,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:64" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -34796,7 +34797,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -34935,7 +34936,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -35074,7 +35075,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -35213,7 +35214,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -35352,7 +35353,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:64" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -35506,7 +35507,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -35635,7 +35636,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -35774,7 +35775,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -35915,7 +35916,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -36054,7 +36055,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:64" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36362,7 +36363,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -36489,7 +36490,7 @@
       </c>
       <c r="BL30" s="12"/>
     </row>
-    <row r="31" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C31" s="22" t="s">
         <v>4</v>
       </c>
@@ -36647,7 +36648,7 @@
       </c>
       <c r="BL31" s="12"/>
     </row>
-    <row r="32" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C32" s="22" t="s">
         <v>4</v>
       </c>
@@ -36805,7 +36806,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -36944,7 +36945,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -37071,7 +37072,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -37500,7 +37501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -37636,7 +37637,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -37789,7 +37790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C40" s="22" t="s">
         <v>4</v>
       </c>
@@ -37942,7 +37943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -38095,7 +38096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -38386,7 +38387,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -38537,7 +38538,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -38663,7 +38664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -38801,7 +38802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="24" t="s">
         <v>7</v>
       </c>
@@ -38954,7 +38955,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -39105,7 +39106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -39231,7 +39232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -39522,7 +39523,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -39660,7 +39661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -39798,7 +39799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -39942,7 +39943,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -40068,7 +40069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -40210,7 +40211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -40361,7 +40362,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -40487,7 +40488,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -40613,7 +40614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -40739,7 +40740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -40877,7 +40878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -41028,7 +41029,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -41154,7 +41155,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -41311,7 +41312,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -41462,7 +41463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -41588,7 +41589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -41714,7 +41715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -41840,7 +41841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -42166,12 +42167,20 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="C10:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Híbrido"/>
+        <filter val="Virtual"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters>
+        <filter val="NO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -42182,6 +42191,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -42267,33 +42281,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="333" t="s">
+      <c r="O3" s="317" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="333"/>
-      <c r="Q3" s="333"/>
-      <c r="R3" s="333"/>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
+      <c r="P3" s="317"/>
+      <c r="Q3" s="317"/>
+      <c r="R3" s="317"/>
+      <c r="S3" s="317"/>
+      <c r="T3" s="317"/>
+      <c r="U3" s="317"/>
+      <c r="V3" s="317"/>
+      <c r="W3" s="317"/>
+      <c r="X3" s="317"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="333"/>
-      <c r="P4" s="333"/>
-      <c r="Q4" s="333"/>
-      <c r="R4" s="333"/>
-      <c r="S4" s="333"/>
-      <c r="T4" s="333"/>
-      <c r="U4" s="333"/>
-      <c r="V4" s="333"/>
-      <c r="W4" s="333"/>
-      <c r="X4" s="333"/>
+      <c r="O4" s="317"/>
+      <c r="P4" s="317"/>
+      <c r="Q4" s="317"/>
+      <c r="R4" s="317"/>
+      <c r="S4" s="317"/>
+      <c r="T4" s="317"/>
+      <c r="U4" s="317"/>
+      <c r="V4" s="317"/>
+      <c r="W4" s="317"/>
+      <c r="X4" s="317"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -42322,16 +42336,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="324" t="s">
+      <c r="J8" s="318" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="324"/>
-      <c r="L8" s="324"/>
-      <c r="M8" s="324"/>
-      <c r="N8" s="324"/>
-      <c r="O8" s="324"/>
-      <c r="P8" s="324"/>
-      <c r="Q8" s="324"/>
+      <c r="K8" s="318"/>
+      <c r="L8" s="318"/>
+      <c r="M8" s="318"/>
+      <c r="N8" s="318"/>
+      <c r="O8" s="318"/>
+      <c r="P8" s="318"/>
+      <c r="Q8" s="318"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -42342,107 +42356,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="325" t="s">
+      <c r="X8" s="319" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="326"/>
-      <c r="Z8" s="326"/>
-      <c r="AA8" s="327"/>
-      <c r="AB8" s="334" t="s">
+      <c r="Y8" s="320"/>
+      <c r="Z8" s="320"/>
+      <c r="AA8" s="321"/>
+      <c r="AB8" s="322" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="336" t="s">
+      <c r="AC8" s="324" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="337"/>
-      <c r="AE8" s="337"/>
-      <c r="AF8" s="337"/>
-      <c r="AG8" s="337"/>
-      <c r="AH8" s="337"/>
-      <c r="AI8" s="328" t="s">
+      <c r="AD8" s="325"/>
+      <c r="AE8" s="325"/>
+      <c r="AF8" s="325"/>
+      <c r="AG8" s="325"/>
+      <c r="AH8" s="325"/>
+      <c r="AI8" s="333" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="328"/>
-      <c r="AK8" s="328"/>
-      <c r="AL8" s="328"/>
-      <c r="AM8" s="328"/>
-      <c r="AN8" s="328"/>
-      <c r="AO8" s="321" t="s">
+      <c r="AJ8" s="333"/>
+      <c r="AK8" s="333"/>
+      <c r="AL8" s="333"/>
+      <c r="AM8" s="333"/>
+      <c r="AN8" s="333"/>
+      <c r="AO8" s="330" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="321"/>
-      <c r="AQ8" s="321"/>
-      <c r="AR8" s="321"/>
-      <c r="AS8" s="322" t="s">
+      <c r="AP8" s="330"/>
+      <c r="AQ8" s="330"/>
+      <c r="AR8" s="330"/>
+      <c r="AS8" s="331" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="322"/>
-      <c r="AU8" s="322"/>
+      <c r="AT8" s="331"/>
+      <c r="AU8" s="331"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="323" t="s">
+      <c r="C9" s="332" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="323"/>
-      <c r="E9" s="323"/>
-      <c r="F9" s="323"/>
-      <c r="G9" s="323"/>
-      <c r="H9" s="323"/>
-      <c r="I9" s="323"/>
-      <c r="J9" s="324" t="s">
+      <c r="D9" s="332"/>
+      <c r="E9" s="332"/>
+      <c r="F9" s="332"/>
+      <c r="G9" s="332"/>
+      <c r="H9" s="332"/>
+      <c r="I9" s="332"/>
+      <c r="J9" s="318" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="324"/>
-      <c r="L9" s="324"/>
-      <c r="M9" s="324"/>
-      <c r="N9" s="324"/>
-      <c r="O9" s="324"/>
-      <c r="P9" s="324"/>
-      <c r="Q9" s="324"/>
+      <c r="K9" s="318"/>
+      <c r="L9" s="318"/>
+      <c r="M9" s="318"/>
+      <c r="N9" s="318"/>
+      <c r="O9" s="318"/>
+      <c r="P9" s="318"/>
+      <c r="Q9" s="318"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="325" t="s">
+      <c r="V9" s="319" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="326"/>
-      <c r="X9" s="326"/>
-      <c r="Y9" s="326"/>
-      <c r="Z9" s="326"/>
-      <c r="AA9" s="327"/>
-      <c r="AB9" s="335"/>
-      <c r="AC9" s="346" t="s">
+      <c r="W9" s="320"/>
+      <c r="X9" s="320"/>
+      <c r="Y9" s="320"/>
+      <c r="Z9" s="320"/>
+      <c r="AA9" s="321"/>
+      <c r="AB9" s="323"/>
+      <c r="AC9" s="349" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="346"/>
-      <c r="AE9" s="346"/>
-      <c r="AF9" s="346"/>
-      <c r="AG9" s="346"/>
-      <c r="AH9" s="346"/>
-      <c r="AI9" s="329" t="s">
+      <c r="AD9" s="349"/>
+      <c r="AE9" s="349"/>
+      <c r="AF9" s="349"/>
+      <c r="AG9" s="349"/>
+      <c r="AH9" s="349"/>
+      <c r="AI9" s="334" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="329"/>
-      <c r="AK9" s="329"/>
-      <c r="AL9" s="329"/>
-      <c r="AM9" s="329"/>
-      <c r="AN9" s="329"/>
-      <c r="AO9" s="317" t="s">
+      <c r="AJ9" s="334"/>
+      <c r="AK9" s="334"/>
+      <c r="AL9" s="334"/>
+      <c r="AM9" s="334"/>
+      <c r="AN9" s="334"/>
+      <c r="AO9" s="326" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="317"/>
-      <c r="AQ9" s="317"/>
-      <c r="AR9" s="317"/>
-      <c r="AS9" s="320" t="s">
+      <c r="AP9" s="326"/>
+      <c r="AQ9" s="326"/>
+      <c r="AR9" s="326"/>
+      <c r="AS9" s="329" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="320"/>
-      <c r="AU9" s="320"/>
+      <c r="AT9" s="329"/>
+      <c r="AU9" s="329"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -48589,6 +48603,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -48599,11 +48618,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -49200,21 +49214,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -49352,31 +49351,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49392,4 +49382,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{112CFA50-3194-417D-B4BC-6D8321F8E0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB3C08E2-BB5E-4514-81CB-995412ADDA10}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{112CFA50-3194-417D-B4BC-6D8321F8E0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{231C229C-C09A-49C4-8378-079081C262DF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3712,33 +3712,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3760,6 +3733,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3774,6 +3759,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3793,15 +3793,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3809,6 +3800,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -15614,43 +15614,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="317" t="s">
+      <c r="O3" s="333" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="317"/>
-      <c r="Q3" s="317"/>
-      <c r="R3" s="317"/>
-      <c r="S3" s="317"/>
-      <c r="T3" s="317"/>
-      <c r="U3" s="317"/>
-      <c r="V3" s="317"/>
-      <c r="W3" s="317"/>
-      <c r="X3" s="317"/>
-      <c r="Y3" s="317"/>
-      <c r="Z3" s="317"/>
-      <c r="AA3" s="317"/>
-      <c r="AB3" s="317"/>
-      <c r="AC3" s="317"/>
+      <c r="P3" s="333"/>
+      <c r="Q3" s="333"/>
+      <c r="R3" s="333"/>
+      <c r="S3" s="333"/>
+      <c r="T3" s="333"/>
+      <c r="U3" s="333"/>
+      <c r="V3" s="333"/>
+      <c r="W3" s="333"/>
+      <c r="X3" s="333"/>
+      <c r="Y3" s="333"/>
+      <c r="Z3" s="333"/>
+      <c r="AA3" s="333"/>
+      <c r="AB3" s="333"/>
+      <c r="AC3" s="333"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="317"/>
-      <c r="P4" s="317"/>
-      <c r="Q4" s="317"/>
-      <c r="R4" s="317"/>
-      <c r="S4" s="317"/>
-      <c r="T4" s="317"/>
-      <c r="U4" s="317"/>
-      <c r="V4" s="317"/>
-      <c r="W4" s="317"/>
-      <c r="X4" s="317"/>
-      <c r="Y4" s="317"/>
-      <c r="Z4" s="317"/>
-      <c r="AA4" s="317"/>
-      <c r="AB4" s="317"/>
-      <c r="AC4" s="317"/>
+      <c r="O4" s="333"/>
+      <c r="P4" s="333"/>
+      <c r="Q4" s="333"/>
+      <c r="R4" s="333"/>
+      <c r="S4" s="333"/>
+      <c r="T4" s="333"/>
+      <c r="U4" s="333"/>
+      <c r="V4" s="333"/>
+      <c r="W4" s="333"/>
+      <c r="X4" s="333"/>
+      <c r="Y4" s="333"/>
+      <c r="Z4" s="333"/>
+      <c r="AA4" s="333"/>
+      <c r="AB4" s="333"/>
+      <c r="AC4" s="333"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -15679,17 +15679,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="318" t="s">
+      <c r="J8" s="324" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="318"/>
-      <c r="L8" s="318"/>
-      <c r="M8" s="318"/>
-      <c r="N8" s="318"/>
-      <c r="O8" s="318"/>
-      <c r="P8" s="318"/>
-      <c r="Q8" s="318"/>
-      <c r="R8" s="318"/>
+      <c r="K8" s="324"/>
+      <c r="L8" s="324"/>
+      <c r="M8" s="324"/>
+      <c r="N8" s="324"/>
+      <c r="O8" s="324"/>
+      <c r="P8" s="324"/>
+      <c r="Q8" s="324"/>
+      <c r="R8" s="324"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -15704,168 +15704,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="319" t="s">
+      <c r="AC8" s="325" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="320"/>
-      <c r="AE8" s="320"/>
-      <c r="AF8" s="320"/>
-      <c r="AG8" s="320"/>
-      <c r="AH8" s="321"/>
-      <c r="AI8" s="322" t="s">
+      <c r="AD8" s="326"/>
+      <c r="AE8" s="326"/>
+      <c r="AF8" s="326"/>
+      <c r="AG8" s="326"/>
+      <c r="AH8" s="327"/>
+      <c r="AI8" s="334" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="324" t="s">
+      <c r="AL8" s="336" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="325"/>
-      <c r="AN8" s="325"/>
-      <c r="AO8" s="325"/>
-      <c r="AP8" s="325"/>
-      <c r="AQ8" s="325"/>
-      <c r="AR8" s="333" t="s">
+      <c r="AM8" s="337"/>
+      <c r="AN8" s="337"/>
+      <c r="AO8" s="337"/>
+      <c r="AP8" s="337"/>
+      <c r="AQ8" s="337"/>
+      <c r="AR8" s="328" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="333"/>
-      <c r="AT8" s="333"/>
-      <c r="AU8" s="333"/>
-      <c r="AV8" s="333"/>
-      <c r="AW8" s="333"/>
-      <c r="AX8" s="333"/>
-      <c r="AY8" s="333"/>
-      <c r="AZ8" s="333"/>
+      <c r="AS8" s="328"/>
+      <c r="AT8" s="328"/>
+      <c r="AU8" s="328"/>
+      <c r="AV8" s="328"/>
+      <c r="AW8" s="328"/>
+      <c r="AX8" s="328"/>
+      <c r="AY8" s="328"/>
+      <c r="AZ8" s="328"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="330" t="s">
+      <c r="BD8" s="321" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="330"/>
-      <c r="BF8" s="330"/>
-      <c r="BG8" s="330"/>
-      <c r="BH8" s="330"/>
-      <c r="BI8" s="330"/>
-      <c r="BJ8" s="330"/>
-      <c r="BK8" s="330"/>
-      <c r="BL8" s="330"/>
-      <c r="BM8" s="330"/>
-      <c r="BN8" s="330"/>
-      <c r="BO8" s="330"/>
-      <c r="BP8" s="330"/>
-      <c r="BQ8" s="331" t="s">
+      <c r="BE8" s="321"/>
+      <c r="BF8" s="321"/>
+      <c r="BG8" s="321"/>
+      <c r="BH8" s="321"/>
+      <c r="BI8" s="321"/>
+      <c r="BJ8" s="321"/>
+      <c r="BK8" s="321"/>
+      <c r="BL8" s="321"/>
+      <c r="BM8" s="321"/>
+      <c r="BN8" s="321"/>
+      <c r="BO8" s="321"/>
+      <c r="BP8" s="321"/>
+      <c r="BQ8" s="322" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="331"/>
-      <c r="BS8" s="331"/>
+      <c r="BR8" s="322"/>
+      <c r="BS8" s="322"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="332" t="s">
+      <c r="C9" s="323" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="332"/>
-      <c r="E9" s="332"/>
-      <c r="F9" s="332"/>
-      <c r="G9" s="332"/>
-      <c r="H9" s="332"/>
-      <c r="I9" s="332"/>
-      <c r="J9" s="318" t="s">
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="318"/>
-      <c r="L9" s="318"/>
-      <c r="M9" s="318"/>
-      <c r="N9" s="318"/>
-      <c r="O9" s="318"/>
-      <c r="P9" s="318"/>
-      <c r="Q9" s="318"/>
-      <c r="R9" s="318"/>
-      <c r="S9" s="346" t="s">
+      <c r="K9" s="324"/>
+      <c r="L9" s="324"/>
+      <c r="M9" s="324"/>
+      <c r="N9" s="324"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
+      <c r="R9" s="324"/>
+      <c r="S9" s="347" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="347" t="s">
+      <c r="T9" s="344" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="347" t="s">
+      <c r="U9" s="344" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="347" t="s">
+      <c r="V9" s="344" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="199"/>
       <c r="X9" s="199"/>
       <c r="Y9" s="199"/>
       <c r="Z9" s="199"/>
-      <c r="AA9" s="319" t="s">
+      <c r="AA9" s="325" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="320"/>
-      <c r="AC9" s="320"/>
-      <c r="AD9" s="320"/>
-      <c r="AE9" s="320"/>
-      <c r="AF9" s="320"/>
-      <c r="AG9" s="320"/>
-      <c r="AH9" s="321"/>
-      <c r="AI9" s="323"/>
+      <c r="AB9" s="326"/>
+      <c r="AC9" s="326"/>
+      <c r="AD9" s="326"/>
+      <c r="AE9" s="326"/>
+      <c r="AF9" s="326"/>
+      <c r="AG9" s="326"/>
+      <c r="AH9" s="327"/>
+      <c r="AI9" s="335"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="349" t="s">
+      <c r="AL9" s="346" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="349"/>
-      <c r="AN9" s="349"/>
-      <c r="AO9" s="349"/>
-      <c r="AP9" s="349"/>
-      <c r="AQ9" s="349"/>
-      <c r="AR9" s="334" t="s">
+      <c r="AM9" s="346"/>
+      <c r="AN9" s="346"/>
+      <c r="AO9" s="346"/>
+      <c r="AP9" s="346"/>
+      <c r="AQ9" s="346"/>
+      <c r="AR9" s="329" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="334"/>
-      <c r="AT9" s="334"/>
-      <c r="AU9" s="334"/>
-      <c r="AV9" s="334"/>
-      <c r="AW9" s="334"/>
-      <c r="AX9" s="334"/>
-      <c r="AY9" s="334"/>
-      <c r="AZ9" s="334"/>
+      <c r="AS9" s="329"/>
+      <c r="AT9" s="329"/>
+      <c r="AU9" s="329"/>
+      <c r="AV9" s="329"/>
+      <c r="AW9" s="329"/>
+      <c r="AX9" s="329"/>
+      <c r="AY9" s="329"/>
+      <c r="AZ9" s="329"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="326" t="s">
+      <c r="BD9" s="317" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="326"/>
-      <c r="BF9" s="326"/>
-      <c r="BG9" s="326"/>
-      <c r="BH9" s="326"/>
-      <c r="BI9" s="326"/>
-      <c r="BJ9" s="326"/>
-      <c r="BK9" s="326"/>
-      <c r="BL9" s="326"/>
-      <c r="BM9" s="326"/>
-      <c r="BN9" s="326"/>
-      <c r="BO9" s="326"/>
-      <c r="BP9" s="326"/>
-      <c r="BQ9" s="329" t="s">
+      <c r="BE9" s="317"/>
+      <c r="BF9" s="317"/>
+      <c r="BG9" s="317"/>
+      <c r="BH9" s="317"/>
+      <c r="BI9" s="317"/>
+      <c r="BJ9" s="317"/>
+      <c r="BK9" s="317"/>
+      <c r="BL9" s="317"/>
+      <c r="BM9" s="317"/>
+      <c r="BN9" s="317"/>
+      <c r="BO9" s="317"/>
+      <c r="BP9" s="317"/>
+      <c r="BQ9" s="320" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="329"/>
-      <c r="BS9" s="329"/>
-      <c r="BT9" s="344" t="s">
+      <c r="BR9" s="320"/>
+      <c r="BS9" s="320"/>
+      <c r="BT9" s="348" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="344" t="s">
+      <c r="BU9" s="348" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="344" t="s">
+      <c r="BV9" s="348" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="345" t="s">
+      <c r="BW9" s="349" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -15921,10 +15921,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="346"/>
-      <c r="T10" s="348"/>
-      <c r="U10" s="348"/>
-      <c r="V10" s="348"/>
+      <c r="S10" s="347"/>
+      <c r="T10" s="345"/>
+      <c r="U10" s="345"/>
+      <c r="V10" s="345"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16050,10 +16050,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="344"/>
-      <c r="BU10" s="344"/>
-      <c r="BV10" s="344"/>
-      <c r="BW10" s="345"/>
+      <c r="BT10" s="348"/>
+      <c r="BU10" s="348"/>
+      <c r="BV10" s="348"/>
+      <c r="BW10" s="349"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33093,6 +33093,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33101,21 +33116,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33236,33 +33236,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="317" t="s">
+      <c r="O3" s="333" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="317"/>
-      <c r="Q3" s="317"/>
-      <c r="R3" s="317"/>
-      <c r="S3" s="317"/>
-      <c r="T3" s="317"/>
-      <c r="U3" s="317"/>
-      <c r="V3" s="317"/>
-      <c r="W3" s="317"/>
-      <c r="X3" s="317"/>
+      <c r="P3" s="333"/>
+      <c r="Q3" s="333"/>
+      <c r="R3" s="333"/>
+      <c r="S3" s="333"/>
+      <c r="T3" s="333"/>
+      <c r="U3" s="333"/>
+      <c r="V3" s="333"/>
+      <c r="W3" s="333"/>
+      <c r="X3" s="333"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="317"/>
-      <c r="P4" s="317"/>
-      <c r="Q4" s="317"/>
-      <c r="R4" s="317"/>
-      <c r="S4" s="317"/>
-      <c r="T4" s="317"/>
-      <c r="U4" s="317"/>
-      <c r="V4" s="317"/>
-      <c r="W4" s="317"/>
-      <c r="X4" s="317"/>
+      <c r="O4" s="333"/>
+      <c r="P4" s="333"/>
+      <c r="Q4" s="333"/>
+      <c r="R4" s="333"/>
+      <c r="S4" s="333"/>
+      <c r="T4" s="333"/>
+      <c r="U4" s="333"/>
+      <c r="V4" s="333"/>
+      <c r="W4" s="333"/>
+      <c r="X4" s="333"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -33291,16 +33291,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="318" t="s">
+      <c r="J8" s="324" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="318"/>
-      <c r="L8" s="318"/>
-      <c r="M8" s="318"/>
-      <c r="N8" s="318"/>
-      <c r="O8" s="318"/>
-      <c r="P8" s="318"/>
-      <c r="Q8" s="318"/>
+      <c r="K8" s="324"/>
+      <c r="L8" s="324"/>
+      <c r="M8" s="324"/>
+      <c r="N8" s="324"/>
+      <c r="O8" s="324"/>
+      <c r="P8" s="324"/>
+      <c r="Q8" s="324"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33311,133 +33311,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="319" t="s">
+      <c r="X8" s="325" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="320"/>
-      <c r="Z8" s="320"/>
-      <c r="AA8" s="320"/>
-      <c r="AB8" s="321"/>
-      <c r="AC8" s="322" t="s">
+      <c r="Y8" s="326"/>
+      <c r="Z8" s="326"/>
+      <c r="AA8" s="326"/>
+      <c r="AB8" s="327"/>
+      <c r="AC8" s="334" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="324" t="s">
+      <c r="AF8" s="336" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="325"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
-      <c r="AJ8" s="325"/>
-      <c r="AK8" s="325"/>
-      <c r="AL8" s="333" t="s">
+      <c r="AG8" s="337"/>
+      <c r="AH8" s="337"/>
+      <c r="AI8" s="337"/>
+      <c r="AJ8" s="337"/>
+      <c r="AK8" s="337"/>
+      <c r="AL8" s="328" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="333"/>
-      <c r="AN8" s="333"/>
-      <c r="AO8" s="333"/>
-      <c r="AP8" s="333"/>
-      <c r="AQ8" s="333"/>
-      <c r="AR8" s="333"/>
-      <c r="AS8" s="333"/>
-      <c r="AT8" s="330" t="s">
+      <c r="AM8" s="328"/>
+      <c r="AN8" s="328"/>
+      <c r="AO8" s="328"/>
+      <c r="AP8" s="328"/>
+      <c r="AQ8" s="328"/>
+      <c r="AR8" s="328"/>
+      <c r="AS8" s="328"/>
+      <c r="AT8" s="321" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="330"/>
-      <c r="AV8" s="330"/>
-      <c r="AW8" s="330"/>
-      <c r="AX8" s="330"/>
-      <c r="AY8" s="330"/>
-      <c r="AZ8" s="330"/>
-      <c r="BA8" s="330"/>
-      <c r="BB8" s="330"/>
-      <c r="BC8" s="331" t="s">
+      <c r="AU8" s="321"/>
+      <c r="AV8" s="321"/>
+      <c r="AW8" s="321"/>
+      <c r="AX8" s="321"/>
+      <c r="AY8" s="321"/>
+      <c r="AZ8" s="321"/>
+      <c r="BA8" s="321"/>
+      <c r="BB8" s="321"/>
+      <c r="BC8" s="322" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="331"/>
-      <c r="BE8" s="331"/>
-      <c r="BF8" s="331"/>
-      <c r="BG8" s="331"/>
-      <c r="BH8" s="331"/>
+      <c r="BD8" s="322"/>
+      <c r="BE8" s="322"/>
+      <c r="BF8" s="322"/>
+      <c r="BG8" s="322"/>
+      <c r="BH8" s="322"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="332" t="s">
+      <c r="C9" s="323" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="332"/>
-      <c r="E9" s="332"/>
-      <c r="F9" s="332"/>
-      <c r="G9" s="332"/>
-      <c r="H9" s="332"/>
-      <c r="I9" s="332"/>
-      <c r="J9" s="318" t="s">
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="318"/>
-      <c r="L9" s="318"/>
-      <c r="M9" s="318"/>
-      <c r="N9" s="318"/>
-      <c r="O9" s="318"/>
-      <c r="P9" s="318"/>
-      <c r="Q9" s="318"/>
+      <c r="K9" s="324"/>
+      <c r="L9" s="324"/>
+      <c r="M9" s="324"/>
+      <c r="N9" s="324"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="319" t="s">
+      <c r="V9" s="325" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="320"/>
-      <c r="X9" s="320"/>
-      <c r="Y9" s="320"/>
-      <c r="Z9" s="320"/>
-      <c r="AA9" s="320"/>
-      <c r="AB9" s="321"/>
-      <c r="AC9" s="323"/>
-      <c r="AD9" s="335" t="s">
+      <c r="W9" s="326"/>
+      <c r="X9" s="326"/>
+      <c r="Y9" s="326"/>
+      <c r="Z9" s="326"/>
+      <c r="AA9" s="326"/>
+      <c r="AB9" s="327"/>
+      <c r="AC9" s="335"/>
+      <c r="AD9" s="330" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="336"/>
-      <c r="AF9" s="336"/>
-      <c r="AG9" s="336"/>
-      <c r="AH9" s="336"/>
-      <c r="AI9" s="336"/>
-      <c r="AJ9" s="336"/>
-      <c r="AK9" s="337"/>
-      <c r="AL9" s="334" t="s">
+      <c r="AE9" s="331"/>
+      <c r="AF9" s="331"/>
+      <c r="AG9" s="331"/>
+      <c r="AH9" s="331"/>
+      <c r="AI9" s="331"/>
+      <c r="AJ9" s="331"/>
+      <c r="AK9" s="332"/>
+      <c r="AL9" s="329" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="334"/>
-      <c r="AN9" s="334"/>
-      <c r="AO9" s="334"/>
-      <c r="AP9" s="334"/>
-      <c r="AQ9" s="334"/>
-      <c r="AR9" s="334"/>
-      <c r="AS9" s="334"/>
-      <c r="AT9" s="326" t="s">
+      <c r="AM9" s="329"/>
+      <c r="AN9" s="329"/>
+      <c r="AO9" s="329"/>
+      <c r="AP9" s="329"/>
+      <c r="AQ9" s="329"/>
+      <c r="AR9" s="329"/>
+      <c r="AS9" s="329"/>
+      <c r="AT9" s="317" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="326"/>
-      <c r="AV9" s="326"/>
-      <c r="AW9" s="326"/>
-      <c r="AX9" s="326"/>
-      <c r="AY9" s="327"/>
-      <c r="AZ9" s="327"/>
-      <c r="BA9" s="327"/>
-      <c r="BB9" s="327"/>
-      <c r="BC9" s="328" t="s">
+      <c r="AU9" s="317"/>
+      <c r="AV9" s="317"/>
+      <c r="AW9" s="317"/>
+      <c r="AX9" s="317"/>
+      <c r="AY9" s="318"/>
+      <c r="AZ9" s="318"/>
+      <c r="BA9" s="318"/>
+      <c r="BB9" s="318"/>
+      <c r="BC9" s="319" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="329"/>
-      <c r="BE9" s="329"/>
-      <c r="BF9" s="329"/>
-      <c r="BG9" s="329"/>
-      <c r="BH9" s="329"/>
+      <c r="BD9" s="320"/>
+      <c r="BE9" s="320"/>
+      <c r="BF9" s="320"/>
+      <c r="BG9" s="320"/>
+      <c r="BH9" s="320"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -42181,6 +42181,11 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -42191,11 +42196,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -42281,33 +42281,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="317" t="s">
+      <c r="O3" s="333" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="317"/>
-      <c r="Q3" s="317"/>
-      <c r="R3" s="317"/>
-      <c r="S3" s="317"/>
-      <c r="T3" s="317"/>
-      <c r="U3" s="317"/>
-      <c r="V3" s="317"/>
-      <c r="W3" s="317"/>
-      <c r="X3" s="317"/>
+      <c r="P3" s="333"/>
+      <c r="Q3" s="333"/>
+      <c r="R3" s="333"/>
+      <c r="S3" s="333"/>
+      <c r="T3" s="333"/>
+      <c r="U3" s="333"/>
+      <c r="V3" s="333"/>
+      <c r="W3" s="333"/>
+      <c r="X3" s="333"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="317"/>
-      <c r="P4" s="317"/>
-      <c r="Q4" s="317"/>
-      <c r="R4" s="317"/>
-      <c r="S4" s="317"/>
-      <c r="T4" s="317"/>
-      <c r="U4" s="317"/>
-      <c r="V4" s="317"/>
-      <c r="W4" s="317"/>
-      <c r="X4" s="317"/>
+      <c r="O4" s="333"/>
+      <c r="P4" s="333"/>
+      <c r="Q4" s="333"/>
+      <c r="R4" s="333"/>
+      <c r="S4" s="333"/>
+      <c r="T4" s="333"/>
+      <c r="U4" s="333"/>
+      <c r="V4" s="333"/>
+      <c r="W4" s="333"/>
+      <c r="X4" s="333"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -42336,16 +42336,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="318" t="s">
+      <c r="J8" s="324" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="318"/>
-      <c r="L8" s="318"/>
-      <c r="M8" s="318"/>
-      <c r="N8" s="318"/>
-      <c r="O8" s="318"/>
-      <c r="P8" s="318"/>
-      <c r="Q8" s="318"/>
+      <c r="K8" s="324"/>
+      <c r="L8" s="324"/>
+      <c r="M8" s="324"/>
+      <c r="N8" s="324"/>
+      <c r="O8" s="324"/>
+      <c r="P8" s="324"/>
+      <c r="Q8" s="324"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -42356,107 +42356,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="319" t="s">
+      <c r="X8" s="325" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="320"/>
-      <c r="Z8" s="320"/>
-      <c r="AA8" s="321"/>
-      <c r="AB8" s="322" t="s">
+      <c r="Y8" s="326"/>
+      <c r="Z8" s="326"/>
+      <c r="AA8" s="327"/>
+      <c r="AB8" s="334" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="324" t="s">
+      <c r="AC8" s="336" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
-      <c r="AG8" s="325"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="333" t="s">
+      <c r="AD8" s="337"/>
+      <c r="AE8" s="337"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="337"/>
+      <c r="AH8" s="337"/>
+      <c r="AI8" s="328" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="333"/>
-      <c r="AK8" s="333"/>
-      <c r="AL8" s="333"/>
-      <c r="AM8" s="333"/>
-      <c r="AN8" s="333"/>
-      <c r="AO8" s="330" t="s">
+      <c r="AJ8" s="328"/>
+      <c r="AK8" s="328"/>
+      <c r="AL8" s="328"/>
+      <c r="AM8" s="328"/>
+      <c r="AN8" s="328"/>
+      <c r="AO8" s="321" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="330"/>
-      <c r="AQ8" s="330"/>
-      <c r="AR8" s="330"/>
-      <c r="AS8" s="331" t="s">
+      <c r="AP8" s="321"/>
+      <c r="AQ8" s="321"/>
+      <c r="AR8" s="321"/>
+      <c r="AS8" s="322" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="331"/>
-      <c r="AU8" s="331"/>
+      <c r="AT8" s="322"/>
+      <c r="AU8" s="322"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="332" t="s">
+      <c r="C9" s="323" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="332"/>
-      <c r="E9" s="332"/>
-      <c r="F9" s="332"/>
-      <c r="G9" s="332"/>
-      <c r="H9" s="332"/>
-      <c r="I9" s="332"/>
-      <c r="J9" s="318" t="s">
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="323"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="318"/>
-      <c r="L9" s="318"/>
-      <c r="M9" s="318"/>
-      <c r="N9" s="318"/>
-      <c r="O9" s="318"/>
-      <c r="P9" s="318"/>
-      <c r="Q9" s="318"/>
+      <c r="K9" s="324"/>
+      <c r="L9" s="324"/>
+      <c r="M9" s="324"/>
+      <c r="N9" s="324"/>
+      <c r="O9" s="324"/>
+      <c r="P9" s="324"/>
+      <c r="Q9" s="324"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="319" t="s">
+      <c r="V9" s="325" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="320"/>
-      <c r="X9" s="320"/>
-      <c r="Y9" s="320"/>
-      <c r="Z9" s="320"/>
-      <c r="AA9" s="321"/>
-      <c r="AB9" s="323"/>
-      <c r="AC9" s="349" t="s">
+      <c r="W9" s="326"/>
+      <c r="X9" s="326"/>
+      <c r="Y9" s="326"/>
+      <c r="Z9" s="326"/>
+      <c r="AA9" s="327"/>
+      <c r="AB9" s="335"/>
+      <c r="AC9" s="346" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="349"/>
-      <c r="AE9" s="349"/>
-      <c r="AF9" s="349"/>
-      <c r="AG9" s="349"/>
-      <c r="AH9" s="349"/>
-      <c r="AI9" s="334" t="s">
+      <c r="AD9" s="346"/>
+      <c r="AE9" s="346"/>
+      <c r="AF9" s="346"/>
+      <c r="AG9" s="346"/>
+      <c r="AH9" s="346"/>
+      <c r="AI9" s="329" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="334"/>
-      <c r="AK9" s="334"/>
-      <c r="AL9" s="334"/>
-      <c r="AM9" s="334"/>
-      <c r="AN9" s="334"/>
-      <c r="AO9" s="326" t="s">
+      <c r="AJ9" s="329"/>
+      <c r="AK9" s="329"/>
+      <c r="AL9" s="329"/>
+      <c r="AM9" s="329"/>
+      <c r="AN9" s="329"/>
+      <c r="AO9" s="317" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="326"/>
-      <c r="AQ9" s="326"/>
-      <c r="AR9" s="326"/>
-      <c r="AS9" s="329" t="s">
+      <c r="AP9" s="317"/>
+      <c r="AQ9" s="317"/>
+      <c r="AR9" s="317"/>
+      <c r="AS9" s="320" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="329"/>
-      <c r="AU9" s="329"/>
+      <c r="AT9" s="320"/>
+      <c r="AU9" s="320"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -48603,11 +48603,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -48618,6 +48613,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -49214,6 +49214,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -49351,22 +49366,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49382,28 +49406,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{112CFA50-3194-417D-B4BC-6D8321F8E0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{231C229C-C09A-49C4-8378-079081C262DF}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{112CFA50-3194-417D-B4BC-6D8321F8E0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F01FA218-6C13-44A8-A194-A389AD1F2D50}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -33204,7 +33204,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="C3:BM83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -33645,7 +33644,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="11" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -33790,7 +33789,7 @@
       </c>
       <c r="BL11" s="12"/>
     </row>
-    <row r="12" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
@@ -33942,7 +33941,7 @@
       </c>
       <c r="BL12" s="12"/>
     </row>
-    <row r="13" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="s">
         <v>4</v>
       </c>
@@ -34098,7 +34097,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:65" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:65" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -34237,7 +34236,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:65" ht="121.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:65" ht="121.8" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -34379,7 +34378,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="3:65" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:65" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -34516,7 +34515,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -34643,7 +34642,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -34797,7 +34796,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -34936,7 +34935,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -35075,7 +35074,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -35214,7 +35213,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -35353,7 +35352,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -35507,7 +35506,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -35636,7 +35635,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -35775,7 +35774,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -35916,7 +35915,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -36055,7 +36054,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:64" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36363,7 +36362,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -36490,7 +36489,7 @@
       </c>
       <c r="BL30" s="12"/>
     </row>
-    <row r="31" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C31" s="22" t="s">
         <v>4</v>
       </c>
@@ -36648,7 +36647,7 @@
       </c>
       <c r="BL31" s="12"/>
     </row>
-    <row r="32" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C32" s="22" t="s">
         <v>4</v>
       </c>
@@ -36806,7 +36805,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -36945,7 +36944,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -37072,7 +37071,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -37501,7 +37500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -37637,7 +37636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -37790,7 +37789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:64" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:64" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C40" s="22" t="s">
         <v>4</v>
       </c>
@@ -37943,7 +37942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -38096,7 +38095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -38387,7 +38386,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -38538,7 +38537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -38664,7 +38663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -38802,7 +38801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C47" s="24" t="s">
         <v>7</v>
       </c>
@@ -38955,7 +38954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:64" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -39106,7 +39105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -39232,7 +39231,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -39523,7 +39522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -39661,7 +39660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -39799,7 +39798,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -39943,7 +39942,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -40069,7 +40068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -40211,7 +40210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -40362,7 +40361,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -40488,7 +40487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -40614,7 +40613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -40740,7 +40739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -40878,7 +40877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -41029,7 +41028,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -41155,7 +41154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -41312,7 +41311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -41463,7 +41462,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -41589,7 +41588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:63" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -41715,7 +41714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -41841,7 +41840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -42167,19 +42166,7 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="C10:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Híbrido"/>
-        <filter val="Virtual"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters>
-        <filter val="NO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="C10:BM10" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}"/>
   <mergeCells count="15">
     <mergeCell ref="O3:X4"/>
     <mergeCell ref="J8:Q8"/>

--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE430BBE-9C5E-47F1-BF0D-141E4E02E8CC}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E41FD244-FF8F-44F9-8C8C-4A1E9CFAA1A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3801,6 +3801,48 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3822,18 +3864,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3848,21 +3878,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3882,6 +3897,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3889,15 +3913,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3911,21 +3926,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9217,11 +9217,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="283"/>
-      <c r="E3" s="357" t="s">
+      <c r="E3" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="358"/>
-      <c r="G3" s="359"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="364"/>
       <c r="H3" s="281" t="s">
         <v>8</v>
       </c>
@@ -12520,21 +12520,21 @@
       <c r="C20" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="360" t="s">
+      <c r="D20" s="365" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="360"/>
-      <c r="F20" s="360"/>
-      <c r="G20" s="361" t="s">
+      <c r="E20" s="365"/>
+      <c r="F20" s="365"/>
+      <c r="G20" s="366" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="361"/>
-      <c r="I20" s="361"/>
-      <c r="J20" s="362" t="s">
+      <c r="H20" s="366"/>
+      <c r="I20" s="366"/>
+      <c r="J20" s="367" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="362"/>
-      <c r="L20" s="362"/>
+      <c r="K20" s="367"/>
+      <c r="L20" s="367"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C21" s="146"/>
@@ -15977,43 +15977,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="352" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="352"/>
-      <c r="Q3" s="352"/>
-      <c r="R3" s="352"/>
-      <c r="S3" s="352"/>
-      <c r="T3" s="352"/>
-      <c r="U3" s="352"/>
-      <c r="V3" s="352"/>
-      <c r="W3" s="352"/>
-      <c r="X3" s="352"/>
-      <c r="Y3" s="352"/>
-      <c r="Z3" s="352"/>
-      <c r="AA3" s="352"/>
-      <c r="AB3" s="352"/>
-      <c r="AC3" s="352"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="352"/>
-      <c r="P4" s="352"/>
-      <c r="Q4" s="352"/>
-      <c r="R4" s="352"/>
-      <c r="S4" s="352"/>
-      <c r="T4" s="352"/>
-      <c r="U4" s="352"/>
-      <c r="V4" s="352"/>
-      <c r="W4" s="352"/>
-      <c r="X4" s="352"/>
-      <c r="Y4" s="352"/>
-      <c r="Z4" s="352"/>
-      <c r="AA4" s="352"/>
-      <c r="AB4" s="352"/>
-      <c r="AC4" s="352"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16042,17 +16042,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="343" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="343"/>
-      <c r="L8" s="343"/>
-      <c r="M8" s="343"/>
-      <c r="N8" s="343"/>
-      <c r="O8" s="343"/>
-      <c r="P8" s="343"/>
-      <c r="Q8" s="343"/>
-      <c r="R8" s="343"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16067,168 +16067,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="344" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="345"/>
-      <c r="AE8" s="345"/>
-      <c r="AF8" s="345"/>
-      <c r="AG8" s="345"/>
-      <c r="AH8" s="346"/>
-      <c r="AI8" s="353" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="355" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="356"/>
-      <c r="AN8" s="356"/>
-      <c r="AO8" s="356"/>
-      <c r="AP8" s="356"/>
-      <c r="AQ8" s="356"/>
-      <c r="AR8" s="347" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="347"/>
-      <c r="AT8" s="347"/>
-      <c r="AU8" s="347"/>
-      <c r="AV8" s="347"/>
-      <c r="AW8" s="347"/>
-      <c r="AX8" s="347"/>
-      <c r="AY8" s="347"/>
-      <c r="AZ8" s="347"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="340" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="340"/>
-      <c r="BF8" s="340"/>
-      <c r="BG8" s="340"/>
-      <c r="BH8" s="340"/>
-      <c r="BI8" s="340"/>
-      <c r="BJ8" s="340"/>
-      <c r="BK8" s="340"/>
-      <c r="BL8" s="340"/>
-      <c r="BM8" s="340"/>
-      <c r="BN8" s="340"/>
-      <c r="BO8" s="340"/>
-      <c r="BP8" s="340"/>
-      <c r="BQ8" s="341" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="341"/>
-      <c r="BS8" s="341"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="342" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="342"/>
-      <c r="E9" s="342"/>
-      <c r="F9" s="342"/>
-      <c r="G9" s="342"/>
-      <c r="H9" s="342"/>
-      <c r="I9" s="342"/>
-      <c r="J9" s="343" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="343"/>
-      <c r="L9" s="343"/>
-      <c r="M9" s="343"/>
-      <c r="N9" s="343"/>
-      <c r="O9" s="343"/>
-      <c r="P9" s="343"/>
-      <c r="Q9" s="343"/>
-      <c r="R9" s="343"/>
-      <c r="S9" s="366" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="363" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="363" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="363" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="344" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="345"/>
-      <c r="AD9" s="345"/>
-      <c r="AE9" s="345"/>
-      <c r="AF9" s="345"/>
-      <c r="AG9" s="345"/>
-      <c r="AH9" s="346"/>
-      <c r="AI9" s="354"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="365" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="365"/>
-      <c r="AN9" s="365"/>
-      <c r="AO9" s="365"/>
-      <c r="AP9" s="365"/>
-      <c r="AQ9" s="365"/>
-      <c r="AR9" s="348" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="348"/>
-      <c r="AT9" s="348"/>
-      <c r="AU9" s="348"/>
-      <c r="AV9" s="348"/>
-      <c r="AW9" s="348"/>
-      <c r="AX9" s="348"/>
-      <c r="AY9" s="348"/>
-      <c r="AZ9" s="348"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="336" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="336"/>
-      <c r="BF9" s="336"/>
-      <c r="BG9" s="336"/>
-      <c r="BH9" s="336"/>
-      <c r="BI9" s="336"/>
-      <c r="BJ9" s="336"/>
-      <c r="BK9" s="336"/>
-      <c r="BL9" s="336"/>
-      <c r="BM9" s="336"/>
-      <c r="BN9" s="336"/>
-      <c r="BO9" s="336"/>
-      <c r="BP9" s="336"/>
-      <c r="BQ9" s="339" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="339"/>
-      <c r="BS9" s="339"/>
-      <c r="BT9" s="367" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="367" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="367" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="368" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16284,10 +16284,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="366"/>
-      <c r="T10" s="364"/>
-      <c r="U10" s="364"/>
-      <c r="V10" s="364"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16413,10 +16413,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="367"/>
-      <c r="BU10" s="367"/>
-      <c r="BV10" s="367"/>
-      <c r="BW10" s="368"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33456,6 +33456,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33464,21 +33479,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33609,34 +33609,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="352" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="352"/>
-      <c r="Q3" s="352"/>
-      <c r="R3" s="352"/>
-      <c r="S3" s="352"/>
-      <c r="T3" s="352"/>
-      <c r="U3" s="352"/>
-      <c r="V3" s="352"/>
-      <c r="W3" s="352"/>
-      <c r="X3" s="352"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="352"/>
-      <c r="P4" s="352"/>
-      <c r="Q4" s="352"/>
-      <c r="R4" s="352"/>
-      <c r="S4" s="352"/>
-      <c r="T4" s="352"/>
-      <c r="U4" s="352"/>
-      <c r="V4" s="352"/>
-      <c r="W4" s="352"/>
-      <c r="X4" s="352"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33669,16 +33669,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="343" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="343"/>
-      <c r="L8" s="343"/>
-      <c r="M8" s="343"/>
-      <c r="N8" s="343"/>
-      <c r="O8" s="343"/>
-      <c r="P8" s="343"/>
-      <c r="Q8" s="343"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33689,133 +33689,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="344" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="345"/>
-      <c r="Z8" s="345"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346"/>
-      <c r="AC8" s="353" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="355" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="356"/>
-      <c r="AH8" s="356"/>
-      <c r="AI8" s="356"/>
-      <c r="AJ8" s="356"/>
-      <c r="AK8" s="356"/>
-      <c r="AL8" s="347" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="347"/>
-      <c r="AN8" s="347"/>
-      <c r="AO8" s="347"/>
-      <c r="AP8" s="347"/>
-      <c r="AQ8" s="347"/>
-      <c r="AR8" s="347"/>
-      <c r="AS8" s="347"/>
-      <c r="AT8" s="340" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="340"/>
-      <c r="AV8" s="340"/>
-      <c r="AW8" s="340"/>
-      <c r="AX8" s="340"/>
-      <c r="AY8" s="340"/>
-      <c r="AZ8" s="340"/>
-      <c r="BA8" s="340"/>
-      <c r="BB8" s="340"/>
-      <c r="BC8" s="341" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="341"/>
-      <c r="BE8" s="341"/>
-      <c r="BF8" s="341"/>
-      <c r="BG8" s="341"/>
-      <c r="BH8" s="341"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="342" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="342"/>
-      <c r="E9" s="342"/>
-      <c r="F9" s="342"/>
-      <c r="G9" s="342"/>
-      <c r="H9" s="342"/>
-      <c r="I9" s="342"/>
-      <c r="J9" s="343" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="343"/>
-      <c r="L9" s="343"/>
-      <c r="M9" s="343"/>
-      <c r="N9" s="343"/>
-      <c r="O9" s="343"/>
-      <c r="P9" s="343"/>
-      <c r="Q9" s="343"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="344" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="345"/>
-      <c r="X9" s="345"/>
-      <c r="Y9" s="345"/>
-      <c r="Z9" s="345"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="346"/>
-      <c r="AC9" s="354"/>
-      <c r="AD9" s="349" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="350"/>
-      <c r="AI9" s="350"/>
-      <c r="AJ9" s="350"/>
-      <c r="AK9" s="351"/>
-      <c r="AL9" s="348" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="348"/>
-      <c r="AN9" s="348"/>
-      <c r="AO9" s="348"/>
-      <c r="AP9" s="348"/>
-      <c r="AQ9" s="348"/>
-      <c r="AR9" s="348"/>
-      <c r="AS9" s="348"/>
-      <c r="AT9" s="336" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="336"/>
-      <c r="AV9" s="336"/>
-      <c r="AW9" s="336"/>
-      <c r="AX9" s="336"/>
-      <c r="AY9" s="337"/>
-      <c r="AZ9" s="337"/>
-      <c r="BA9" s="337"/>
-      <c r="BB9" s="337"/>
-      <c r="BC9" s="338" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="339"/>
-      <c r="BE9" s="339"/>
-      <c r="BF9" s="339"/>
-      <c r="BG9" s="339"/>
-      <c r="BH9" s="339"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -34179,7 +34179,7 @@
       <c r="D12" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="E12" s="374" t="s">
+      <c r="E12" s="337" t="s">
         <v>105</v>
       </c>
       <c r="F12" s="34" t="s">
@@ -35914,7 +35914,7 @@
       </c>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11"/>
-      <c r="AK23" s="373">
+      <c r="AK23" s="336">
         <v>6.25E-2</v>
       </c>
       <c r="AL23" s="12" t="s">
@@ -37027,7 +37027,7 @@
       <c r="D31" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="E31" s="375" t="s">
+      <c r="E31" s="338" t="s">
         <v>283</v>
       </c>
       <c r="F31" s="34" t="s">
@@ -37185,7 +37185,7 @@
       <c r="D32" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="E32" s="374" t="s">
+      <c r="E32" s="337" t="s">
         <v>284</v>
       </c>
       <c r="F32" s="34" t="s">
@@ -37794,7 +37794,7 @@
       <c r="D36" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="E36" s="376" t="s">
+      <c r="E36" s="339" t="s">
         <v>288</v>
       </c>
       <c r="F36" s="21" t="s">
@@ -38239,7 +38239,7 @@
       <c r="D39" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="E39" s="376" t="s">
+      <c r="E39" s="339" t="s">
         <v>118</v>
       </c>
       <c r="F39" s="21" t="s">
@@ -40523,7 +40523,7 @@
       <c r="D54" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="E54" s="377" t="s">
+      <c r="E54" s="340" t="s">
         <v>94</v>
       </c>
       <c r="F54" s="34" t="s">
@@ -43152,11 +43152,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43167,6 +43162,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43179,7 +43179,7 @@
       <formula>NOT(ISERROR(SEARCH("SI",M11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations disablePrompts="1" count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11:H70" xr:uid="{B7C40B7F-3E14-4970-8D0A-638F8CF92B79}">
       <formula1>"Bogotá,Medellín,Nacional"</formula1>
     </dataValidation>
@@ -43208,10 +43208,10 @@
   </cols>
   <sheetData>
     <row r="10" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D10" s="369" t="s">
+      <c r="D10" s="374" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="369"/>
+      <c r="E10" s="374"/>
     </row>
     <row r="11" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D11" s="329" t="s">
@@ -43404,33 +43404,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="352" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="352"/>
-      <c r="Q3" s="352"/>
-      <c r="R3" s="352"/>
-      <c r="S3" s="352"/>
-      <c r="T3" s="352"/>
-      <c r="U3" s="352"/>
-      <c r="V3" s="352"/>
-      <c r="W3" s="352"/>
-      <c r="X3" s="352"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="352"/>
-      <c r="P4" s="352"/>
-      <c r="Q4" s="352"/>
-      <c r="R4" s="352"/>
-      <c r="S4" s="352"/>
-      <c r="T4" s="352"/>
-      <c r="U4" s="352"/>
-      <c r="V4" s="352"/>
-      <c r="W4" s="352"/>
-      <c r="X4" s="352"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43459,16 +43459,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="343" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="343"/>
-      <c r="L8" s="343"/>
-      <c r="M8" s="343"/>
-      <c r="N8" s="343"/>
-      <c r="O8" s="343"/>
-      <c r="P8" s="343"/>
-      <c r="Q8" s="343"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43479,107 +43479,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="344" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="345"/>
-      <c r="Z8" s="345"/>
-      <c r="AA8" s="346"/>
-      <c r="AB8" s="353" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="355" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="356"/>
-      <c r="AE8" s="356"/>
-      <c r="AF8" s="356"/>
-      <c r="AG8" s="356"/>
-      <c r="AH8" s="356"/>
-      <c r="AI8" s="347" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="347"/>
-      <c r="AK8" s="347"/>
-      <c r="AL8" s="347"/>
-      <c r="AM8" s="347"/>
-      <c r="AN8" s="347"/>
-      <c r="AO8" s="340" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="340"/>
-      <c r="AQ8" s="340"/>
-      <c r="AR8" s="340"/>
-      <c r="AS8" s="341" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="341"/>
-      <c r="AU8" s="341"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="342" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="342"/>
-      <c r="E9" s="342"/>
-      <c r="F9" s="342"/>
-      <c r="G9" s="342"/>
-      <c r="H9" s="342"/>
-      <c r="I9" s="342"/>
-      <c r="J9" s="343" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="343"/>
-      <c r="L9" s="343"/>
-      <c r="M9" s="343"/>
-      <c r="N9" s="343"/>
-      <c r="O9" s="343"/>
-      <c r="P9" s="343"/>
-      <c r="Q9" s="343"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="344" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="345"/>
-      <c r="X9" s="345"/>
-      <c r="Y9" s="345"/>
-      <c r="Z9" s="345"/>
-      <c r="AA9" s="346"/>
-      <c r="AB9" s="354"/>
-      <c r="AC9" s="365" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="365"/>
-      <c r="AE9" s="365"/>
-      <c r="AF9" s="365"/>
-      <c r="AG9" s="365"/>
-      <c r="AH9" s="365"/>
-      <c r="AI9" s="348" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="348"/>
-      <c r="AK9" s="348"/>
-      <c r="AL9" s="348"/>
-      <c r="AM9" s="348"/>
-      <c r="AN9" s="348"/>
-      <c r="AO9" s="336" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="336"/>
-      <c r="AQ9" s="336"/>
-      <c r="AR9" s="336"/>
-      <c r="AS9" s="339" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="339"/>
-      <c r="AU9" s="339"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49726,6 +49726,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49736,11 +49741,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -49793,41 +49793,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="371" t="s">
+      <c r="A2" s="376" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="371"/>
-      <c r="C2" s="371"/>
+      <c r="B2" s="376"/>
+      <c r="C2" s="376"/>
       <c r="D2" t="s">
         <v>381</v>
       </c>
-      <c r="E2" s="371" t="s">
+      <c r="E2" s="376" t="s">
         <v>382</v>
       </c>
-      <c r="F2" s="371"/>
+      <c r="F2" s="376"/>
       <c r="G2" s="181" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="370" t="s">
+      <c r="H2" s="375" t="s">
         <v>383</v>
       </c>
-      <c r="I2" s="370"/>
-      <c r="J2" s="370"/>
-      <c r="K2" s="370" t="s">
+      <c r="I2" s="375"/>
+      <c r="J2" s="375"/>
+      <c r="K2" s="375" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="371"/>
-      <c r="M2" s="371"/>
-      <c r="N2" s="370" t="s">
+      <c r="L2" s="376"/>
+      <c r="M2" s="376"/>
+      <c r="N2" s="375" t="s">
         <v>384</v>
       </c>
-      <c r="O2" s="371"/>
-      <c r="P2" s="371"/>
-      <c r="Q2" s="372"/>
-      <c r="R2" s="370" t="s">
+      <c r="O2" s="376"/>
+      <c r="P2" s="376"/>
+      <c r="Q2" s="377"/>
+      <c r="R2" s="375" t="s">
         <v>211</v>
       </c>
-      <c r="S2" s="371"/>
+      <c r="S2" s="376"/>
     </row>
     <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="85" t="s">
@@ -50219,18 +50219,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50252,6 +50252,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50265,12 +50273,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E41FD244-FF8F-44F9-8C8C-4A1E9CFAA1A4}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86D1CAD6-A992-4F3E-B828-D0B23F74A025}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -33567,6 +33567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="C1:BM83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -34023,7 +34024,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="11" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -34488,7 +34489,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -34627,7 +34628,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:65" customFormat="1" ht="121.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:65" customFormat="1" ht="121.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -34771,7 +34772,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="3:65" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:65" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -34921,7 +34922,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -35075,7 +35076,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -35229,7 +35230,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -35377,7 +35378,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -35525,7 +35526,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -35673,7 +35674,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -35821,7 +35822,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -35975,7 +35976,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -36120,7 +36121,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -36268,7 +36269,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -36409,7 +36410,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -36557,7 +36558,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36865,7 +36866,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -37336,7 +37337,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -37484,7 +37485,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -37639,7 +37640,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -37787,7 +37788,7 @@
       </c>
       <c r="BL35" s="12"/>
     </row>
-    <row r="36" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C36" s="24" t="s">
         <v>7</v>
       </c>
@@ -37945,7 +37946,7 @@
       </c>
       <c r="BL36" s="12"/>
     </row>
-    <row r="37" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C37" s="24" t="s">
         <v>7</v>
       </c>
@@ -38085,7 +38086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -38232,7 +38233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -38538,7 +38539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -38697,7 +38698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -38997,7 +38998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -39154,7 +39155,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -39307,7 +39308,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -39609,7 +39610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -39766,7 +39767,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -39916,7 +39917,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -40065,7 +40066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C51" s="24" t="s">
         <v>7</v>
       </c>
@@ -40218,7 +40219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -40367,7 +40368,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -40516,7 +40517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -40660,7 +40661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -40813,7 +40814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -40961,7 +40962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -41118,7 +41119,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -41271,7 +41272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -41424,7 +41425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -41577,7 +41578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -41726,7 +41727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -41883,7 +41884,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -42036,7 +42037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -42192,7 +42193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -42349,7 +42350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -42503,7 +42504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -42658,7 +42659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -42813,7 +42814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -42974,7 +42975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -43151,6 +43152,23 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="C10:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
+    <filterColumn colId="34">
+      <filters>
+        <filter val="0%"/>
+        <filter val="11%"/>
+        <filter val="18,00%"/>
+        <filter val="72%"/>
+        <filter val="77%"/>
+        <filter val="90%"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="60">
+      <filters>
+        <filter val="2026-2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="15">
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>

--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86D1CAD6-A992-4F3E-B828-D0B23F74A025}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF7B452-E3B3-466F-BDCB-B0D314B5AC98}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -33567,7 +33567,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="C1:BM83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -34024,7 +34023,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="11" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -34489,7 +34488,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -34628,7 +34627,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:65" customFormat="1" ht="121.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:65" customFormat="1" ht="121.8" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -34772,7 +34771,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="3:65" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:65" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -34922,7 +34921,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -35076,7 +35075,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -35230,7 +35229,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -35378,7 +35377,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -35526,7 +35525,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -35674,7 +35673,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -35822,7 +35821,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -35976,7 +35975,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -36121,7 +36120,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -36269,7 +36268,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -36410,7 +36409,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -36558,7 +36557,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36866,7 +36865,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -37337,7 +37336,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -37485,7 +37484,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -37640,7 +37639,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -37788,7 +37787,7 @@
       </c>
       <c r="BL35" s="12"/>
     </row>
-    <row r="36" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C36" s="24" t="s">
         <v>7</v>
       </c>
@@ -37946,7 +37945,7 @@
       </c>
       <c r="BL36" s="12"/>
     </row>
-    <row r="37" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C37" s="24" t="s">
         <v>7</v>
       </c>
@@ -38086,7 +38085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -38233,7 +38232,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -38539,7 +38538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -38698,7 +38697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -38998,7 +38997,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -39155,7 +39154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -39308,7 +39307,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -39610,7 +39609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -39767,7 +39766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -39917,7 +39916,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -40066,7 +40065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C51" s="24" t="s">
         <v>7</v>
       </c>
@@ -40219,7 +40218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -40368,7 +40367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -40517,7 +40516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -40661,7 +40660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -40814,7 +40813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -40962,7 +40961,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -41119,7 +41118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -41272,7 +41271,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -41425,7 +41424,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -41578,7 +41577,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -41727,7 +41726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -41884,7 +41883,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -42037,7 +42036,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -42193,7 +42192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -42350,7 +42349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -42504,7 +42503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -42659,7 +42658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -42814,7 +42813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -42975,7 +42974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -43152,23 +43151,6 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="C10:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-    <filterColumn colId="34">
-      <filters>
-        <filter val="0%"/>
-        <filter val="11%"/>
-        <filter val="18,00%"/>
-        <filter val="72%"/>
-        <filter val="77%"/>
-        <filter val="90%"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="60">
-      <filters>
-        <filter val="2026-2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="15">
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
@@ -43197,7 +43179,7 @@
       <formula>NOT(ISERROR(SEARCH("SI",M11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="4">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11:H70" xr:uid="{B7C40B7F-3E14-4970-8D0A-638F8CF92B79}">
       <formula1>"Bogotá,Medellín,Nacional"</formula1>
     </dataValidation>

--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF7B452-E3B3-466F-BDCB-B0D314B5AC98}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C1BAD2-9A1B-4090-8DC9-B6A987B968EB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3816,33 +3816,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3864,6 +3837,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3878,6 +3863,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3897,15 +3897,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3913,6 +3904,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15977,43 +15977,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16042,17 +16042,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16067,168 +16067,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16284,10 +16284,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16413,10 +16413,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33456,6 +33456,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33464,21 +33479,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33609,34 +33609,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33669,16 +33669,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33689,133 +33689,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43152,6 +43152,11 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43162,11 +43167,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43404,33 +43404,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43459,16 +43459,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43479,107 +43479,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49726,11 +49726,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49741,6 +49736,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50219,18 +50219,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50252,14 +50252,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50273,4 +50265,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C1BAD2-9A1B-4090-8DC9-B6A987B968EB}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4AF78DC-EA05-431F-85CA-1B2E8F676D25}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3816,6 +3816,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3837,18 +3864,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3863,21 +3878,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3897,6 +3897,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3904,15 +3913,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15977,43 +15977,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16042,17 +16042,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16067,168 +16067,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16284,10 +16284,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16413,10 +16413,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33456,6 +33456,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33464,21 +33479,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33609,34 +33609,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33669,16 +33669,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33689,133 +33689,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43152,11 +43152,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43167,6 +43162,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43404,33 +43404,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43459,16 +43459,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43479,107 +43479,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49726,6 +49726,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49736,11 +49741,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50219,18 +50219,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50252,6 +50252,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50265,12 +50273,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4AF78DC-EA05-431F-85CA-1B2E8F676D25}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{573AEFEC-C9E8-4629-BBA4-99C46E3702F5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3816,33 +3816,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3864,6 +3837,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3878,6 +3863,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3897,15 +3897,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3913,6 +3904,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15977,43 +15977,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16042,17 +16042,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16067,168 +16067,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16284,10 +16284,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16413,10 +16413,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33456,6 +33456,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33464,21 +33479,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33609,34 +33609,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33669,16 +33669,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33689,133 +33689,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43152,6 +43152,11 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43162,11 +43167,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43404,33 +43404,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43459,16 +43459,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43479,107 +43479,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49726,11 +49726,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49741,6 +49736,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50219,18 +50219,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50252,14 +50252,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50273,4 +50265,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{573AEFEC-C9E8-4629-BBA4-99C46E3702F5}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39724A58-FEB2-4FF0-AA1C-489A80FF6A2E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -499,7 +499,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="420">
   <si>
     <t>RC</t>
   </si>
@@ -1785,6 +1785,9 @@
   </si>
   <si>
     <t>ENVIO CORREO PARA IMPLEMENTACIÓN</t>
+  </si>
+  <si>
+    <t>% avance</t>
   </si>
 </sst>
 </file>
@@ -3816,6 +3819,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3837,18 +3867,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3863,21 +3881,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3897,6 +3900,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3904,15 +3916,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5942,7 +5945,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="ctr"/>
-              <a:t>22%</a:t>
+              <a:t>16%</a:t>
             </a:fld>
             <a:endParaRPr lang="es-US" sz="1100">
               <a:solidFill>
@@ -6180,7 +6183,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="ctr"/>
-              <a:t>5</a:t>
+              <a:t>3</a:t>
             </a:fld>
             <a:endParaRPr lang="es-US" sz="1100">
               <a:solidFill>
@@ -6408,7 +6411,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="ctr"/>
-              <a:t>5</a:t>
+              <a:t>3</a:t>
             </a:fld>
             <a:endParaRPr lang="es-US" sz="1100">
               <a:solidFill>
@@ -7808,7 +7811,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="ctr"/>
-              <a:t>25%</a:t>
+              <a:t>0%</a:t>
             </a:fld>
             <a:endParaRPr lang="es-US" sz="8800">
               <a:solidFill>
@@ -8035,7 +8038,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="ctr"/>
-              <a:t>25%</a:t>
+              <a:t>0%</a:t>
             </a:fld>
             <a:endParaRPr lang="es-US" sz="8800">
               <a:solidFill>
@@ -9307,7 +9310,7 @@
       <c r="C9" s="301"/>
       <c r="D9" s="303" t="str" cm="1">
         <f t="array" ref="D9">(IFERROR(ROUND(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*((ISNUMBER(SEARCH("finalizado",Maestro!J11:J70))*1)+(ISNUMBER(SEARCH("finalizado",Maestro!Y11:Y70))*1)+((ISNUMBER(SEARCH("finalizado",Maestro!AB11:AB70))+ISNUMBER(SEARCH("resolución",Maestro!AB11:AB70))+ISNUMBER(SEARCH("aprobado",Maestro!AB11:AB70))+ISNUMBER(SEARCH("notificado",Maestro!AB11:AB70))&gt;0)*1)+((NOT(ISNUMBER(SEARCH("sin iniciar",Maestro!AI11:AI70)))*NOT(ISNUMBER(SEARCH("no aplica",Maestro!AI11:AI70)))*(Maestro!AI11:AI70&lt;&gt;""))*1)+((ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1)))+((ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;=1)))+((ISNUMBER(Maestro!BG11:BG70)*(Maestro!BG11:BG70&gt;=1)))+((ISNUMBER(Maestro!BL11:BL70)*(Maestro!BL11:BL70&gt;=1)))+(ISNUMBER(SEARCH("en proceso",Maestro!J11:J70))*1)*0.5+(ISNUMBER(SEARCH("en proceso",Maestro!Y11:Y70))*1)*0.5+((ISNUMBER(SEARCH("evaluación",Maestro!AB11:AB70))+ISNUMBER(SEARCH("elaboración",Maestro!AB11:AB70))+ISNUMBER(SEARCH("pares",Maestro!AB11:AB70))&gt;0)*1)*0.5+(0)*0.5+((ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1)))*0.5+((ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;0)*(Maestro!AZ11:AZ70&lt;1)))*0.5+((ISNUMBER(Maestro!BG11:BG70)*(Maestro!BG11:BG70&gt;0)*(Maestro!BG11:BG70&lt;1)))*0.5+((ISNUMBER(Maestro!BL11:BL70)*(Maestro!BL11:BL70&gt;0)*(Maestro!BL11:BL70&lt;1)))*0.5))/(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))*8)*100,0),0)&amp;"%")</f>
-        <v>22%</v>
+        <v>16%</v>
       </c>
       <c r="E9" s="301"/>
       <c r="F9" s="303" cm="1">
@@ -9317,12 +9320,12 @@
       <c r="G9" s="301"/>
       <c r="H9" s="303" cm="1">
         <f t="array" ref="H9">IFERROR(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*((ISNUMBER(SEARCH("en proceso",Maestro!J11:J70))*1)+(ISNUMBER(SEARCH("en proceso",Maestro!Y11:Y70))*1)+((ISNUMBER(SEARCH("evaluación",Maestro!AB11:AB70))+ISNUMBER(SEARCH("elaboración",Maestro!AB11:AB70))+ISNUMBER(SEARCH("pares",Maestro!AB11:AB70))&gt;0)*1)+(0)+((ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1)))+((ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;0)*(Maestro!AZ11:AZ70&lt;1)))+((ISNUMBER(Maestro!BG11:BG70)*(Maestro!BG11:BG70&gt;0)*(Maestro!BG11:BG70&lt;1)))+((ISNUMBER(Maestro!BL11:BL70)*(Maestro!BL11:BL70&gt;0)*(Maestro!BL11:BL70&lt;1))))),0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" s="301"/>
       <c r="J9" s="303" cm="1">
         <f t="array" ref="J9">IFERROR(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))*8-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*((ISNUMBER(SEARCH("finalizado",Maestro!J11:J70))*1+ISNUMBER(SEARCH("no aplica",Maestro!J11:J70))*1)+(ISNUMBER(SEARCH("finalizado",Maestro!Y11:Y70))*1+ISNUMBER(SEARCH("no aplica",Maestro!Y11:Y70))*1)+((ISNUMBER(SEARCH("finalizado",Maestro!AB11:AB70))+ISNUMBER(SEARCH("resolución",Maestro!AB11:AB70))+ISNUMBER(SEARCH("aprobado",Maestro!AB11:AB70))+ISNUMBER(SEARCH("notificado",Maestro!AB11:AB70))&gt;0)*1+ISNUMBER(SEARCH("no aplica",Maestro!AB11:AB70))*1)+((NOT(ISNUMBER(SEARCH("sin iniciar",Maestro!AI11:AI70)))*NOT(ISNUMBER(SEARCH("no aplica",Maestro!AI11:AI70)))*(Maestro!AI11:AI70&lt;&gt;""))*1+ISNUMBER(SEARCH("no aplica",Maestro!AI11:AI70))*1)+((ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))+ISNUMBER(SEARCH("no aplica",Maestro!AQ11:AQ70))*1)+((ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;=1))+ISNUMBER(SEARCH("no aplica",Maestro!AZ11:AZ70))*1)+((ISNUMBER(Maestro!BG11:BG70)*(Maestro!BG11:BG70&gt;=1))+ISNUMBER(SEARCH("no aplica",Maestro!BG11:BG70))*1)+((ISNUMBER(Maestro!BL11:BL70)*(Maestro!BL11:BL70&gt;=1))+ISNUMBER(SEARCH("no aplica",Maestro!BL11:BL70))*1)))-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*((ISNUMBER(SEARCH("en proceso",Maestro!J11:J70))*1)+(ISNUMBER(SEARCH("en proceso",Maestro!Y11:Y70))*1)+((ISNUMBER(SEARCH("evaluación",Maestro!AB11:AB70))+ISNUMBER(SEARCH("elaboración",Maestro!AB11:AB70))+ISNUMBER(SEARCH("pares",Maestro!AB11:AB70))&gt;0)*1)+(0)+((ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1)))+((ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;0)*(Maestro!AZ11:AZ70&lt;1)))+((ISNUMBER(Maestro!BG11:BG70)*(Maestro!BG11:BG70&gt;0)*(Maestro!BG11:BG70&lt;1)))+((ISNUMBER(Maestro!BL11:BL70)*(Maestro!BL11:BL70&gt;0)*(Maestro!BL11:BL70&lt;1))))),0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" s="301"/>
       <c r="L9" s="303" cm="1">
@@ -9494,7 +9497,7 @@
       <c r="C19" s="236"/>
       <c r="D19" s="306" cm="1">
         <f t="array" ref="D19">IFERROR(ROUND((SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))*1)+(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1))*1))*0.5)/SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))*100,0),0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E19" s="243" t="s">
         <v>23</v>
@@ -9502,7 +9505,7 @@
       <c r="F19" s="236"/>
       <c r="G19" s="308" cm="1">
         <f t="array" ref="G19">IFERROR(ROUND((SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;=1))*1)+(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;0)*(Maestro!AZ11:AZ70&lt;1))*1))*0.5)/SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))*100,0),0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H19" s="244" t="s">
         <v>24</v>
@@ -9540,13 +9543,13 @@
       <c r="A21" s="202"/>
       <c r="B21" s="309" t="str" cm="1">
         <f t="array" ref="B21">CONCATENATE("✔ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))*1),"0"),"  Final.     ◑ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1))*1),"0"),"  En proc.     ○ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AQ11:AQ70))*1),"0"),"  Sin inic.     — ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AQ11:AQ70))*1),"0"),"  N/A")</f>
-        <v>✔ 0  Final.     ◑ 1  En proc.     ○ 1  Sin inic.     — 0  N/A</v>
+        <v>✔ 0  Final.     ◑ 0  En proc.     ○ 2  Sin inic.     — 0  N/A</v>
       </c>
       <c r="C21" s="201"/>
       <c r="D21" s="201"/>
       <c r="E21" s="309" t="str" cm="1">
         <f t="array" ref="E21">CONCATENATE("✔ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;=1))*1),"0"),"  Final.     ◑ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;0)*(Maestro!AZ11:AZ70&lt;1))*1),"0"),"  En proc.     ○ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;=1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AZ11:AZ70)*(Maestro!AZ11:AZ70&gt;0)*(Maestro!AZ11:AZ70&lt;1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AZ11:AZ70))*1),"0"),"  Sin inic.     — ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AZ11:AZ70))*1),"0"),"  N/A")</f>
-        <v>✔ 0  Final.     ◑ 1  En proc.     ○ 1  Sin inic.     — 0  N/A</v>
+        <v>✔ 0  Final.     ◑ 0  En proc.     ○ 2  Sin inic.     — 0  N/A</v>
       </c>
       <c r="F21" s="201"/>
       <c r="G21" s="201"/>
@@ -12229,23 +12232,23 @@
       </c>
       <c r="E11" s="141">
         <f>COUNTIFS(Maestro!AQ11:AQ70,"&gt;0",Maestro!AQ11:AQ70,"&lt;1")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" s="142">
         <f t="shared" si="1"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="143">
         <f>COUNTIF(Maestro!AQ11:AQ70,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H11" s="144">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I11" s="145">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J11" s="145">
         <f>COUNTA(Maestro!E11:E70)</f>
@@ -12257,7 +12260,7 @@
       </c>
       <c r="L11" s="138" t="str">
         <f t="shared" si="5"/>
-        <v>⏳ En marcha</v>
+        <v>✖ Sin iniciar</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
@@ -12702,11 +12705,11 @@
       </c>
       <c r="E25" s="154">
         <f>COUNTIFS(Maestro!F11:F70,"Presencial",Maestro!AQ11:AQ70,"&gt;0",Maestro!AQ11:AQ70,"&lt;1")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="155">
         <f>COUNTIFS(Maestro!F11:F70,"Presencial",Maestro!AQ11:AQ70,0)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G25" s="153">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!AQ11:AQ70,"&gt;=1")</f>
@@ -12714,11 +12717,11 @@
       </c>
       <c r="H25" s="154">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!AQ11:AQ70,"&gt;0",Maestro!AQ11:AQ70,"&lt;1")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="155">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!AQ11:AQ70,0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J25" s="153">
         <f>COUNTIFS(Maestro!F11:F70,"Híbrido",Maestro!AQ11:AQ70,"&gt;=1")</f>
@@ -12726,11 +12729,11 @@
       </c>
       <c r="K25" s="154">
         <f>COUNTIFS(Maestro!F11:F70,"Híbrido",Maestro!AQ11:AQ70,"&gt;0",Maestro!AQ11:AQ70,"&lt;1")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="155">
         <f>COUNTIFS(Maestro!F11:F70,"Híbrido",Maestro!AQ11:AQ70,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
@@ -13033,7 +13036,7 @@
       </c>
       <c r="H35" s="157" t="str">
         <f>IF(B35="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B35,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I35" s="157" t="str">
         <f>IF(B35="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B35,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13079,7 +13082,7 @@
       </c>
       <c r="H36" s="137" t="str">
         <f>IF(B36="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B36,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I36" s="137" t="str">
         <f>IF(B36="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B36,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13125,7 +13128,7 @@
       </c>
       <c r="H37" s="157" t="str">
         <f>IF(B37="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B37,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I37" s="157" t="str">
         <f>IF(B37="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B37,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13171,7 +13174,7 @@
       </c>
       <c r="H38" s="137" t="str">
         <f>IF(B38="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B38,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I38" s="137" t="str">
         <f>IF(B38="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B38,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13217,7 +13220,7 @@
       </c>
       <c r="H39" s="157" t="str">
         <f>IF(B39="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B39,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I39" s="157" t="str">
         <f>IF(B39="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B39,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13263,7 +13266,7 @@
       </c>
       <c r="H40" s="137" t="str">
         <f>IF(B40="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B40,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I40" s="137" t="str">
         <f>IF(B40="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B40,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13309,7 +13312,7 @@
       </c>
       <c r="H41" s="157" t="str">
         <f>IF(B41="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B41,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I41" s="157" t="str">
         <f>IF(B41="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B41,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13355,7 +13358,7 @@
       </c>
       <c r="H42" s="137" t="str">
         <f>IF(B42="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B42,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I42" s="137" t="str">
         <f>IF(B42="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B42,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13401,7 +13404,7 @@
       </c>
       <c r="H43" s="157" t="str">
         <f>IF(B43="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B43,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I43" s="157" t="str">
         <f>IF(B43="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B43,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13447,7 +13450,7 @@
       </c>
       <c r="H44" s="137" t="str">
         <f>IF(B44="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B44,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I44" s="137" t="str">
         <f>IF(B44="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B44,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13493,7 +13496,7 @@
       </c>
       <c r="H45" s="157" t="str">
         <f>IF(B45="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B45,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I45" s="157" t="str">
         <f>IF(B45="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B45,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13539,7 +13542,7 @@
       </c>
       <c r="H46" s="137" t="str">
         <f>IF(B46="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B46,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I46" s="137" t="str">
         <f>IF(B46="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B46,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13585,7 +13588,7 @@
       </c>
       <c r="H47" s="157" t="str">
         <f>IF(B47="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B47,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I47" s="157" t="str">
         <f>IF(B47="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B47,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13631,7 +13634,7 @@
       </c>
       <c r="H48" s="137" t="str">
         <f>IF(B48="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B48,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I48" s="137" t="str">
         <f>IF(B48="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B48,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13677,7 +13680,7 @@
       </c>
       <c r="H49" s="157" t="str">
         <f>IF(B49="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B49,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I49" s="157" t="str">
         <f>IF(B49="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B49,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13723,7 +13726,7 @@
       </c>
       <c r="H50" s="137" t="str">
         <f>IF(B50="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B50,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I50" s="137" t="str">
         <f>IF(B50="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B50,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13769,7 +13772,7 @@
       </c>
       <c r="H51" s="157" t="str">
         <f>IF(B51="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B51,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I51" s="157" t="str">
         <f>IF(B51="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B51,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13815,7 +13818,7 @@
       </c>
       <c r="H52" s="137" t="str">
         <f>IF(B52="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B52,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I52" s="137" t="str">
         <f>IF(B52="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B52,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13861,7 +13864,7 @@
       </c>
       <c r="H53" s="157" t="str">
         <f>IF(B53="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B53,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I53" s="157" t="str">
         <f>IF(B53="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B53,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13907,7 +13910,7 @@
       </c>
       <c r="H54" s="137" t="str">
         <f>IF(B54="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B54,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I54" s="137" t="str">
         <f>IF(B54="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B54,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13953,7 +13956,7 @@
       </c>
       <c r="H55" s="157" t="str">
         <f>IF(B55="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B55,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>10%</v>
+        <v>—</v>
       </c>
       <c r="I55" s="157" t="str">
         <f>IF(B55="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B55,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -13999,7 +14002,7 @@
       </c>
       <c r="H56" s="137" t="str">
         <f>IF(B56="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B56,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I56" s="137" t="str">
         <f>IF(B56="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B56,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14045,7 +14048,7 @@
       </c>
       <c r="H57" s="157" t="str">
         <f>IF(B57="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B57,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I57" s="157" t="str">
         <f>IF(B57="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B57,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14091,7 +14094,7 @@
       </c>
       <c r="H58" s="137" t="str">
         <f>IF(B58="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B58,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I58" s="137" t="str">
         <f>IF(B58="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B58,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14137,7 +14140,7 @@
       </c>
       <c r="H59" s="157" t="str">
         <f>IF(B59="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B59,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I59" s="157" t="str">
         <f>IF(B59="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B59,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14183,7 +14186,7 @@
       </c>
       <c r="H60" s="137" t="str">
         <f>IF(B60="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B60,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>10%</v>
+        <v>—</v>
       </c>
       <c r="I60" s="137" t="str">
         <f>IF(B60="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B60,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14229,7 +14232,7 @@
       </c>
       <c r="H61" s="157" t="str">
         <f>IF(B61="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B61,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>10%</v>
+        <v>—</v>
       </c>
       <c r="I61" s="157" t="str">
         <f>IF(B61="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B61,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14275,7 +14278,7 @@
       </c>
       <c r="H62" s="137" t="str">
         <f>IF(B62="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B62,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I62" s="137" t="str">
         <f>IF(B62="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B62,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14321,7 +14324,7 @@
       </c>
       <c r="H63" s="157" t="str">
         <f>IF(B63="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B63,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I63" s="157" t="str">
         <f>IF(B63="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B63,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14367,7 +14370,7 @@
       </c>
       <c r="H64" s="137" t="str">
         <f>IF(B64="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B64,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I64" s="137" t="str">
         <f>IF(B64="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B64,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14413,7 +14416,7 @@
       </c>
       <c r="H65" s="157" t="str">
         <f>IF(B65="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B65,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I65" s="157" t="str">
         <f>IF(B65="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B65,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14459,7 +14462,7 @@
       </c>
       <c r="H66" s="137" t="str">
         <f>IF(B66="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B66,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I66" s="137" t="str">
         <f>IF(B66="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B66,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14505,7 +14508,7 @@
       </c>
       <c r="H67" s="157" t="str">
         <f>IF(B67="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B67,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I67" s="157" t="str">
         <f>IF(B67="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B67,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14551,7 +14554,7 @@
       </c>
       <c r="H68" s="137" t="str">
         <f>IF(B68="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B68,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I68" s="137" t="str">
         <f>IF(B68="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B68,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14597,7 +14600,7 @@
       </c>
       <c r="H69" s="157" t="str">
         <f>IF(B69="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B69,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>10%</v>
+        <v>—</v>
       </c>
       <c r="I69" s="157" t="str">
         <f>IF(B69="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B69,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14643,7 +14646,7 @@
       </c>
       <c r="H70" s="137" t="str">
         <f>IF(B70="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B70,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>10%</v>
+        <v>—</v>
       </c>
       <c r="I70" s="137" t="str">
         <f>IF(B70="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B70,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14689,7 +14692,7 @@
       </c>
       <c r="H71" s="157" t="str">
         <f>IF(B71="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B71,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I71" s="157" t="str">
         <f>IF(B71="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B71,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14735,7 +14738,7 @@
       </c>
       <c r="H72" s="137" t="str">
         <f>IF(B72="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B72,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I72" s="137" t="str">
         <f>IF(B72="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B72,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14781,7 +14784,7 @@
       </c>
       <c r="H73" s="157" t="str">
         <f>IF(B73="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B73,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I73" s="157" t="str">
         <f>IF(B73="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B73,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14827,7 +14830,7 @@
       </c>
       <c r="H74" s="137" t="str">
         <f>IF(B74="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B74,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I74" s="137" t="str">
         <f>IF(B74="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B74,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14873,7 +14876,7 @@
       </c>
       <c r="H75" s="157" t="str">
         <f>IF(B75="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B75,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I75" s="157" t="str">
         <f>IF(B75="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B75,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14919,7 +14922,7 @@
       </c>
       <c r="H76" s="137" t="str">
         <f>IF(B76="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B76,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I76" s="137" t="str">
         <f>IF(B76="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B76,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -14965,7 +14968,7 @@
       </c>
       <c r="H77" s="157" t="str">
         <f>IF(B77="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B77,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I77" s="157" t="str">
         <f>IF(B77="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B77,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15011,7 +15014,7 @@
       </c>
       <c r="H78" s="137" t="str">
         <f>IF(B78="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B78,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I78" s="137" t="str">
         <f>IF(B78="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B78,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15057,7 +15060,7 @@
       </c>
       <c r="H79" s="157" t="str">
         <f>IF(B79="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B79,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I79" s="157" t="str">
         <f>IF(B79="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B79,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15103,7 +15106,7 @@
       </c>
       <c r="H80" s="137" t="str">
         <f>IF(B80="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B80,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I80" s="137" t="str">
         <f>IF(B80="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B80,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15149,7 +15152,7 @@
       </c>
       <c r="H81" s="157" t="str">
         <f>IF(B81="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B81,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I81" s="157" t="str">
         <f>IF(B81="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B81,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15195,7 +15198,7 @@
       </c>
       <c r="H82" s="137" t="str">
         <f>IF(B82="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B82,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I82" s="137" t="str">
         <f>IF(B82="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B82,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15241,7 +15244,7 @@
       </c>
       <c r="H83" s="157" t="str">
         <f>IF(B83="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B83,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I83" s="157" t="str">
         <f>IF(B83="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B83,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15287,7 +15290,7 @@
       </c>
       <c r="H84" s="137" t="str">
         <f>IF(B84="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B84,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I84" s="137" t="str">
         <f>IF(B84="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B84,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15333,7 +15336,7 @@
       </c>
       <c r="H85" s="157" t="str">
         <f>IF(B85="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B85,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I85" s="157" t="str">
         <f>IF(B85="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B85,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15379,7 +15382,7 @@
       </c>
       <c r="H86" s="137" t="str">
         <f>IF(B86="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B86,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I86" s="137" t="str">
         <f>IF(B86="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B86,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15425,7 +15428,7 @@
       </c>
       <c r="H87" s="157" t="str">
         <f>IF(B87="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B87,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="I87" s="157" t="str">
         <f>IF(B87="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B87,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15471,7 +15474,7 @@
       </c>
       <c r="H88" s="137" t="str">
         <f>IF(B88="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B88,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I88" s="137" t="str">
         <f>IF(B88="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B88,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15517,7 +15520,7 @@
       </c>
       <c r="H89" s="157" t="str">
         <f>IF(B89="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B89,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I89" s="157" t="str">
         <f>IF(B89="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B89,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15563,7 +15566,7 @@
       </c>
       <c r="H90" s="137" t="str">
         <f>IF(B90="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B90,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I90" s="137" t="str">
         <f>IF(B90="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B90,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15609,7 +15612,7 @@
       </c>
       <c r="H91" s="157" t="str">
         <f>IF(B91="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B91,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I91" s="157" t="str">
         <f>IF(B91="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B91,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15655,7 +15658,7 @@
       </c>
       <c r="H92" s="137" t="str">
         <f>IF(B92="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B92,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I92" s="137" t="str">
         <f>IF(B92="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B92,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15701,7 +15704,7 @@
       </c>
       <c r="H93" s="157" t="str">
         <f>IF(B93="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B93,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I93" s="157" t="str">
         <f>IF(B93="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B93,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15747,7 +15750,7 @@
       </c>
       <c r="H94" s="137" t="str">
         <f>IF(B94="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B94,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
-        <v>No aplica</v>
+        <v>—</v>
       </c>
       <c r="I94" s="137" t="str">
         <f>IF(B94="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B94,Maestro!$I$11:$I$70,Maestro!$AR$11:$AR$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
@@ -15977,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16042,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16067,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16284,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16413,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -16569,9 +16572,9 @@
         <f t="array" ref="AP11">IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ11" s="11" cm="1">
+      <c r="AQ11" s="11" t="str" cm="1">
         <f t="array" ref="AQ11">IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR11" s="12" t="str" cm="1">
         <f t="array" ref="AR11">IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -16605,9 +16608,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ11" s="11" cm="1">
+      <c r="AZ11" s="11" t="str" cm="1">
         <f t="array" ref="AZ11">IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA11" s="11" cm="1">
         <f t="array" ref="BA11">IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -16855,7 +16858,7 @@
       </c>
       <c r="AQ12" s="11" t="str" cm="1">
         <f t="array" ref="AQ12">IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR12" s="12" t="str" cm="1">
         <f t="array" ref="AR12">IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -16891,7 +16894,7 @@
       </c>
       <c r="AZ12" s="11" t="str" cm="1">
         <f t="array" ref="AZ12">IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA12" s="11" cm="1">
         <f t="array" ref="BA12">IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17137,9 +17140,9 @@
         <f t="array" ref="AP13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="11" cm="1">
+      <c r="AQ13" s="11" t="str" cm="1">
         <f t="array" ref="AQ13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR13" s="12" t="str" cm="1">
         <f t="array" ref="AR13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17173,9 +17176,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ13" s="11" cm="1">
+      <c r="AZ13" s="11" t="str" cm="1">
         <f t="array" ref="AZ13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA13" s="11" t="str" cm="1">
         <f t="array" ref="BA13">IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17421,9 +17424,9 @@
         <f t="array" ref="AP14">IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="11" cm="1">
+      <c r="AQ14" s="11" t="str" cm="1">
         <f t="array" ref="AQ14">IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR14" s="12" t="str" cm="1">
         <f t="array" ref="AR14">IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17457,9 +17460,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ14" s="11" cm="1">
+      <c r="AZ14" s="11" t="str" cm="1">
         <f t="array" ref="AZ14">IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA14" s="11" t="str" cm="1">
         <f t="array" ref="BA14">IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17705,9 +17708,9 @@
         <f t="array" ref="AP15">IFERROR(_xlfn.XLOOKUP($I15,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ15" s="11" cm="1">
+      <c r="AQ15" s="11" t="str" cm="1">
         <f t="array" ref="AQ15">IFERROR(_xlfn.XLOOKUP($I15,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR15" s="12" t="str" cm="1">
         <f t="array" ref="AR15">IFERROR(_xlfn.XLOOKUP($I15,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17741,9 +17744,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I15,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ15" s="11" cm="1">
+      <c r="AZ15" s="11" t="str" cm="1">
         <f t="array" ref="AZ15">IFERROR(_xlfn.XLOOKUP($I15,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA15" s="11" t="str" cm="1">
         <f t="array" ref="BA15">IFERROR(_xlfn.XLOOKUP($I15,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -17991,7 +17994,7 @@
       </c>
       <c r="AQ16" s="11" t="str" cm="1">
         <f t="array" ref="AQ16">IFERROR(_xlfn.XLOOKUP($I16,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR16" s="12" t="str" cm="1">
         <f t="array" ref="AR16">IFERROR(_xlfn.XLOOKUP($I16,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -18027,7 +18030,7 @@
       </c>
       <c r="AZ16" s="11" t="str" cm="1">
         <f t="array" ref="AZ16">IFERROR(_xlfn.XLOOKUP($I16,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA16" s="11" t="str" cm="1">
         <f t="array" ref="BA16">IFERROR(_xlfn.XLOOKUP($I16,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -18273,9 +18276,9 @@
         <f t="array" ref="AP17">IFERROR(_xlfn.XLOOKUP($I17,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ17" s="11" cm="1">
+      <c r="AQ17" s="11" t="str" cm="1">
         <f t="array" ref="AQ17">IFERROR(_xlfn.XLOOKUP($I17,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR17" s="12" t="str" cm="1">
         <f t="array" ref="AR17">IFERROR(_xlfn.XLOOKUP($I17,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -18309,9 +18312,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I17,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ17" s="11" cm="1">
+      <c r="AZ17" s="11" t="str" cm="1">
         <f t="array" ref="AZ17">IFERROR(_xlfn.XLOOKUP($I17,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA17" s="11" cm="1">
         <f t="array" ref="BA17">IFERROR(_xlfn.XLOOKUP($I17,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -18557,9 +18560,9 @@
         <f t="array" ref="AP18">IFERROR(_xlfn.XLOOKUP($I18,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ18" s="11" cm="1">
+      <c r="AQ18" s="11" t="str" cm="1">
         <f t="array" ref="AQ18">IFERROR(_xlfn.XLOOKUP($I18,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR18" s="12" t="str" cm="1">
         <f t="array" ref="AR18">IFERROR(_xlfn.XLOOKUP($I18,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -18593,9 +18596,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I18,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ18" s="11" cm="1">
+      <c r="AZ18" s="11" t="str" cm="1">
         <f t="array" ref="AZ18">IFERROR(_xlfn.XLOOKUP($I18,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA18" s="11" t="str" cm="1">
         <f t="array" ref="BA18">IFERROR(_xlfn.XLOOKUP($I18,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -18842,9 +18845,9 @@
         <f t="array" ref="AP19">IFERROR(_xlfn.XLOOKUP($I19,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ19" s="11" cm="1">
+      <c r="AQ19" s="11" t="str" cm="1">
         <f t="array" ref="AQ19">IFERROR(_xlfn.XLOOKUP($I19,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR19" s="12" t="str" cm="1">
         <f t="array" ref="AR19">IFERROR(_xlfn.XLOOKUP($I19,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -18878,9 +18881,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I19,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ19" s="11" cm="1">
+      <c r="AZ19" s="11" t="str" cm="1">
         <f t="array" ref="AZ19">IFERROR(_xlfn.XLOOKUP($I19,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA19" s="11" t="str" cm="1">
         <f t="array" ref="BA19">IFERROR(_xlfn.XLOOKUP($I19,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19126,9 +19129,9 @@
         <f t="array" ref="AP20">IFERROR(_xlfn.XLOOKUP($I20,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="11" cm="1">
+      <c r="AQ20" s="11" t="str" cm="1">
         <f t="array" ref="AQ20">IFERROR(_xlfn.XLOOKUP($I20,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR20" s="12" t="str" cm="1">
         <f t="array" ref="AR20">IFERROR(_xlfn.XLOOKUP($I20,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19162,9 +19165,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I20,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ20" s="11" cm="1">
+      <c r="AZ20" s="11" t="str" cm="1">
         <f t="array" ref="AZ20">IFERROR(_xlfn.XLOOKUP($I20,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA20" s="11" t="str" cm="1">
         <f t="array" ref="BA20">IFERROR(_xlfn.XLOOKUP($I20,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19410,9 +19413,9 @@
         <f t="array" ref="AP21">IFERROR(_xlfn.XLOOKUP($I21,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ21" s="11" cm="1">
+      <c r="AQ21" s="11" t="str" cm="1">
         <f t="array" ref="AQ21">IFERROR(_xlfn.XLOOKUP($I21,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR21" s="12" t="str" cm="1">
         <f t="array" ref="AR21">IFERROR(_xlfn.XLOOKUP($I21,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19446,9 +19449,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I21,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ21" s="11" cm="1">
+      <c r="AZ21" s="11" t="str" cm="1">
         <f t="array" ref="AZ21">IFERROR(_xlfn.XLOOKUP($I21,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA21" s="11" t="str" cm="1">
         <f t="array" ref="BA21">IFERROR(_xlfn.XLOOKUP($I21,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19694,9 +19697,9 @@
         <f t="array" ref="AP22">IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ22" s="11" cm="1">
+      <c r="AQ22" s="11" t="str" cm="1">
         <f t="array" ref="AQ22">IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR22" s="12" t="str" cm="1">
         <f t="array" ref="AR22">IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19730,9 +19733,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ22" s="11" cm="1">
+      <c r="AZ22" s="11" t="str" cm="1">
         <f t="array" ref="AZ22">IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA22" s="11" cm="1">
         <f t="array" ref="BA22">IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -19980,7 +19983,7 @@
       </c>
       <c r="AQ23" s="11" t="str" cm="1">
         <f t="array" ref="AQ23">IFERROR(_xlfn.XLOOKUP($I23,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR23" s="12" t="str" cm="1">
         <f t="array" ref="AR23">IFERROR(_xlfn.XLOOKUP($I23,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20016,7 +20019,7 @@
       </c>
       <c r="AZ23" s="11" t="str" cm="1">
         <f t="array" ref="AZ23">IFERROR(_xlfn.XLOOKUP($I23,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA23" s="11" t="str" cm="1">
         <f t="array" ref="BA23">IFERROR(_xlfn.XLOOKUP($I23,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20262,9 +20265,9 @@
         <f t="array" ref="AP24">IFERROR(_xlfn.XLOOKUP($I24,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ24" s="11" cm="1">
+      <c r="AQ24" s="11" t="str" cm="1">
         <f t="array" ref="AQ24">IFERROR(_xlfn.XLOOKUP($I24,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR24" s="12" t="str" cm="1">
         <f t="array" ref="AR24">IFERROR(_xlfn.XLOOKUP($I24,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20298,9 +20301,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I24,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ24" s="11" cm="1">
+      <c r="AZ24" s="11" t="str" cm="1">
         <f t="array" ref="AZ24">IFERROR(_xlfn.XLOOKUP($I24,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA24" s="11" t="str" cm="1">
         <f t="array" ref="BA24">IFERROR(_xlfn.XLOOKUP($I24,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20546,9 +20549,9 @@
         <f t="array" ref="AP25">IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ25" s="11" cm="1">
+      <c r="AQ25" s="11" t="str" cm="1">
         <f t="array" ref="AQ25">IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR25" s="12" t="str" cm="1">
         <f t="array" ref="AR25">IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20582,9 +20585,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ25" s="11" cm="1">
+      <c r="AZ25" s="11" t="str" cm="1">
         <f t="array" ref="AZ25">IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA25" s="11" t="str" cm="1">
         <f t="array" ref="BA25">IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20830,9 +20833,9 @@
         <f t="array" ref="AP26">IFERROR(_xlfn.XLOOKUP($I26,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ26" s="11" cm="1">
+      <c r="AQ26" s="11" t="str" cm="1">
         <f t="array" ref="AQ26">IFERROR(_xlfn.XLOOKUP($I26,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR26" s="12" t="str" cm="1">
         <f t="array" ref="AR26">IFERROR(_xlfn.XLOOKUP($I26,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -20866,9 +20869,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I26,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ26" s="11" cm="1">
+      <c r="AZ26" s="11" t="str" cm="1">
         <f t="array" ref="AZ26">IFERROR(_xlfn.XLOOKUP($I26,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA26" s="11" t="str" cm="1">
         <f t="array" ref="BA26">IFERROR(_xlfn.XLOOKUP($I26,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21114,9 +21117,9 @@
         <f t="array" ref="AP27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="11" cm="1">
+      <c r="AQ27" s="11" t="str" cm="1">
         <f t="array" ref="AQ27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR27" s="12" t="str" cm="1">
         <f t="array" ref="AR27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21150,9 +21153,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ27" s="11" cm="1">
+      <c r="AZ27" s="11" t="str" cm="1">
         <f t="array" ref="AZ27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA27" s="11" cm="1">
         <f t="array" ref="BA27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21398,9 +21401,9 @@
         <f t="array" ref="AP28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ28" s="11" cm="1">
+      <c r="AQ28" s="11" t="str" cm="1">
         <f t="array" ref="AQ28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR28" s="12" t="str" cm="1">
         <f t="array" ref="AR28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21434,9 +21437,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ28" s="11" cm="1">
+      <c r="AZ28" s="11" t="str" cm="1">
         <f t="array" ref="AZ28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA28" s="11" cm="1">
         <f t="array" ref="BA28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21684,7 +21687,7 @@
       </c>
       <c r="AQ29" s="11" t="str" cm="1">
         <f t="array" ref="AQ29">IFERROR(_xlfn.XLOOKUP($I29,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR29" s="12" t="str" cm="1">
         <f t="array" ref="AR29">IFERROR(_xlfn.XLOOKUP($I29,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21720,7 +21723,7 @@
       </c>
       <c r="AZ29" s="11" t="str" cm="1">
         <f t="array" ref="AZ29">IFERROR(_xlfn.XLOOKUP($I29,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA29" s="11" t="str" cm="1">
         <f t="array" ref="BA29">IFERROR(_xlfn.XLOOKUP($I29,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21966,9 +21969,9 @@
         <f t="array" ref="AP30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>46152</v>
       </c>
-      <c r="AQ30" s="11" cm="1">
+      <c r="AQ30" s="11" t="str" cm="1">
         <f t="array" ref="AQ30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR30" s="12" t="str" cm="1">
         <f t="array" ref="AR30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22002,9 +22005,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ30" s="11" cm="1">
+      <c r="AZ30" s="11" t="str" cm="1">
         <f t="array" ref="AZ30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA30" s="11" cm="1">
         <f t="array" ref="BA30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22251,9 +22254,9 @@
         <f t="array" ref="AP31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>46152</v>
       </c>
-      <c r="AQ31" s="11" cm="1">
+      <c r="AQ31" s="11" t="str" cm="1">
         <f t="array" ref="AQ31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="AR31" s="12" t="str" cm="1">
         <f t="array" ref="AR31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22287,9 +22290,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0.1</v>
       </c>
-      <c r="AZ31" s="11" cm="1">
+      <c r="AZ31" s="11" t="str" cm="1">
         <f t="array" ref="AZ31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="BA31" s="11" cm="1">
         <f t="array" ref="BA31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22536,9 +22539,9 @@
         <f t="array" ref="AP32">IFERROR(_xlfn.XLOOKUP($I32,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ32" s="11" cm="1">
+      <c r="AQ32" s="11" t="str" cm="1">
         <f t="array" ref="AQ32">IFERROR(_xlfn.XLOOKUP($I32,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR32" s="12" t="str" cm="1">
         <f t="array" ref="AR32">IFERROR(_xlfn.XLOOKUP($I32,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22572,9 +22575,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I32,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ32" s="11" cm="1">
+      <c r="AZ32" s="11" t="str" cm="1">
         <f t="array" ref="AZ32">IFERROR(_xlfn.XLOOKUP($I32,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA32" s="11" t="str" cm="1">
         <f t="array" ref="BA32">IFERROR(_xlfn.XLOOKUP($I32,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22823,7 +22826,7 @@
       </c>
       <c r="AQ33" s="11" t="str" cm="1">
         <f t="array" ref="AQ33">IFERROR(_xlfn.XLOOKUP($I33,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR33" s="12" t="str" cm="1">
         <f t="array" ref="AR33">IFERROR(_xlfn.XLOOKUP($I33,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22859,7 +22862,7 @@
       </c>
       <c r="AZ33" s="11" t="str" cm="1">
         <f t="array" ref="AZ33">IFERROR(_xlfn.XLOOKUP($I33,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA33" s="11" t="str" cm="1">
         <f t="array" ref="BA33">IFERROR(_xlfn.XLOOKUP($I33,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23106,9 +23109,9 @@
         <f t="array" ref="AP34">IFERROR(_xlfn.XLOOKUP($I34,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ34" s="11" cm="1">
+      <c r="AQ34" s="11" t="str" cm="1">
         <f t="array" ref="AQ34">IFERROR(_xlfn.XLOOKUP($I34,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR34" s="12" t="str" cm="1">
         <f t="array" ref="AR34">IFERROR(_xlfn.XLOOKUP($I34,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23142,9 +23145,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I34,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ34" s="11" cm="1">
+      <c r="AZ34" s="11" t="str" cm="1">
         <f t="array" ref="AZ34">IFERROR(_xlfn.XLOOKUP($I34,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA34" s="11" t="str" cm="1">
         <f t="array" ref="BA34">IFERROR(_xlfn.XLOOKUP($I34,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23393,7 +23396,7 @@
       </c>
       <c r="AQ35" s="11" t="str" cm="1">
         <f t="array" ref="AQ35">IFERROR(_xlfn.XLOOKUP($I35,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR35" s="12" t="str" cm="1">
         <f t="array" ref="AR35">IFERROR(_xlfn.XLOOKUP($I35,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23429,7 +23432,7 @@
       </c>
       <c r="AZ35" s="11" t="str" cm="1">
         <f t="array" ref="AZ35">IFERROR(_xlfn.XLOOKUP($I35,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA35" s="11" cm="1">
         <f t="array" ref="BA35">IFERROR(_xlfn.XLOOKUP($I35,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23676,9 +23679,9 @@
         <f t="array" ref="AP36">IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ36" s="11" cm="1">
+      <c r="AQ36" s="11" t="str" cm="1">
         <f t="array" ref="AQ36">IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="AR36" s="12" t="str" cm="1">
         <f t="array" ref="AR36">IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23712,9 +23715,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0.1</v>
       </c>
-      <c r="AZ36" s="11" cm="1">
+      <c r="AZ36" s="11" t="str" cm="1">
         <f t="array" ref="AZ36">IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="BA36" s="11" t="str" cm="1">
         <f t="array" ref="BA36">IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23961,9 +23964,9 @@
         <f t="array" ref="AP37">IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ37" s="11" cm="1">
+      <c r="AQ37" s="11" t="str" cm="1">
         <f t="array" ref="AQ37">IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="AR37" s="12" t="str" cm="1">
         <f t="array" ref="AR37">IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -23997,9 +24000,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0.1</v>
       </c>
-      <c r="AZ37" s="11" cm="1">
+      <c r="AZ37" s="11" t="str" cm="1">
         <f t="array" ref="AZ37">IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="BA37" s="11" t="str" cm="1">
         <f t="array" ref="BA37">IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24246,9 +24249,9 @@
         <f t="array" ref="AP38">IFERROR(_xlfn.XLOOKUP($I38,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ38" s="11" cm="1">
+      <c r="AQ38" s="11" t="str" cm="1">
         <f t="array" ref="AQ38">IFERROR(_xlfn.XLOOKUP($I38,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR38" s="12" t="str" cm="1">
         <f t="array" ref="AR38">IFERROR(_xlfn.XLOOKUP($I38,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24282,9 +24285,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I38,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ38" s="11" cm="1">
+      <c r="AZ38" s="11" t="str" cm="1">
         <f t="array" ref="AZ38">IFERROR(_xlfn.XLOOKUP($I38,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA38" s="11" cm="1">
         <f t="array" ref="BA38">IFERROR(_xlfn.XLOOKUP($I38,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24531,9 +24534,9 @@
         <f t="array" ref="AP39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ39" s="11" cm="1">
+      <c r="AQ39" s="11" t="str" cm="1">
         <f t="array" ref="AQ39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR39" s="12" t="str" cm="1">
         <f t="array" ref="AR39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24567,9 +24570,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ39" s="11" cm="1">
+      <c r="AZ39" s="11" t="str" cm="1">
         <f t="array" ref="AZ39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA39" s="11" cm="1">
         <f t="array" ref="BA39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24817,7 +24820,7 @@
       </c>
       <c r="AQ40" s="11" t="str" cm="1">
         <f t="array" ref="AQ40">IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR40" s="12" t="str" cm="1">
         <f t="array" ref="AR40">IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24853,7 +24856,7 @@
       </c>
       <c r="AZ40" s="11" t="str" cm="1">
         <f t="array" ref="AZ40">IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA40" s="11" cm="1">
         <f t="array" ref="BA40">IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25100,9 +25103,9 @@
         <f t="array" ref="AP41">IFERROR(_xlfn.XLOOKUP($I41,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="11" cm="1">
+      <c r="AQ41" s="11" t="str" cm="1">
         <f t="array" ref="AQ41">IFERROR(_xlfn.XLOOKUP($I41,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR41" s="12" t="str" cm="1">
         <f t="array" ref="AR41">IFERROR(_xlfn.XLOOKUP($I41,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25136,9 +25139,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I41,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ41" s="11" cm="1">
+      <c r="AZ41" s="11" t="str" cm="1">
         <f t="array" ref="AZ41">IFERROR(_xlfn.XLOOKUP($I41,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA41" s="11" t="str" cm="1">
         <f t="array" ref="BA41">IFERROR(_xlfn.XLOOKUP($I41,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25385,9 +25388,9 @@
         <f t="array" ref="AP42">IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ42" s="11" cm="1">
+      <c r="AQ42" s="11" t="str" cm="1">
         <f t="array" ref="AQ42">IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR42" s="12" t="str" cm="1">
         <f t="array" ref="AR42">IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25421,9 +25424,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ42" s="11" cm="1">
+      <c r="AZ42" s="11" t="str" cm="1">
         <f t="array" ref="AZ42">IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA42" s="11" cm="1">
         <f t="array" ref="BA42">IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25672,7 +25675,7 @@
       </c>
       <c r="AQ43" s="11" t="str" cm="1">
         <f t="array" ref="AQ43">IFERROR(_xlfn.XLOOKUP($I43,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR43" s="12" t="str" cm="1">
         <f t="array" ref="AR43">IFERROR(_xlfn.XLOOKUP($I43,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25708,7 +25711,7 @@
       </c>
       <c r="AZ43" s="11" t="str" cm="1">
         <f t="array" ref="AZ43">IFERROR(_xlfn.XLOOKUP($I43,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA43" s="11" cm="1">
         <f t="array" ref="BA43">IFERROR(_xlfn.XLOOKUP($I43,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25956,7 +25959,7 @@
       </c>
       <c r="AQ44" s="11" t="str" cm="1">
         <f t="array" ref="AQ44">IFERROR(_xlfn.XLOOKUP($I44,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR44" s="12" t="str" cm="1">
         <f t="array" ref="AR44">IFERROR(_xlfn.XLOOKUP($I44,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25992,7 +25995,7 @@
       </c>
       <c r="AZ44" s="11" t="str" cm="1">
         <f t="array" ref="AZ44">IFERROR(_xlfn.XLOOKUP($I44,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA44" s="11" t="str" cm="1">
         <f t="array" ref="BA44">IFERROR(_xlfn.XLOOKUP($I44,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26238,9 +26241,9 @@
         <f t="array" ref="AP45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ45" s="11" cm="1">
+      <c r="AQ45" s="11" t="str" cm="1">
         <f t="array" ref="AQ45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="AR45" s="12" t="str" cm="1">
         <f t="array" ref="AR45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26274,9 +26277,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0.1</v>
       </c>
-      <c r="AZ45" s="11" cm="1">
+      <c r="AZ45" s="11" t="str" cm="1">
         <f t="array" ref="AZ45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="BA45" s="11" t="str" cm="1">
         <f t="array" ref="BA45">IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26522,9 +26525,9 @@
         <f t="array" ref="AP46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ46" s="11" cm="1">
+      <c r="AQ46" s="11" t="str" cm="1">
         <f t="array" ref="AQ46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="AR46" s="12" t="str" cm="1">
         <f t="array" ref="AR46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26558,9 +26561,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0.1</v>
       </c>
-      <c r="AZ46" s="11" cm="1">
+      <c r="AZ46" s="11" t="str" cm="1">
         <f t="array" ref="AZ46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="BA46" s="11" cm="1">
         <f t="array" ref="BA46">IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26808,7 +26811,7 @@
       </c>
       <c r="AQ47" s="11" t="str" cm="1">
         <f t="array" ref="AQ47">IFERROR(_xlfn.XLOOKUP($I47,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR47" s="12" t="str" cm="1">
         <f t="array" ref="AR47">IFERROR(_xlfn.XLOOKUP($I47,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -26844,7 +26847,7 @@
       </c>
       <c r="AZ47" s="11" t="str" cm="1">
         <f t="array" ref="AZ47">IFERROR(_xlfn.XLOOKUP($I47,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA47" s="11" cm="1">
         <f t="array" ref="BA47">IFERROR(_xlfn.XLOOKUP($I47,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27090,9 +27093,9 @@
         <f t="array" ref="AP48">IFERROR(_xlfn.XLOOKUP($I48,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ48" s="11" cm="1">
+      <c r="AQ48" s="11" t="str" cm="1">
         <f t="array" ref="AQ48">IFERROR(_xlfn.XLOOKUP($I48,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR48" s="12" t="str" cm="1">
         <f t="array" ref="AR48">IFERROR(_xlfn.XLOOKUP($I48,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27126,9 +27129,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I48,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ48" s="11" cm="1">
+      <c r="AZ48" s="11" t="str" cm="1">
         <f t="array" ref="AZ48">IFERROR(_xlfn.XLOOKUP($I48,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA48" s="11" t="str" cm="1">
         <f t="array" ref="BA48">IFERROR(_xlfn.XLOOKUP($I48,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27374,9 +27377,9 @@
         <f t="array" ref="AP49">IFERROR(_xlfn.XLOOKUP($I49,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ49" s="11" cm="1">
+      <c r="AQ49" s="11" t="str" cm="1">
         <f t="array" ref="AQ49">IFERROR(_xlfn.XLOOKUP($I49,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR49" s="12" t="str" cm="1">
         <f t="array" ref="AR49">IFERROR(_xlfn.XLOOKUP($I49,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27410,9 +27413,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I49,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ49" s="11" cm="1">
+      <c r="AZ49" s="11" t="str" cm="1">
         <f t="array" ref="AZ49">IFERROR(_xlfn.XLOOKUP($I49,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA49" s="11" t="str" cm="1">
         <f t="array" ref="BA49">IFERROR(_xlfn.XLOOKUP($I49,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27658,9 +27661,9 @@
         <f t="array" ref="AP50">IFERROR(_xlfn.XLOOKUP($I50,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ50" s="11" cm="1">
+      <c r="AQ50" s="11" t="str" cm="1">
         <f t="array" ref="AQ50">IFERROR(_xlfn.XLOOKUP($I50,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR50" s="12" t="str" cm="1">
         <f t="array" ref="AR50">IFERROR(_xlfn.XLOOKUP($I50,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27694,9 +27697,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I50,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ50" s="11" cm="1">
+      <c r="AZ50" s="11" t="str" cm="1">
         <f t="array" ref="AZ50">IFERROR(_xlfn.XLOOKUP($I50,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA50" s="11" cm="1">
         <f t="array" ref="BA50">IFERROR(_xlfn.XLOOKUP($I50,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27942,9 +27945,9 @@
         <f t="array" ref="AP51">IFERROR(_xlfn.XLOOKUP($I51,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ51" s="11" cm="1">
+      <c r="AQ51" s="11" t="str" cm="1">
         <f t="array" ref="AQ51">IFERROR(_xlfn.XLOOKUP($I51,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR51" s="12" t="str" cm="1">
         <f t="array" ref="AR51">IFERROR(_xlfn.XLOOKUP($I51,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -27978,9 +27981,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I51,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ51" s="11" cm="1">
+      <c r="AZ51" s="11" t="str" cm="1">
         <f t="array" ref="AZ51">IFERROR(_xlfn.XLOOKUP($I51,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA51" s="11" t="str" cm="1">
         <f t="array" ref="BA51">IFERROR(_xlfn.XLOOKUP($I51,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28226,9 +28229,9 @@
         <f t="array" ref="AP52">IFERROR(_xlfn.XLOOKUP($I52,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ52" s="11" cm="1">
+      <c r="AQ52" s="11" t="str" cm="1">
         <f t="array" ref="AQ52">IFERROR(_xlfn.XLOOKUP($I52,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR52" s="12" t="str" cm="1">
         <f t="array" ref="AR52">IFERROR(_xlfn.XLOOKUP($I52,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28262,9 +28265,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I52,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ52" s="11" cm="1">
+      <c r="AZ52" s="11" t="str" cm="1">
         <f t="array" ref="AZ52">IFERROR(_xlfn.XLOOKUP($I52,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA52" s="11" t="str" cm="1">
         <f t="array" ref="BA52">IFERROR(_xlfn.XLOOKUP($I52,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28510,9 +28513,9 @@
         <f t="array" ref="AP53">IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ53" s="11" cm="1">
+      <c r="AQ53" s="11" t="str" cm="1">
         <f t="array" ref="AQ53">IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR53" s="12" t="str" cm="1">
         <f t="array" ref="AR53">IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28546,9 +28549,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ53" s="11" cm="1">
+      <c r="AZ53" s="11" t="str" cm="1">
         <f t="array" ref="AZ53">IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA53" s="11" cm="1">
         <f t="array" ref="BA53">IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28796,7 +28799,7 @@
       </c>
       <c r="AQ54" s="11" t="str" cm="1">
         <f t="array" ref="AQ54">IFERROR(_xlfn.XLOOKUP($I54,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR54" s="12" t="str" cm="1">
         <f t="array" ref="AR54">IFERROR(_xlfn.XLOOKUP($I54,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -28832,7 +28835,7 @@
       </c>
       <c r="AZ54" s="11" t="str" cm="1">
         <f t="array" ref="AZ54">IFERROR(_xlfn.XLOOKUP($I54,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA54" s="11" t="str" cm="1">
         <f t="array" ref="BA54">IFERROR(_xlfn.XLOOKUP($I54,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29080,7 +29083,7 @@
       </c>
       <c r="AQ55" s="11" t="str" cm="1">
         <f t="array" ref="AQ55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR55" s="12" t="str" cm="1">
         <f t="array" ref="AR55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29116,7 +29119,7 @@
       </c>
       <c r="AZ55" s="11" t="str" cm="1">
         <f t="array" ref="AZ55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA55" s="11" cm="1">
         <f t="array" ref="BA55">IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29364,7 +29367,7 @@
       </c>
       <c r="AQ56" s="11" t="str" cm="1">
         <f t="array" ref="AQ56">IFERROR(_xlfn.XLOOKUP($I56,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR56" s="12" t="str" cm="1">
         <f t="array" ref="AR56">IFERROR(_xlfn.XLOOKUP($I56,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29400,7 +29403,7 @@
       </c>
       <c r="AZ56" s="11" t="str" cm="1">
         <f t="array" ref="AZ56">IFERROR(_xlfn.XLOOKUP($I56,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA56" s="11" cm="1">
         <f t="array" ref="BA56">IFERROR(_xlfn.XLOOKUP($I56,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29648,7 +29651,7 @@
       </c>
       <c r="AQ57" s="11" t="str" cm="1">
         <f t="array" ref="AQ57">IFERROR(_xlfn.XLOOKUP($I57,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR57" s="12" t="str" cm="1">
         <f t="array" ref="AR57">IFERROR(_xlfn.XLOOKUP($I57,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29684,7 +29687,7 @@
       </c>
       <c r="AZ57" s="11" t="str" cm="1">
         <f t="array" ref="AZ57">IFERROR(_xlfn.XLOOKUP($I57,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA57" s="11" t="str" cm="1">
         <f t="array" ref="BA57">IFERROR(_xlfn.XLOOKUP($I57,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29932,7 +29935,7 @@
       </c>
       <c r="AQ58" s="11" t="str" cm="1">
         <f t="array" ref="AQ58">IFERROR(_xlfn.XLOOKUP($I58,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR58" s="12" t="str" cm="1">
         <f t="array" ref="AR58">IFERROR(_xlfn.XLOOKUP($I58,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -29968,7 +29971,7 @@
       </c>
       <c r="AZ58" s="11" t="str" cm="1">
         <f t="array" ref="AZ58">IFERROR(_xlfn.XLOOKUP($I58,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA58" s="11" t="str" cm="1">
         <f t="array" ref="BA58">IFERROR(_xlfn.XLOOKUP($I58,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -30216,7 +30219,7 @@
       </c>
       <c r="AQ59" s="11" t="str" cm="1">
         <f t="array" ref="AQ59">IFERROR(_xlfn.XLOOKUP($I59,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR59" s="12" t="str" cm="1">
         <f t="array" ref="AR59">IFERROR(_xlfn.XLOOKUP($I59,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -30252,7 +30255,7 @@
       </c>
       <c r="AZ59" s="11" t="str" cm="1">
         <f t="array" ref="AZ59">IFERROR(_xlfn.XLOOKUP($I59,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA59" s="11" t="str" cm="1">
         <f t="array" ref="BA59">IFERROR(_xlfn.XLOOKUP($I59,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -30498,9 +30501,9 @@
         <f t="array" ref="AP60">IFERROR(_xlfn.XLOOKUP($I60,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>0</v>
       </c>
-      <c r="AQ60" s="11" cm="1">
+      <c r="AQ60" s="11" t="str" cm="1">
         <f t="array" ref="AQ60">IFERROR(_xlfn.XLOOKUP($I60,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR60" s="12" t="str" cm="1">
         <f t="array" ref="AR60">IFERROR(_xlfn.XLOOKUP($I60,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -30534,9 +30537,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I60,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ60" s="11" cm="1">
+      <c r="AZ60" s="11" t="str" cm="1">
         <f t="array" ref="AZ60">IFERROR(_xlfn.XLOOKUP($I60,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA60" s="11" t="str" cm="1">
         <f t="array" ref="BA60">IFERROR(_xlfn.XLOOKUP($I60,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -30784,7 +30787,7 @@
       </c>
       <c r="AQ61" s="11" t="str" cm="1">
         <f t="array" ref="AQ61">IFERROR(_xlfn.XLOOKUP($I61,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR61" s="12" t="str" cm="1">
         <f t="array" ref="AR61">IFERROR(_xlfn.XLOOKUP($I61,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -30820,7 +30823,7 @@
       </c>
       <c r="AZ61" s="11" t="str" cm="1">
         <f t="array" ref="AZ61">IFERROR(_xlfn.XLOOKUP($I61,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA61" s="11" cm="1">
         <f t="array" ref="BA61">IFERROR(_xlfn.XLOOKUP($I61,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31068,7 +31071,7 @@
       </c>
       <c r="AQ62" s="11" t="str" cm="1">
         <f t="array" ref="AQ62">IFERROR(_xlfn.XLOOKUP($I62,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR62" s="12" t="str" cm="1">
         <f t="array" ref="AR62">IFERROR(_xlfn.XLOOKUP($I62,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31104,7 +31107,7 @@
       </c>
       <c r="AZ62" s="11" t="str" cm="1">
         <f t="array" ref="AZ62">IFERROR(_xlfn.XLOOKUP($I62,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA62" s="11" t="str" cm="1">
         <f t="array" ref="BA62">IFERROR(_xlfn.XLOOKUP($I62,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31350,9 +31353,9 @@
         <f t="array" ref="AP63">IFERROR(_xlfn.XLOOKUP($I63,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v>46122</v>
       </c>
-      <c r="AQ63" s="11" cm="1">
+      <c r="AQ63" s="11" t="str" cm="1">
         <f t="array" ref="AQ63">IFERROR(_xlfn.XLOOKUP($I63,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AR63" s="12" t="str" cm="1">
         <f t="array" ref="AR63">IFERROR(_xlfn.XLOOKUP($I63,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31386,9 +31389,9 @@
         <f>IFERROR(_xlfn.XLOOKUP($I63,Borrador!$I$11:$I$70,Borrador!$AS$11:$AS$70,""),"")</f>
         <v>0</v>
       </c>
-      <c r="AZ63" s="11" cm="1">
+      <c r="AZ63" s="11" t="str" cm="1">
         <f t="array" ref="AZ63">IFERROR(_xlfn.XLOOKUP($I63,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA63" s="11" cm="1">
         <f t="array" ref="BA63">IFERROR(_xlfn.XLOOKUP($I63,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31636,7 +31639,7 @@
       </c>
       <c r="AQ64" s="11" t="str" cm="1">
         <f t="array" ref="AQ64">IFERROR(_xlfn.XLOOKUP($I64,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR64" s="12" t="str" cm="1">
         <f t="array" ref="AR64">IFERROR(_xlfn.XLOOKUP($I64,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31672,7 +31675,7 @@
       </c>
       <c r="AZ64" s="11" t="str" cm="1">
         <f t="array" ref="AZ64">IFERROR(_xlfn.XLOOKUP($I64,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA64" s="11" cm="1">
         <f t="array" ref="BA64">IFERROR(_xlfn.XLOOKUP($I64,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31920,7 +31923,7 @@
       </c>
       <c r="AQ65" s="11" t="str" cm="1">
         <f t="array" ref="AQ65">IFERROR(_xlfn.XLOOKUP($I65,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR65" s="12" t="str" cm="1">
         <f t="array" ref="AR65">IFERROR(_xlfn.XLOOKUP($I65,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -31956,7 +31959,7 @@
       </c>
       <c r="AZ65" s="11" t="str" cm="1">
         <f t="array" ref="AZ65">IFERROR(_xlfn.XLOOKUP($I65,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA65" s="11" t="str" cm="1">
         <f t="array" ref="BA65">IFERROR(_xlfn.XLOOKUP($I65,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -32204,7 +32207,7 @@
       </c>
       <c r="AQ66" s="11" t="str" cm="1">
         <f t="array" ref="AQ66">IFERROR(_xlfn.XLOOKUP($I66,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR66" s="12" t="str" cm="1">
         <f t="array" ref="AR66">IFERROR(_xlfn.XLOOKUP($I66,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -32240,7 +32243,7 @@
       </c>
       <c r="AZ66" s="11" t="str" cm="1">
         <f t="array" ref="AZ66">IFERROR(_xlfn.XLOOKUP($I66,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA66" s="11" t="str" cm="1">
         <f t="array" ref="BA66">IFERROR(_xlfn.XLOOKUP($I66,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -32488,7 +32491,7 @@
       </c>
       <c r="AQ67" s="11" t="str" cm="1">
         <f t="array" ref="AQ67">IFERROR(_xlfn.XLOOKUP($I67,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR67" s="12" t="str" cm="1">
         <f t="array" ref="AR67">IFERROR(_xlfn.XLOOKUP($I67,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -32524,7 +32527,7 @@
       </c>
       <c r="AZ67" s="11" t="str" cm="1">
         <f t="array" ref="AZ67">IFERROR(_xlfn.XLOOKUP($I67,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA67" s="11" t="str" cm="1">
         <f t="array" ref="BA67">IFERROR(_xlfn.XLOOKUP($I67,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -32773,7 +32776,7 @@
       </c>
       <c r="AQ68" s="11" t="str" cm="1">
         <f t="array" ref="AQ68">IFERROR(_xlfn.XLOOKUP($I68,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR68" s="12" t="str" cm="1">
         <f t="array" ref="AR68">IFERROR(_xlfn.XLOOKUP($I68,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -32809,7 +32812,7 @@
       </c>
       <c r="AZ68" s="11" t="str" cm="1">
         <f t="array" ref="AZ68">IFERROR(_xlfn.XLOOKUP($I68,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA68" s="11" cm="1">
         <f t="array" ref="BA68">IFERROR(_xlfn.XLOOKUP($I68,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -33058,7 +33061,7 @@
       </c>
       <c r="AQ69" s="11" t="str" cm="1">
         <f t="array" ref="AQ69">IFERROR(_xlfn.XLOOKUP($I69,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR69" s="12" t="str" cm="1">
         <f t="array" ref="AR69">IFERROR(_xlfn.XLOOKUP($I69,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -33094,7 +33097,7 @@
       </c>
       <c r="AZ69" s="11" t="str" cm="1">
         <f t="array" ref="AZ69">IFERROR(_xlfn.XLOOKUP($I69,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA69" s="11" cm="1">
         <f t="array" ref="BA69">IFERROR(_xlfn.XLOOKUP($I69,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -33328,7 +33331,7 @@
       </c>
       <c r="AQ70" s="70" t="str" cm="1">
         <f t="array" ref="AQ70">IFERROR(_xlfn.XLOOKUP($I70,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AQ$10,Borrador!$A$10:$BM$10,Borrador!$A$11:$BM$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="AR70" s="12" t="str" cm="1">
         <f t="array" ref="AR70">IFERROR(_xlfn.XLOOKUP($I70,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AR$10,Borrador!$A$10:$BM$10,Borrador!$A$11:$BM$70,"",0,1),""),"")</f>
@@ -33355,7 +33358,7 @@
       <c r="AY70" s="12"/>
       <c r="AZ70" s="11" t="str" cm="1">
         <f t="array" ref="AZ70">IFERROR(_xlfn.XLOOKUP($I70,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$A$10:$BM$10,Borrador!$A$11:$BM$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v/>
       </c>
       <c r="BA70" s="11" cm="1">
         <f t="array" ref="BA70">IFERROR(_xlfn.XLOOKUP($I70,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$A$10:$BM$10,Borrador!$A$11:$BM$70,"",0,1),""),"")</f>
@@ -33456,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33464,21 +33482,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33609,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33669,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33689,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -33960,7 +33963,7 @@
         <v>246</v>
       </c>
       <c r="AS10" s="88" t="s">
-        <v>247</v>
+        <v>419</v>
       </c>
       <c r="AT10" s="15" t="s">
         <v>252</v>
@@ -43152,11 +43155,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43167,6 +43165,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43404,33 +43407,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43459,16 +43462,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43479,107 +43482,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49726,6 +49729,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49736,11 +49744,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50219,18 +50222,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50252,6 +50255,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50265,12 +50276,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39724A58-FEB2-4FF0-AA1C-489A80FF6A2E}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0AFBDE5-868C-4C07-A311-B62DA41284D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,33 +3819,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3867,6 +3840,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3881,6 +3866,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,15 +3900,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3916,6 +3907,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43155,6 +43155,11 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43165,11 +43170,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43407,33 +43407,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43462,16 +43462,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43482,107 +43482,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49729,11 +49729,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49744,6 +49739,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50222,18 +50222,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50255,14 +50255,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50276,4 +50268,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0AFBDE5-868C-4C07-A311-B62DA41284D6}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D68B88-DEA4-4FDF-AE06-4EEF0A3A1052}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,6 +3819,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3840,18 +3867,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3866,21 +3881,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,6 +3900,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3907,15 +3916,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43155,11 +43155,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43170,6 +43165,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43407,33 +43407,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43462,16 +43462,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43482,107 +43482,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49729,6 +49729,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49739,11 +49744,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50222,18 +50222,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50255,6 +50255,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50268,12 +50276,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D68B88-DEA4-4FDF-AE06-4EEF0A3A1052}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F3D6B1-FC2F-4776-AE41-84CCE139B4FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$8:$BM$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -3819,33 +3819,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3867,6 +3840,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3881,6 +3866,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,15 +3900,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3916,6 +3907,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43154,7 +43154,50 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="C8:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
+    <filterColumn colId="7" showButton="0"/>
+    <filterColumn colId="8" showButton="0"/>
+    <filterColumn colId="9" showButton="0"/>
+    <filterColumn colId="10" showButton="0"/>
+    <filterColumn colId="11" showButton="0"/>
+    <filterColumn colId="12" showButton="0"/>
+    <filterColumn colId="13" showButton="0"/>
+    <filterColumn colId="21" showButton="0"/>
+    <filterColumn colId="22" showButton="0"/>
+    <filterColumn colId="23" showButton="0"/>
+    <filterColumn colId="24" showButton="0"/>
+    <filterColumn colId="29" showButton="0"/>
+    <filterColumn colId="30" showButton="0"/>
+    <filterColumn colId="31" showButton="0"/>
+    <filterColumn colId="32" showButton="0"/>
+    <filterColumn colId="33" showButton="0"/>
+    <filterColumn colId="35" showButton="0"/>
+    <filterColumn colId="36" showButton="0"/>
+    <filterColumn colId="37" showButton="0"/>
+    <filterColumn colId="38" showButton="0"/>
+    <filterColumn colId="39" showButton="0"/>
+    <filterColumn colId="40" showButton="0"/>
+    <filterColumn colId="41" showButton="0"/>
+    <filterColumn colId="43" showButton="0"/>
+    <filterColumn colId="44" showButton="0"/>
+    <filterColumn colId="45" showButton="0"/>
+    <filterColumn colId="46" showButton="0"/>
+    <filterColumn colId="47" showButton="0"/>
+    <filterColumn colId="48" showButton="0"/>
+    <filterColumn colId="49" showButton="0"/>
+    <filterColumn colId="50" showButton="0"/>
+    <filterColumn colId="52" showButton="0"/>
+    <filterColumn colId="53" showButton="0"/>
+    <filterColumn colId="54" showButton="0"/>
+    <filterColumn colId="55" showButton="0"/>
+    <filterColumn colId="56" showButton="0"/>
+  </autoFilter>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43165,11 +43208,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43407,33 +43445,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43462,16 +43500,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43482,107 +43520,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49729,11 +49767,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49744,6 +49777,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50222,18 +50260,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50255,14 +50293,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50276,4 +50306,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F3D6B1-FC2F-4776-AE41-84CCE139B4FD}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAFA8AB0-8A9F-4034-8AD3-507B53ACF238}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$8:$BM$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -3819,6 +3819,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3840,18 +3867,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3866,21 +3881,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,6 +3900,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3907,15 +3916,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43154,50 +43154,7 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="C8:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-    <filterColumn colId="7" showButton="0"/>
-    <filterColumn colId="8" showButton="0"/>
-    <filterColumn colId="9" showButton="0"/>
-    <filterColumn colId="10" showButton="0"/>
-    <filterColumn colId="11" showButton="0"/>
-    <filterColumn colId="12" showButton="0"/>
-    <filterColumn colId="13" showButton="0"/>
-    <filterColumn colId="21" showButton="0"/>
-    <filterColumn colId="22" showButton="0"/>
-    <filterColumn colId="23" showButton="0"/>
-    <filterColumn colId="24" showButton="0"/>
-    <filterColumn colId="29" showButton="0"/>
-    <filterColumn colId="30" showButton="0"/>
-    <filterColumn colId="31" showButton="0"/>
-    <filterColumn colId="32" showButton="0"/>
-    <filterColumn colId="33" showButton="0"/>
-    <filterColumn colId="35" showButton="0"/>
-    <filterColumn colId="36" showButton="0"/>
-    <filterColumn colId="37" showButton="0"/>
-    <filterColumn colId="38" showButton="0"/>
-    <filterColumn colId="39" showButton="0"/>
-    <filterColumn colId="40" showButton="0"/>
-    <filterColumn colId="41" showButton="0"/>
-    <filterColumn colId="43" showButton="0"/>
-    <filterColumn colId="44" showButton="0"/>
-    <filterColumn colId="45" showButton="0"/>
-    <filterColumn colId="46" showButton="0"/>
-    <filterColumn colId="47" showButton="0"/>
-    <filterColumn colId="48" showButton="0"/>
-    <filterColumn colId="49" showButton="0"/>
-    <filterColumn colId="50" showButton="0"/>
-    <filterColumn colId="52" showButton="0"/>
-    <filterColumn colId="53" showButton="0"/>
-    <filterColumn colId="54" showButton="0"/>
-    <filterColumn colId="55" showButton="0"/>
-    <filterColumn colId="56" showButton="0"/>
-  </autoFilter>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43208,6 +43165,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43220,7 +43182,7 @@
       <formula>NOT(ISERROR(SEARCH("SI",M11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations disablePrompts="1" count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11:H70" xr:uid="{B7C40B7F-3E14-4970-8D0A-638F8CF92B79}">
       <formula1>"Bogotá,Medellín,Nacional"</formula1>
     </dataValidation>
@@ -43445,33 +43407,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43500,16 +43462,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43520,107 +43482,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49767,6 +49729,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49777,11 +49744,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50260,18 +50222,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50293,6 +50255,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50306,12 +50276,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAFA8AB0-8A9F-4034-8AD3-507B53ACF238}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F991757-EEFA-4435-A532-E609069BF98E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -3819,33 +3819,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3867,6 +3840,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3881,6 +3866,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,15 +3900,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3916,6 +3907,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43154,7 +43154,13 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="C10:BM10" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}"/>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43165,11 +43171,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43407,33 +43408,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43462,16 +43463,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43482,107 +43483,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49729,11 +49730,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49744,6 +49740,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50222,18 +50223,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50255,14 +50256,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50276,4 +50269,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F991757-EEFA-4435-A532-E609069BF98E}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C7CC2F7-105C-44B2-A2C1-C4984B2D79A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,6 +3819,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3840,18 +3867,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3866,21 +3881,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,6 +3900,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3907,15 +3916,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43156,11 +43156,6 @@
   </sheetData>
   <autoFilter ref="C10:BM10" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}"/>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43171,6 +43166,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43408,33 +43408,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43463,16 +43463,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43483,107 +43483,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49730,6 +49730,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49740,11 +49745,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50223,18 +50223,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50256,6 +50256,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50269,12 +50277,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C7CC2F7-105C-44B2-A2C1-C4984B2D79A4}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A7723D-F4FB-413A-A0BE-3A3BCE29AB27}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -34592,7 +34592,9 @@
       </c>
       <c r="AQ14" s="12"/>
       <c r="AR14" s="12"/>
-      <c r="AS14" s="332"/>
+      <c r="AS14" s="332">
+        <v>0</v>
+      </c>
       <c r="AT14" s="12" t="s">
         <v>194</v>
       </c>
@@ -43154,7 +43156,6 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="C10:BM10" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}"/>
   <mergeCells count="15">
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
@@ -43183,7 +43184,7 @@
       <formula>NOT(ISERROR(SEARCH("SI",M11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="4">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11:H70" xr:uid="{B7C40B7F-3E14-4970-8D0A-638F8CF92B79}">
       <formula1>"Bogotá,Medellín,Nacional"</formula1>
     </dataValidation>

--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A7723D-F4FB-413A-A0BE-3A3BCE29AB27}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFA12CA-2FBC-47E1-BBBC-81AD2DF45B77}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,33 +3819,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3867,6 +3840,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3881,6 +3866,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,15 +3900,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3916,6 +3907,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43157,6 +43157,11 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43167,11 +43172,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43409,33 +43409,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43464,16 +43464,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43484,107 +43484,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49731,11 +49731,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49746,6 +49741,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50224,18 +50224,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50257,14 +50257,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50278,4 +50270,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="233" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFA12CA-2FBC-47E1-BBBC-81AD2DF45B77}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DEAC7D7-2BF3-4E61-A543-48A9BC661843}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,6 +3819,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3840,18 +3867,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3866,21 +3881,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,6 +3900,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3907,15 +3916,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43157,11 +43157,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43172,6 +43167,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43409,33 +43409,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43464,16 +43464,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43484,107 +43484,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49731,6 +49731,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49741,11 +49746,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50224,18 +50224,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50257,6 +50257,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50270,12 +50278,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DEAC7D7-2BF3-4E61-A543-48A9BC661843}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{993265D1-0B81-45B7-9AE3-F729C72906BE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,33 +3819,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3867,6 +3840,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3881,6 +3866,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,15 +3900,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3916,6 +3907,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43157,6 +43157,11 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43167,11 +43172,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43409,33 +43409,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43464,16 +43464,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43484,107 +43484,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49731,11 +49731,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49746,6 +49741,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50224,18 +50224,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50257,14 +50257,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50278,4 +50270,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{993265D1-0B81-45B7-9AE3-F729C72906BE}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C562B46-D3A5-40F0-B517-D6DB483E89A7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$A$10:$BM$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -3819,6 +3819,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3840,18 +3867,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3866,21 +3881,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,6 +3900,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3907,15 +3916,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43157,11 +43157,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43172,6 +43167,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43409,33 +43409,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43464,16 +43464,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43484,107 +43484,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49731,6 +49731,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49741,11 +49746,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50224,18 +50224,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50257,6 +50257,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50270,12 +50278,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C562B46-D3A5-40F0-B517-D6DB483E89A7}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94FD5A8-3D16-4C15-9423-1E51C242F7AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,33 +3819,6 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3867,6 +3840,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3881,6 +3866,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,15 +3900,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3916,6 +3907,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15980,43 +15980,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
-      <c r="Y3" s="341"/>
-      <c r="Z3" s="341"/>
-      <c r="AA3" s="341"/>
-      <c r="AB3" s="341"/>
-      <c r="AC3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
+      <c r="Y3" s="357"/>
+      <c r="Z3" s="357"/>
+      <c r="AA3" s="357"/>
+      <c r="AB3" s="357"/>
+      <c r="AC3" s="357"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
-      <c r="Y4" s="341"/>
-      <c r="Z4" s="341"/>
-      <c r="AA4" s="341"/>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
+      <c r="Y4" s="357"/>
+      <c r="Z4" s="357"/>
+      <c r="AA4" s="357"/>
+      <c r="AB4" s="357"/>
+      <c r="AC4" s="357"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16045,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
-      <c r="R8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
+      <c r="R8" s="348"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16070,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="346" t="s">
+      <c r="AD8" s="350"/>
+      <c r="AE8" s="350"/>
+      <c r="AF8" s="350"/>
+      <c r="AG8" s="350"/>
+      <c r="AH8" s="351"/>
+      <c r="AI8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AL8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="357" t="s">
+      <c r="AM8" s="361"/>
+      <c r="AN8" s="361"/>
+      <c r="AO8" s="361"/>
+      <c r="AP8" s="361"/>
+      <c r="AQ8" s="361"/>
+      <c r="AR8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="357"/>
-      <c r="AU8" s="357"/>
-      <c r="AV8" s="357"/>
-      <c r="AW8" s="357"/>
-      <c r="AX8" s="357"/>
-      <c r="AY8" s="357"/>
-      <c r="AZ8" s="357"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="352"/>
+      <c r="AU8" s="352"/>
+      <c r="AV8" s="352"/>
+      <c r="AW8" s="352"/>
+      <c r="AX8" s="352"/>
+      <c r="AY8" s="352"/>
+      <c r="AZ8" s="352"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="354" t="s">
+      <c r="BD8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="354"/>
-      <c r="BF8" s="354"/>
-      <c r="BG8" s="354"/>
-      <c r="BH8" s="354"/>
-      <c r="BI8" s="354"/>
-      <c r="BJ8" s="354"/>
-      <c r="BK8" s="354"/>
-      <c r="BL8" s="354"/>
-      <c r="BM8" s="354"/>
-      <c r="BN8" s="354"/>
-      <c r="BO8" s="354"/>
-      <c r="BP8" s="354"/>
-      <c r="BQ8" s="355" t="s">
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
+      <c r="BI8" s="345"/>
+      <c r="BJ8" s="345"/>
+      <c r="BK8" s="345"/>
+      <c r="BL8" s="345"/>
+      <c r="BM8" s="345"/>
+      <c r="BN8" s="345"/>
+      <c r="BO8" s="345"/>
+      <c r="BP8" s="345"/>
+      <c r="BQ8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="355"/>
-      <c r="BS8" s="355"/>
+      <c r="BR8" s="346"/>
+      <c r="BS8" s="346"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
-      <c r="R9" s="342"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
+      <c r="R9" s="348"/>
+      <c r="S9" s="371" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="371" t="s">
+      <c r="T9" s="368" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="371" t="s">
+      <c r="U9" s="368" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="371" t="s">
+      <c r="V9" s="368" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="344"/>
-      <c r="AC9" s="344"/>
-      <c r="AD9" s="344"/>
-      <c r="AE9" s="344"/>
-      <c r="AF9" s="344"/>
-      <c r="AG9" s="344"/>
-      <c r="AH9" s="345"/>
-      <c r="AI9" s="347"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="350"/>
+      <c r="AD9" s="350"/>
+      <c r="AE9" s="350"/>
+      <c r="AF9" s="350"/>
+      <c r="AG9" s="350"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="359"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="373" t="s">
+      <c r="AL9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="373"/>
-      <c r="AN9" s="373"/>
-      <c r="AO9" s="373"/>
-      <c r="AP9" s="373"/>
-      <c r="AQ9" s="373"/>
-      <c r="AR9" s="358" t="s">
+      <c r="AM9" s="370"/>
+      <c r="AN9" s="370"/>
+      <c r="AO9" s="370"/>
+      <c r="AP9" s="370"/>
+      <c r="AQ9" s="370"/>
+      <c r="AR9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="358"/>
-      <c r="AU9" s="358"/>
-      <c r="AV9" s="358"/>
-      <c r="AW9" s="358"/>
-      <c r="AX9" s="358"/>
-      <c r="AY9" s="358"/>
-      <c r="AZ9" s="358"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
+      <c r="AV9" s="353"/>
+      <c r="AW9" s="353"/>
+      <c r="AX9" s="353"/>
+      <c r="AY9" s="353"/>
+      <c r="AZ9" s="353"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="350" t="s">
+      <c r="BD9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="350"/>
-      <c r="BM9" s="350"/>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="353" t="s">
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
+      <c r="BI9" s="341"/>
+      <c r="BJ9" s="341"/>
+      <c r="BK9" s="341"/>
+      <c r="BL9" s="341"/>
+      <c r="BM9" s="341"/>
+      <c r="BN9" s="341"/>
+      <c r="BO9" s="341"/>
+      <c r="BP9" s="341"/>
+      <c r="BQ9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="353"/>
-      <c r="BS9" s="353"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="344"/>
+      <c r="BS9" s="344"/>
+      <c r="BT9" s="372" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="372" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="372" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="373" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16287,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="372"/>
-      <c r="U10" s="372"/>
-      <c r="V10" s="372"/>
+      <c r="S10" s="371"/>
+      <c r="T10" s="369"/>
+      <c r="U10" s="369"/>
+      <c r="V10" s="369"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16416,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="372"/>
+      <c r="BU10" s="372"/>
+      <c r="BV10" s="372"/>
+      <c r="BW10" s="373"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33459,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33467,21 +33482,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33612,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33672,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33692,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="344"/>
-      <c r="AB8" s="345"/>
-      <c r="AC8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="351"/>
+      <c r="AC8" s="358" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="348" t="s">
+      <c r="AF8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="357" t="s">
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="361"/>
+      <c r="AJ8" s="361"/>
+      <c r="AK8" s="361"/>
+      <c r="AL8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="357"/>
-      <c r="AS8" s="357"/>
-      <c r="AT8" s="354" t="s">
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="352"/>
+      <c r="AP8" s="352"/>
+      <c r="AQ8" s="352"/>
+      <c r="AR8" s="352"/>
+      <c r="AS8" s="352"/>
+      <c r="AT8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="354"/>
-      <c r="AV8" s="354"/>
-      <c r="AW8" s="354"/>
-      <c r="AX8" s="354"/>
-      <c r="AY8" s="354"/>
-      <c r="AZ8" s="354"/>
-      <c r="BA8" s="354"/>
-      <c r="BB8" s="354"/>
-      <c r="BC8" s="355" t="s">
+      <c r="AU8" s="345"/>
+      <c r="AV8" s="345"/>
+      <c r="AW8" s="345"/>
+      <c r="AX8" s="345"/>
+      <c r="AY8" s="345"/>
+      <c r="AZ8" s="345"/>
+      <c r="BA8" s="345"/>
+      <c r="BB8" s="345"/>
+      <c r="BC8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
+      <c r="BD8" s="346"/>
+      <c r="BE8" s="346"/>
+      <c r="BF8" s="346"/>
+      <c r="BG8" s="346"/>
+      <c r="BH8" s="346"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="344"/>
-      <c r="AB9" s="345"/>
-      <c r="AC9" s="347"/>
-      <c r="AD9" s="359" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="351"/>
+      <c r="AC9" s="359"/>
+      <c r="AD9" s="354" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="360"/>
-      <c r="AF9" s="360"/>
-      <c r="AG9" s="360"/>
-      <c r="AH9" s="360"/>
-      <c r="AI9" s="360"/>
-      <c r="AJ9" s="360"/>
-      <c r="AK9" s="361"/>
-      <c r="AL9" s="358" t="s">
+      <c r="AE9" s="355"/>
+      <c r="AF9" s="355"/>
+      <c r="AG9" s="355"/>
+      <c r="AH9" s="355"/>
+      <c r="AI9" s="355"/>
+      <c r="AJ9" s="355"/>
+      <c r="AK9" s="356"/>
+      <c r="AL9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="358"/>
-      <c r="AP9" s="358"/>
-      <c r="AQ9" s="358"/>
-      <c r="AR9" s="358"/>
-      <c r="AS9" s="358"/>
-      <c r="AT9" s="350" t="s">
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="353"/>
+      <c r="AP9" s="353"/>
+      <c r="AQ9" s="353"/>
+      <c r="AR9" s="353"/>
+      <c r="AS9" s="353"/>
+      <c r="AT9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="350"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="350"/>
-      <c r="AY9" s="351"/>
-      <c r="AZ9" s="351"/>
-      <c r="BA9" s="351"/>
-      <c r="BB9" s="351"/>
-      <c r="BC9" s="352" t="s">
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="341"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="341"/>
+      <c r="AY9" s="342"/>
+      <c r="AZ9" s="342"/>
+      <c r="BA9" s="342"/>
+      <c r="BB9" s="342"/>
+      <c r="BC9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="353"/>
-      <c r="BE9" s="353"/>
-      <c r="BF9" s="353"/>
-      <c r="BG9" s="353"/>
-      <c r="BH9" s="353"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43157,6 +43157,11 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43167,11 +43172,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43409,33 +43409,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="341" t="s">
+      <c r="O3" s="357" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="341"/>
-      <c r="Q3" s="341"/>
-      <c r="R3" s="341"/>
-      <c r="S3" s="341"/>
-      <c r="T3" s="341"/>
-      <c r="U3" s="341"/>
-      <c r="V3" s="341"/>
-      <c r="W3" s="341"/>
-      <c r="X3" s="341"/>
+      <c r="P3" s="357"/>
+      <c r="Q3" s="357"/>
+      <c r="R3" s="357"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="357"/>
+      <c r="U3" s="357"/>
+      <c r="V3" s="357"/>
+      <c r="W3" s="357"/>
+      <c r="X3" s="357"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="341"/>
-      <c r="P4" s="341"/>
-      <c r="Q4" s="341"/>
-      <c r="R4" s="341"/>
-      <c r="S4" s="341"/>
-      <c r="T4" s="341"/>
-      <c r="U4" s="341"/>
-      <c r="V4" s="341"/>
-      <c r="W4" s="341"/>
-      <c r="X4" s="341"/>
+      <c r="O4" s="357"/>
+      <c r="P4" s="357"/>
+      <c r="Q4" s="357"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="357"/>
+      <c r="T4" s="357"/>
+      <c r="U4" s="357"/>
+      <c r="V4" s="357"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43464,16 +43464,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="342" t="s">
+      <c r="J8" s="348" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="342"/>
-      <c r="P8" s="342"/>
-      <c r="Q8" s="342"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
+      <c r="Q8" s="348"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43484,107 +43484,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="343" t="s">
+      <c r="X8" s="349" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="344"/>
-      <c r="Z8" s="344"/>
-      <c r="AA8" s="345"/>
-      <c r="AB8" s="346" t="s">
+      <c r="Y8" s="350"/>
+      <c r="Z8" s="350"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="358" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="360" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="361"/>
+      <c r="AE8" s="361"/>
+      <c r="AF8" s="361"/>
+      <c r="AG8" s="361"/>
+      <c r="AH8" s="361"/>
+      <c r="AI8" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="357"/>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="354" t="s">
+      <c r="AJ8" s="352"/>
+      <c r="AK8" s="352"/>
+      <c r="AL8" s="352"/>
+      <c r="AM8" s="352"/>
+      <c r="AN8" s="352"/>
+      <c r="AO8" s="345" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="354"/>
-      <c r="AQ8" s="354"/>
-      <c r="AR8" s="354"/>
-      <c r="AS8" s="355" t="s">
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="345"/>
+      <c r="AS8" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="355"/>
-      <c r="AU8" s="355"/>
+      <c r="AT8" s="346"/>
+      <c r="AU8" s="346"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="356" t="s">
+      <c r="C9" s="347" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="356"/>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="G9" s="356"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="342" t="s">
+      <c r="D9" s="347"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="348" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="342"/>
-      <c r="N9" s="342"/>
-      <c r="O9" s="342"/>
-      <c r="P9" s="342"/>
-      <c r="Q9" s="342"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
+      <c r="Q9" s="348"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="343" t="s">
+      <c r="V9" s="349" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="344"/>
-      <c r="Y9" s="344"/>
-      <c r="Z9" s="344"/>
-      <c r="AA9" s="345"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="373" t="s">
+      <c r="W9" s="350"/>
+      <c r="X9" s="350"/>
+      <c r="Y9" s="350"/>
+      <c r="Z9" s="350"/>
+      <c r="AA9" s="351"/>
+      <c r="AB9" s="359"/>
+      <c r="AC9" s="370" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="373"/>
-      <c r="AE9" s="373"/>
-      <c r="AF9" s="373"/>
-      <c r="AG9" s="373"/>
-      <c r="AH9" s="373"/>
-      <c r="AI9" s="358" t="s">
+      <c r="AD9" s="370"/>
+      <c r="AE9" s="370"/>
+      <c r="AF9" s="370"/>
+      <c r="AG9" s="370"/>
+      <c r="AH9" s="370"/>
+      <c r="AI9" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="358"/>
-      <c r="AK9" s="358"/>
-      <c r="AL9" s="358"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="358"/>
-      <c r="AO9" s="350" t="s">
+      <c r="AJ9" s="353"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="353"/>
+      <c r="AM9" s="353"/>
+      <c r="AN9" s="353"/>
+      <c r="AO9" s="341" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="353" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="344" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
+      <c r="AT9" s="344"/>
+      <c r="AU9" s="344"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49731,11 +49731,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49746,6 +49741,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50224,18 +50224,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50257,14 +50257,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50278,4 +50270,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94FD5A8-3D16-4C15-9423-1E51C242F7AF}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="8_{9A2943AE-6812-4C89-8676-A6093C4C8CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CC64549-CB32-4982-87A0-2B9644866E7B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3819,6 +3819,33 @@
     <xf numFmtId="0" fontId="82" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3840,18 +3867,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3866,21 +3881,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3900,6 +3900,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3907,15 +3916,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9127,7 +9127,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -9139,9 +9139,7 @@
   <we:alternateReferences>
     <we:reference id="WA200009404" version="1.0.0.5" store="WA200009404" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties>
-    <we:property name="Office.AutoShowTaskpaneWithDocument" value="true"/>
-  </we:properties>
+  <we:properties/>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
@@ -15980,43 +15978,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
-      <c r="Y3" s="357"/>
-      <c r="Z3" s="357"/>
-      <c r="AA3" s="357"/>
-      <c r="AB3" s="357"/>
-      <c r="AC3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
+      <c r="Y3" s="341"/>
+      <c r="Z3" s="341"/>
+      <c r="AA3" s="341"/>
+      <c r="AB3" s="341"/>
+      <c r="AC3" s="341"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-      <c r="Y4" s="357"/>
-      <c r="Z4" s="357"/>
-      <c r="AA4" s="357"/>
-      <c r="AB4" s="357"/>
-      <c r="AC4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
+      <c r="Y4" s="341"/>
+      <c r="Z4" s="341"/>
+      <c r="AA4" s="341"/>
+      <c r="AB4" s="341"/>
+      <c r="AC4" s="341"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16045,17 +16043,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
-      <c r="R8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
+      <c r="R8" s="342"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16070,168 +16068,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="349" t="s">
+      <c r="AC8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="350"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="351"/>
-      <c r="AI8" s="358" t="s">
+      <c r="AD8" s="344"/>
+      <c r="AE8" s="344"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="360" t="s">
+      <c r="AL8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="361"/>
-      <c r="AN8" s="361"/>
-      <c r="AO8" s="361"/>
-      <c r="AP8" s="361"/>
-      <c r="AQ8" s="361"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="357"/>
+      <c r="AU8" s="357"/>
+      <c r="AV8" s="357"/>
+      <c r="AW8" s="357"/>
+      <c r="AX8" s="357"/>
+      <c r="AY8" s="357"/>
+      <c r="AZ8" s="357"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="345" t="s">
+      <c r="BD8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
-      <c r="BI8" s="345"/>
-      <c r="BJ8" s="345"/>
-      <c r="BK8" s="345"/>
-      <c r="BL8" s="345"/>
-      <c r="BM8" s="345"/>
-      <c r="BN8" s="345"/>
-      <c r="BO8" s="345"/>
-      <c r="BP8" s="345"/>
-      <c r="BQ8" s="346" t="s">
+      <c r="BE8" s="354"/>
+      <c r="BF8" s="354"/>
+      <c r="BG8" s="354"/>
+      <c r="BH8" s="354"/>
+      <c r="BI8" s="354"/>
+      <c r="BJ8" s="354"/>
+      <c r="BK8" s="354"/>
+      <c r="BL8" s="354"/>
+      <c r="BM8" s="354"/>
+      <c r="BN8" s="354"/>
+      <c r="BO8" s="354"/>
+      <c r="BP8" s="354"/>
+      <c r="BQ8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="346"/>
-      <c r="BS8" s="346"/>
+      <c r="BR8" s="355"/>
+      <c r="BS8" s="355"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
-      <c r="R9" s="348"/>
-      <c r="S9" s="371" t="s">
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
+      <c r="R9" s="342"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="368" t="s">
+      <c r="T9" s="371" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="368" t="s">
+      <c r="U9" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="368" t="s">
+      <c r="V9" s="371" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="349" t="s">
+      <c r="AA9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="350"/>
-      <c r="AD9" s="350"/>
-      <c r="AE9" s="350"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="359"/>
+      <c r="AB9" s="344"/>
+      <c r="AC9" s="344"/>
+      <c r="AD9" s="344"/>
+      <c r="AE9" s="344"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="345"/>
+      <c r="AI9" s="347"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="370" t="s">
+      <c r="AL9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="370"/>
-      <c r="AN9" s="370"/>
-      <c r="AO9" s="370"/>
-      <c r="AP9" s="370"/>
-      <c r="AQ9" s="370"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="373"/>
+      <c r="AN9" s="373"/>
+      <c r="AO9" s="373"/>
+      <c r="AP9" s="373"/>
+      <c r="AQ9" s="373"/>
+      <c r="AR9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="358"/>
+      <c r="AU9" s="358"/>
+      <c r="AV9" s="358"/>
+      <c r="AW9" s="358"/>
+      <c r="AX9" s="358"/>
+      <c r="AY9" s="358"/>
+      <c r="AZ9" s="358"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="341" t="s">
+      <c r="BD9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="341"/>
-      <c r="BF9" s="341"/>
-      <c r="BG9" s="341"/>
-      <c r="BH9" s="341"/>
-      <c r="BI9" s="341"/>
-      <c r="BJ9" s="341"/>
-      <c r="BK9" s="341"/>
-      <c r="BL9" s="341"/>
-      <c r="BM9" s="341"/>
-      <c r="BN9" s="341"/>
-      <c r="BO9" s="341"/>
-      <c r="BP9" s="341"/>
-      <c r="BQ9" s="344" t="s">
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="350"/>
+      <c r="BM9" s="350"/>
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="344"/>
-      <c r="BS9" s="344"/>
-      <c r="BT9" s="372" t="s">
+      <c r="BR9" s="353"/>
+      <c r="BS9" s="353"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="372" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="372" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="373" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16287,10 +16285,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="371"/>
-      <c r="T10" s="369"/>
-      <c r="U10" s="369"/>
-      <c r="V10" s="369"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="372"/>
+      <c r="U10" s="372"/>
+      <c r="V10" s="372"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16416,10 +16414,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="372"/>
-      <c r="BU10" s="372"/>
-      <c r="BV10" s="372"/>
-      <c r="BW10" s="373"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33459,6 +33457,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33467,21 +33480,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33612,34 +33610,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33672,16 +33670,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33692,133 +33690,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="351"/>
-      <c r="AC8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="344"/>
+      <c r="AB8" s="345"/>
+      <c r="AC8" s="346" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="360" t="s">
+      <c r="AF8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="361"/>
-      <c r="AJ8" s="361"/>
-      <c r="AK8" s="361"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="345" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="357"/>
+      <c r="AS8" s="357"/>
+      <c r="AT8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="345"/>
-      <c r="AV8" s="345"/>
-      <c r="AW8" s="345"/>
-      <c r="AX8" s="345"/>
-      <c r="AY8" s="345"/>
-      <c r="AZ8" s="345"/>
-      <c r="BA8" s="345"/>
-      <c r="BB8" s="345"/>
-      <c r="BC8" s="346" t="s">
+      <c r="AU8" s="354"/>
+      <c r="AV8" s="354"/>
+      <c r="AW8" s="354"/>
+      <c r="AX8" s="354"/>
+      <c r="AY8" s="354"/>
+      <c r="AZ8" s="354"/>
+      <c r="BA8" s="354"/>
+      <c r="BB8" s="354"/>
+      <c r="BC8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="346"/>
-      <c r="BE8" s="346"/>
-      <c r="BF8" s="346"/>
-      <c r="BG8" s="346"/>
-      <c r="BH8" s="346"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="351"/>
-      <c r="AC9" s="359"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="344"/>
+      <c r="AB9" s="345"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="359" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="360"/>
+      <c r="AF9" s="360"/>
+      <c r="AG9" s="360"/>
+      <c r="AH9" s="360"/>
+      <c r="AI9" s="360"/>
+      <c r="AJ9" s="360"/>
+      <c r="AK9" s="361"/>
+      <c r="AL9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="341" t="s">
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="358"/>
+      <c r="AP9" s="358"/>
+      <c r="AQ9" s="358"/>
+      <c r="AR9" s="358"/>
+      <c r="AS9" s="358"/>
+      <c r="AT9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="341"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="341"/>
-      <c r="AY9" s="342"/>
-      <c r="AZ9" s="342"/>
-      <c r="BA9" s="342"/>
-      <c r="BB9" s="342"/>
-      <c r="BC9" s="343" t="s">
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="351"/>
+      <c r="AZ9" s="351"/>
+      <c r="BA9" s="351"/>
+      <c r="BB9" s="351"/>
+      <c r="BC9" s="352" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
+      <c r="BD9" s="353"/>
+      <c r="BE9" s="353"/>
+      <c r="BF9" s="353"/>
+      <c r="BG9" s="353"/>
+      <c r="BH9" s="353"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43156,12 +43154,8 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="A10:BM10" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}"/>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43172,6 +43166,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43409,33 +43408,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="357" t="s">
+      <c r="O3" s="341" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="357"/>
-      <c r="Q3" s="357"/>
-      <c r="R3" s="357"/>
-      <c r="S3" s="357"/>
-      <c r="T3" s="357"/>
-      <c r="U3" s="357"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="357"/>
-      <c r="X3" s="357"/>
+      <c r="P3" s="341"/>
+      <c r="Q3" s="341"/>
+      <c r="R3" s="341"/>
+      <c r="S3" s="341"/>
+      <c r="T3" s="341"/>
+      <c r="U3" s="341"/>
+      <c r="V3" s="341"/>
+      <c r="W3" s="341"/>
+      <c r="X3" s="341"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="357"/>
-      <c r="P4" s="357"/>
-      <c r="Q4" s="357"/>
-      <c r="R4" s="357"/>
-      <c r="S4" s="357"/>
-      <c r="T4" s="357"/>
-      <c r="U4" s="357"/>
-      <c r="V4" s="357"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
+      <c r="O4" s="341"/>
+      <c r="P4" s="341"/>
+      <c r="Q4" s="341"/>
+      <c r="R4" s="341"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="341"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43464,16 +43463,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="348" t="s">
+      <c r="J8" s="342" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="348"/>
-      <c r="P8" s="348"/>
-      <c r="Q8" s="348"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="342"/>
+      <c r="P8" s="342"/>
+      <c r="Q8" s="342"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43484,107 +43483,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="349" t="s">
+      <c r="X8" s="343" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="350"/>
-      <c r="Z8" s="350"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="358" t="s">
+      <c r="Y8" s="344"/>
+      <c r="Z8" s="344"/>
+      <c r="AA8" s="345"/>
+      <c r="AB8" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="360" t="s">
+      <c r="AC8" s="348" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="361"/>
-      <c r="AE8" s="361"/>
-      <c r="AF8" s="361"/>
-      <c r="AG8" s="361"/>
-      <c r="AH8" s="361"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="357" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="345" t="s">
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="357"/>
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="345"/>
-      <c r="AS8" s="346" t="s">
+      <c r="AP8" s="354"/>
+      <c r="AQ8" s="354"/>
+      <c r="AR8" s="354"/>
+      <c r="AS8" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="346"/>
-      <c r="AU8" s="346"/>
+      <c r="AT8" s="355"/>
+      <c r="AU8" s="355"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="347" t="s">
+      <c r="C9" s="356" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="347"/>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="348" t="s">
+      <c r="D9" s="356"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="G9" s="356"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="342" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="348"/>
-      <c r="L9" s="348"/>
-      <c r="M9" s="348"/>
-      <c r="N9" s="348"/>
-      <c r="O9" s="348"/>
-      <c r="P9" s="348"/>
-      <c r="Q9" s="348"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="342"/>
+      <c r="N9" s="342"/>
+      <c r="O9" s="342"/>
+      <c r="P9" s="342"/>
+      <c r="Q9" s="342"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="349" t="s">
+      <c r="V9" s="343" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="350"/>
-      <c r="X9" s="350"/>
-      <c r="Y9" s="350"/>
-      <c r="Z9" s="350"/>
-      <c r="AA9" s="351"/>
-      <c r="AB9" s="359"/>
-      <c r="AC9" s="370" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="344"/>
+      <c r="Y9" s="344"/>
+      <c r="Z9" s="344"/>
+      <c r="AA9" s="345"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="373" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="370"/>
-      <c r="AE9" s="370"/>
-      <c r="AF9" s="370"/>
-      <c r="AG9" s="370"/>
-      <c r="AH9" s="370"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="373"/>
+      <c r="AE9" s="373"/>
+      <c r="AF9" s="373"/>
+      <c r="AG9" s="373"/>
+      <c r="AH9" s="373"/>
+      <c r="AI9" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="341" t="s">
+      <c r="AJ9" s="358"/>
+      <c r="AK9" s="358"/>
+      <c r="AL9" s="358"/>
+      <c r="AM9" s="358"/>
+      <c r="AN9" s="358"/>
+      <c r="AO9" s="350" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="344" t="s">
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="353" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="344"/>
-      <c r="AU9" s="344"/>
+      <c r="AT9" s="353"/>
+      <c r="AU9" s="353"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49731,6 +49730,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49741,11 +49745,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50086,6 +50085,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -50223,35 +50237,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -50273,9 +50262,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ximen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F284E1-7F0C-4711-B144-6978B10ED4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{A5F284E1-7F0C-4711-B144-6978B10ED4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{792173EF-C6B5-4931-94DA-726F892E0572}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
@@ -3805,33 +3805,6 @@
     <xf numFmtId="0" fontId="34" fillId="35" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3853,6 +3826,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3867,6 +3852,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3886,15 +3886,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3902,6 +3893,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15964,43 +15964,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="337" t="s">
+      <c r="O3" s="353" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="337"/>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
-      <c r="V3" s="337"/>
-      <c r="W3" s="337"/>
-      <c r="X3" s="337"/>
-      <c r="Y3" s="337"/>
-      <c r="Z3" s="337"/>
-      <c r="AA3" s="337"/>
-      <c r="AB3" s="337"/>
-      <c r="AC3" s="337"/>
+      <c r="P3" s="353"/>
+      <c r="Q3" s="353"/>
+      <c r="R3" s="353"/>
+      <c r="S3" s="353"/>
+      <c r="T3" s="353"/>
+      <c r="U3" s="353"/>
+      <c r="V3" s="353"/>
+      <c r="W3" s="353"/>
+      <c r="X3" s="353"/>
+      <c r="Y3" s="353"/>
+      <c r="Z3" s="353"/>
+      <c r="AA3" s="353"/>
+      <c r="AB3" s="353"/>
+      <c r="AC3" s="353"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337"/>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
-      <c r="V4" s="337"/>
-      <c r="W4" s="337"/>
-      <c r="X4" s="337"/>
-      <c r="Y4" s="337"/>
-      <c r="Z4" s="337"/>
-      <c r="AA4" s="337"/>
-      <c r="AB4" s="337"/>
-      <c r="AC4" s="337"/>
+      <c r="O4" s="353"/>
+      <c r="P4" s="353"/>
+      <c r="Q4" s="353"/>
+      <c r="R4" s="353"/>
+      <c r="S4" s="353"/>
+      <c r="T4" s="353"/>
+      <c r="U4" s="353"/>
+      <c r="V4" s="353"/>
+      <c r="W4" s="353"/>
+      <c r="X4" s="353"/>
+      <c r="Y4" s="353"/>
+      <c r="Z4" s="353"/>
+      <c r="AA4" s="353"/>
+      <c r="AB4" s="353"/>
+      <c r="AC4" s="353"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16029,17 +16029,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="338" t="s">
+      <c r="J8" s="344" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="338"/>
-      <c r="N8" s="338"/>
-      <c r="O8" s="338"/>
-      <c r="P8" s="338"/>
-      <c r="Q8" s="338"/>
-      <c r="R8" s="338"/>
+      <c r="K8" s="344"/>
+      <c r="L8" s="344"/>
+      <c r="M8" s="344"/>
+      <c r="N8" s="344"/>
+      <c r="O8" s="344"/>
+      <c r="P8" s="344"/>
+      <c r="Q8" s="344"/>
+      <c r="R8" s="344"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16054,168 +16054,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="339" t="s">
+      <c r="AC8" s="345" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="340"/>
-      <c r="AE8" s="340"/>
-      <c r="AF8" s="340"/>
-      <c r="AG8" s="340"/>
-      <c r="AH8" s="341"/>
-      <c r="AI8" s="342" t="s">
+      <c r="AD8" s="346"/>
+      <c r="AE8" s="346"/>
+      <c r="AF8" s="346"/>
+      <c r="AG8" s="346"/>
+      <c r="AH8" s="347"/>
+      <c r="AI8" s="354" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="344" t="s">
+      <c r="AL8" s="356" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="345"/>
-      <c r="AN8" s="345"/>
-      <c r="AO8" s="345"/>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="353" t="s">
+      <c r="AM8" s="357"/>
+      <c r="AN8" s="357"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="357"/>
+      <c r="AQ8" s="357"/>
+      <c r="AR8" s="348" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="353"/>
-      <c r="AT8" s="353"/>
-      <c r="AU8" s="353"/>
-      <c r="AV8" s="353"/>
-      <c r="AW8" s="353"/>
-      <c r="AX8" s="353"/>
-      <c r="AY8" s="353"/>
-      <c r="AZ8" s="353"/>
+      <c r="AS8" s="348"/>
+      <c r="AT8" s="348"/>
+      <c r="AU8" s="348"/>
+      <c r="AV8" s="348"/>
+      <c r="AW8" s="348"/>
+      <c r="AX8" s="348"/>
+      <c r="AY8" s="348"/>
+      <c r="AZ8" s="348"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="350" t="s">
+      <c r="BD8" s="341" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="350"/>
-      <c r="BF8" s="350"/>
-      <c r="BG8" s="350"/>
-      <c r="BH8" s="350"/>
-      <c r="BI8" s="350"/>
-      <c r="BJ8" s="350"/>
-      <c r="BK8" s="350"/>
-      <c r="BL8" s="350"/>
-      <c r="BM8" s="350"/>
-      <c r="BN8" s="350"/>
-      <c r="BO8" s="350"/>
-      <c r="BP8" s="350"/>
-      <c r="BQ8" s="351" t="s">
+      <c r="BE8" s="341"/>
+      <c r="BF8" s="341"/>
+      <c r="BG8" s="341"/>
+      <c r="BH8" s="341"/>
+      <c r="BI8" s="341"/>
+      <c r="BJ8" s="341"/>
+      <c r="BK8" s="341"/>
+      <c r="BL8" s="341"/>
+      <c r="BM8" s="341"/>
+      <c r="BN8" s="341"/>
+      <c r="BO8" s="341"/>
+      <c r="BP8" s="341"/>
+      <c r="BQ8" s="342" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="351"/>
-      <c r="BS8" s="351"/>
+      <c r="BR8" s="342"/>
+      <c r="BS8" s="342"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="352" t="s">
+      <c r="C9" s="343" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="352"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
-      <c r="G9" s="352"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="338" t="s">
+      <c r="D9" s="343"/>
+      <c r="E9" s="343"/>
+      <c r="F9" s="343"/>
+      <c r="G9" s="343"/>
+      <c r="H9" s="343"/>
+      <c r="I9" s="343"/>
+      <c r="J9" s="344" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="338"/>
-      <c r="N9" s="338"/>
-      <c r="O9" s="338"/>
-      <c r="P9" s="338"/>
-      <c r="Q9" s="338"/>
-      <c r="R9" s="338"/>
-      <c r="S9" s="366" t="s">
+      <c r="K9" s="344"/>
+      <c r="L9" s="344"/>
+      <c r="M9" s="344"/>
+      <c r="N9" s="344"/>
+      <c r="O9" s="344"/>
+      <c r="P9" s="344"/>
+      <c r="Q9" s="344"/>
+      <c r="R9" s="344"/>
+      <c r="S9" s="367" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="367" t="s">
+      <c r="T9" s="364" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="367" t="s">
+      <c r="U9" s="364" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="367" t="s">
+      <c r="V9" s="364" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="339" t="s">
+      <c r="AA9" s="345" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="340"/>
-      <c r="AC9" s="340"/>
-      <c r="AD9" s="340"/>
-      <c r="AE9" s="340"/>
-      <c r="AF9" s="340"/>
-      <c r="AG9" s="340"/>
-      <c r="AH9" s="341"/>
-      <c r="AI9" s="343"/>
+      <c r="AB9" s="346"/>
+      <c r="AC9" s="346"/>
+      <c r="AD9" s="346"/>
+      <c r="AE9" s="346"/>
+      <c r="AF9" s="346"/>
+      <c r="AG9" s="346"/>
+      <c r="AH9" s="347"/>
+      <c r="AI9" s="355"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="369" t="s">
+      <c r="AL9" s="366" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="369"/>
-      <c r="AN9" s="369"/>
-      <c r="AO9" s="369"/>
-      <c r="AP9" s="369"/>
-      <c r="AQ9" s="369"/>
-      <c r="AR9" s="354" t="s">
+      <c r="AM9" s="366"/>
+      <c r="AN9" s="366"/>
+      <c r="AO9" s="366"/>
+      <c r="AP9" s="366"/>
+      <c r="AQ9" s="366"/>
+      <c r="AR9" s="349" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="354"/>
-      <c r="AT9" s="354"/>
-      <c r="AU9" s="354"/>
-      <c r="AV9" s="354"/>
-      <c r="AW9" s="354"/>
-      <c r="AX9" s="354"/>
-      <c r="AY9" s="354"/>
-      <c r="AZ9" s="354"/>
+      <c r="AS9" s="349"/>
+      <c r="AT9" s="349"/>
+      <c r="AU9" s="349"/>
+      <c r="AV9" s="349"/>
+      <c r="AW9" s="349"/>
+      <c r="AX9" s="349"/>
+      <c r="AY9" s="349"/>
+      <c r="AZ9" s="349"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="346" t="s">
+      <c r="BD9" s="337" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="346"/>
-      <c r="BF9" s="346"/>
-      <c r="BG9" s="346"/>
-      <c r="BH9" s="346"/>
-      <c r="BI9" s="346"/>
-      <c r="BJ9" s="346"/>
-      <c r="BK9" s="346"/>
-      <c r="BL9" s="346"/>
-      <c r="BM9" s="346"/>
-      <c r="BN9" s="346"/>
-      <c r="BO9" s="346"/>
-      <c r="BP9" s="346"/>
-      <c r="BQ9" s="349" t="s">
+      <c r="BE9" s="337"/>
+      <c r="BF9" s="337"/>
+      <c r="BG9" s="337"/>
+      <c r="BH9" s="337"/>
+      <c r="BI9" s="337"/>
+      <c r="BJ9" s="337"/>
+      <c r="BK9" s="337"/>
+      <c r="BL9" s="337"/>
+      <c r="BM9" s="337"/>
+      <c r="BN9" s="337"/>
+      <c r="BO9" s="337"/>
+      <c r="BP9" s="337"/>
+      <c r="BQ9" s="340" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="349"/>
-      <c r="BS9" s="349"/>
-      <c r="BT9" s="364" t="s">
+      <c r="BR9" s="340"/>
+      <c r="BS9" s="340"/>
+      <c r="BT9" s="368" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="364" t="s">
+      <c r="BU9" s="368" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="364" t="s">
+      <c r="BV9" s="368" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="365" t="s">
+      <c r="BW9" s="369" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16271,10 +16271,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="366"/>
-      <c r="T10" s="368"/>
-      <c r="U10" s="368"/>
-      <c r="V10" s="368"/>
+      <c r="S10" s="367"/>
+      <c r="T10" s="365"/>
+      <c r="U10" s="365"/>
+      <c r="V10" s="365"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16400,10 +16400,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="364"/>
-      <c r="BU10" s="364"/>
-      <c r="BV10" s="364"/>
-      <c r="BW10" s="365"/>
+      <c r="BT10" s="368"/>
+      <c r="BU10" s="368"/>
+      <c r="BV10" s="368"/>
+      <c r="BW10" s="369"/>
     </row>
     <row r="11" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33443,6 +33443,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33451,21 +33466,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33554,7 +33554,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="C1:BM83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -33598,34 +33597,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="337" t="s">
+      <c r="O3" s="353" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="337"/>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
-      <c r="V3" s="337"/>
-      <c r="W3" s="337"/>
-      <c r="X3" s="337"/>
+      <c r="P3" s="353"/>
+      <c r="Q3" s="353"/>
+      <c r="R3" s="353"/>
+      <c r="S3" s="353"/>
+      <c r="T3" s="353"/>
+      <c r="U3" s="353"/>
+      <c r="V3" s="353"/>
+      <c r="W3" s="353"/>
+      <c r="X3" s="353"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337"/>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
-      <c r="V4" s="337"/>
-      <c r="W4" s="337"/>
-      <c r="X4" s="337"/>
+      <c r="O4" s="353"/>
+      <c r="P4" s="353"/>
+      <c r="Q4" s="353"/>
+      <c r="R4" s="353"/>
+      <c r="S4" s="353"/>
+      <c r="T4" s="353"/>
+      <c r="U4" s="353"/>
+      <c r="V4" s="353"/>
+      <c r="W4" s="353"/>
+      <c r="X4" s="353"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33658,16 +33657,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="338" t="s">
+      <c r="J8" s="344" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="338"/>
-      <c r="N8" s="338"/>
-      <c r="O8" s="338"/>
-      <c r="P8" s="338"/>
-      <c r="Q8" s="338"/>
+      <c r="K8" s="344"/>
+      <c r="L8" s="344"/>
+      <c r="M8" s="344"/>
+      <c r="N8" s="344"/>
+      <c r="O8" s="344"/>
+      <c r="P8" s="344"/>
+      <c r="Q8" s="344"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33678,133 +33677,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="339" t="s">
+      <c r="X8" s="345" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="340"/>
-      <c r="Z8" s="340"/>
-      <c r="AA8" s="340"/>
-      <c r="AB8" s="341"/>
-      <c r="AC8" s="342" t="s">
+      <c r="Y8" s="346"/>
+      <c r="Z8" s="346"/>
+      <c r="AA8" s="346"/>
+      <c r="AB8" s="347"/>
+      <c r="AC8" s="354" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="344" t="s">
+      <c r="AF8" s="356" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="345"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="345"/>
-      <c r="AJ8" s="345"/>
-      <c r="AK8" s="345"/>
-      <c r="AL8" s="353" t="s">
+      <c r="AG8" s="357"/>
+      <c r="AH8" s="357"/>
+      <c r="AI8" s="357"/>
+      <c r="AJ8" s="357"/>
+      <c r="AK8" s="357"/>
+      <c r="AL8" s="348" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="353"/>
-      <c r="AN8" s="353"/>
-      <c r="AO8" s="353"/>
-      <c r="AP8" s="353"/>
-      <c r="AQ8" s="353"/>
-      <c r="AR8" s="353"/>
-      <c r="AS8" s="353"/>
-      <c r="AT8" s="350" t="s">
+      <c r="AM8" s="348"/>
+      <c r="AN8" s="348"/>
+      <c r="AO8" s="348"/>
+      <c r="AP8" s="348"/>
+      <c r="AQ8" s="348"/>
+      <c r="AR8" s="348"/>
+      <c r="AS8" s="348"/>
+      <c r="AT8" s="341" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="350"/>
-      <c r="AV8" s="350"/>
-      <c r="AW8" s="350"/>
-      <c r="AX8" s="350"/>
-      <c r="AY8" s="350"/>
-      <c r="AZ8" s="350"/>
-      <c r="BA8" s="350"/>
-      <c r="BB8" s="350"/>
-      <c r="BC8" s="351" t="s">
+      <c r="AU8" s="341"/>
+      <c r="AV8" s="341"/>
+      <c r="AW8" s="341"/>
+      <c r="AX8" s="341"/>
+      <c r="AY8" s="341"/>
+      <c r="AZ8" s="341"/>
+      <c r="BA8" s="341"/>
+      <c r="BB8" s="341"/>
+      <c r="BC8" s="342" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="351"/>
-      <c r="BE8" s="351"/>
-      <c r="BF8" s="351"/>
-      <c r="BG8" s="351"/>
-      <c r="BH8" s="351"/>
+      <c r="BD8" s="342"/>
+      <c r="BE8" s="342"/>
+      <c r="BF8" s="342"/>
+      <c r="BG8" s="342"/>
+      <c r="BH8" s="342"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="352" t="s">
+      <c r="C9" s="343" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="352"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
-      <c r="G9" s="352"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="338" t="s">
+      <c r="D9" s="343"/>
+      <c r="E9" s="343"/>
+      <c r="F9" s="343"/>
+      <c r="G9" s="343"/>
+      <c r="H9" s="343"/>
+      <c r="I9" s="343"/>
+      <c r="J9" s="344" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="338"/>
-      <c r="N9" s="338"/>
-      <c r="O9" s="338"/>
-      <c r="P9" s="338"/>
-      <c r="Q9" s="338"/>
+      <c r="K9" s="344"/>
+      <c r="L9" s="344"/>
+      <c r="M9" s="344"/>
+      <c r="N9" s="344"/>
+      <c r="O9" s="344"/>
+      <c r="P9" s="344"/>
+      <c r="Q9" s="344"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="339" t="s">
+      <c r="V9" s="345" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="340"/>
-      <c r="X9" s="340"/>
-      <c r="Y9" s="340"/>
-      <c r="Z9" s="340"/>
-      <c r="AA9" s="340"/>
-      <c r="AB9" s="341"/>
-      <c r="AC9" s="343"/>
-      <c r="AD9" s="355" t="s">
+      <c r="W9" s="346"/>
+      <c r="X9" s="346"/>
+      <c r="Y9" s="346"/>
+      <c r="Z9" s="346"/>
+      <c r="AA9" s="346"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="355"/>
+      <c r="AD9" s="350" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="356"/>
-      <c r="AF9" s="356"/>
-      <c r="AG9" s="356"/>
-      <c r="AH9" s="356"/>
-      <c r="AI9" s="356"/>
-      <c r="AJ9" s="356"/>
-      <c r="AK9" s="357"/>
-      <c r="AL9" s="354" t="s">
+      <c r="AE9" s="351"/>
+      <c r="AF9" s="351"/>
+      <c r="AG9" s="351"/>
+      <c r="AH9" s="351"/>
+      <c r="AI9" s="351"/>
+      <c r="AJ9" s="351"/>
+      <c r="AK9" s="352"/>
+      <c r="AL9" s="349" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="354"/>
-      <c r="AN9" s="354"/>
-      <c r="AO9" s="354"/>
-      <c r="AP9" s="354"/>
-      <c r="AQ9" s="354"/>
-      <c r="AR9" s="354"/>
-      <c r="AS9" s="354"/>
-      <c r="AT9" s="346" t="s">
+      <c r="AM9" s="349"/>
+      <c r="AN9" s="349"/>
+      <c r="AO9" s="349"/>
+      <c r="AP9" s="349"/>
+      <c r="AQ9" s="349"/>
+      <c r="AR9" s="349"/>
+      <c r="AS9" s="349"/>
+      <c r="AT9" s="337" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="346"/>
-      <c r="AV9" s="346"/>
-      <c r="AW9" s="346"/>
-      <c r="AX9" s="346"/>
-      <c r="AY9" s="347"/>
-      <c r="AZ9" s="347"/>
-      <c r="BA9" s="347"/>
-      <c r="BB9" s="347"/>
-      <c r="BC9" s="348" t="s">
+      <c r="AU9" s="337"/>
+      <c r="AV9" s="337"/>
+      <c r="AW9" s="337"/>
+      <c r="AX9" s="337"/>
+      <c r="AY9" s="338"/>
+      <c r="AZ9" s="338"/>
+      <c r="BA9" s="338"/>
+      <c r="BB9" s="338"/>
+      <c r="BC9" s="339" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="349"/>
-      <c r="BE9" s="349"/>
-      <c r="BF9" s="349"/>
-      <c r="BG9" s="349"/>
-      <c r="BH9" s="349"/>
+      <c r="BD9" s="340"/>
+      <c r="BE9" s="340"/>
+      <c r="BF9" s="340"/>
+      <c r="BG9" s="340"/>
+      <c r="BH9" s="340"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -34012,7 +34011,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -34476,7 +34475,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -34615,7 +34614,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:65" customFormat="1" ht="121.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:65" customFormat="1" ht="121.8" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -34759,7 +34758,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="16" spans="3:65" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:65" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -34909,7 +34908,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -35063,7 +35062,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -35217,7 +35216,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -35365,7 +35364,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -35513,7 +35512,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -35661,7 +35660,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -35809,7 +35808,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -35963,7 +35962,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -36108,7 +36107,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -36256,7 +36255,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -36397,7 +36396,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -36545,7 +36544,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36852,7 +36851,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -37322,7 +37321,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -37470,7 +37469,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -37625,7 +37624,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -37773,7 +37772,7 @@
       </c>
       <c r="BL35" s="12"/>
     </row>
-    <row r="36" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C36" s="24" t="s">
         <v>7</v>
       </c>
@@ -37931,7 +37930,7 @@
       </c>
       <c r="BL36" s="12"/>
     </row>
-    <row r="37" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C37" s="24" t="s">
         <v>7</v>
       </c>
@@ -38218,7 +38217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -38523,7 +38522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -38682,7 +38681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -38981,7 +38980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -39138,7 +39137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -39592,7 +39591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -39749,7 +39748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -39899,7 +39898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -40048,7 +40047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C51" s="24" t="s">
         <v>7</v>
       </c>
@@ -40201,7 +40200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -40350,7 +40349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -40499,7 +40498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -40643,7 +40642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -40796,7 +40795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -40944,7 +40943,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -41101,7 +41100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -41254,7 +41253,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -41407,7 +41406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -41560,7 +41559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -41709,7 +41708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -41866,7 +41865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -42019,7 +42018,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -42175,7 +42174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -42332,7 +42331,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -42486,7 +42485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -42641,7 +42640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -42796,7 +42795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -42957,7 +42956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -43134,14 +43133,12 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="C10:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
-    <filterColumn colId="60">
-      <filters>
-        <filter val="2026-2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43152,11 +43149,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43393,33 +43385,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="337" t="s">
+      <c r="O3" s="353" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="337"/>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
-      <c r="V3" s="337"/>
-      <c r="W3" s="337"/>
-      <c r="X3" s="337"/>
+      <c r="P3" s="353"/>
+      <c r="Q3" s="353"/>
+      <c r="R3" s="353"/>
+      <c r="S3" s="353"/>
+      <c r="T3" s="353"/>
+      <c r="U3" s="353"/>
+      <c r="V3" s="353"/>
+      <c r="W3" s="353"/>
+      <c r="X3" s="353"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337"/>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
-      <c r="V4" s="337"/>
-      <c r="W4" s="337"/>
-      <c r="X4" s="337"/>
+      <c r="O4" s="353"/>
+      <c r="P4" s="353"/>
+      <c r="Q4" s="353"/>
+      <c r="R4" s="353"/>
+      <c r="S4" s="353"/>
+      <c r="T4" s="353"/>
+      <c r="U4" s="353"/>
+      <c r="V4" s="353"/>
+      <c r="W4" s="353"/>
+      <c r="X4" s="353"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43448,16 +43440,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="338" t="s">
+      <c r="J8" s="344" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="338"/>
-      <c r="N8" s="338"/>
-      <c r="O8" s="338"/>
-      <c r="P8" s="338"/>
-      <c r="Q8" s="338"/>
+      <c r="K8" s="344"/>
+      <c r="L8" s="344"/>
+      <c r="M8" s="344"/>
+      <c r="N8" s="344"/>
+      <c r="O8" s="344"/>
+      <c r="P8" s="344"/>
+      <c r="Q8" s="344"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43468,107 +43460,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="339" t="s">
+      <c r="X8" s="345" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="340"/>
-      <c r="Z8" s="340"/>
-      <c r="AA8" s="341"/>
-      <c r="AB8" s="342" t="s">
+      <c r="Y8" s="346"/>
+      <c r="Z8" s="346"/>
+      <c r="AA8" s="347"/>
+      <c r="AB8" s="354" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="344" t="s">
+      <c r="AC8" s="356" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="345"/>
-      <c r="AE8" s="345"/>
-      <c r="AF8" s="345"/>
-      <c r="AG8" s="345"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="353" t="s">
+      <c r="AD8" s="357"/>
+      <c r="AE8" s="357"/>
+      <c r="AF8" s="357"/>
+      <c r="AG8" s="357"/>
+      <c r="AH8" s="357"/>
+      <c r="AI8" s="348" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="353"/>
-      <c r="AK8" s="353"/>
-      <c r="AL8" s="353"/>
-      <c r="AM8" s="353"/>
-      <c r="AN8" s="353"/>
-      <c r="AO8" s="350" t="s">
+      <c r="AJ8" s="348"/>
+      <c r="AK8" s="348"/>
+      <c r="AL8" s="348"/>
+      <c r="AM8" s="348"/>
+      <c r="AN8" s="348"/>
+      <c r="AO8" s="341" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="350"/>
-      <c r="AQ8" s="350"/>
-      <c r="AR8" s="350"/>
-      <c r="AS8" s="351" t="s">
+      <c r="AP8" s="341"/>
+      <c r="AQ8" s="341"/>
+      <c r="AR8" s="341"/>
+      <c r="AS8" s="342" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="351"/>
-      <c r="AU8" s="351"/>
+      <c r="AT8" s="342"/>
+      <c r="AU8" s="342"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="352" t="s">
+      <c r="C9" s="343" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="352"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
-      <c r="G9" s="352"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="338" t="s">
+      <c r="D9" s="343"/>
+      <c r="E9" s="343"/>
+      <c r="F9" s="343"/>
+      <c r="G9" s="343"/>
+      <c r="H9" s="343"/>
+      <c r="I9" s="343"/>
+      <c r="J9" s="344" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="338"/>
-      <c r="N9" s="338"/>
-      <c r="O9" s="338"/>
-      <c r="P9" s="338"/>
-      <c r="Q9" s="338"/>
+      <c r="K9" s="344"/>
+      <c r="L9" s="344"/>
+      <c r="M9" s="344"/>
+      <c r="N9" s="344"/>
+      <c r="O9" s="344"/>
+      <c r="P9" s="344"/>
+      <c r="Q9" s="344"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="339" t="s">
+      <c r="V9" s="345" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="340"/>
-      <c r="X9" s="340"/>
-      <c r="Y9" s="340"/>
-      <c r="Z9" s="340"/>
-      <c r="AA9" s="341"/>
-      <c r="AB9" s="343"/>
-      <c r="AC9" s="369" t="s">
+      <c r="W9" s="346"/>
+      <c r="X9" s="346"/>
+      <c r="Y9" s="346"/>
+      <c r="Z9" s="346"/>
+      <c r="AA9" s="347"/>
+      <c r="AB9" s="355"/>
+      <c r="AC9" s="366" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="369"/>
-      <c r="AE9" s="369"/>
-      <c r="AF9" s="369"/>
-      <c r="AG9" s="369"/>
-      <c r="AH9" s="369"/>
-      <c r="AI9" s="354" t="s">
+      <c r="AD9" s="366"/>
+      <c r="AE9" s="366"/>
+      <c r="AF9" s="366"/>
+      <c r="AG9" s="366"/>
+      <c r="AH9" s="366"/>
+      <c r="AI9" s="349" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="354"/>
-      <c r="AK9" s="354"/>
-      <c r="AL9" s="354"/>
-      <c r="AM9" s="354"/>
-      <c r="AN9" s="354"/>
-      <c r="AO9" s="346" t="s">
+      <c r="AJ9" s="349"/>
+      <c r="AK9" s="349"/>
+      <c r="AL9" s="349"/>
+      <c r="AM9" s="349"/>
+      <c r="AN9" s="349"/>
+      <c r="AO9" s="337" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="346"/>
-      <c r="AQ9" s="346"/>
-      <c r="AR9" s="346"/>
-      <c r="AS9" s="349" t="s">
+      <c r="AP9" s="337"/>
+      <c r="AQ9" s="337"/>
+      <c r="AR9" s="337"/>
+      <c r="AS9" s="340" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="349"/>
-      <c r="AU9" s="349"/>
+      <c r="AT9" s="340"/>
+      <c r="AU9" s="340"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49715,11 +49707,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49730,6 +49717,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50079,12 +50071,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -50222,6 +50208,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
@@ -50231,15 +50223,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50255,4 +50238,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{A5F284E1-7F0C-4711-B144-6978B10ED4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{792173EF-C6B5-4931-94DA-726F892E0572}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A5F284E1-7F0C-4711-B144-6978B10ED4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55B297ED-414A-4844-A21A-651E9B65A9EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -499,7 +499,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4421" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="421">
   <si>
     <t>RC</t>
   </si>
@@ -2967,7 +2967,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="374">
+  <cellXfs count="375">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3805,6 +3805,33 @@
     <xf numFmtId="0" fontId="34" fillId="35" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3826,18 +3853,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3852,21 +3867,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3886,6 +3886,15 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3893,15 +3902,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3915,6 +3915,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15964,43 +15967,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="353" t="s">
+      <c r="O3" s="337" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="353"/>
-      <c r="Q3" s="353"/>
-      <c r="R3" s="353"/>
-      <c r="S3" s="353"/>
-      <c r="T3" s="353"/>
-      <c r="U3" s="353"/>
-      <c r="V3" s="353"/>
-      <c r="W3" s="353"/>
-      <c r="X3" s="353"/>
-      <c r="Y3" s="353"/>
-      <c r="Z3" s="353"/>
-      <c r="AA3" s="353"/>
-      <c r="AB3" s="353"/>
-      <c r="AC3" s="353"/>
+      <c r="P3" s="337"/>
+      <c r="Q3" s="337"/>
+      <c r="R3" s="337"/>
+      <c r="S3" s="337"/>
+      <c r="T3" s="337"/>
+      <c r="U3" s="337"/>
+      <c r="V3" s="337"/>
+      <c r="W3" s="337"/>
+      <c r="X3" s="337"/>
+      <c r="Y3" s="337"/>
+      <c r="Z3" s="337"/>
+      <c r="AA3" s="337"/>
+      <c r="AB3" s="337"/>
+      <c r="AC3" s="337"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="353"/>
-      <c r="P4" s="353"/>
-      <c r="Q4" s="353"/>
-      <c r="R4" s="353"/>
-      <c r="S4" s="353"/>
-      <c r="T4" s="353"/>
-      <c r="U4" s="353"/>
-      <c r="V4" s="353"/>
-      <c r="W4" s="353"/>
-      <c r="X4" s="353"/>
-      <c r="Y4" s="353"/>
-      <c r="Z4" s="353"/>
-      <c r="AA4" s="353"/>
-      <c r="AB4" s="353"/>
-      <c r="AC4" s="353"/>
+      <c r="O4" s="337"/>
+      <c r="P4" s="337"/>
+      <c r="Q4" s="337"/>
+      <c r="R4" s="337"/>
+      <c r="S4" s="337"/>
+      <c r="T4" s="337"/>
+      <c r="U4" s="337"/>
+      <c r="V4" s="337"/>
+      <c r="W4" s="337"/>
+      <c r="X4" s="337"/>
+      <c r="Y4" s="337"/>
+      <c r="Z4" s="337"/>
+      <c r="AA4" s="337"/>
+      <c r="AB4" s="337"/>
+      <c r="AC4" s="337"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16029,17 +16032,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="344" t="s">
+      <c r="J8" s="338" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="344"/>
-      <c r="L8" s="344"/>
-      <c r="M8" s="344"/>
-      <c r="N8" s="344"/>
-      <c r="O8" s="344"/>
-      <c r="P8" s="344"/>
-      <c r="Q8" s="344"/>
-      <c r="R8" s="344"/>
+      <c r="K8" s="338"/>
+      <c r="L8" s="338"/>
+      <c r="M8" s="338"/>
+      <c r="N8" s="338"/>
+      <c r="O8" s="338"/>
+      <c r="P8" s="338"/>
+      <c r="Q8" s="338"/>
+      <c r="R8" s="338"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16054,168 +16057,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="345" t="s">
+      <c r="AC8" s="339" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="346"/>
-      <c r="AE8" s="346"/>
-      <c r="AF8" s="346"/>
-      <c r="AG8" s="346"/>
-      <c r="AH8" s="347"/>
-      <c r="AI8" s="354" t="s">
+      <c r="AD8" s="340"/>
+      <c r="AE8" s="340"/>
+      <c r="AF8" s="340"/>
+      <c r="AG8" s="340"/>
+      <c r="AH8" s="341"/>
+      <c r="AI8" s="342" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="356" t="s">
+      <c r="AL8" s="344" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="357"/>
-      <c r="AN8" s="357"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="357"/>
-      <c r="AQ8" s="357"/>
-      <c r="AR8" s="348" t="s">
+      <c r="AM8" s="345"/>
+      <c r="AN8" s="345"/>
+      <c r="AO8" s="345"/>
+      <c r="AP8" s="345"/>
+      <c r="AQ8" s="345"/>
+      <c r="AR8" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="348"/>
-      <c r="AT8" s="348"/>
-      <c r="AU8" s="348"/>
-      <c r="AV8" s="348"/>
-      <c r="AW8" s="348"/>
-      <c r="AX8" s="348"/>
-      <c r="AY8" s="348"/>
-      <c r="AZ8" s="348"/>
+      <c r="AS8" s="353"/>
+      <c r="AT8" s="353"/>
+      <c r="AU8" s="353"/>
+      <c r="AV8" s="353"/>
+      <c r="AW8" s="353"/>
+      <c r="AX8" s="353"/>
+      <c r="AY8" s="353"/>
+      <c r="AZ8" s="353"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="341" t="s">
+      <c r="BD8" s="350" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="341"/>
-      <c r="BF8" s="341"/>
-      <c r="BG8" s="341"/>
-      <c r="BH8" s="341"/>
-      <c r="BI8" s="341"/>
-      <c r="BJ8" s="341"/>
-      <c r="BK8" s="341"/>
-      <c r="BL8" s="341"/>
-      <c r="BM8" s="341"/>
-      <c r="BN8" s="341"/>
-      <c r="BO8" s="341"/>
-      <c r="BP8" s="341"/>
-      <c r="BQ8" s="342" t="s">
+      <c r="BE8" s="350"/>
+      <c r="BF8" s="350"/>
+      <c r="BG8" s="350"/>
+      <c r="BH8" s="350"/>
+      <c r="BI8" s="350"/>
+      <c r="BJ8" s="350"/>
+      <c r="BK8" s="350"/>
+      <c r="BL8" s="350"/>
+      <c r="BM8" s="350"/>
+      <c r="BN8" s="350"/>
+      <c r="BO8" s="350"/>
+      <c r="BP8" s="350"/>
+      <c r="BQ8" s="351" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="342"/>
-      <c r="BS8" s="342"/>
+      <c r="BR8" s="351"/>
+      <c r="BS8" s="351"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="343" t="s">
+      <c r="C9" s="352" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="343"/>
-      <c r="E9" s="343"/>
-      <c r="F9" s="343"/>
-      <c r="G9" s="343"/>
-      <c r="H9" s="343"/>
-      <c r="I9" s="343"/>
-      <c r="J9" s="344" t="s">
+      <c r="D9" s="352"/>
+      <c r="E9" s="352"/>
+      <c r="F9" s="352"/>
+      <c r="G9" s="352"/>
+      <c r="H9" s="352"/>
+      <c r="I9" s="352"/>
+      <c r="J9" s="338" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="344"/>
-      <c r="L9" s="344"/>
-      <c r="M9" s="344"/>
-      <c r="N9" s="344"/>
-      <c r="O9" s="344"/>
-      <c r="P9" s="344"/>
-      <c r="Q9" s="344"/>
-      <c r="R9" s="344"/>
-      <c r="S9" s="367" t="s">
+      <c r="K9" s="338"/>
+      <c r="L9" s="338"/>
+      <c r="M9" s="338"/>
+      <c r="N9" s="338"/>
+      <c r="O9" s="338"/>
+      <c r="P9" s="338"/>
+      <c r="Q9" s="338"/>
+      <c r="R9" s="338"/>
+      <c r="S9" s="366" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="364" t="s">
+      <c r="T9" s="367" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="364" t="s">
+      <c r="U9" s="367" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="364" t="s">
+      <c r="V9" s="367" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="345" t="s">
+      <c r="AA9" s="339" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="346"/>
-      <c r="AC9" s="346"/>
-      <c r="AD9" s="346"/>
-      <c r="AE9" s="346"/>
-      <c r="AF9" s="346"/>
-      <c r="AG9" s="346"/>
-      <c r="AH9" s="347"/>
-      <c r="AI9" s="355"/>
+      <c r="AB9" s="340"/>
+      <c r="AC9" s="340"/>
+      <c r="AD9" s="340"/>
+      <c r="AE9" s="340"/>
+      <c r="AF9" s="340"/>
+      <c r="AG9" s="340"/>
+      <c r="AH9" s="341"/>
+      <c r="AI9" s="343"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="366" t="s">
+      <c r="AL9" s="369" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="366"/>
-      <c r="AN9" s="366"/>
-      <c r="AO9" s="366"/>
-      <c r="AP9" s="366"/>
-      <c r="AQ9" s="366"/>
-      <c r="AR9" s="349" t="s">
+      <c r="AM9" s="369"/>
+      <c r="AN9" s="369"/>
+      <c r="AO9" s="369"/>
+      <c r="AP9" s="369"/>
+      <c r="AQ9" s="369"/>
+      <c r="AR9" s="354" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="349"/>
-      <c r="AT9" s="349"/>
-      <c r="AU9" s="349"/>
-      <c r="AV9" s="349"/>
-      <c r="AW9" s="349"/>
-      <c r="AX9" s="349"/>
-      <c r="AY9" s="349"/>
-      <c r="AZ9" s="349"/>
+      <c r="AS9" s="354"/>
+      <c r="AT9" s="354"/>
+      <c r="AU9" s="354"/>
+      <c r="AV9" s="354"/>
+      <c r="AW9" s="354"/>
+      <c r="AX9" s="354"/>
+      <c r="AY9" s="354"/>
+      <c r="AZ9" s="354"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="337" t="s">
+      <c r="BD9" s="346" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="337"/>
-      <c r="BF9" s="337"/>
-      <c r="BG9" s="337"/>
-      <c r="BH9" s="337"/>
-      <c r="BI9" s="337"/>
-      <c r="BJ9" s="337"/>
-      <c r="BK9" s="337"/>
-      <c r="BL9" s="337"/>
-      <c r="BM9" s="337"/>
-      <c r="BN9" s="337"/>
-      <c r="BO9" s="337"/>
-      <c r="BP9" s="337"/>
-      <c r="BQ9" s="340" t="s">
+      <c r="BE9" s="346"/>
+      <c r="BF9" s="346"/>
+      <c r="BG9" s="346"/>
+      <c r="BH9" s="346"/>
+      <c r="BI9" s="346"/>
+      <c r="BJ9" s="346"/>
+      <c r="BK9" s="346"/>
+      <c r="BL9" s="346"/>
+      <c r="BM9" s="346"/>
+      <c r="BN9" s="346"/>
+      <c r="BO9" s="346"/>
+      <c r="BP9" s="346"/>
+      <c r="BQ9" s="349" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="340"/>
-      <c r="BS9" s="340"/>
-      <c r="BT9" s="368" t="s">
+      <c r="BR9" s="349"/>
+      <c r="BS9" s="349"/>
+      <c r="BT9" s="364" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="368" t="s">
+      <c r="BU9" s="364" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="368" t="s">
+      <c r="BV9" s="364" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="369" t="s">
+      <c r="BW9" s="365" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16271,10 +16274,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="367"/>
-      <c r="T10" s="365"/>
-      <c r="U10" s="365"/>
-      <c r="V10" s="365"/>
+      <c r="S10" s="366"/>
+      <c r="T10" s="368"/>
+      <c r="U10" s="368"/>
+      <c r="V10" s="368"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16400,10 +16403,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="368"/>
-      <c r="BU10" s="368"/>
-      <c r="BV10" s="368"/>
-      <c r="BW10" s="369"/>
+      <c r="BT10" s="364"/>
+      <c r="BU10" s="364"/>
+      <c r="BV10" s="364"/>
+      <c r="BW10" s="365"/>
     </row>
     <row r="11" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -19721,9 +19724,9 @@
         <f t="array" ref="AZ22">IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AZ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
         <v/>
       </c>
-      <c r="BA22" s="11" t="str" cm="1">
+      <c r="BA22" s="11" cm="1">
         <f t="array" ref="BA22">IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BA$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>6, 25%</v>
+        <v>6.25E-2</v>
       </c>
       <c r="BB22" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,Borrador!$AZ$11:$AZ$70,""),"")</f>
@@ -33443,6 +33446,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33451,21 +33469,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33597,34 +33600,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="353" t="s">
+      <c r="O3" s="337" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="353"/>
-      <c r="Q3" s="353"/>
-      <c r="R3" s="353"/>
-      <c r="S3" s="353"/>
-      <c r="T3" s="353"/>
-      <c r="U3" s="353"/>
-      <c r="V3" s="353"/>
-      <c r="W3" s="353"/>
-      <c r="X3" s="353"/>
+      <c r="P3" s="337"/>
+      <c r="Q3" s="337"/>
+      <c r="R3" s="337"/>
+      <c r="S3" s="337"/>
+      <c r="T3" s="337"/>
+      <c r="U3" s="337"/>
+      <c r="V3" s="337"/>
+      <c r="W3" s="337"/>
+      <c r="X3" s="337"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="353"/>
-      <c r="P4" s="353"/>
-      <c r="Q4" s="353"/>
-      <c r="R4" s="353"/>
-      <c r="S4" s="353"/>
-      <c r="T4" s="353"/>
-      <c r="U4" s="353"/>
-      <c r="V4" s="353"/>
-      <c r="W4" s="353"/>
-      <c r="X4" s="353"/>
+      <c r="O4" s="337"/>
+      <c r="P4" s="337"/>
+      <c r="Q4" s="337"/>
+      <c r="R4" s="337"/>
+      <c r="S4" s="337"/>
+      <c r="T4" s="337"/>
+      <c r="U4" s="337"/>
+      <c r="V4" s="337"/>
+      <c r="W4" s="337"/>
+      <c r="X4" s="337"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33657,16 +33660,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="344" t="s">
+      <c r="J8" s="338" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="344"/>
-      <c r="L8" s="344"/>
-      <c r="M8" s="344"/>
-      <c r="N8" s="344"/>
-      <c r="O8" s="344"/>
-      <c r="P8" s="344"/>
-      <c r="Q8" s="344"/>
+      <c r="K8" s="338"/>
+      <c r="L8" s="338"/>
+      <c r="M8" s="338"/>
+      <c r="N8" s="338"/>
+      <c r="O8" s="338"/>
+      <c r="P8" s="338"/>
+      <c r="Q8" s="338"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33677,133 +33680,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="345" t="s">
+      <c r="X8" s="339" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="346"/>
-      <c r="Z8" s="346"/>
-      <c r="AA8" s="346"/>
-      <c r="AB8" s="347"/>
-      <c r="AC8" s="354" t="s">
+      <c r="Y8" s="340"/>
+      <c r="Z8" s="340"/>
+      <c r="AA8" s="340"/>
+      <c r="AB8" s="341"/>
+      <c r="AC8" s="342" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="356" t="s">
+      <c r="AF8" s="344" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="357"/>
-      <c r="AH8" s="357"/>
-      <c r="AI8" s="357"/>
-      <c r="AJ8" s="357"/>
-      <c r="AK8" s="357"/>
-      <c r="AL8" s="348" t="s">
+      <c r="AG8" s="345"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="345"/>
+      <c r="AJ8" s="345"/>
+      <c r="AK8" s="345"/>
+      <c r="AL8" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="348"/>
-      <c r="AN8" s="348"/>
-      <c r="AO8" s="348"/>
-      <c r="AP8" s="348"/>
-      <c r="AQ8" s="348"/>
-      <c r="AR8" s="348"/>
-      <c r="AS8" s="348"/>
-      <c r="AT8" s="341" t="s">
+      <c r="AM8" s="353"/>
+      <c r="AN8" s="353"/>
+      <c r="AO8" s="353"/>
+      <c r="AP8" s="353"/>
+      <c r="AQ8" s="353"/>
+      <c r="AR8" s="353"/>
+      <c r="AS8" s="353"/>
+      <c r="AT8" s="350" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="341"/>
-      <c r="AV8" s="341"/>
-      <c r="AW8" s="341"/>
-      <c r="AX8" s="341"/>
-      <c r="AY8" s="341"/>
-      <c r="AZ8" s="341"/>
-      <c r="BA8" s="341"/>
-      <c r="BB8" s="341"/>
-      <c r="BC8" s="342" t="s">
+      <c r="AU8" s="350"/>
+      <c r="AV8" s="350"/>
+      <c r="AW8" s="350"/>
+      <c r="AX8" s="350"/>
+      <c r="AY8" s="350"/>
+      <c r="AZ8" s="350"/>
+      <c r="BA8" s="350"/>
+      <c r="BB8" s="350"/>
+      <c r="BC8" s="351" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="342"/>
-      <c r="BE8" s="342"/>
-      <c r="BF8" s="342"/>
-      <c r="BG8" s="342"/>
-      <c r="BH8" s="342"/>
+      <c r="BD8" s="351"/>
+      <c r="BE8" s="351"/>
+      <c r="BF8" s="351"/>
+      <c r="BG8" s="351"/>
+      <c r="BH8" s="351"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="343" t="s">
+      <c r="C9" s="352" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="343"/>
-      <c r="E9" s="343"/>
-      <c r="F9" s="343"/>
-      <c r="G9" s="343"/>
-      <c r="H9" s="343"/>
-      <c r="I9" s="343"/>
-      <c r="J9" s="344" t="s">
+      <c r="D9" s="352"/>
+      <c r="E9" s="352"/>
+      <c r="F9" s="352"/>
+      <c r="G9" s="352"/>
+      <c r="H9" s="352"/>
+      <c r="I9" s="352"/>
+      <c r="J9" s="338" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="344"/>
-      <c r="L9" s="344"/>
-      <c r="M9" s="344"/>
-      <c r="N9" s="344"/>
-      <c r="O9" s="344"/>
-      <c r="P9" s="344"/>
-      <c r="Q9" s="344"/>
+      <c r="K9" s="338"/>
+      <c r="L9" s="338"/>
+      <c r="M9" s="338"/>
+      <c r="N9" s="338"/>
+      <c r="O9" s="338"/>
+      <c r="P9" s="338"/>
+      <c r="Q9" s="338"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="345" t="s">
+      <c r="V9" s="339" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="346"/>
-      <c r="X9" s="346"/>
-      <c r="Y9" s="346"/>
-      <c r="Z9" s="346"/>
-      <c r="AA9" s="346"/>
-      <c r="AB9" s="347"/>
-      <c r="AC9" s="355"/>
-      <c r="AD9" s="350" t="s">
+      <c r="W9" s="340"/>
+      <c r="X9" s="340"/>
+      <c r="Y9" s="340"/>
+      <c r="Z9" s="340"/>
+      <c r="AA9" s="340"/>
+      <c r="AB9" s="341"/>
+      <c r="AC9" s="343"/>
+      <c r="AD9" s="355" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="351"/>
-      <c r="AF9" s="351"/>
-      <c r="AG9" s="351"/>
-      <c r="AH9" s="351"/>
-      <c r="AI9" s="351"/>
-      <c r="AJ9" s="351"/>
-      <c r="AK9" s="352"/>
-      <c r="AL9" s="349" t="s">
+      <c r="AE9" s="356"/>
+      <c r="AF9" s="356"/>
+      <c r="AG9" s="356"/>
+      <c r="AH9" s="356"/>
+      <c r="AI9" s="356"/>
+      <c r="AJ9" s="356"/>
+      <c r="AK9" s="357"/>
+      <c r="AL9" s="354" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="349"/>
-      <c r="AN9" s="349"/>
-      <c r="AO9" s="349"/>
-      <c r="AP9" s="349"/>
-      <c r="AQ9" s="349"/>
-      <c r="AR9" s="349"/>
-      <c r="AS9" s="349"/>
-      <c r="AT9" s="337" t="s">
+      <c r="AM9" s="354"/>
+      <c r="AN9" s="354"/>
+      <c r="AO9" s="354"/>
+      <c r="AP9" s="354"/>
+      <c r="AQ9" s="354"/>
+      <c r="AR9" s="354"/>
+      <c r="AS9" s="354"/>
+      <c r="AT9" s="346" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="337"/>
-      <c r="AV9" s="337"/>
-      <c r="AW9" s="337"/>
-      <c r="AX9" s="337"/>
-      <c r="AY9" s="338"/>
-      <c r="AZ9" s="338"/>
-      <c r="BA9" s="338"/>
-      <c r="BB9" s="338"/>
-      <c r="BC9" s="339" t="s">
+      <c r="AU9" s="346"/>
+      <c r="AV9" s="346"/>
+      <c r="AW9" s="346"/>
+      <c r="AX9" s="346"/>
+      <c r="AY9" s="347"/>
+      <c r="AZ9" s="347"/>
+      <c r="BA9" s="347"/>
+      <c r="BB9" s="347"/>
+      <c r="BC9" s="348" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="340"/>
-      <c r="BE9" s="340"/>
-      <c r="BF9" s="340"/>
-      <c r="BG9" s="340"/>
-      <c r="BH9" s="340"/>
+      <c r="BD9" s="349"/>
+      <c r="BE9" s="349"/>
+      <c r="BF9" s="349"/>
+      <c r="BG9" s="349"/>
+      <c r="BH9" s="349"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -35901,8 +35904,8 @@
       </c>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11"/>
-      <c r="AK23" s="72" t="s">
-        <v>308</v>
+      <c r="AK23" s="374">
+        <v>6.25E-2</v>
       </c>
       <c r="AL23" s="12" t="s">
         <v>194</v>
@@ -43134,11 +43137,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43149,6 +43147,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43385,33 +43388,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="353" t="s">
+      <c r="O3" s="337" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="353"/>
-      <c r="Q3" s="353"/>
-      <c r="R3" s="353"/>
-      <c r="S3" s="353"/>
-      <c r="T3" s="353"/>
-      <c r="U3" s="353"/>
-      <c r="V3" s="353"/>
-      <c r="W3" s="353"/>
-      <c r="X3" s="353"/>
+      <c r="P3" s="337"/>
+      <c r="Q3" s="337"/>
+      <c r="R3" s="337"/>
+      <c r="S3" s="337"/>
+      <c r="T3" s="337"/>
+      <c r="U3" s="337"/>
+      <c r="V3" s="337"/>
+      <c r="W3" s="337"/>
+      <c r="X3" s="337"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="353"/>
-      <c r="P4" s="353"/>
-      <c r="Q4" s="353"/>
-      <c r="R4" s="353"/>
-      <c r="S4" s="353"/>
-      <c r="T4" s="353"/>
-      <c r="U4" s="353"/>
-      <c r="V4" s="353"/>
-      <c r="W4" s="353"/>
-      <c r="X4" s="353"/>
+      <c r="O4" s="337"/>
+      <c r="P4" s="337"/>
+      <c r="Q4" s="337"/>
+      <c r="R4" s="337"/>
+      <c r="S4" s="337"/>
+      <c r="T4" s="337"/>
+      <c r="U4" s="337"/>
+      <c r="V4" s="337"/>
+      <c r="W4" s="337"/>
+      <c r="X4" s="337"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43440,16 +43443,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="344" t="s">
+      <c r="J8" s="338" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="344"/>
-      <c r="L8" s="344"/>
-      <c r="M8" s="344"/>
-      <c r="N8" s="344"/>
-      <c r="O8" s="344"/>
-      <c r="P8" s="344"/>
-      <c r="Q8" s="344"/>
+      <c r="K8" s="338"/>
+      <c r="L8" s="338"/>
+      <c r="M8" s="338"/>
+      <c r="N8" s="338"/>
+      <c r="O8" s="338"/>
+      <c r="P8" s="338"/>
+      <c r="Q8" s="338"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43460,107 +43463,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="345" t="s">
+      <c r="X8" s="339" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="346"/>
-      <c r="Z8" s="346"/>
-      <c r="AA8" s="347"/>
-      <c r="AB8" s="354" t="s">
+      <c r="Y8" s="340"/>
+      <c r="Z8" s="340"/>
+      <c r="AA8" s="341"/>
+      <c r="AB8" s="342" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="356" t="s">
+      <c r="AC8" s="344" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="357"/>
-      <c r="AE8" s="357"/>
-      <c r="AF8" s="357"/>
-      <c r="AG8" s="357"/>
-      <c r="AH8" s="357"/>
-      <c r="AI8" s="348" t="s">
+      <c r="AD8" s="345"/>
+      <c r="AE8" s="345"/>
+      <c r="AF8" s="345"/>
+      <c r="AG8" s="345"/>
+      <c r="AH8" s="345"/>
+      <c r="AI8" s="353" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="348"/>
-      <c r="AK8" s="348"/>
-      <c r="AL8" s="348"/>
-      <c r="AM8" s="348"/>
-      <c r="AN8" s="348"/>
-      <c r="AO8" s="341" t="s">
+      <c r="AJ8" s="353"/>
+      <c r="AK8" s="353"/>
+      <c r="AL8" s="353"/>
+      <c r="AM8" s="353"/>
+      <c r="AN8" s="353"/>
+      <c r="AO8" s="350" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="341"/>
-      <c r="AQ8" s="341"/>
-      <c r="AR8" s="341"/>
-      <c r="AS8" s="342" t="s">
+      <c r="AP8" s="350"/>
+      <c r="AQ8" s="350"/>
+      <c r="AR8" s="350"/>
+      <c r="AS8" s="351" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="342"/>
-      <c r="AU8" s="342"/>
+      <c r="AT8" s="351"/>
+      <c r="AU8" s="351"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="343" t="s">
+      <c r="C9" s="352" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="343"/>
-      <c r="E9" s="343"/>
-      <c r="F9" s="343"/>
-      <c r="G9" s="343"/>
-      <c r="H9" s="343"/>
-      <c r="I9" s="343"/>
-      <c r="J9" s="344" t="s">
+      <c r="D9" s="352"/>
+      <c r="E9" s="352"/>
+      <c r="F9" s="352"/>
+      <c r="G9" s="352"/>
+      <c r="H9" s="352"/>
+      <c r="I9" s="352"/>
+      <c r="J9" s="338" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="344"/>
-      <c r="L9" s="344"/>
-      <c r="M9" s="344"/>
-      <c r="N9" s="344"/>
-      <c r="O9" s="344"/>
-      <c r="P9" s="344"/>
-      <c r="Q9" s="344"/>
+      <c r="K9" s="338"/>
+      <c r="L9" s="338"/>
+      <c r="M9" s="338"/>
+      <c r="N9" s="338"/>
+      <c r="O9" s="338"/>
+      <c r="P9" s="338"/>
+      <c r="Q9" s="338"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="345" t="s">
+      <c r="V9" s="339" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="346"/>
-      <c r="X9" s="346"/>
-      <c r="Y9" s="346"/>
-      <c r="Z9" s="346"/>
-      <c r="AA9" s="347"/>
-      <c r="AB9" s="355"/>
-      <c r="AC9" s="366" t="s">
+      <c r="W9" s="340"/>
+      <c r="X9" s="340"/>
+      <c r="Y9" s="340"/>
+      <c r="Z9" s="340"/>
+      <c r="AA9" s="341"/>
+      <c r="AB9" s="343"/>
+      <c r="AC9" s="369" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="366"/>
-      <c r="AE9" s="366"/>
-      <c r="AF9" s="366"/>
-      <c r="AG9" s="366"/>
-      <c r="AH9" s="366"/>
-      <c r="AI9" s="349" t="s">
+      <c r="AD9" s="369"/>
+      <c r="AE9" s="369"/>
+      <c r="AF9" s="369"/>
+      <c r="AG9" s="369"/>
+      <c r="AH9" s="369"/>
+      <c r="AI9" s="354" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="349"/>
-      <c r="AK9" s="349"/>
-      <c r="AL9" s="349"/>
-      <c r="AM9" s="349"/>
-      <c r="AN9" s="349"/>
-      <c r="AO9" s="337" t="s">
+      <c r="AJ9" s="354"/>
+      <c r="AK9" s="354"/>
+      <c r="AL9" s="354"/>
+      <c r="AM9" s="354"/>
+      <c r="AN9" s="354"/>
+      <c r="AO9" s="346" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="337"/>
-      <c r="AQ9" s="337"/>
-      <c r="AR9" s="337"/>
-      <c r="AS9" s="340" t="s">
+      <c r="AP9" s="346"/>
+      <c r="AQ9" s="346"/>
+      <c r="AR9" s="346"/>
+      <c r="AS9" s="349" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="340"/>
-      <c r="AU9" s="340"/>
+      <c r="AT9" s="349"/>
+      <c r="AU9" s="349"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49707,6 +49710,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49717,11 +49725,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -50062,12 +50065,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50209,15 +50209,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -50241,10 +50245,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A5F284E1-7F0C-4711-B144-6978B10ED4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55B297ED-414A-4844-A21A-651E9B65A9EF}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{A5F284E1-7F0C-4711-B144-6978B10ED4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{482BE175-532B-4CF9-9DD3-523CA398D465}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -3805,32 +3805,8 @@
     <xf numFmtId="0" fontId="34" fillId="35" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3853,6 +3829,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3867,6 +3855,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3886,15 +3889,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3902,6 +3896,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3915,9 +3918,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9207,11 +9207,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="283"/>
-      <c r="E3" s="358" t="s">
+      <c r="E3" s="359" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="359"/>
-      <c r="G3" s="360"/>
+      <c r="F3" s="360"/>
+      <c r="G3" s="361"/>
       <c r="H3" s="281" t="s">
         <v>8</v>
       </c>
@@ -12510,21 +12510,21 @@
       <c r="C20" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="361" t="s">
+      <c r="D20" s="362" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="361"/>
-      <c r="F20" s="361"/>
-      <c r="G20" s="362" t="s">
+      <c r="E20" s="362"/>
+      <c r="F20" s="362"/>
+      <c r="G20" s="363" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="362"/>
-      <c r="I20" s="362"/>
-      <c r="J20" s="363" t="s">
+      <c r="H20" s="363"/>
+      <c r="I20" s="363"/>
+      <c r="J20" s="364" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="363"/>
-      <c r="L20" s="363"/>
+      <c r="K20" s="364"/>
+      <c r="L20" s="364"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C21" s="146"/>
@@ -15967,43 +15967,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="337" t="s">
+      <c r="O3" s="354" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="337"/>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
-      <c r="V3" s="337"/>
-      <c r="W3" s="337"/>
-      <c r="X3" s="337"/>
-      <c r="Y3" s="337"/>
-      <c r="Z3" s="337"/>
-      <c r="AA3" s="337"/>
-      <c r="AB3" s="337"/>
-      <c r="AC3" s="337"/>
+      <c r="P3" s="354"/>
+      <c r="Q3" s="354"/>
+      <c r="R3" s="354"/>
+      <c r="S3" s="354"/>
+      <c r="T3" s="354"/>
+      <c r="U3" s="354"/>
+      <c r="V3" s="354"/>
+      <c r="W3" s="354"/>
+      <c r="X3" s="354"/>
+      <c r="Y3" s="354"/>
+      <c r="Z3" s="354"/>
+      <c r="AA3" s="354"/>
+      <c r="AB3" s="354"/>
+      <c r="AC3" s="354"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337"/>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
-      <c r="V4" s="337"/>
-      <c r="W4" s="337"/>
-      <c r="X4" s="337"/>
-      <c r="Y4" s="337"/>
-      <c r="Z4" s="337"/>
-      <c r="AA4" s="337"/>
-      <c r="AB4" s="337"/>
-      <c r="AC4" s="337"/>
+      <c r="O4" s="354"/>
+      <c r="P4" s="354"/>
+      <c r="Q4" s="354"/>
+      <c r="R4" s="354"/>
+      <c r="S4" s="354"/>
+      <c r="T4" s="354"/>
+      <c r="U4" s="354"/>
+      <c r="V4" s="354"/>
+      <c r="W4" s="354"/>
+      <c r="X4" s="354"/>
+      <c r="Y4" s="354"/>
+      <c r="Z4" s="354"/>
+      <c r="AA4" s="354"/>
+      <c r="AB4" s="354"/>
+      <c r="AC4" s="354"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16032,17 +16032,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="338" t="s">
+      <c r="J8" s="345" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="338"/>
-      <c r="N8" s="338"/>
-      <c r="O8" s="338"/>
-      <c r="P8" s="338"/>
-      <c r="Q8" s="338"/>
-      <c r="R8" s="338"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="345"/>
+      <c r="M8" s="345"/>
+      <c r="N8" s="345"/>
+      <c r="O8" s="345"/>
+      <c r="P8" s="345"/>
+      <c r="Q8" s="345"/>
+      <c r="R8" s="345"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16057,168 +16057,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="339" t="s">
+      <c r="AC8" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="340"/>
-      <c r="AE8" s="340"/>
-      <c r="AF8" s="340"/>
-      <c r="AG8" s="340"/>
-      <c r="AH8" s="341"/>
-      <c r="AI8" s="342" t="s">
+      <c r="AD8" s="347"/>
+      <c r="AE8" s="347"/>
+      <c r="AF8" s="347"/>
+      <c r="AG8" s="347"/>
+      <c r="AH8" s="348"/>
+      <c r="AI8" s="355" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="344" t="s">
+      <c r="AL8" s="357" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="345"/>
-      <c r="AN8" s="345"/>
-      <c r="AO8" s="345"/>
-      <c r="AP8" s="345"/>
-      <c r="AQ8" s="345"/>
-      <c r="AR8" s="353" t="s">
+      <c r="AM8" s="358"/>
+      <c r="AN8" s="358"/>
+      <c r="AO8" s="358"/>
+      <c r="AP8" s="358"/>
+      <c r="AQ8" s="358"/>
+      <c r="AR8" s="349" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="353"/>
-      <c r="AT8" s="353"/>
-      <c r="AU8" s="353"/>
-      <c r="AV8" s="353"/>
-      <c r="AW8" s="353"/>
-      <c r="AX8" s="353"/>
-      <c r="AY8" s="353"/>
-      <c r="AZ8" s="353"/>
+      <c r="AS8" s="349"/>
+      <c r="AT8" s="349"/>
+      <c r="AU8" s="349"/>
+      <c r="AV8" s="349"/>
+      <c r="AW8" s="349"/>
+      <c r="AX8" s="349"/>
+      <c r="AY8" s="349"/>
+      <c r="AZ8" s="349"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="350" t="s">
+      <c r="BD8" s="342" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="350"/>
-      <c r="BF8" s="350"/>
-      <c r="BG8" s="350"/>
-      <c r="BH8" s="350"/>
-      <c r="BI8" s="350"/>
-      <c r="BJ8" s="350"/>
-      <c r="BK8" s="350"/>
-      <c r="BL8" s="350"/>
-      <c r="BM8" s="350"/>
-      <c r="BN8" s="350"/>
-      <c r="BO8" s="350"/>
-      <c r="BP8" s="350"/>
-      <c r="BQ8" s="351" t="s">
+      <c r="BE8" s="342"/>
+      <c r="BF8" s="342"/>
+      <c r="BG8" s="342"/>
+      <c r="BH8" s="342"/>
+      <c r="BI8" s="342"/>
+      <c r="BJ8" s="342"/>
+      <c r="BK8" s="342"/>
+      <c r="BL8" s="342"/>
+      <c r="BM8" s="342"/>
+      <c r="BN8" s="342"/>
+      <c r="BO8" s="342"/>
+      <c r="BP8" s="342"/>
+      <c r="BQ8" s="343" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="351"/>
-      <c r="BS8" s="351"/>
+      <c r="BR8" s="343"/>
+      <c r="BS8" s="343"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="352" t="s">
+      <c r="C9" s="344" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="352"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
-      <c r="G9" s="352"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="338" t="s">
+      <c r="D9" s="344"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
+      <c r="G9" s="344"/>
+      <c r="H9" s="344"/>
+      <c r="I9" s="344"/>
+      <c r="J9" s="345" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="338"/>
-      <c r="N9" s="338"/>
-      <c r="O9" s="338"/>
-      <c r="P9" s="338"/>
-      <c r="Q9" s="338"/>
-      <c r="R9" s="338"/>
-      <c r="S9" s="366" t="s">
+      <c r="K9" s="345"/>
+      <c r="L9" s="345"/>
+      <c r="M9" s="345"/>
+      <c r="N9" s="345"/>
+      <c r="O9" s="345"/>
+      <c r="P9" s="345"/>
+      <c r="Q9" s="345"/>
+      <c r="R9" s="345"/>
+      <c r="S9" s="368" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="367" t="s">
+      <c r="T9" s="365" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="367" t="s">
+      <c r="U9" s="365" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="367" t="s">
+      <c r="V9" s="365" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="339" t="s">
+      <c r="AA9" s="346" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="340"/>
-      <c r="AC9" s="340"/>
-      <c r="AD9" s="340"/>
-      <c r="AE9" s="340"/>
-      <c r="AF9" s="340"/>
-      <c r="AG9" s="340"/>
-      <c r="AH9" s="341"/>
-      <c r="AI9" s="343"/>
+      <c r="AB9" s="347"/>
+      <c r="AC9" s="347"/>
+      <c r="AD9" s="347"/>
+      <c r="AE9" s="347"/>
+      <c r="AF9" s="347"/>
+      <c r="AG9" s="347"/>
+      <c r="AH9" s="348"/>
+      <c r="AI9" s="356"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="369" t="s">
+      <c r="AL9" s="367" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="369"/>
-      <c r="AN9" s="369"/>
-      <c r="AO9" s="369"/>
-      <c r="AP9" s="369"/>
-      <c r="AQ9" s="369"/>
-      <c r="AR9" s="354" t="s">
+      <c r="AM9" s="367"/>
+      <c r="AN9" s="367"/>
+      <c r="AO9" s="367"/>
+      <c r="AP9" s="367"/>
+      <c r="AQ9" s="367"/>
+      <c r="AR9" s="350" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="354"/>
-      <c r="AT9" s="354"/>
-      <c r="AU9" s="354"/>
-      <c r="AV9" s="354"/>
-      <c r="AW9" s="354"/>
-      <c r="AX9" s="354"/>
-      <c r="AY9" s="354"/>
-      <c r="AZ9" s="354"/>
+      <c r="AS9" s="350"/>
+      <c r="AT9" s="350"/>
+      <c r="AU9" s="350"/>
+      <c r="AV9" s="350"/>
+      <c r="AW9" s="350"/>
+      <c r="AX9" s="350"/>
+      <c r="AY9" s="350"/>
+      <c r="AZ9" s="350"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="346" t="s">
+      <c r="BD9" s="338" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="346"/>
-      <c r="BF9" s="346"/>
-      <c r="BG9" s="346"/>
-      <c r="BH9" s="346"/>
-      <c r="BI9" s="346"/>
-      <c r="BJ9" s="346"/>
-      <c r="BK9" s="346"/>
-      <c r="BL9" s="346"/>
-      <c r="BM9" s="346"/>
-      <c r="BN9" s="346"/>
-      <c r="BO9" s="346"/>
-      <c r="BP9" s="346"/>
-      <c r="BQ9" s="349" t="s">
+      <c r="BE9" s="338"/>
+      <c r="BF9" s="338"/>
+      <c r="BG9" s="338"/>
+      <c r="BH9" s="338"/>
+      <c r="BI9" s="338"/>
+      <c r="BJ9" s="338"/>
+      <c r="BK9" s="338"/>
+      <c r="BL9" s="338"/>
+      <c r="BM9" s="338"/>
+      <c r="BN9" s="338"/>
+      <c r="BO9" s="338"/>
+      <c r="BP9" s="338"/>
+      <c r="BQ9" s="341" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="349"/>
-      <c r="BS9" s="349"/>
-      <c r="BT9" s="364" t="s">
+      <c r="BR9" s="341"/>
+      <c r="BS9" s="341"/>
+      <c r="BT9" s="369" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="364" t="s">
+      <c r="BU9" s="369" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="364" t="s">
+      <c r="BV9" s="369" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="365" t="s">
+      <c r="BW9" s="370" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16274,10 +16274,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="366"/>
-      <c r="T10" s="368"/>
-      <c r="U10" s="368"/>
-      <c r="V10" s="368"/>
+      <c r="S10" s="368"/>
+      <c r="T10" s="366"/>
+      <c r="U10" s="366"/>
+      <c r="V10" s="366"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16403,10 +16403,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="364"/>
-      <c r="BU10" s="364"/>
-      <c r="BV10" s="364"/>
-      <c r="BW10" s="365"/>
+      <c r="BT10" s="369"/>
+      <c r="BU10" s="369"/>
+      <c r="BV10" s="369"/>
+      <c r="BW10" s="370"/>
     </row>
     <row r="11" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -33446,6 +33446,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33454,21 +33469,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33557,6 +33557,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="C1:BM83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -33600,34 +33601,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="337" t="s">
+      <c r="O3" s="354" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="337"/>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
-      <c r="V3" s="337"/>
-      <c r="W3" s="337"/>
-      <c r="X3" s="337"/>
+      <c r="P3" s="354"/>
+      <c r="Q3" s="354"/>
+      <c r="R3" s="354"/>
+      <c r="S3" s="354"/>
+      <c r="T3" s="354"/>
+      <c r="U3" s="354"/>
+      <c r="V3" s="354"/>
+      <c r="W3" s="354"/>
+      <c r="X3" s="354"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337"/>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
-      <c r="V4" s="337"/>
-      <c r="W4" s="337"/>
-      <c r="X4" s="337"/>
+      <c r="O4" s="354"/>
+      <c r="P4" s="354"/>
+      <c r="Q4" s="354"/>
+      <c r="R4" s="354"/>
+      <c r="S4" s="354"/>
+      <c r="T4" s="354"/>
+      <c r="U4" s="354"/>
+      <c r="V4" s="354"/>
+      <c r="W4" s="354"/>
+      <c r="X4" s="354"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33660,16 +33661,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="338" t="s">
+      <c r="J8" s="345" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="338"/>
-      <c r="N8" s="338"/>
-      <c r="O8" s="338"/>
-      <c r="P8" s="338"/>
-      <c r="Q8" s="338"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="345"/>
+      <c r="M8" s="345"/>
+      <c r="N8" s="345"/>
+      <c r="O8" s="345"/>
+      <c r="P8" s="345"/>
+      <c r="Q8" s="345"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33680,133 +33681,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="339" t="s">
+      <c r="X8" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="340"/>
-      <c r="Z8" s="340"/>
-      <c r="AA8" s="340"/>
-      <c r="AB8" s="341"/>
-      <c r="AC8" s="342" t="s">
+      <c r="Y8" s="347"/>
+      <c r="Z8" s="347"/>
+      <c r="AA8" s="347"/>
+      <c r="AB8" s="348"/>
+      <c r="AC8" s="355" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="344" t="s">
+      <c r="AF8" s="357" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="345"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="345"/>
-      <c r="AJ8" s="345"/>
-      <c r="AK8" s="345"/>
-      <c r="AL8" s="353" t="s">
+      <c r="AG8" s="358"/>
+      <c r="AH8" s="358"/>
+      <c r="AI8" s="358"/>
+      <c r="AJ8" s="358"/>
+      <c r="AK8" s="358"/>
+      <c r="AL8" s="349" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="353"/>
-      <c r="AN8" s="353"/>
-      <c r="AO8" s="353"/>
-      <c r="AP8" s="353"/>
-      <c r="AQ8" s="353"/>
-      <c r="AR8" s="353"/>
-      <c r="AS8" s="353"/>
-      <c r="AT8" s="350" t="s">
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="349"/>
+      <c r="AP8" s="349"/>
+      <c r="AQ8" s="349"/>
+      <c r="AR8" s="349"/>
+      <c r="AS8" s="349"/>
+      <c r="AT8" s="342" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="350"/>
-      <c r="AV8" s="350"/>
-      <c r="AW8" s="350"/>
-      <c r="AX8" s="350"/>
-      <c r="AY8" s="350"/>
-      <c r="AZ8" s="350"/>
-      <c r="BA8" s="350"/>
-      <c r="BB8" s="350"/>
-      <c r="BC8" s="351" t="s">
+      <c r="AU8" s="342"/>
+      <c r="AV8" s="342"/>
+      <c r="AW8" s="342"/>
+      <c r="AX8" s="342"/>
+      <c r="AY8" s="342"/>
+      <c r="AZ8" s="342"/>
+      <c r="BA8" s="342"/>
+      <c r="BB8" s="342"/>
+      <c r="BC8" s="343" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="351"/>
-      <c r="BE8" s="351"/>
-      <c r="BF8" s="351"/>
-      <c r="BG8" s="351"/>
-      <c r="BH8" s="351"/>
+      <c r="BD8" s="343"/>
+      <c r="BE8" s="343"/>
+      <c r="BF8" s="343"/>
+      <c r="BG8" s="343"/>
+      <c r="BH8" s="343"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="352" t="s">
+      <c r="C9" s="344" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="352"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
-      <c r="G9" s="352"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="338" t="s">
+      <c r="D9" s="344"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
+      <c r="G9" s="344"/>
+      <c r="H9" s="344"/>
+      <c r="I9" s="344"/>
+      <c r="J9" s="345" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="338"/>
-      <c r="N9" s="338"/>
-      <c r="O9" s="338"/>
-      <c r="P9" s="338"/>
-      <c r="Q9" s="338"/>
+      <c r="K9" s="345"/>
+      <c r="L9" s="345"/>
+      <c r="M9" s="345"/>
+      <c r="N9" s="345"/>
+      <c r="O9" s="345"/>
+      <c r="P9" s="345"/>
+      <c r="Q9" s="345"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="339" t="s">
+      <c r="V9" s="346" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="340"/>
-      <c r="X9" s="340"/>
-      <c r="Y9" s="340"/>
-      <c r="Z9" s="340"/>
-      <c r="AA9" s="340"/>
-      <c r="AB9" s="341"/>
-      <c r="AC9" s="343"/>
-      <c r="AD9" s="355" t="s">
+      <c r="W9" s="347"/>
+      <c r="X9" s="347"/>
+      <c r="Y9" s="347"/>
+      <c r="Z9" s="347"/>
+      <c r="AA9" s="347"/>
+      <c r="AB9" s="348"/>
+      <c r="AC9" s="356"/>
+      <c r="AD9" s="351" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="356"/>
-      <c r="AF9" s="356"/>
-      <c r="AG9" s="356"/>
-      <c r="AH9" s="356"/>
-      <c r="AI9" s="356"/>
-      <c r="AJ9" s="356"/>
-      <c r="AK9" s="357"/>
-      <c r="AL9" s="354" t="s">
+      <c r="AE9" s="352"/>
+      <c r="AF9" s="352"/>
+      <c r="AG9" s="352"/>
+      <c r="AH9" s="352"/>
+      <c r="AI9" s="352"/>
+      <c r="AJ9" s="352"/>
+      <c r="AK9" s="353"/>
+      <c r="AL9" s="350" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="354"/>
-      <c r="AN9" s="354"/>
-      <c r="AO9" s="354"/>
-      <c r="AP9" s="354"/>
-      <c r="AQ9" s="354"/>
-      <c r="AR9" s="354"/>
-      <c r="AS9" s="354"/>
-      <c r="AT9" s="346" t="s">
+      <c r="AM9" s="350"/>
+      <c r="AN9" s="350"/>
+      <c r="AO9" s="350"/>
+      <c r="AP9" s="350"/>
+      <c r="AQ9" s="350"/>
+      <c r="AR9" s="350"/>
+      <c r="AS9" s="350"/>
+      <c r="AT9" s="338" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="346"/>
-      <c r="AV9" s="346"/>
-      <c r="AW9" s="346"/>
-      <c r="AX9" s="346"/>
-      <c r="AY9" s="347"/>
-      <c r="AZ9" s="347"/>
-      <c r="BA9" s="347"/>
-      <c r="BB9" s="347"/>
-      <c r="BC9" s="348" t="s">
+      <c r="AU9" s="338"/>
+      <c r="AV9" s="338"/>
+      <c r="AW9" s="338"/>
+      <c r="AX9" s="338"/>
+      <c r="AY9" s="339"/>
+      <c r="AZ9" s="339"/>
+      <c r="BA9" s="339"/>
+      <c r="BB9" s="339"/>
+      <c r="BC9" s="340" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="349"/>
-      <c r="BE9" s="349"/>
-      <c r="BF9" s="349"/>
-      <c r="BG9" s="349"/>
-      <c r="BH9" s="349"/>
+      <c r="BD9" s="341"/>
+      <c r="BE9" s="341"/>
+      <c r="BF9" s="341"/>
+      <c r="BG9" s="341"/>
+      <c r="BH9" s="341"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -34014,7 +34015,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -34163,7 +34164,7 @@
       </c>
       <c r="BL11" s="12"/>
     </row>
-    <row r="12" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
@@ -34478,7 +34479,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:65" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -34617,7 +34618,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:65" customFormat="1" ht="121.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:65" customFormat="1" ht="121.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -34761,7 +34762,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="16" spans="3:65" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:65" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -34911,7 +34912,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -35065,7 +35066,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -35219,7 +35220,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -35367,7 +35368,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -35515,7 +35516,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -35663,7 +35664,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -35811,7 +35812,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -35904,7 +35905,7 @@
       </c>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11"/>
-      <c r="AK23" s="374">
+      <c r="AK23" s="337">
         <v>6.25E-2</v>
       </c>
       <c r="AL23" s="12" t="s">
@@ -35965,7 +35966,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -36110,7 +36111,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -36258,7 +36259,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -36399,7 +36400,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -36547,7 +36548,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:64" customFormat="1" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36701,7 +36702,7 @@
       </c>
       <c r="BL28" s="12"/>
     </row>
-    <row r="29" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C29" s="23" t="s">
         <v>10</v>
       </c>
@@ -36854,7 +36855,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -37009,7 +37010,7 @@
       </c>
       <c r="BL30" s="12"/>
     </row>
-    <row r="31" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C31" s="22" t="s">
         <v>4</v>
       </c>
@@ -37166,7 +37167,7 @@
       </c>
       <c r="BL31" s="12"/>
     </row>
-    <row r="32" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C32" s="22" t="s">
         <v>4</v>
       </c>
@@ -37324,7 +37325,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -37472,7 +37473,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -37627,7 +37628,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -37775,7 +37776,7 @@
       </c>
       <c r="BL35" s="12"/>
     </row>
-    <row r="36" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C36" s="24" t="s">
         <v>7</v>
       </c>
@@ -37933,7 +37934,7 @@
       </c>
       <c r="BL36" s="12"/>
     </row>
-    <row r="37" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C37" s="24" t="s">
         <v>7</v>
       </c>
@@ -38073,7 +38074,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -38220,7 +38221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -38373,7 +38374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:64" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C40" s="22" t="s">
         <v>4</v>
       </c>
@@ -38525,7 +38526,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -38684,7 +38685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -38831,7 +38832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C43" s="23" t="s">
         <v>10</v>
       </c>
@@ -38983,7 +38984,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -39140,7 +39141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -39293,7 +39294,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -39442,7 +39443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="24" t="s">
         <v>7</v>
       </c>
@@ -39594,7 +39595,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:64" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -39751,7 +39752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -39901,7 +39902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -40050,7 +40051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C51" s="24" t="s">
         <v>7</v>
       </c>
@@ -40203,7 +40204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -40352,7 +40353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -40501,7 +40502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -40645,7 +40646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -40798,7 +40799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -40946,7 +40947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -41103,7 +41104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -41256,7 +41257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -41409,7 +41410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -41562,7 +41563,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -41711,7 +41712,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -41868,7 +41869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -42021,7 +42022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:63" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -42177,7 +42178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -42334,7 +42335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -42488,7 +42489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -42643,7 +42644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -42798,7 +42799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -42959,7 +42960,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:63" customFormat="1" ht="52.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -43136,7 +43137,19 @@
     <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="C10:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Técnica Profesional Judicial"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43147,11 +43160,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43192,10 +43200,10 @@
   </cols>
   <sheetData>
     <row r="10" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D10" s="370" t="s">
+      <c r="D10" s="371" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="370"/>
+      <c r="E10" s="371"/>
     </row>
     <row r="11" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D11" s="329" t="s">
@@ -43388,33 +43396,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="337" t="s">
+      <c r="O3" s="354" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="337"/>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
-      <c r="V3" s="337"/>
-      <c r="W3" s="337"/>
-      <c r="X3" s="337"/>
+      <c r="P3" s="354"/>
+      <c r="Q3" s="354"/>
+      <c r="R3" s="354"/>
+      <c r="S3" s="354"/>
+      <c r="T3" s="354"/>
+      <c r="U3" s="354"/>
+      <c r="V3" s="354"/>
+      <c r="W3" s="354"/>
+      <c r="X3" s="354"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337"/>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
-      <c r="V4" s="337"/>
-      <c r="W4" s="337"/>
-      <c r="X4" s="337"/>
+      <c r="O4" s="354"/>
+      <c r="P4" s="354"/>
+      <c r="Q4" s="354"/>
+      <c r="R4" s="354"/>
+      <c r="S4" s="354"/>
+      <c r="T4" s="354"/>
+      <c r="U4" s="354"/>
+      <c r="V4" s="354"/>
+      <c r="W4" s="354"/>
+      <c r="X4" s="354"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43443,16 +43451,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="338" t="s">
+      <c r="J8" s="345" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="338"/>
-      <c r="N8" s="338"/>
-      <c r="O8" s="338"/>
-      <c r="P8" s="338"/>
-      <c r="Q8" s="338"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="345"/>
+      <c r="M8" s="345"/>
+      <c r="N8" s="345"/>
+      <c r="O8" s="345"/>
+      <c r="P8" s="345"/>
+      <c r="Q8" s="345"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43463,107 +43471,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="339" t="s">
+      <c r="X8" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="340"/>
-      <c r="Z8" s="340"/>
-      <c r="AA8" s="341"/>
-      <c r="AB8" s="342" t="s">
+      <c r="Y8" s="347"/>
+      <c r="Z8" s="347"/>
+      <c r="AA8" s="348"/>
+      <c r="AB8" s="355" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="344" t="s">
+      <c r="AC8" s="357" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="345"/>
-      <c r="AE8" s="345"/>
-      <c r="AF8" s="345"/>
-      <c r="AG8" s="345"/>
-      <c r="AH8" s="345"/>
-      <c r="AI8" s="353" t="s">
+      <c r="AD8" s="358"/>
+      <c r="AE8" s="358"/>
+      <c r="AF8" s="358"/>
+      <c r="AG8" s="358"/>
+      <c r="AH8" s="358"/>
+      <c r="AI8" s="349" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="353"/>
-      <c r="AK8" s="353"/>
-      <c r="AL8" s="353"/>
-      <c r="AM8" s="353"/>
-      <c r="AN8" s="353"/>
-      <c r="AO8" s="350" t="s">
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="349"/>
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="342" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="350"/>
-      <c r="AQ8" s="350"/>
-      <c r="AR8" s="350"/>
-      <c r="AS8" s="351" t="s">
+      <c r="AP8" s="342"/>
+      <c r="AQ8" s="342"/>
+      <c r="AR8" s="342"/>
+      <c r="AS8" s="343" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="351"/>
-      <c r="AU8" s="351"/>
+      <c r="AT8" s="343"/>
+      <c r="AU8" s="343"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="352" t="s">
+      <c r="C9" s="344" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="352"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
-      <c r="G9" s="352"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="338" t="s">
+      <c r="D9" s="344"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
+      <c r="G9" s="344"/>
+      <c r="H9" s="344"/>
+      <c r="I9" s="344"/>
+      <c r="J9" s="345" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="338"/>
-      <c r="N9" s="338"/>
-      <c r="O9" s="338"/>
-      <c r="P9" s="338"/>
-      <c r="Q9" s="338"/>
+      <c r="K9" s="345"/>
+      <c r="L9" s="345"/>
+      <c r="M9" s="345"/>
+      <c r="N9" s="345"/>
+      <c r="O9" s="345"/>
+      <c r="P9" s="345"/>
+      <c r="Q9" s="345"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="339" t="s">
+      <c r="V9" s="346" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="340"/>
-      <c r="X9" s="340"/>
-      <c r="Y9" s="340"/>
-      <c r="Z9" s="340"/>
-      <c r="AA9" s="341"/>
-      <c r="AB9" s="343"/>
-      <c r="AC9" s="369" t="s">
+      <c r="W9" s="347"/>
+      <c r="X9" s="347"/>
+      <c r="Y9" s="347"/>
+      <c r="Z9" s="347"/>
+      <c r="AA9" s="348"/>
+      <c r="AB9" s="356"/>
+      <c r="AC9" s="367" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="369"/>
-      <c r="AE9" s="369"/>
-      <c r="AF9" s="369"/>
-      <c r="AG9" s="369"/>
-      <c r="AH9" s="369"/>
-      <c r="AI9" s="354" t="s">
+      <c r="AD9" s="367"/>
+      <c r="AE9" s="367"/>
+      <c r="AF9" s="367"/>
+      <c r="AG9" s="367"/>
+      <c r="AH9" s="367"/>
+      <c r="AI9" s="350" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="354"/>
-      <c r="AK9" s="354"/>
-      <c r="AL9" s="354"/>
-      <c r="AM9" s="354"/>
-      <c r="AN9" s="354"/>
-      <c r="AO9" s="346" t="s">
+      <c r="AJ9" s="350"/>
+      <c r="AK9" s="350"/>
+      <c r="AL9" s="350"/>
+      <c r="AM9" s="350"/>
+      <c r="AN9" s="350"/>
+      <c r="AO9" s="338" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="346"/>
-      <c r="AQ9" s="346"/>
-      <c r="AR9" s="346"/>
-      <c r="AS9" s="349" t="s">
+      <c r="AP9" s="338"/>
+      <c r="AQ9" s="338"/>
+      <c r="AR9" s="338"/>
+      <c r="AS9" s="341" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="349"/>
-      <c r="AU9" s="349"/>
+      <c r="AT9" s="341"/>
+      <c r="AU9" s="341"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -49710,11 +49718,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49725,6 +49728,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -49777,41 +49785,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="372" t="s">
+      <c r="A2" s="373" t="s">
         <v>391</v>
       </c>
-      <c r="B2" s="372"/>
-      <c r="C2" s="372"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
       <c r="D2" t="s">
         <v>392</v>
       </c>
-      <c r="E2" s="372" t="s">
+      <c r="E2" s="373" t="s">
         <v>393</v>
       </c>
-      <c r="F2" s="372"/>
+      <c r="F2" s="373"/>
       <c r="G2" s="181" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="371" t="s">
+      <c r="H2" s="372" t="s">
         <v>394</v>
       </c>
-      <c r="I2" s="371"/>
-      <c r="J2" s="371"/>
-      <c r="K2" s="371" t="s">
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="372"/>
-      <c r="M2" s="372"/>
-      <c r="N2" s="371" t="s">
+      <c r="L2" s="373"/>
+      <c r="M2" s="373"/>
+      <c r="N2" s="372" t="s">
         <v>395</v>
       </c>
-      <c r="O2" s="372"/>
-      <c r="P2" s="372"/>
-      <c r="Q2" s="373"/>
-      <c r="R2" s="371" t="s">
+      <c r="O2" s="373"/>
+      <c r="P2" s="373"/>
+      <c r="Q2" s="374"/>
+      <c r="R2" s="372" t="s">
         <v>211</v>
       </c>
-      <c r="S2" s="372"/>
+      <c r="S2" s="373"/>
     </row>
     <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="85" t="s">
@@ -50071,6 +50079,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -50208,15 +50225,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
@@ -50227,6 +50235,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50242,12 +50258,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran.sharepoint.com/sites/PlaneacinyGestinInstitucional-REFORMACURRICULAR/Documentos compartidos/REFORMA CURRICULAR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13475" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8C11E0-12C5-4221-8127-906874FA4D7C}"/>
+  <xr:revisionPtr revIDLastSave="13476" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1335EB00-23C1-43D4-9807-C9F588968DB8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Ejecutivo" sheetId="9" state="hidden" r:id="rId1"/>
@@ -1818,7 +1818,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="83" x14ac:knownFonts="1">
+  <fonts count="82" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2432,12 +2432,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="52">
@@ -3832,32 +3826,17 @@
     <xf numFmtId="0" fontId="34" fillId="35" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3880,6 +3859,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3894,6 +3885,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3913,15 +3919,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3929,6 +3926,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3942,18 +3948,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5342,8 +5336,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="382814" y="2315028"/>
-          <a:ext cx="2481943" cy="1211943"/>
+          <a:off x="380999" y="2351314"/>
+          <a:ext cx="2438401" cy="1208314"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1121230"/>
         </a:xfrm>
@@ -5550,8 +5544,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6037942" y="2371273"/>
-          <a:ext cx="2022930" cy="1177472"/>
+          <a:off x="5932713" y="2405744"/>
+          <a:ext cx="2002973" cy="1175658"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1090927"/>
         </a:xfrm>
@@ -5784,8 +5778,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3104241" y="2325914"/>
-          <a:ext cx="2803074" cy="1179287"/>
+          <a:off x="3058884" y="2362200"/>
+          <a:ext cx="2743202" cy="1175658"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1090927"/>
         </a:xfrm>
@@ -6009,8 +6003,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8158842" y="2325914"/>
-          <a:ext cx="2162630" cy="1179287"/>
+          <a:off x="8033656" y="2362200"/>
+          <a:ext cx="2122716" cy="1175658"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1090927"/>
         </a:xfrm>
@@ -6247,8 +6241,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10452099" y="2315028"/>
-          <a:ext cx="2162630" cy="1250043"/>
+          <a:off x="10286999" y="2351314"/>
+          <a:ext cx="2122715" cy="1251857"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1262646"/>
         </a:xfrm>
@@ -6475,8 +6469,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12767129" y="2315028"/>
-          <a:ext cx="2162630" cy="1250043"/>
+          <a:off x="12562114" y="2351314"/>
+          <a:ext cx="2122716" cy="1251857"/>
           <a:chOff x="5268685" y="1915885"/>
           <a:chExt cx="2971800" cy="1262646"/>
         </a:xfrm>
@@ -6757,8 +6751,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="252185" y="4971140"/>
-          <a:ext cx="2013859" cy="1444173"/>
+          <a:off x="250370" y="5018312"/>
+          <a:ext cx="2013859" cy="1447801"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -6984,8 +6978,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2353128" y="4927597"/>
-          <a:ext cx="2207988" cy="1444173"/>
+          <a:off x="2351313" y="4974769"/>
+          <a:ext cx="2144488" cy="1447801"/>
           <a:chOff x="195776" y="5029198"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -7211,8 +7205,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4724401" y="4938483"/>
-          <a:ext cx="2238829" cy="1444173"/>
+          <a:off x="4659086" y="4985655"/>
+          <a:ext cx="2198915" cy="1447801"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -7438,8 +7432,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7092042" y="4916712"/>
-          <a:ext cx="1837872" cy="1444173"/>
+          <a:off x="6966856" y="4963884"/>
+          <a:ext cx="1817916" cy="1447801"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -7665,8 +7659,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9125855" y="4916712"/>
-          <a:ext cx="1846944" cy="1444173"/>
+          <a:off x="8980713" y="4963884"/>
+          <a:ext cx="1807029" cy="1447801"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -7875,8 +7869,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11103427" y="4916712"/>
-          <a:ext cx="1846944" cy="1444173"/>
+          <a:off x="10918370" y="4963884"/>
+          <a:ext cx="1807030" cy="1447801"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -8102,8 +8096,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14309271" y="4553853"/>
-          <a:ext cx="2840264" cy="1941289"/>
+          <a:off x="14064342" y="4599210"/>
+          <a:ext cx="2800351" cy="1943104"/>
           <a:chOff x="250370" y="5018312"/>
           <a:chExt cx="2688773" cy="1447801"/>
         </a:xfrm>
@@ -8457,8 +8451,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="772583" y="4746624"/>
-          <a:ext cx="1942042" cy="656168"/>
+          <a:off x="772583" y="4614333"/>
+          <a:ext cx="1915584" cy="635000"/>
           <a:chOff x="772583" y="4614333"/>
           <a:chExt cx="1915584" cy="635000"/>
         </a:xfrm>
@@ -8611,10 +8605,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9189,14 +9179,14 @@
     <tabColor rgb="FF0E2841"/>
   </sheetPr>
   <dimension ref="A1:Q179"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.453125" customWidth="1"/>
-    <col min="2" max="2" width="33.453125" customWidth="1"/>
-    <col min="3" max="16" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.44140625" customWidth="1"/>
+    <col min="3" max="16" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="199"/>
       <c r="B1" s="206" t="s">
         <v>0</v>
@@ -9222,7 +9212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="199"/>
       <c r="B2" s="206"/>
       <c r="C2" s="207"/>
@@ -9242,7 +9232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="287" customFormat="1" ht="41.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" s="287" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="283"/>
       <c r="B3" s="284" t="s">
         <v>5</v>
@@ -9251,11 +9241,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="283"/>
-      <c r="E3" s="357" t="s">
+      <c r="E3" s="361" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="358"/>
-      <c r="G3" s="359"/>
+      <c r="F3" s="362"/>
+      <c r="G3" s="363"/>
       <c r="H3" s="281" t="s">
         <v>8</v>
       </c>
@@ -9276,12 +9266,12 @@
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P4" s="288" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="199"/>
       <c r="B5" s="206"/>
       <c r="C5" s="207"/>
@@ -9298,12 +9288,12 @@
       <c r="N5" s="199"/>
       <c r="O5" s="208"/>
     </row>
-    <row r="6" spans="1:17" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P6" s="288" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="200"/>
       <c r="B7" s="271" t="s">
         <v>11</v>
@@ -9327,12 +9317,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P8" s="288" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="288" customFormat="1" ht="68.150000000000006" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="9" spans="1:17" s="288" customFormat="1" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A9" s="302"/>
       <c r="B9" s="303" cm="1">
         <f t="array" ref="B9">SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))</f>
@@ -9368,7 +9358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="288" customFormat="1" ht="28.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" s="288" customFormat="1" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="302"/>
       <c r="B10" s="301"/>
       <c r="C10" s="301"/>
@@ -9386,7 +9376,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="28.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="246"/>
       <c r="B11" s="304"/>
       <c r="C11" s="304"/>
@@ -9401,8 +9391,8 @@
       <c r="L11" s="304"/>
       <c r="M11" s="304"/>
     </row>
-    <row r="12" spans="1:17" ht="28.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="28.35" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="202"/>
       <c r="B13" s="274" t="s">
         <v>17</v>
@@ -9421,14 +9411,14 @@
       <c r="N13" s="272"/>
       <c r="O13" s="272"/>
     </row>
-    <row r="14" spans="1:17" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="202"/>
       <c r="B14" s="310" t="str" cm="1">
         <f t="array" ref="B14">CONCATENATE("AVANCE POR ETAPA  —  8 procesos según hoja Estructura  ·  ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))),"0")," programas")</f>
         <v>AVANCE POR ETAPA  —  8 procesos según hoja Estructura  ·  2 programas</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="36.65" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:17" ht="36.6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="202"/>
       <c r="B15" s="238" t="s">
         <v>18</v>
@@ -9463,7 +9453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="68.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="202"/>
       <c r="B16" s="311"/>
       <c r="C16" s="201"/>
@@ -9478,7 +9468,7 @@
       <c r="L16" s="201"/>
       <c r="M16" s="237"/>
     </row>
-    <row r="17" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="202"/>
       <c r="B17" s="309" t="str" cm="1">
         <f t="array" ref="B17">CONCATENATE("✔ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("finalizado",Maestro!J11:J70))*1),"0"),"  Final.     ◑ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("en proceso",Maestro!J11:J70))*1),"0"),"  En proc.     ○ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("finalizado",Maestro!J11:J70))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("en proceso",Maestro!J11:J70))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!J11:J70))*1),"0"),"  Sin inic.     — ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!J11:J70))*1),"0"),"  N/A")</f>
@@ -9505,7 +9495,7 @@
       <c r="L17" s="201"/>
       <c r="M17" s="237"/>
     </row>
-    <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="202"/>
       <c r="B18" s="203"/>
       <c r="C18" s="203"/>
@@ -9520,7 +9510,7 @@
       <c r="L18" s="205"/>
       <c r="M18" s="205"/>
     </row>
-    <row r="19" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="202"/>
       <c r="B19" s="242" t="s">
         <v>22</v>
@@ -9555,7 +9545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="202"/>
       <c r="B20" s="312"/>
       <c r="C20" s="201"/>
@@ -9570,7 +9560,7 @@
       <c r="L20" s="201"/>
       <c r="M20" s="237"/>
     </row>
-    <row r="21" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="202"/>
       <c r="B21" s="309" t="str" cm="1">
         <f t="array" ref="B21">CONCATENATE("✔ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))*1),"0"),"  Final.     ◑ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1))*1),"0"),"  En proc.     ○ ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0)))-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;=1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*(ISNUMBER(Maestro!AQ11:AQ70)*(Maestro!AQ11:AQ70&gt;0)*(Maestro!AQ11:AQ70&lt;1))*1)-SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AQ11:AQ70))*1),"0"),"  Sin inic.     — ",TEXT(SUMPRODUCT(((('Resumen Ejecutivo'!C3="Todas las modalidades")+(Maestro!F11:F70='Resumen Ejecutivo'!C3)&gt;0)*(('Resumen Ejecutivo'!E3="Todas las facultades")+(Maestro!C11:C70='Resumen Ejecutivo'!E3)&gt;0)*(('Resumen Ejecutivo'!H3="Todos los periodos")+(Maestro!BV11:BV70='Resumen Ejecutivo'!H3)&gt;0))*ISNUMBER(SEARCH("no aplica",Maestro!AQ11:AQ70))*1),"0"),"  N/A")</f>
@@ -9597,7 +9587,7 @@
       <c r="L21" s="201"/>
       <c r="M21" s="237"/>
     </row>
-    <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="202"/>
       <c r="B22" s="205"/>
       <c r="C22" s="205"/>
@@ -9612,8 +9602,8 @@
       <c r="L22" s="205"/>
       <c r="M22" s="205"/>
     </row>
-    <row r="23" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="204"/>
       <c r="B24" s="274" t="s">
         <v>26</v>
@@ -9634,10 +9624,10 @@
       <c r="N24" s="272"/>
       <c r="O24" s="272"/>
     </row>
-    <row r="25" spans="1:15" ht="10.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="10.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="204"/>
     </row>
-    <row r="26" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="204"/>
       <c r="B26" s="211" t="s">
         <v>28</v>
@@ -9669,7 +9659,7 @@
       </c>
       <c r="O26" s="199"/>
     </row>
-    <row r="27" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="204"/>
       <c r="B27" s="247" t="s">
         <v>36</v>
@@ -9701,7 +9691,7 @@
       </c>
       <c r="O27" s="215"/>
     </row>
-    <row r="28" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="204"/>
       <c r="B28" s="256" t="s">
         <v>39</v>
@@ -9733,7 +9723,7 @@
       </c>
       <c r="O28" s="201"/>
     </row>
-    <row r="29" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="204"/>
       <c r="B29" s="261" t="s">
         <v>42</v>
@@ -9765,7 +9755,7 @@
       </c>
       <c r="O29" s="212"/>
     </row>
-    <row r="30" spans="1:15" ht="10.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="10.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="204"/>
       <c r="B30" s="266" t="s">
         <v>45</v>
@@ -9797,7 +9787,7 @@
       </c>
       <c r="O30" s="201"/>
     </row>
-    <row r="31" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="204"/>
       <c r="B31" s="267" t="s">
         <v>48</v>
@@ -9829,7 +9819,7 @@
       </c>
       <c r="O31" s="212"/>
     </row>
-    <row r="32" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="204"/>
       <c r="B32" s="268" t="s">
         <v>50</v>
@@ -9861,7 +9851,7 @@
       </c>
       <c r="O32" s="201"/>
     </row>
-    <row r="33" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="204"/>
       <c r="B33" s="269" t="s">
         <v>52</v>
@@ -9893,7 +9883,7 @@
       </c>
       <c r="O33" s="212"/>
     </row>
-    <row r="34" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="204"/>
       <c r="B34" s="270" t="s">
         <v>54</v>
@@ -9925,7 +9915,7 @@
       </c>
       <c r="O34" s="201"/>
     </row>
-    <row r="35" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="204"/>
       <c r="H35" s="218" t="s">
         <v>56</v>
@@ -9942,11 +9932,11 @@
       </c>
       <c r="O35" s="212"/>
     </row>
-    <row r="36" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="204"/>
       <c r="M36" s="297"/>
     </row>
-    <row r="37" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="204"/>
       <c r="H37" s="217" t="s">
         <v>57</v>
@@ -9963,7 +9953,7 @@
       </c>
       <c r="O37" s="215"/>
     </row>
-    <row r="38" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="204"/>
       <c r="H38" s="210" t="s">
         <v>59</v>
@@ -9980,7 +9970,7 @@
       </c>
       <c r="O38" s="201"/>
     </row>
-    <row r="39" spans="1:15" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="204"/>
       <c r="H39" s="218" t="s">
         <v>60</v>
@@ -9997,7 +9987,7 @@
       </c>
       <c r="O39" s="212"/>
     </row>
-    <row r="40" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="204"/>
       <c r="H40" s="210" t="s">
         <v>61</v>
@@ -10014,7 +10004,7 @@
       </c>
       <c r="O40" s="201"/>
     </row>
-    <row r="41" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="204"/>
       <c r="H41" s="218" t="s">
         <v>62</v>
@@ -10031,7 +10021,7 @@
       </c>
       <c r="O41" s="212"/>
     </row>
-    <row r="42" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="204"/>
       <c r="H42" s="210" t="s">
         <v>63</v>
@@ -10048,7 +10038,7 @@
       </c>
       <c r="O42" s="201"/>
     </row>
-    <row r="43" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="204"/>
       <c r="H43" s="218" t="s">
         <v>64</v>
@@ -10065,11 +10055,11 @@
       </c>
       <c r="O43" s="212"/>
     </row>
-    <row r="44" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="204"/>
       <c r="M44" s="297"/>
     </row>
-    <row r="45" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="204"/>
       <c r="H45" s="217" t="s">
         <v>65</v>
@@ -10086,7 +10076,7 @@
       </c>
       <c r="O45" s="215"/>
     </row>
-    <row r="46" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H46" s="210" t="s">
         <v>66</v>
       </c>
@@ -10102,7 +10092,7 @@
       </c>
       <c r="O46" s="201"/>
     </row>
-    <row r="47" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H47" s="218" t="s">
         <v>67</v>
       </c>
@@ -10118,7 +10108,7 @@
       </c>
       <c r="O47" s="212"/>
     </row>
-    <row r="48" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H48" s="210" t="s">
         <v>68</v>
       </c>
@@ -10134,7 +10124,7 @@
       </c>
       <c r="O48" s="201"/>
     </row>
-    <row r="49" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H49" s="218" t="s">
         <v>69</v>
       </c>
@@ -10150,7 +10140,7 @@
       </c>
       <c r="O49" s="212"/>
     </row>
-    <row r="50" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H50" s="210" t="s">
         <v>70</v>
       </c>
@@ -10166,8 +10156,8 @@
       </c>
       <c r="O50" s="201"/>
     </row>
-    <row r="51" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="200"/>
       <c r="B52" s="209" t="s">
         <v>71</v>
@@ -10186,7 +10176,7 @@
       <c r="N52" s="200"/>
       <c r="O52" s="200"/>
     </row>
-    <row r="53" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="219" t="s">
         <v>72</v>
       </c>
@@ -10230,7 +10220,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="220" t="s">
         <v>40</v>
       </c>
@@ -10274,7 +10264,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="226" t="s">
         <v>93</v>
       </c>
@@ -10318,7 +10308,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="220" t="s">
         <v>46</v>
       </c>
@@ -10362,7 +10352,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="226" t="s">
         <v>98</v>
       </c>
@@ -10406,7 +10396,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="220" t="s">
         <v>102</v>
       </c>
@@ -10450,7 +10440,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="226" t="s">
         <v>104</v>
       </c>
@@ -10494,7 +10484,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="220" t="s">
         <v>107</v>
       </c>
@@ -10538,7 +10528,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="226" t="s">
         <v>108</v>
       </c>
@@ -10582,7 +10572,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="220" t="s">
         <v>109</v>
       </c>
@@ -10626,7 +10616,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="226" t="s">
         <v>110</v>
       </c>
@@ -10670,7 +10660,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="220" t="s">
         <v>111</v>
       </c>
@@ -10714,7 +10704,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="226" t="s">
         <v>114</v>
       </c>
@@ -10758,7 +10748,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="220" t="s">
         <v>68</v>
       </c>
@@ -10802,7 +10792,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="67" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="226" t="s">
         <v>116</v>
       </c>
@@ -10846,7 +10836,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="68" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="220" t="s">
         <v>118</v>
       </c>
@@ -10890,7 +10880,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="226" t="s">
         <v>59</v>
       </c>
@@ -10934,7 +10924,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="70" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="220" t="s">
         <v>60</v>
       </c>
@@ -10978,7 +10968,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="226" t="s">
         <v>122</v>
       </c>
@@ -11022,7 +11012,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="72" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="220" t="s">
         <v>62</v>
       </c>
@@ -11066,7 +11056,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="73" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="226" t="s">
         <v>61</v>
       </c>
@@ -11110,7 +11100,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="74" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="220" t="s">
         <v>124</v>
       </c>
@@ -11154,7 +11144,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="75" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="226" t="s">
         <v>126</v>
       </c>
@@ -11198,7 +11188,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="76" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="220" t="s">
         <v>127</v>
       </c>
@@ -11242,7 +11232,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="226" t="s">
         <v>128</v>
       </c>
@@ -11286,7 +11276,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="78" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="220" t="s">
         <v>63</v>
       </c>
@@ -11330,7 +11320,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="79" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="226" t="s">
         <v>129</v>
       </c>
@@ -11374,7 +11364,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="80" spans="2:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="220" t="s">
         <v>130</v>
       </c>
@@ -11418,7 +11408,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="226" t="s">
         <v>131</v>
       </c>
@@ -11462,7 +11452,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="220" t="s">
         <v>132</v>
       </c>
@@ -11506,7 +11496,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="226" t="s">
         <v>133</v>
       </c>
@@ -11550,7 +11540,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="212"/>
       <c r="B84" s="232" t="s">
         <v>134</v>
@@ -11577,24 +11567,24 @@
       <c r="N84" s="212"/>
       <c r="O84" s="212"/>
     </row>
-    <row r="85" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" spans="1:16" ht="68.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" spans="1:16" s="169" customFormat="1" ht="59.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="1:16" ht="68.55" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="1:16" s="169" customFormat="1" ht="59.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175"/>
       <c r="B175"/>
       <c r="C175"/>
@@ -11612,8 +11602,8 @@
       <c r="O175"/>
       <c r="P175"/>
     </row>
-    <row r="177" ht="65.150000000000006" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="84.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="84.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E3:G3"/>
@@ -11733,18 +11723,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E3B875-7ADC-4741-BE27-E237F70F3A60}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
-    <col min="6" max="6" width="22.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="18" max="18" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="196" t="s">
         <v>399</v>
       </c>
@@ -11752,7 +11742,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="195" t="s">
         <v>391</v>
       </c>
@@ -11760,7 +11750,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="195" t="s">
         <v>391</v>
       </c>
@@ -11768,7 +11758,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="195" t="s">
         <v>391</v>
       </c>
@@ -11779,7 +11769,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="195" t="s">
         <v>402</v>
       </c>
@@ -11790,7 +11780,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="195" t="s">
         <v>404</v>
       </c>
@@ -11801,7 +11791,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="195" t="s">
         <v>404</v>
       </c>
@@ -11809,7 +11799,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="195" t="s">
         <v>405</v>
       </c>
@@ -11817,7 +11807,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="195" t="s">
         <v>407</v>
       </c>
@@ -11825,7 +11815,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="195" t="s">
         <v>407</v>
       </c>
@@ -11833,7 +11823,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="195" t="s">
         <v>407</v>
       </c>
@@ -11841,7 +11831,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="195" t="s">
         <v>409</v>
       </c>
@@ -11849,7 +11839,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="195" t="s">
         <v>409</v>
       </c>
@@ -11857,7 +11847,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="195" t="s">
         <v>409</v>
       </c>
@@ -11865,7 +11855,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="195" t="s">
         <v>410</v>
       </c>
@@ -11873,7 +11863,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="195" t="s">
         <v>410</v>
       </c>
@@ -11881,7 +11871,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="195" t="s">
         <v>410</v>
       </c>
@@ -11889,7 +11879,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="195" t="s">
         <v>410</v>
       </c>
@@ -11897,7 +11887,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="195" t="s">
         <v>415</v>
       </c>
@@ -11905,7 +11895,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="195" t="s">
         <v>415</v>
       </c>
@@ -11913,7 +11903,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="195" t="s">
         <v>415</v>
       </c>
@@ -11930,9 +11920,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BABA1AD-5F60-4CF2-9381-F579E93FA4C9}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>419</v>
       </c>
@@ -11943,7 +11933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -11954,7 +11944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -11965,7 +11955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -11976,7 +11966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -11989,28 +11979,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB500005-09F1-4E6A-9C5B-5530F5C9D660}">
   <dimension ref="B1:N230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" customWidth="1"/>
-    <col min="4" max="4" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="4.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="32" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
       <c r="J1"/>
     </row>
-    <row r="2" spans="2:14" ht="19.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:14" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B2" s="114" t="s">
         <v>139</v>
       </c>
@@ -12027,14 +12017,14 @@
       <c r="M2" s="113"/>
       <c r="N2" s="113"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="115" t="s">
         <v>140</v>
       </c>
@@ -12057,14 +12047,14 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
     </row>
-    <row r="6" spans="2:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="120" t="s">
         <v>146</v>
       </c>
@@ -12079,7 +12069,7 @@
       <c r="K6" s="119"/>
       <c r="L6" s="119"/>
     </row>
-    <row r="7" spans="2:14" ht="24.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" ht="24.6" x14ac:dyDescent="0.3">
       <c r="B7" s="122" t="s">
         <v>147</v>
       </c>
@@ -12114,7 +12104,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="124" t="s">
         <v>157</v>
       </c>
@@ -12159,7 +12149,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="135" t="s">
         <v>158</v>
       </c>
@@ -12204,7 +12194,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="123" t="s">
         <v>159</v>
       </c>
@@ -12249,7 +12239,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="134" t="s">
         <v>160</v>
       </c>
@@ -12294,7 +12284,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="123" t="s">
         <v>161</v>
       </c>
@@ -12339,7 +12329,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>162</v>
       </c>
@@ -12384,7 +12374,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="123" t="s">
         <v>163</v>
       </c>
@@ -12429,7 +12419,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="134" t="s">
         <v>164</v>
       </c>
@@ -12474,7 +12464,7 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="123" t="s">
         <v>165</v>
       </c>
@@ -12519,14 +12509,14 @@
         <v>⏳ En marcha</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="2:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18" s="120" t="s">
         <v>166</v>
       </c>
@@ -12543,34 +12533,34 @@
       <c r="M18" s="119"/>
       <c r="N18" s="119"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C20" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="360" t="s">
+      <c r="D20" s="364" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="360"/>
-      <c r="F20" s="360"/>
-      <c r="G20" s="361" t="s">
+      <c r="E20" s="364"/>
+      <c r="F20" s="364"/>
+      <c r="G20" s="365" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="361"/>
-      <c r="I20" s="361"/>
-      <c r="J20" s="362" t="s">
+      <c r="H20" s="365"/>
+      <c r="I20" s="365"/>
+      <c r="J20" s="366" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="362"/>
-      <c r="L20" s="362"/>
+      <c r="K20" s="366"/>
+      <c r="L20" s="366"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C21" s="146"/>
       <c r="D21" s="147" t="s">
         <v>167</v>
@@ -12600,7 +12590,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>170</v>
       </c>
@@ -12644,7 +12634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C23" s="135" t="s">
         <v>172</v>
       </c>
@@ -12685,7 +12675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C24" s="123" t="s">
         <v>173</v>
       </c>
@@ -12726,7 +12716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C25" s="134" t="s">
         <v>174</v>
       </c>
@@ -12767,7 +12757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C26" s="123" t="s">
         <v>175</v>
       </c>
@@ -12808,7 +12798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C27" s="134" t="s">
         <v>162</v>
       </c>
@@ -12849,7 +12839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C28" s="123" t="s">
         <v>176</v>
       </c>
@@ -12890,7 +12880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C29" s="134" t="s">
         <v>177</v>
       </c>
@@ -12931,7 +12921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C30" s="123" t="s">
         <v>178</v>
       </c>
@@ -12972,21 +12962,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F31"/>
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F32"/>
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32"/>
     </row>
-    <row r="33" spans="2:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33" s="120" t="s">
         <v>179</v>
       </c>
@@ -13005,7 +12995,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="122" t="s">
         <v>181</v>
       </c>
@@ -13040,7 +13030,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" s="165">
         <f>IF(Maestro!I11="","",Maestro!I11)</f>
         <v>111231</v>
@@ -13086,7 +13076,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B36" s="166">
         <f>IF(Maestro!I12="","",Maestro!I12)</f>
         <v>101647</v>
@@ -13132,7 +13122,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B37" s="165">
         <f>IF(Maestro!I13="","",Maestro!I13)</f>
         <v>102464</v>
@@ -13178,7 +13168,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B38" s="166">
         <f>IF(Maestro!I14="","",Maestro!I14)</f>
         <v>107733</v>
@@ -13224,7 +13214,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B39" s="165">
         <f>IF(Maestro!I15="","",Maestro!I15)</f>
         <v>101525</v>
@@ -13270,7 +13260,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B40" s="166">
         <f>IF(Maestro!I16="","",Maestro!I16)</f>
         <v>111116</v>
@@ -13316,7 +13306,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B41" s="165">
         <f>IF(Maestro!I17="","",Maestro!I17)</f>
         <v>101388</v>
@@ -13362,7 +13352,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B42" s="166">
         <f>IF(Maestro!I18="","",Maestro!I18)</f>
         <v>54534</v>
@@ -13408,7 +13398,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B43" s="165">
         <f>IF(Maestro!I19="","",Maestro!I19)</f>
         <v>102743</v>
@@ -13454,7 +13444,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B44" s="166">
         <f>IF(Maestro!I20="","",Maestro!I20)</f>
         <v>10561</v>
@@ -13500,7 +13490,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B45" s="165">
         <f>IF(Maestro!I21="","",Maestro!I21)</f>
         <v>102473</v>
@@ -13546,7 +13536,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B46" s="166">
         <f>IF(Maestro!I22="","",Maestro!I22)</f>
         <v>101389</v>
@@ -13592,7 +13582,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B47" s="165">
         <f>IF(Maestro!I23="","",Maestro!I23)</f>
         <v>4078</v>
@@ -13638,7 +13628,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B48" s="166">
         <f>IF(Maestro!I24="","",Maestro!I24)</f>
         <v>53835</v>
@@ -13684,7 +13674,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="165">
         <f>IF(Maestro!I25="","",Maestro!I25)</f>
         <v>105309</v>
@@ -13730,7 +13720,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="166">
         <f>IF(Maestro!I26="","",Maestro!I26)</f>
         <v>7470</v>
@@ -13776,7 +13766,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="165">
         <f>IF(Maestro!I27="","",Maestro!I27)</f>
         <v>101492</v>
@@ -13822,7 +13812,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="166">
         <f>IF(Maestro!I28="","",Maestro!I28)</f>
         <v>105591</v>
@@ -13868,7 +13858,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="165">
         <f>IF(Maestro!I29="","",Maestro!I29)</f>
         <v>3638</v>
@@ -13914,7 +13904,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="166">
         <f>IF(Maestro!I30="","",Maestro!I30)</f>
         <v>111399</v>
@@ -13960,7 +13950,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="165">
         <f>IF(Maestro!I31="","",Maestro!I31)</f>
         <v>111178</v>
@@ -14006,7 +13996,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="166">
         <f>IF(Maestro!I32="","",Maestro!I32)</f>
         <v>1892</v>
@@ -14052,7 +14042,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="165">
         <f>IF(Maestro!I33="","",Maestro!I33)</f>
         <v>107647</v>
@@ -14098,7 +14088,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="166">
         <f>IF(Maestro!I34="","",Maestro!I34)</f>
         <v>1895</v>
@@ -14144,7 +14134,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="165">
         <f>IF(Maestro!I35="","",Maestro!I35)</f>
         <v>103090</v>
@@ -14190,7 +14180,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="166">
         <f>IF(Maestro!I36="","",Maestro!I36)</f>
         <v>102847</v>
@@ -14236,7 +14226,7 @@
         <v>⏳ 0/6</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="165">
         <f>IF(Maestro!I37="","",Maestro!I37)</f>
         <v>101382</v>
@@ -14282,7 +14272,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="166">
         <f>IF(Maestro!I38="","",Maestro!I38)</f>
         <v>53140</v>
@@ -14328,7 +14318,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="165">
         <f>IF(Maestro!I39="","",Maestro!I39)</f>
         <v>103799</v>
@@ -14374,7 +14364,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="166">
         <f>IF(Maestro!I40="","",Maestro!I40)</f>
         <v>91360</v>
@@ -14420,7 +14410,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="165">
         <f>IF(Maestro!I41="","",Maestro!I41)</f>
         <v>54726</v>
@@ -14466,7 +14456,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="166">
         <f>IF(Maestro!I42="","",Maestro!I42)</f>
         <v>110697</v>
@@ -14512,7 +14502,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="165">
         <f>IF(Maestro!I43="","",Maestro!I43)</f>
         <v>103640</v>
@@ -14558,7 +14548,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="166">
         <f>IF(Maestro!I44="","",Maestro!I44)</f>
         <v>3209</v>
@@ -14604,7 +14594,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="165">
         <f>IF(Maestro!I45="","",Maestro!I45)</f>
         <v>1894</v>
@@ -14650,7 +14640,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="166">
         <f>IF(Maestro!I46="","",Maestro!I46)</f>
         <v>53632</v>
@@ -14696,7 +14686,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="165">
         <f>IF(Maestro!I47="","",Maestro!I47)</f>
         <v>110267</v>
@@ -14742,7 +14732,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="166">
         <f>IF(Maestro!I48="","",Maestro!I48)</f>
         <v>102633</v>
@@ -14788,7 +14778,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="165">
         <f>IF(Maestro!I49="","",Maestro!I49)</f>
         <v>102632</v>
@@ -14834,7 +14824,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="166">
         <f>IF(Maestro!I50="","",Maestro!I50)</f>
         <v>110043</v>
@@ -14880,7 +14870,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="165">
         <f>IF(Maestro!I51="","",Maestro!I51)</f>
         <v>16017</v>
@@ -14926,7 +14916,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="166">
         <f>IF(Maestro!I52="","",Maestro!I52)</f>
         <v>103752</v>
@@ -14972,7 +14962,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="165">
         <f>IF(Maestro!I53="","",Maestro!I53)</f>
         <v>110286</v>
@@ -15018,7 +15008,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="166">
         <f>IF(Maestro!I54="","",Maestro!I54)</f>
         <v>53237</v>
@@ -15064,7 +15054,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="165">
         <f>IF(Maestro!I55="","",Maestro!I55)</f>
         <v>116661</v>
@@ -15110,7 +15100,7 @@
         <v>⏳ 3/6</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="166">
         <f>IF(Maestro!I56="","",Maestro!I56)</f>
         <v>91501</v>
@@ -15156,7 +15146,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="165">
         <f>IF(Maestro!I57="","",Maestro!I57)</f>
         <v>101288</v>
@@ -15202,7 +15192,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="166">
         <f>IF(Maestro!I58="","",Maestro!I58)</f>
         <v>91502</v>
@@ -15248,7 +15238,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="165">
         <f>IF(Maestro!I59="","",Maestro!I59)</f>
         <v>107852</v>
@@ -15294,7 +15284,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="166">
         <f>IF(Maestro!I60="","",Maestro!I60)</f>
         <v>102630</v>
@@ -15340,7 +15330,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="165">
         <f>IF(Maestro!I61="","",Maestro!I61)</f>
         <v>109274</v>
@@ -15386,7 +15376,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="166">
         <f>IF(Maestro!I62="","",Maestro!I62)</f>
         <v>111589</v>
@@ -15432,7 +15422,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="165">
         <f>IF(Maestro!I63="","",Maestro!I63)</f>
         <v>101660</v>
@@ -15478,7 +15468,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="166">
         <f>IF(Maestro!I64="","",Maestro!I64)</f>
         <v>110642</v>
@@ -15524,7 +15514,7 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="165">
         <f>IF(Maestro!I65="","",Maestro!I65)</f>
         <v>3208</v>
@@ -15570,7 +15560,7 @@
         <v>✖ Pendiente</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="166">
         <f>IF(Maestro!I66="","",Maestro!I66)</f>
         <v>103681</v>
@@ -15616,7 +15606,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="165">
         <f>IF(Maestro!I67="","",Maestro!I67)</f>
         <v>3207</v>
@@ -15662,7 +15652,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="166">
         <f>IF(Maestro!I68="","",Maestro!I68)</f>
         <v>110425</v>
@@ -15708,7 +15698,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="165">
         <f>IF(Maestro!I69="","",Maestro!I69)</f>
         <v>110425</v>
@@ -15754,7 +15744,7 @@
         <v>⏳ 1/6</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="166">
         <f>IF(Maestro!I70="","",Maestro!I70)</f>
         <v>54768</v>
@@ -15800,154 +15790,154 @@
         <v>⏳ 2/6</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="F95"/>
       <c r="G95"/>
       <c r="H95"/>
       <c r="I95"/>
       <c r="J95"/>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="F96"/>
       <c r="G96"/>
       <c r="H96"/>
       <c r="I96"/>
       <c r="J96"/>
     </row>
-    <row r="97" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="98" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="99" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="100" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="101" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="102" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="103" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="104" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="105" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="106" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="107" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="108" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="109" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="110" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="111" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="112" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="120" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="121" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="122" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="123" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="124" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="125" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="126" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="127" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="128" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="129" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="130" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="131" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="132" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="133" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="134" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="135" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="136" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="137" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="138" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="139" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="140" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="141" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="142" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="143" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="144" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="145" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="146" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="147" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="148" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="149" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="150" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="151" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="152" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="153" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="154" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="155" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="156" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="157" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="158" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="159" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="160" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="161" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="162" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="163" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="164" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="165" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="166" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="167" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="168" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="169" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="170" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="171" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="172" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="173" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="174" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="175" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="176" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="177" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="178" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="179" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="180" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="181" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="182" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="183" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="184" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="185" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="186" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="187" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="188" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="189" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="190" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="191" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="192" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="193" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="194" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="195" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="196" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="197" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="198" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="199" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="200" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="201" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="202" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="203" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="204" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="205" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="206" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="207" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="208" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="209" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="210" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="211" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="212" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="213" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="214" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="215" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="216" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="217" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="218" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="219" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="220" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="221" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="222" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="223" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="224" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="225" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="226" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="227" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="228" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="229" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="230" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="97" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="98" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="99" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="100" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="101" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="102" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="103" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="104" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="105" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="106" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="107" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="108" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="109" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="110" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="111" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="112" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="113" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="114" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="115" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="116" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="117" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="118" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="119" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="120" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="121" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="122" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="123" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="124" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="125" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="126" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="127" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="128" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="129" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="130" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="131" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="132" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="133" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="134" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="135" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="136" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="137" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="138" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="139" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="140" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="141" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="142" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="143" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="144" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="145" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="146" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="147" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="148" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="149" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="150" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="151" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="152" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="153" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="154" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="155" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="156" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="157" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="158" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="159" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="160" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="161" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="162" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="163" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="164" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="165" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="166" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="167" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="168" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="169" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="170" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="171" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="172" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="173" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="174" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="175" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="176" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="177" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="178" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="179" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="180" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="181" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="182" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="183" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="184" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="185" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="186" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="187" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="188" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="189" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="190" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="191" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="192" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="193" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="194" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="195" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="196" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="197" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="198" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="199" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="200" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="201" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="202" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="203" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="204" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="205" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="206" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="207" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="208" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="209" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="210" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="211" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="212" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="213" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="214" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="215" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="216" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="217" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="218" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="219" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="220" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="221" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="222" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="223" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="224" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="225" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="226" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="227" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="228" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="229" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="230" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D20:F20"/>
@@ -15983,83 +15973,83 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}">
   <dimension ref="C3:BZ83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.453125" customWidth="1"/>
-    <col min="2" max="2" width="5.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" customWidth="1"/>
-    <col min="9" max="9" width="14.453125" style="78" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="15.54296875" style="1" customWidth="1"/>
-    <col min="19" max="28" width="18.453125" customWidth="1"/>
-    <col min="29" max="40" width="17.453125" customWidth="1"/>
-    <col min="41" max="41" width="9.54296875" customWidth="1"/>
-    <col min="42" max="42" width="8.54296875" customWidth="1"/>
-    <col min="43" max="43" width="17.453125" customWidth="1"/>
-    <col min="44" max="44" width="13.54296875" customWidth="1"/>
-    <col min="45" max="45" width="19.54296875" customWidth="1"/>
-    <col min="46" max="46" width="25.54296875" customWidth="1"/>
-    <col min="47" max="47" width="17.453125" customWidth="1"/>
-    <col min="48" max="51" width="14.54296875" customWidth="1"/>
-    <col min="52" max="55" width="21.54296875" customWidth="1"/>
-    <col min="71" max="71" width="18.54296875" customWidth="1"/>
-    <col min="72" max="72" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" style="78" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="15.5546875" style="1" customWidth="1"/>
+    <col min="19" max="28" width="18.44140625" customWidth="1"/>
+    <col min="29" max="40" width="17.44140625" customWidth="1"/>
+    <col min="41" max="41" width="9.5546875" customWidth="1"/>
+    <col min="42" max="42" width="8.5546875" customWidth="1"/>
+    <col min="43" max="43" width="17.44140625" customWidth="1"/>
+    <col min="44" max="44" width="13.5546875" customWidth="1"/>
+    <col min="45" max="45" width="19.5546875" customWidth="1"/>
+    <col min="46" max="46" width="25.5546875" customWidth="1"/>
+    <col min="47" max="47" width="17.44140625" customWidth="1"/>
+    <col min="48" max="51" width="14.5546875" customWidth="1"/>
+    <col min="52" max="55" width="21.5546875" customWidth="1"/>
+    <col min="71" max="71" width="18.5546875" customWidth="1"/>
+    <col min="72" max="72" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:78" ht="32.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="O3" s="336" t="s">
+    <row r="3" spans="3:78" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="356" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="336"/>
-      <c r="Q3" s="336"/>
-      <c r="R3" s="336"/>
-      <c r="S3" s="336"/>
-      <c r="T3" s="336"/>
-      <c r="U3" s="336"/>
-      <c r="V3" s="336"/>
-      <c r="W3" s="336"/>
-      <c r="X3" s="336"/>
-      <c r="Y3" s="336"/>
-      <c r="Z3" s="336"/>
-      <c r="AA3" s="336"/>
-      <c r="AB3" s="336"/>
-      <c r="AC3" s="336"/>
+      <c r="P3" s="356"/>
+      <c r="Q3" s="356"/>
+      <c r="R3" s="356"/>
+      <c r="S3" s="356"/>
+      <c r="T3" s="356"/>
+      <c r="U3" s="356"/>
+      <c r="V3" s="356"/>
+      <c r="W3" s="356"/>
+      <c r="X3" s="356"/>
+      <c r="Y3" s="356"/>
+      <c r="Z3" s="356"/>
+      <c r="AA3" s="356"/>
+      <c r="AB3" s="356"/>
+      <c r="AC3" s="356"/>
     </row>
-    <row r="4" spans="3:78" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="336"/>
-      <c r="P4" s="336"/>
-      <c r="Q4" s="336"/>
-      <c r="R4" s="336"/>
-      <c r="S4" s="336"/>
-      <c r="T4" s="336"/>
-      <c r="U4" s="336"/>
-      <c r="V4" s="336"/>
-      <c r="W4" s="336"/>
-      <c r="X4" s="336"/>
-      <c r="Y4" s="336"/>
-      <c r="Z4" s="336"/>
-      <c r="AA4" s="336"/>
-      <c r="AB4" s="336"/>
-      <c r="AC4" s="336"/>
+      <c r="O4" s="356"/>
+      <c r="P4" s="356"/>
+      <c r="Q4" s="356"/>
+      <c r="R4" s="356"/>
+      <c r="S4" s="356"/>
+      <c r="T4" s="356"/>
+      <c r="U4" s="356"/>
+      <c r="V4" s="356"/>
+      <c r="W4" s="356"/>
+      <c r="X4" s="356"/>
+      <c r="Y4" s="356"/>
+      <c r="Z4" s="356"/>
+      <c r="AA4" s="356"/>
+      <c r="AB4" s="356"/>
+      <c r="AC4" s="356"/>
     </row>
-    <row r="5" spans="3:78" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="3:78" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J6" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="3:78" ht="14.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:78" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -16068,7 +16058,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="77"/>
     </row>
-    <row r="8" spans="3:78" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:78" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -16076,17 +16066,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="337" t="s">
+      <c r="J8" s="347" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="337"/>
-      <c r="N8" s="337"/>
-      <c r="O8" s="337"/>
-      <c r="P8" s="337"/>
-      <c r="Q8" s="337"/>
-      <c r="R8" s="337"/>
+      <c r="K8" s="347"/>
+      <c r="L8" s="347"/>
+      <c r="M8" s="347"/>
+      <c r="N8" s="347"/>
+      <c r="O8" s="347"/>
+      <c r="P8" s="347"/>
+      <c r="Q8" s="347"/>
+      <c r="R8" s="347"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16101,175 +16091,175 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="338" t="s">
+      <c r="AC8" s="348" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="339"/>
-      <c r="AE8" s="339"/>
-      <c r="AF8" s="339"/>
-      <c r="AG8" s="339"/>
-      <c r="AH8" s="340"/>
-      <c r="AI8" s="341" t="s">
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="350"/>
+      <c r="AI8" s="357" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="343" t="s">
+      <c r="AL8" s="359" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="344"/>
-      <c r="AN8" s="344"/>
-      <c r="AO8" s="344"/>
-      <c r="AP8" s="344"/>
-      <c r="AQ8" s="344"/>
-      <c r="AR8" s="352" t="s">
+      <c r="AM8" s="360"/>
+      <c r="AN8" s="360"/>
+      <c r="AO8" s="360"/>
+      <c r="AP8" s="360"/>
+      <c r="AQ8" s="360"/>
+      <c r="AR8" s="351" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="352"/>
-      <c r="AU8" s="352"/>
-      <c r="AV8" s="352"/>
-      <c r="AW8" s="352"/>
-      <c r="AX8" s="352"/>
-      <c r="AY8" s="352"/>
-      <c r="AZ8" s="352"/>
+      <c r="AS8" s="351"/>
+      <c r="AT8" s="351"/>
+      <c r="AU8" s="351"/>
+      <c r="AV8" s="351"/>
+      <c r="AW8" s="351"/>
+      <c r="AX8" s="351"/>
+      <c r="AY8" s="351"/>
+      <c r="AZ8" s="351"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="349" t="s">
+      <c r="BD8" s="344" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="349"/>
-      <c r="BF8" s="349"/>
-      <c r="BG8" s="349"/>
-      <c r="BH8" s="349"/>
-      <c r="BI8" s="349"/>
-      <c r="BJ8" s="349"/>
-      <c r="BK8" s="349"/>
-      <c r="BL8" s="349"/>
-      <c r="BM8" s="349"/>
-      <c r="BN8" s="349"/>
-      <c r="BO8" s="349"/>
-      <c r="BP8" s="349"/>
-      <c r="BQ8" s="350" t="s">
+      <c r="BE8" s="344"/>
+      <c r="BF8" s="344"/>
+      <c r="BG8" s="344"/>
+      <c r="BH8" s="344"/>
+      <c r="BI8" s="344"/>
+      <c r="BJ8" s="344"/>
+      <c r="BK8" s="344"/>
+      <c r="BL8" s="344"/>
+      <c r="BM8" s="344"/>
+      <c r="BN8" s="344"/>
+      <c r="BO8" s="344"/>
+      <c r="BP8" s="344"/>
+      <c r="BQ8" s="345" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="350"/>
-      <c r="BS8" s="350"/>
+      <c r="BR8" s="345"/>
+      <c r="BS8" s="345"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
-    <row r="9" spans="3:78" s="2" customFormat="1" ht="58.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="351" t="s">
+    <row r="9" spans="3:78" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="346" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="351"/>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
-      <c r="G9" s="351"/>
-      <c r="H9" s="351"/>
-      <c r="I9" s="351"/>
-      <c r="J9" s="337" t="s">
+      <c r="D9" s="346"/>
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="G9" s="346"/>
+      <c r="H9" s="346"/>
+      <c r="I9" s="346"/>
+      <c r="J9" s="347" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="337"/>
-      <c r="L9" s="337"/>
-      <c r="M9" s="337"/>
-      <c r="N9" s="337"/>
-      <c r="O9" s="337"/>
-      <c r="P9" s="337"/>
-      <c r="Q9" s="337"/>
-      <c r="R9" s="337"/>
-      <c r="S9" s="365" t="s">
+      <c r="K9" s="347"/>
+      <c r="L9" s="347"/>
+      <c r="M9" s="347"/>
+      <c r="N9" s="347"/>
+      <c r="O9" s="347"/>
+      <c r="P9" s="347"/>
+      <c r="Q9" s="347"/>
+      <c r="R9" s="347"/>
+      <c r="S9" s="370" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="366" t="s">
+      <c r="T9" s="367" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="366" t="s">
+      <c r="U9" s="367" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="366" t="s">
+      <c r="V9" s="367" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="338" t="s">
+      <c r="AA9" s="348" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="339"/>
-      <c r="AC9" s="339"/>
-      <c r="AD9" s="339"/>
-      <c r="AE9" s="339"/>
-      <c r="AF9" s="339"/>
-      <c r="AG9" s="339"/>
-      <c r="AH9" s="340"/>
-      <c r="AI9" s="342"/>
+      <c r="AB9" s="349"/>
+      <c r="AC9" s="349"/>
+      <c r="AD9" s="349"/>
+      <c r="AE9" s="349"/>
+      <c r="AF9" s="349"/>
+      <c r="AG9" s="349"/>
+      <c r="AH9" s="350"/>
+      <c r="AI9" s="358"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="368" t="s">
+      <c r="AL9" s="369" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="368"/>
-      <c r="AN9" s="368"/>
-      <c r="AO9" s="368"/>
-      <c r="AP9" s="368"/>
-      <c r="AQ9" s="368"/>
-      <c r="AR9" s="353" t="s">
+      <c r="AM9" s="369"/>
+      <c r="AN9" s="369"/>
+      <c r="AO9" s="369"/>
+      <c r="AP9" s="369"/>
+      <c r="AQ9" s="369"/>
+      <c r="AR9" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="353"/>
-      <c r="AU9" s="353"/>
-      <c r="AV9" s="353"/>
-      <c r="AW9" s="353"/>
-      <c r="AX9" s="353"/>
-      <c r="AY9" s="353"/>
-      <c r="AZ9" s="353"/>
+      <c r="AS9" s="352"/>
+      <c r="AT9" s="352"/>
+      <c r="AU9" s="352"/>
+      <c r="AV9" s="352"/>
+      <c r="AW9" s="352"/>
+      <c r="AX9" s="352"/>
+      <c r="AY9" s="352"/>
+      <c r="AZ9" s="352"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="345" t="s">
+      <c r="BD9" s="340" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="345"/>
-      <c r="BF9" s="345"/>
-      <c r="BG9" s="345"/>
-      <c r="BH9" s="345"/>
-      <c r="BI9" s="345"/>
-      <c r="BJ9" s="345"/>
-      <c r="BK9" s="345"/>
-      <c r="BL9" s="345"/>
-      <c r="BM9" s="345"/>
-      <c r="BN9" s="345"/>
-      <c r="BO9" s="345"/>
-      <c r="BP9" s="345"/>
-      <c r="BQ9" s="348" t="s">
+      <c r="BE9" s="340"/>
+      <c r="BF9" s="340"/>
+      <c r="BG9" s="340"/>
+      <c r="BH9" s="340"/>
+      <c r="BI9" s="340"/>
+      <c r="BJ9" s="340"/>
+      <c r="BK9" s="340"/>
+      <c r="BL9" s="340"/>
+      <c r="BM9" s="340"/>
+      <c r="BN9" s="340"/>
+      <c r="BO9" s="340"/>
+      <c r="BP9" s="340"/>
+      <c r="BQ9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="348"/>
-      <c r="BS9" s="348"/>
-      <c r="BT9" s="363" t="s">
+      <c r="BR9" s="343"/>
+      <c r="BS9" s="343"/>
+      <c r="BT9" s="371" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="363" t="s">
+      <c r="BU9" s="371" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="363" t="s">
+      <c r="BV9" s="371" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="364" t="s">
+      <c r="BW9" s="372" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="3:78" ht="62.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:78" ht="62.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
         <v>217</v>
       </c>
@@ -16318,10 +16308,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="365"/>
-      <c r="T10" s="367"/>
-      <c r="U10" s="367"/>
-      <c r="V10" s="367"/>
+      <c r="S10" s="370"/>
+      <c r="T10" s="368"/>
+      <c r="U10" s="368"/>
+      <c r="V10" s="368"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16447,12 +16437,12 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="363"/>
-      <c r="BU10" s="363"/>
-      <c r="BV10" s="363"/>
-      <c r="BW10" s="364"/>
+      <c r="BT10" s="371"/>
+      <c r="BU10" s="371"/>
+      <c r="BV10" s="371"/>
+      <c r="BW10" s="372"/>
     </row>
-    <row r="11" spans="3:78" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -16736,7 +16726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:78" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -17020,7 +17010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:78" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I13,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -17304,7 +17294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:78" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I14,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -17588,7 +17578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:78" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:78" ht="87" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I15,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -17872,7 +17862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:78" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:78" ht="87" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I16,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -18156,7 +18146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I17,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -18440,7 +18430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:75" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:75" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I18,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -18724,7 +18714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I19,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -19009,7 +18999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I20,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -19293,7 +19283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I21,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -19577,7 +19567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I22,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -19861,7 +19851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:75" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:75" ht="87" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I23,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -20145,7 +20135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I24,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -20429,7 +20419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I25,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -20713,7 +20703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I26,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -20997,7 +20987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -21281,7 +21271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:75" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:75" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -21565,7 +21555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I29,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -21849,7 +21839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -22133,7 +22123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -22418,7 +22408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I32,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -22703,7 +22693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I33,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -22988,7 +22978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I34,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -23273,7 +23263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I35,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -23558,7 +23548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I36,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -23843,7 +23833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -24128,7 +24118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I38,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -24413,7 +24403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -24698,7 +24688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -24982,7 +24972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I41,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -25267,7 +25257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -25552,7 +25542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I43,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -25837,7 +25827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I44,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -26121,7 +26111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -26405,7 +26395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -26689,7 +26679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I47,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -26973,7 +26963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I48,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -27257,7 +27247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I49,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -27541,7 +27531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I50,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -27825,7 +27815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I51,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -28109,7 +28099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I52,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -28393,7 +28383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I53,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -28677,7 +28667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I54,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -28961,7 +28951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C55" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I55,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -29245,7 +29235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I56,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -29529,7 +29519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I57,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Ingeniería, Diseño e Innovación</v>
@@ -29813,7 +29803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I58,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -30097,7 +30087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I59,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -30381,7 +30371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I60,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -30665,7 +30655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C61" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I61,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -30949,7 +30939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I62,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -31233,7 +31223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I63,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -31517,7 +31507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I64,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -31801,7 +31791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I65,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Negocios, Gestión y Sostenibilidad</v>
@@ -32085,7 +32075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I66,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -32369,7 +32359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="3:75" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="3:75" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I67,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -32653,7 +32643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I68,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -32938,7 +32928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="3:75" ht="52.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="3:75" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I69,Borrador!$I$11:$I$70,Borrador!$C$11:$C$70,""),"")</f>
         <v>Facultad de Sociedad, Cultura y Creatividad</v>
@@ -33223,7 +33213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="3:75" ht="51" x14ac:dyDescent="0.35">
+    <row r="70" spans="3:75" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -33448,48 +33438,63 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="71" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB71" s="12"/>
     </row>
-    <row r="72" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="72" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB72" s="12"/>
     </row>
-    <row r="73" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="73" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB73" s="12"/>
     </row>
-    <row r="74" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="74" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB74" s="12"/>
     </row>
-    <row r="75" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="75" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB75" s="12"/>
     </row>
-    <row r="76" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="76" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB76" s="12"/>
     </row>
-    <row r="77" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="77" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB77" s="12"/>
     </row>
-    <row r="78" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="78" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB78" s="12"/>
     </row>
-    <row r="79" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="79" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB79" s="12"/>
     </row>
-    <row r="80" spans="3:75" x14ac:dyDescent="0.35">
+    <row r="80" spans="3:75" x14ac:dyDescent="0.3">
       <c r="AB80" s="12"/>
     </row>
-    <row r="81" spans="28:28" x14ac:dyDescent="0.35">
+    <row r="81" spans="28:28" x14ac:dyDescent="0.3">
       <c r="AB81" s="12"/>
     </row>
-    <row r="82" spans="28:28" x14ac:dyDescent="0.35">
+    <row r="82" spans="28:28" x14ac:dyDescent="0.3">
       <c r="AB82" s="12"/>
     </row>
-    <row r="83" spans="28:28" x14ac:dyDescent="0.35">
+    <row r="83" spans="28:28" x14ac:dyDescent="0.3">
       <c r="AB83" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="BU9:BU10"/>
+    <mergeCell ref="BV9:BV10"/>
+    <mergeCell ref="BW9:BW10"/>
+    <mergeCell ref="BD8:BP8"/>
+    <mergeCell ref="BQ8:BS8"/>
+    <mergeCell ref="BD9:BP9"/>
+    <mergeCell ref="BQ9:BS9"/>
+    <mergeCell ref="BT9:BT10"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="O3:AC4"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -33498,21 +33503,6 @@
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="AA9:AH9"/>
     <mergeCell ref="AL9:AQ9"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="BU9:BU10"/>
-    <mergeCell ref="BV9:BV10"/>
-    <mergeCell ref="BW9:BW10"/>
-    <mergeCell ref="BD8:BP8"/>
-    <mergeCell ref="BQ8:BS8"/>
-    <mergeCell ref="BD9:BP9"/>
-    <mergeCell ref="BQ9:BS9"/>
-    <mergeCell ref="BT9:BT10"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33550,49 +33540,49 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7359DEE8-DAE5-49AE-B446-489A3C2FECD3}">
   <dimension ref="A1:M37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="13" width="11.54296875" customWidth="1"/>
-    <col min="14" max="16384" width="11.54296875" hidden="1"/>
+    <col min="1" max="13" width="11.5546875" customWidth="1"/>
+    <col min="14" max="16384" width="11.5546875" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.35"/>
-    <row r="2" x14ac:dyDescent="0.35"/>
-    <row r="3" x14ac:dyDescent="0.35"/>
-    <row r="4" x14ac:dyDescent="0.35"/>
-    <row r="5" x14ac:dyDescent="0.35"/>
-    <row r="6" x14ac:dyDescent="0.35"/>
-    <row r="7" x14ac:dyDescent="0.35"/>
-    <row r="8" x14ac:dyDescent="0.35"/>
-    <row r="9" x14ac:dyDescent="0.35"/>
-    <row r="10" x14ac:dyDescent="0.35"/>
-    <row r="11" x14ac:dyDescent="0.35"/>
-    <row r="12" x14ac:dyDescent="0.35"/>
-    <row r="13" x14ac:dyDescent="0.35"/>
-    <row r="14" x14ac:dyDescent="0.35"/>
-    <row r="15" x14ac:dyDescent="0.35"/>
-    <row r="16" x14ac:dyDescent="0.35"/>
-    <row r="17" x14ac:dyDescent="0.35"/>
-    <row r="18" x14ac:dyDescent="0.35"/>
-    <row r="19" x14ac:dyDescent="0.35"/>
-    <row r="20" x14ac:dyDescent="0.35"/>
-    <row r="21" x14ac:dyDescent="0.35"/>
-    <row r="22" x14ac:dyDescent="0.35"/>
-    <row r="23" x14ac:dyDescent="0.35"/>
-    <row r="24" x14ac:dyDescent="0.35"/>
-    <row r="25" x14ac:dyDescent="0.35"/>
-    <row r="26" x14ac:dyDescent="0.35"/>
-    <row r="27" x14ac:dyDescent="0.35"/>
-    <row r="28" x14ac:dyDescent="0.35"/>
-    <row r="29" x14ac:dyDescent="0.35"/>
-    <row r="30" x14ac:dyDescent="0.35"/>
-    <row r="31" x14ac:dyDescent="0.35"/>
-    <row r="32" x14ac:dyDescent="0.35"/>
-    <row r="33" x14ac:dyDescent="0.35"/>
-    <row r="34" x14ac:dyDescent="0.35"/>
-    <row r="35" x14ac:dyDescent="0.35"/>
-    <row r="36" x14ac:dyDescent="0.35"/>
-    <row r="37" x14ac:dyDescent="0.35"/>
+    <row r="1" x14ac:dyDescent="0.3"/>
+    <row r="2" x14ac:dyDescent="0.3"/>
+    <row r="3" x14ac:dyDescent="0.3"/>
+    <row r="4" x14ac:dyDescent="0.3"/>
+    <row r="5" x14ac:dyDescent="0.3"/>
+    <row r="6" x14ac:dyDescent="0.3"/>
+    <row r="7" x14ac:dyDescent="0.3"/>
+    <row r="8" x14ac:dyDescent="0.3"/>
+    <row r="9" x14ac:dyDescent="0.3"/>
+    <row r="10" x14ac:dyDescent="0.3"/>
+    <row r="11" x14ac:dyDescent="0.3"/>
+    <row r="12" x14ac:dyDescent="0.3"/>
+    <row r="13" x14ac:dyDescent="0.3"/>
+    <row r="14" x14ac:dyDescent="0.3"/>
+    <row r="15" x14ac:dyDescent="0.3"/>
+    <row r="16" x14ac:dyDescent="0.3"/>
+    <row r="17" x14ac:dyDescent="0.3"/>
+    <row r="18" x14ac:dyDescent="0.3"/>
+    <row r="19" x14ac:dyDescent="0.3"/>
+    <row r="20" x14ac:dyDescent="0.3"/>
+    <row r="21" x14ac:dyDescent="0.3"/>
+    <row r="22" x14ac:dyDescent="0.3"/>
+    <row r="23" x14ac:dyDescent="0.3"/>
+    <row r="24" x14ac:dyDescent="0.3"/>
+    <row r="25" x14ac:dyDescent="0.3"/>
+    <row r="26" x14ac:dyDescent="0.3"/>
+    <row r="27" x14ac:dyDescent="0.3"/>
+    <row r="28" x14ac:dyDescent="0.3"/>
+    <row r="29" x14ac:dyDescent="0.3"/>
+    <row r="30" x14ac:dyDescent="0.3"/>
+    <row r="31" x14ac:dyDescent="0.3"/>
+    <row r="32" x14ac:dyDescent="0.3"/>
+    <row r="33" x14ac:dyDescent="0.3"/>
+    <row r="34" x14ac:dyDescent="0.3"/>
+    <row r="35" x14ac:dyDescent="0.3"/>
+    <row r="36" x14ac:dyDescent="0.3"/>
+    <row r="37" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -33602,91 +33592,91 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}">
   <dimension ref="C1:BM83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.453125" style="316" customWidth="1"/>
-    <col min="2" max="2" width="5.453125" style="316" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" style="316" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" style="316" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" style="316" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" style="316" customWidth="1"/>
-    <col min="7" max="8" width="11.453125" style="316"/>
-    <col min="9" max="9" width="14.453125" style="78" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="15.54296875" style="317" customWidth="1"/>
-    <col min="18" max="23" width="18.453125" style="316" customWidth="1"/>
-    <col min="24" max="31" width="17.453125" style="316" customWidth="1"/>
-    <col min="32" max="34" width="17.453125" style="78" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" style="316" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" style="316" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="316" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="316" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" style="316" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" style="316" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" style="316"/>
+    <col min="9" max="9" width="14.44140625" style="78" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="15.5546875" style="317" customWidth="1"/>
+    <col min="18" max="23" width="18.44140625" style="316" customWidth="1"/>
+    <col min="24" max="31" width="17.44140625" style="316" customWidth="1"/>
+    <col min="32" max="34" width="17.44140625" style="78" customWidth="1"/>
     <col min="35" max="35" width="16" style="316" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.453125" style="316" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17.453125" style="316" customWidth="1"/>
-    <col min="38" max="38" width="13.54296875" style="316" customWidth="1"/>
-    <col min="39" max="39" width="19.54296875" style="316" customWidth="1"/>
-    <col min="40" max="40" width="25.54296875" style="316" customWidth="1"/>
-    <col min="41" max="41" width="17.453125" style="316" customWidth="1"/>
-    <col min="42" max="44" width="14.54296875" style="316" customWidth="1"/>
-    <col min="45" max="45" width="21.54296875" style="334" customWidth="1"/>
-    <col min="46" max="47" width="11.453125" style="316"/>
-    <col min="48" max="49" width="11.453125" style="78"/>
-    <col min="50" max="53" width="11.453125" style="316"/>
-    <col min="54" max="54" width="11.453125" style="78"/>
-    <col min="55" max="59" width="11.453125" style="316"/>
-    <col min="60" max="60" width="18.54296875" style="316" customWidth="1"/>
-    <col min="61" max="61" width="19.54296875" style="316" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="17.54296875" style="316" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="18.453125" style="316" bestFit="1" customWidth="1"/>
-    <col min="64" max="16384" width="11.453125" style="316"/>
+    <col min="36" max="36" width="14.44140625" style="316" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.44140625" style="316" customWidth="1"/>
+    <col min="38" max="38" width="13.5546875" style="316" customWidth="1"/>
+    <col min="39" max="39" width="19.5546875" style="316" customWidth="1"/>
+    <col min="40" max="40" width="25.5546875" style="316" customWidth="1"/>
+    <col min="41" max="41" width="17.44140625" style="316" customWidth="1"/>
+    <col min="42" max="44" width="14.5546875" style="316" customWidth="1"/>
+    <col min="45" max="45" width="21.5546875" style="334" customWidth="1"/>
+    <col min="46" max="47" width="11.44140625" style="316"/>
+    <col min="48" max="49" width="11.44140625" style="78"/>
+    <col min="50" max="53" width="11.44140625" style="316"/>
+    <col min="54" max="54" width="11.44140625" style="78"/>
+    <col min="55" max="59" width="11.44140625" style="316"/>
+    <col min="60" max="60" width="18.5546875" style="316" customWidth="1"/>
+    <col min="61" max="61" width="19.5546875" style="316" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="17.5546875" style="316" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="18.44140625" style="316" bestFit="1" customWidth="1"/>
+    <col min="64" max="16384" width="11.44140625" style="316"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:65" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AS1" s="316"/>
     </row>
-    <row r="2" spans="3:65" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:65" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AS2" s="316"/>
     </row>
-    <row r="3" spans="3:65" ht="32.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="O3" s="336" t="s">
+    <row r="3" spans="3:65" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="356" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="336"/>
-      <c r="Q3" s="336"/>
-      <c r="R3" s="336"/>
-      <c r="S3" s="336"/>
-      <c r="T3" s="336"/>
-      <c r="U3" s="336"/>
-      <c r="V3" s="336"/>
-      <c r="W3" s="336"/>
-      <c r="X3" s="336"/>
+      <c r="P3" s="356"/>
+      <c r="Q3" s="356"/>
+      <c r="R3" s="356"/>
+      <c r="S3" s="356"/>
+      <c r="T3" s="356"/>
+      <c r="U3" s="356"/>
+      <c r="V3" s="356"/>
+      <c r="W3" s="356"/>
+      <c r="X3" s="356"/>
       <c r="AS3" s="316"/>
     </row>
-    <row r="4" spans="3:65" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="336"/>
-      <c r="P4" s="336"/>
-      <c r="Q4" s="336"/>
-      <c r="R4" s="336"/>
-      <c r="S4" s="336"/>
-      <c r="T4" s="336"/>
-      <c r="U4" s="336"/>
-      <c r="V4" s="336"/>
-      <c r="W4" s="336"/>
-      <c r="X4" s="336"/>
+      <c r="O4" s="356"/>
+      <c r="P4" s="356"/>
+      <c r="Q4" s="356"/>
+      <c r="R4" s="356"/>
+      <c r="S4" s="356"/>
+      <c r="T4" s="356"/>
+      <c r="U4" s="356"/>
+      <c r="V4" s="356"/>
+      <c r="W4" s="356"/>
+      <c r="X4" s="356"/>
       <c r="AS4" s="316"/>
     </row>
-    <row r="5" spans="3:65" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J5" s="318" t="s">
         <v>193</v>
       </c>
       <c r="AS5" s="316"/>
     </row>
-    <row r="6" spans="3:65" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J6" s="318" t="s">
         <v>194</v>
       </c>
       <c r="AS6" s="316"/>
     </row>
-    <row r="7" spans="3:65" ht="14.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:65" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -33696,7 +33686,7 @@
       <c r="I7" s="77"/>
       <c r="AS7" s="316"/>
     </row>
-    <row r="8" spans="3:65" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:65" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -33704,16 +33694,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="337" t="s">
+      <c r="J8" s="347" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="337"/>
-      <c r="N8" s="337"/>
-      <c r="O8" s="337"/>
-      <c r="P8" s="337"/>
-      <c r="Q8" s="337"/>
+      <c r="K8" s="347"/>
+      <c r="L8" s="347"/>
+      <c r="M8" s="347"/>
+      <c r="N8" s="347"/>
+      <c r="O8" s="347"/>
+      <c r="P8" s="347"/>
+      <c r="Q8" s="347"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33724,133 +33714,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="338" t="s">
+      <c r="X8" s="348" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="339"/>
-      <c r="Z8" s="339"/>
-      <c r="AA8" s="339"/>
-      <c r="AB8" s="340"/>
-      <c r="AC8" s="341" t="s">
+      <c r="Y8" s="349"/>
+      <c r="Z8" s="349"/>
+      <c r="AA8" s="349"/>
+      <c r="AB8" s="350"/>
+      <c r="AC8" s="357" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="343" t="s">
+      <c r="AF8" s="359" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="344"/>
-      <c r="AI8" s="344"/>
-      <c r="AJ8" s="344"/>
-      <c r="AK8" s="344"/>
-      <c r="AL8" s="352" t="s">
+      <c r="AG8" s="360"/>
+      <c r="AH8" s="360"/>
+      <c r="AI8" s="360"/>
+      <c r="AJ8" s="360"/>
+      <c r="AK8" s="360"/>
+      <c r="AL8" s="351" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="352"/>
-      <c r="AP8" s="352"/>
-      <c r="AQ8" s="352"/>
-      <c r="AR8" s="352"/>
-      <c r="AS8" s="352"/>
-      <c r="AT8" s="349" t="s">
+      <c r="AM8" s="351"/>
+      <c r="AN8" s="351"/>
+      <c r="AO8" s="351"/>
+      <c r="AP8" s="351"/>
+      <c r="AQ8" s="351"/>
+      <c r="AR8" s="351"/>
+      <c r="AS8" s="351"/>
+      <c r="AT8" s="344" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="349"/>
-      <c r="AV8" s="349"/>
-      <c r="AW8" s="349"/>
-      <c r="AX8" s="349"/>
-      <c r="AY8" s="349"/>
-      <c r="AZ8" s="349"/>
-      <c r="BA8" s="349"/>
-      <c r="BB8" s="349"/>
-      <c r="BC8" s="350" t="s">
+      <c r="AU8" s="344"/>
+      <c r="AV8" s="344"/>
+      <c r="AW8" s="344"/>
+      <c r="AX8" s="344"/>
+      <c r="AY8" s="344"/>
+      <c r="AZ8" s="344"/>
+      <c r="BA8" s="344"/>
+      <c r="BB8" s="344"/>
+      <c r="BC8" s="345" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="350"/>
-      <c r="BE8" s="350"/>
-      <c r="BF8" s="350"/>
-      <c r="BG8" s="350"/>
-      <c r="BH8" s="350"/>
+      <c r="BD8" s="345"/>
+      <c r="BE8" s="345"/>
+      <c r="BF8" s="345"/>
+      <c r="BG8" s="345"/>
+      <c r="BH8" s="345"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
-    <row r="9" spans="3:65" s="319" customFormat="1" ht="58.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="351" t="s">
+    <row r="9" spans="3:65" s="319" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="346" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="351"/>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
-      <c r="G9" s="351"/>
-      <c r="H9" s="351"/>
-      <c r="I9" s="351"/>
-      <c r="J9" s="337" t="s">
+      <c r="D9" s="346"/>
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="G9" s="346"/>
+      <c r="H9" s="346"/>
+      <c r="I9" s="346"/>
+      <c r="J9" s="347" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="337"/>
-      <c r="L9" s="337"/>
-      <c r="M9" s="337"/>
-      <c r="N9" s="337"/>
-      <c r="O9" s="337"/>
-      <c r="P9" s="337"/>
-      <c r="Q9" s="337"/>
+      <c r="K9" s="347"/>
+      <c r="L9" s="347"/>
+      <c r="M9" s="347"/>
+      <c r="N9" s="347"/>
+      <c r="O9" s="347"/>
+      <c r="P9" s="347"/>
+      <c r="Q9" s="347"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="338" t="s">
+      <c r="V9" s="348" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="339"/>
-      <c r="X9" s="339"/>
-      <c r="Y9" s="339"/>
-      <c r="Z9" s="339"/>
-      <c r="AA9" s="339"/>
-      <c r="AB9" s="340"/>
-      <c r="AC9" s="342"/>
-      <c r="AD9" s="354" t="s">
+      <c r="W9" s="349"/>
+      <c r="X9" s="349"/>
+      <c r="Y9" s="349"/>
+      <c r="Z9" s="349"/>
+      <c r="AA9" s="349"/>
+      <c r="AB9" s="350"/>
+      <c r="AC9" s="358"/>
+      <c r="AD9" s="353" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="355"/>
-      <c r="AF9" s="355"/>
-      <c r="AG9" s="355"/>
-      <c r="AH9" s="355"/>
-      <c r="AI9" s="355"/>
-      <c r="AJ9" s="355"/>
-      <c r="AK9" s="356"/>
-      <c r="AL9" s="353" t="s">
+      <c r="AE9" s="354"/>
+      <c r="AF9" s="354"/>
+      <c r="AG9" s="354"/>
+      <c r="AH9" s="354"/>
+      <c r="AI9" s="354"/>
+      <c r="AJ9" s="354"/>
+      <c r="AK9" s="355"/>
+      <c r="AL9" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="353"/>
-      <c r="AP9" s="353"/>
-      <c r="AQ9" s="353"/>
-      <c r="AR9" s="353"/>
-      <c r="AS9" s="353"/>
-      <c r="AT9" s="345" t="s">
+      <c r="AM9" s="352"/>
+      <c r="AN9" s="352"/>
+      <c r="AO9" s="352"/>
+      <c r="AP9" s="352"/>
+      <c r="AQ9" s="352"/>
+      <c r="AR9" s="352"/>
+      <c r="AS9" s="352"/>
+      <c r="AT9" s="340" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="345"/>
-      <c r="AV9" s="345"/>
-      <c r="AW9" s="345"/>
-      <c r="AX9" s="345"/>
-      <c r="AY9" s="346"/>
-      <c r="AZ9" s="346"/>
-      <c r="BA9" s="346"/>
-      <c r="BB9" s="346"/>
-      <c r="BC9" s="347" t="s">
+      <c r="AU9" s="340"/>
+      <c r="AV9" s="340"/>
+      <c r="AW9" s="340"/>
+      <c r="AX9" s="340"/>
+      <c r="AY9" s="341"/>
+      <c r="AZ9" s="341"/>
+      <c r="BA9" s="341"/>
+      <c r="BB9" s="341"/>
+      <c r="BC9" s="342" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="348"/>
-      <c r="BE9" s="348"/>
-      <c r="BF9" s="348"/>
-      <c r="BG9" s="348"/>
-      <c r="BH9" s="348"/>
+      <c r="BD9" s="343"/>
+      <c r="BE9" s="343"/>
+      <c r="BF9" s="343"/>
+      <c r="BG9" s="343"/>
+      <c r="BH9" s="343"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -33867,7 +33857,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="3:65" ht="62.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:65" ht="62.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
         <v>217</v>
       </c>
@@ -34058,7 +34048,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="3:65" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>4</v>
       </c>
@@ -34207,7 +34197,7 @@
       </c>
       <c r="BL11" s="12"/>
     </row>
-    <row r="12" spans="3:65" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
@@ -34338,7 +34328,7 @@
       <c r="AX12" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY12" s="373">
+      <c r="AY12" s="336">
         <v>0.22</v>
       </c>
       <c r="AZ12" s="12"/>
@@ -34360,7 +34350,7 @@
       </c>
       <c r="BL12" s="12"/>
     </row>
-    <row r="13" spans="3:65" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="s">
         <v>4</v>
       </c>
@@ -34408,7 +34398,7 @@
         <v>193</v>
       </c>
       <c r="S13" s="12"/>
-      <c r="T13" s="374" t="s">
+      <c r="T13" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U13" s="12"/>
@@ -34499,7 +34489,7 @@
       <c r="AX13" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY13" s="373">
+      <c r="AY13" s="336">
         <v>0.9</v>
       </c>
       <c r="AZ13" s="12"/>
@@ -34521,7 +34511,7 @@
       </c>
       <c r="BL13" s="12"/>
     </row>
-    <row r="14" spans="3:65" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:65" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>4</v>
       </c>
@@ -34660,7 +34650,7 @@
       </c>
       <c r="BL14" s="12"/>
     </row>
-    <row r="15" spans="3:65" customFormat="1" ht="119" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:65" customFormat="1" ht="121.8" x14ac:dyDescent="0.3">
       <c r="C15" s="23" t="s">
         <v>10</v>
       </c>
@@ -34804,7 +34794,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="16" spans="3:65" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:65" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>10</v>
       </c>
@@ -34850,7 +34840,7 @@
         <v>193</v>
       </c>
       <c r="S16" s="12"/>
-      <c r="T16" s="374" t="s">
+      <c r="T16" s="337" t="s">
         <v>421</v>
       </c>
       <c r="U16" s="12"/>
@@ -34954,7 +34944,7 @@
       </c>
       <c r="BL16" s="12"/>
     </row>
-    <row r="17" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>10</v>
       </c>
@@ -35000,7 +34990,7 @@
         <v>193</v>
       </c>
       <c r="S17" s="12"/>
-      <c r="T17" s="374" t="s">
+      <c r="T17" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U17" s="12"/>
@@ -35108,7 +35098,7 @@
       </c>
       <c r="BL17" s="12"/>
     </row>
-    <row r="18" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>10</v>
       </c>
@@ -35156,7 +35146,7 @@
         <v>193</v>
       </c>
       <c r="S18" s="12"/>
-      <c r="T18" s="374" t="s">
+      <c r="T18" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U18" s="12"/>
@@ -35266,7 +35256,7 @@
       </c>
       <c r="BL18" s="12"/>
     </row>
-    <row r="19" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="23" t="s">
         <v>10</v>
       </c>
@@ -35312,7 +35302,7 @@
         <v>193</v>
       </c>
       <c r="S19" s="12"/>
-      <c r="T19" s="374" t="s">
+      <c r="T19" s="337" t="s">
         <v>421</v>
       </c>
       <c r="U19" s="12"/>
@@ -35414,7 +35404,7 @@
       </c>
       <c r="BL19" s="12"/>
     </row>
-    <row r="20" spans="3:64" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="23" t="s">
         <v>10</v>
       </c>
@@ -35460,7 +35450,7 @@
         <v>193</v>
       </c>
       <c r="S20" s="12"/>
-      <c r="T20" s="374" t="s">
+      <c r="T20" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U20" s="12"/>
@@ -35562,7 +35552,7 @@
       </c>
       <c r="BL20" s="12"/>
     </row>
-    <row r="21" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="23" t="s">
         <v>10</v>
       </c>
@@ -35608,7 +35598,7 @@
         <v>193</v>
       </c>
       <c r="S21" s="12"/>
-      <c r="T21" s="374" t="s">
+      <c r="T21" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U21" s="12"/>
@@ -35710,7 +35700,7 @@
       </c>
       <c r="BL21" s="12"/>
     </row>
-    <row r="22" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="23" t="s">
         <v>10</v>
       </c>
@@ -35756,7 +35746,7 @@
         <v>193</v>
       </c>
       <c r="S22" s="12"/>
-      <c r="T22" s="374" t="s">
+      <c r="T22" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U22" s="12"/>
@@ -35858,7 +35848,7 @@
       </c>
       <c r="BL22" s="12"/>
     </row>
-    <row r="23" spans="3:64" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C23" s="23" t="s">
         <v>10</v>
       </c>
@@ -35906,7 +35896,7 @@
         <v>193</v>
       </c>
       <c r="S23" s="12"/>
-      <c r="T23" s="374" t="s">
+      <c r="T23" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U23" s="12"/>
@@ -35951,7 +35941,7 @@
       </c>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11"/>
-      <c r="AK23" s="376">
+      <c r="AK23" s="339">
         <v>0.1</v>
       </c>
       <c r="AL23" s="12" t="s">
@@ -36012,7 +36002,7 @@
       </c>
       <c r="BL23" s="12"/>
     </row>
-    <row r="24" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="23" t="s">
         <v>10</v>
       </c>
@@ -36056,7 +36046,7 @@
         <v>193</v>
       </c>
       <c r="S24" s="12"/>
-      <c r="T24" s="374" t="s">
+      <c r="T24" s="337" t="s">
         <v>421</v>
       </c>
       <c r="U24" s="12"/>
@@ -36157,7 +36147,7 @@
       </c>
       <c r="BL24" s="12"/>
     </row>
-    <row r="25" spans="3:64" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
@@ -36203,7 +36193,7 @@
         <v>193</v>
       </c>
       <c r="S25" s="12"/>
-      <c r="T25" s="374" t="s">
+      <c r="T25" s="337" t="s">
         <v>421</v>
       </c>
       <c r="U25" s="12"/>
@@ -36305,7 +36295,7 @@
       </c>
       <c r="BL25" s="12"/>
     </row>
-    <row r="26" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>7</v>
       </c>
@@ -36349,7 +36339,7 @@
         <v>193</v>
       </c>
       <c r="S26" s="12"/>
-      <c r="T26" s="374" t="s">
+      <c r="T26" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U26" s="12"/>
@@ -36446,7 +36436,7 @@
       </c>
       <c r="BL26" s="12"/>
     </row>
-    <row r="27" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>7</v>
       </c>
@@ -36594,7 +36584,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36748,7 +36738,7 @@
       </c>
       <c r="BL28" s="12"/>
     </row>
-    <row r="29" spans="3:64" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C29" s="23" t="s">
         <v>10</v>
       </c>
@@ -36796,7 +36786,7 @@
         <v>193</v>
       </c>
       <c r="S29" s="12"/>
-      <c r="T29" s="374" t="s">
+      <c r="T29" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U29" s="12"/>
@@ -36879,7 +36869,7 @@
       <c r="AX29" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY29" s="373">
+      <c r="AY29" s="336">
         <v>0.22</v>
       </c>
       <c r="AZ29" s="12"/>
@@ -36901,7 +36891,7 @@
       </c>
       <c r="BL29" s="12"/>
     </row>
-    <row r="30" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="22" t="s">
         <v>4</v>
       </c>
@@ -37056,7 +37046,7 @@
       </c>
       <c r="BL30" s="12"/>
     </row>
-    <row r="31" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C31" s="22" t="s">
         <v>4</v>
       </c>
@@ -37191,7 +37181,7 @@
       <c r="AX31" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY31" s="373">
+      <c r="AY31" s="336">
         <v>0.22</v>
       </c>
       <c r="AZ31" s="12"/>
@@ -37213,7 +37203,7 @@
       </c>
       <c r="BL31" s="12"/>
     </row>
-    <row r="32" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C32" s="22" t="s">
         <v>4</v>
       </c>
@@ -37349,7 +37339,7 @@
       <c r="AX32" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY32" s="373">
+      <c r="AY32" s="336">
         <v>0.22</v>
       </c>
       <c r="AZ32" s="12"/>
@@ -37371,7 +37361,7 @@
       </c>
       <c r="BL32" s="12"/>
     </row>
-    <row r="33" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="22" t="s">
         <v>4</v>
       </c>
@@ -37417,7 +37407,7 @@
         <v>193</v>
       </c>
       <c r="S33" s="12"/>
-      <c r="T33" s="374" t="s">
+      <c r="T33" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U33" s="12"/>
@@ -37519,7 +37509,7 @@
       </c>
       <c r="BL33" s="12"/>
     </row>
-    <row r="34" spans="3:64" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
         <v>10</v>
       </c>
@@ -37565,7 +37555,7 @@
         <v>193</v>
       </c>
       <c r="S34" s="12"/>
-      <c r="T34" s="374" t="s">
+      <c r="T34" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U34" s="12"/>
@@ -37674,7 +37664,7 @@
       </c>
       <c r="BL34" s="12"/>
     </row>
-    <row r="35" spans="3:64" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
         <v>10</v>
       </c>
@@ -37720,7 +37710,7 @@
         <v>193</v>
       </c>
       <c r="S35" s="12"/>
-      <c r="T35" s="374" t="s">
+      <c r="T35" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U35" s="12"/>
@@ -37822,7 +37812,7 @@
       </c>
       <c r="BL35" s="12"/>
     </row>
-    <row r="36" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C36" s="24" t="s">
         <v>7</v>
       </c>
@@ -37870,7 +37860,7 @@
         <v>193</v>
       </c>
       <c r="S36" s="12"/>
-      <c r="T36" s="374" t="s">
+      <c r="T36" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U36" s="12"/>
@@ -37980,7 +37970,7 @@
       </c>
       <c r="BL36" s="12"/>
     </row>
-    <row r="37" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C37" s="24" t="s">
         <v>7</v>
       </c>
@@ -38024,7 +38014,7 @@
         <v>192</v>
       </c>
       <c r="S37" s="12"/>
-      <c r="T37" s="374" t="s">
+      <c r="T37" s="337" t="s">
         <v>421</v>
       </c>
       <c r="U37" s="12"/>
@@ -38120,7 +38110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C38" s="24" t="s">
         <v>7</v>
       </c>
@@ -38166,7 +38156,7 @@
         <v>193</v>
       </c>
       <c r="S38" s="12"/>
-      <c r="T38" s="374" t="s">
+      <c r="T38" s="337" t="s">
         <v>421</v>
       </c>
       <c r="U38" s="12"/>
@@ -38267,7 +38257,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="24" t="s">
         <v>7</v>
       </c>
@@ -38315,7 +38305,7 @@
         <v>193</v>
       </c>
       <c r="S39" s="12"/>
-      <c r="T39" s="374" t="s">
+      <c r="T39" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U39" s="12"/>
@@ -38420,7 +38410,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:64" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:64" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C40" s="22" t="s">
         <v>4</v>
       </c>
@@ -38551,7 +38541,7 @@
       <c r="AX40" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY40" s="373">
+      <c r="AY40" s="336">
         <v>0.22</v>
       </c>
       <c r="AZ40" s="12"/>
@@ -38572,7 +38562,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -38620,7 +38610,7 @@
         <v>193</v>
       </c>
       <c r="S41" s="12"/>
-      <c r="T41" s="374" t="s">
+      <c r="T41" s="337" t="s">
         <v>423</v>
       </c>
       <c r="U41" s="12"/>
@@ -38731,7 +38721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
         <v>10</v>
       </c>
@@ -38777,7 +38767,7 @@
         <v>193</v>
       </c>
       <c r="S42" s="12"/>
-      <c r="T42" s="374" t="s">
+      <c r="T42" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U42" s="12"/>
@@ -38878,7 +38868,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C43" s="23" t="s">
         <v>10</v>
       </c>
@@ -38926,7 +38916,7 @@
         <v>193</v>
       </c>
       <c r="S43" s="12"/>
-      <c r="T43" s="374" t="s">
+      <c r="T43" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U43" s="12"/>
@@ -39009,7 +38999,7 @@
       <c r="AX43" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY43" s="373">
+      <c r="AY43" s="336">
         <v>0.3</v>
       </c>
       <c r="AZ43" s="12"/>
@@ -39030,7 +39020,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -39187,7 +39177,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="24" t="s">
         <v>7</v>
       </c>
@@ -39233,7 +39223,7 @@
         <v>193</v>
       </c>
       <c r="S45" s="12"/>
-      <c r="T45" s="374" t="s">
+      <c r="T45" s="337" t="s">
         <v>421</v>
       </c>
       <c r="U45" s="12"/>
@@ -39340,7 +39330,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C46" s="24" t="s">
         <v>7</v>
       </c>
@@ -39386,7 +39376,7 @@
         <v>193</v>
       </c>
       <c r="S46" s="12"/>
-      <c r="T46" s="374" t="s">
+      <c r="T46" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U46" s="12"/>
@@ -39489,7 +39479,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C47" s="24" t="s">
         <v>7</v>
       </c>
@@ -39537,7 +39527,7 @@
         <v>193</v>
       </c>
       <c r="S47" s="12"/>
-      <c r="T47" s="374" t="s">
+      <c r="T47" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U47" s="12"/>
@@ -39620,7 +39610,7 @@
       <c r="AX47" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="AY47" s="373">
+      <c r="AY47" s="336">
         <v>0.5</v>
       </c>
       <c r="AZ47" s="12"/>
@@ -39641,7 +39631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:64" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="24" t="s">
         <v>7</v>
       </c>
@@ -39689,7 +39679,7 @@
         <v>193</v>
       </c>
       <c r="S48" s="12"/>
-      <c r="T48" s="374" t="s">
+      <c r="T48" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U48" s="12"/>
@@ -39798,7 +39788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="22" t="s">
         <v>4</v>
       </c>
@@ -39844,7 +39834,7 @@
         <v>193</v>
       </c>
       <c r="S49" s="12"/>
-      <c r="T49" s="374" t="s">
+      <c r="T49" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U49" s="12"/>
@@ -39948,7 +39938,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="22" t="s">
         <v>4</v>
       </c>
@@ -39994,7 +39984,7 @@
         <v>193</v>
       </c>
       <c r="S50" s="12"/>
-      <c r="T50" s="374" t="s">
+      <c r="T50" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U50" s="12"/>
@@ -40097,7 +40087,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C51" s="24" t="s">
         <v>7</v>
       </c>
@@ -40145,7 +40135,7 @@
         <v>193</v>
       </c>
       <c r="S51" s="12"/>
-      <c r="T51" s="374" t="s">
+      <c r="T51" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U51" s="12"/>
@@ -40250,7 +40240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:63" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="22" t="s">
         <v>4</v>
       </c>
@@ -40399,7 +40389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:63" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="22" t="s">
         <v>4</v>
       </c>
@@ -40548,7 +40538,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:63" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="22" t="s">
         <v>4</v>
       </c>
@@ -40692,7 +40682,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="24" t="s">
         <v>7</v>
       </c>
@@ -40738,7 +40728,7 @@
         <v>193</v>
       </c>
       <c r="S55" s="12"/>
-      <c r="T55" s="374" t="s">
+      <c r="T55" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U55" s="12"/>
@@ -40845,7 +40835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
         <v>10</v>
       </c>
@@ -40893,7 +40883,7 @@
         <v>193</v>
       </c>
       <c r="S56" s="12"/>
-      <c r="T56" s="374" t="s">
+      <c r="T56" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U56" s="12"/>
@@ -40993,7 +40983,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="57" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
         <v>10</v>
       </c>
@@ -41041,7 +41031,7 @@
         <v>193</v>
       </c>
       <c r="S57" s="12"/>
-      <c r="T57" s="374" t="s">
+      <c r="T57" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U57" s="12"/>
@@ -41150,7 +41140,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:63" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="58" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
         <v>10</v>
       </c>
@@ -41196,7 +41186,7 @@
         <v>193</v>
       </c>
       <c r="S58" s="12"/>
-      <c r="T58" s="374" t="s">
+      <c r="T58" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U58" s="12"/>
@@ -41303,7 +41293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="59" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="24" t="s">
         <v>7</v>
       </c>
@@ -41456,7 +41446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="60" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="24" t="s">
         <v>7</v>
       </c>
@@ -41609,7 +41599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="61" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="24" t="s">
         <v>7</v>
       </c>
@@ -41758,7 +41748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="62" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="22" t="s">
         <v>4</v>
       </c>
@@ -41806,7 +41796,7 @@
         <v>193</v>
       </c>
       <c r="S62" s="12"/>
-      <c r="T62" s="374" t="s">
+      <c r="T62" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U62" s="12"/>
@@ -41915,7 +41905,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="63" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="22" t="s">
         <v>4</v>
       </c>
@@ -42068,7 +42058,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:63" ht="51" x14ac:dyDescent="0.35">
+    <row r="64" spans="3:63" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="22" t="s">
         <v>4</v>
       </c>
@@ -42116,7 +42106,7 @@
         <v>193</v>
       </c>
       <c r="S64" s="322"/>
-      <c r="T64" s="375" t="s">
+      <c r="T64" s="338" t="s">
         <v>422</v>
       </c>
       <c r="U64" s="322"/>
@@ -42224,7 +42214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:63" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="65" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="22" t="s">
         <v>4</v>
       </c>
@@ -42272,7 +42262,7 @@
         <v>193</v>
       </c>
       <c r="S65" s="12"/>
-      <c r="T65" s="374" t="s">
+      <c r="T65" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U65" s="12"/>
@@ -42381,7 +42371,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="66" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
@@ -42535,7 +42525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:63" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+    <row r="67" spans="3:63" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="22" t="s">
         <v>4</v>
       </c>
@@ -42581,7 +42571,7 @@
         <v>193</v>
       </c>
       <c r="S67" s="12"/>
-      <c r="T67" s="374" t="s">
+      <c r="T67" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U67" s="12"/>
@@ -42690,7 +42680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="22" t="s">
         <v>4</v>
       </c>
@@ -42736,7 +42726,7 @@
         <v>193</v>
       </c>
       <c r="S68" s="12"/>
-      <c r="T68" s="374" t="s">
+      <c r="T68" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U68" s="12"/>
@@ -42845,7 +42835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="69" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="22" t="s">
         <v>4</v>
       </c>
@@ -43006,7 +42996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:63" customFormat="1" ht="51" x14ac:dyDescent="0.35">
+    <row r="70" spans="3:63" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="22" t="s">
         <v>4</v>
       </c>
@@ -43054,7 +43044,7 @@
         <v>193</v>
       </c>
       <c r="S70" s="12"/>
-      <c r="T70" s="374" t="s">
+      <c r="T70" s="337" t="s">
         <v>422</v>
       </c>
       <c r="U70" s="12"/>
@@ -43167,24 +43157,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="3:63" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="3:63" ht="14.4" x14ac:dyDescent="0.3">
       <c r="BB71" s="315"/>
     </row>
-    <row r="72" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="3:63" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="14.5" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="3:63" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="C10:BM70" xr:uid="{FBC881F8-DB0A-4697-B988-05828068AF4E}"/>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43195,11 +43189,6 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43234,18 +43223,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12261760-D070-4F72-AB6C-8BA999431303}">
   <dimension ref="D10:E20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D10" s="369" t="s">
+    <row r="10" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D10" s="373" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="369"/>
+      <c r="E10" s="373"/>
     </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D11" s="328" t="s">
         <v>182</v>
       </c>
@@ -43253,7 +43242,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D12" s="11" t="s">
         <v>378</v>
       </c>
@@ -43261,7 +43250,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D13" s="11" t="s">
         <v>379</v>
       </c>
@@ -43269,7 +43258,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D14" s="11" t="s">
         <v>380</v>
       </c>
@@ -43277,7 +43266,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D15" s="11" t="s">
         <v>381</v>
       </c>
@@ -43285,7 +43274,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D16" s="11" t="s">
         <v>382</v>
       </c>
@@ -43293,7 +43282,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17" s="329" t="s">
         <v>382</v>
       </c>
@@ -43301,7 +43290,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D18" s="330" t="s">
         <v>383</v>
       </c>
@@ -43309,7 +43298,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D19" s="330" t="s">
         <v>384</v>
       </c>
@@ -43317,7 +43306,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D20" s="330" t="s">
         <v>384</v>
       </c>
@@ -43333,9 +43322,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ABDD32E-E34E-4D94-AE5C-77F41968FB62}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>219</v>
       </c>
@@ -43349,7 +43338,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="51" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>124</v>
       </c>
@@ -43363,7 +43352,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="51" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>325</v>
       </c>
@@ -43385,96 +43374,96 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E45BE9-C0E2-407D-BCEF-D4C7A244596E}">
   <dimension ref="C3:BB83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.453125" customWidth="1"/>
-    <col min="2" max="2" width="5.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" style="78" customWidth="1"/>
-    <col min="10" max="10" width="35.54296875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="34.54296875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="48.453125" style="1" customWidth="1"/>
-    <col min="13" max="14" width="15.54296875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="26.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" style="78" customWidth="1"/>
+    <col min="10" max="10" width="35.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="48.44140625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="15.5546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="26.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="23" style="1" customWidth="1"/>
-    <col min="17" max="17" width="25.453125" style="1" customWidth="1"/>
-    <col min="18" max="19" width="45.54296875" customWidth="1"/>
+    <col min="17" max="17" width="25.44140625" style="1" customWidth="1"/>
+    <col min="18" max="19" width="45.5546875" customWidth="1"/>
     <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="31.453125" customWidth="1"/>
-    <col min="22" max="22" width="49.54296875" customWidth="1"/>
-    <col min="23" max="23" width="20.54296875" customWidth="1"/>
-    <col min="24" max="25" width="17.453125" customWidth="1"/>
-    <col min="26" max="26" width="36.54296875" customWidth="1"/>
-    <col min="27" max="27" width="17.453125" customWidth="1"/>
-    <col min="28" max="28" width="37.81640625" customWidth="1"/>
-    <col min="29" max="29" width="30.453125" customWidth="1"/>
-    <col min="30" max="30" width="37.54296875" customWidth="1"/>
-    <col min="31" max="31" width="31.453125" customWidth="1"/>
-    <col min="32" max="32" width="15.453125" customWidth="1"/>
-    <col min="33" max="33" width="12.453125" customWidth="1"/>
-    <col min="34" max="34" width="28.54296875" customWidth="1"/>
-    <col min="35" max="35" width="21.54296875" customWidth="1"/>
-    <col min="36" max="36" width="54.453125" customWidth="1"/>
-    <col min="37" max="37" width="78.81640625" customWidth="1"/>
+    <col min="21" max="21" width="31.44140625" customWidth="1"/>
+    <col min="22" max="22" width="49.5546875" customWidth="1"/>
+    <col min="23" max="23" width="20.5546875" customWidth="1"/>
+    <col min="24" max="25" width="17.44140625" customWidth="1"/>
+    <col min="26" max="26" width="36.5546875" customWidth="1"/>
+    <col min="27" max="27" width="17.44140625" customWidth="1"/>
+    <col min="28" max="28" width="37.77734375" customWidth="1"/>
+    <col min="29" max="29" width="30.44140625" customWidth="1"/>
+    <col min="30" max="30" width="37.5546875" customWidth="1"/>
+    <col min="31" max="31" width="31.44140625" customWidth="1"/>
+    <col min="32" max="32" width="15.44140625" customWidth="1"/>
+    <col min="33" max="33" width="12.44140625" customWidth="1"/>
+    <col min="34" max="34" width="28.5546875" customWidth="1"/>
+    <col min="35" max="35" width="21.5546875" customWidth="1"/>
+    <col min="36" max="36" width="54.44140625" customWidth="1"/>
+    <col min="37" max="37" width="78.77734375" customWidth="1"/>
     <col min="38" max="38" width="37" customWidth="1"/>
     <col min="39" max="39" width="44" customWidth="1"/>
-    <col min="40" max="40" width="21.54296875" customWidth="1"/>
-    <col min="41" max="41" width="19.81640625" customWidth="1"/>
-    <col min="42" max="42" width="23.54296875" customWidth="1"/>
-    <col min="43" max="43" width="43.54296875" customWidth="1"/>
-    <col min="44" max="44" width="35.453125" customWidth="1"/>
-    <col min="45" max="45" width="27.54296875" customWidth="1"/>
-    <col min="46" max="46" width="31.453125" customWidth="1"/>
-    <col min="47" max="47" width="56.54296875" customWidth="1"/>
-    <col min="48" max="48" width="29.453125" customWidth="1"/>
+    <col min="40" max="40" width="21.5546875" customWidth="1"/>
+    <col min="41" max="41" width="19.77734375" customWidth="1"/>
+    <col min="42" max="42" width="23.5546875" customWidth="1"/>
+    <col min="43" max="43" width="43.5546875" customWidth="1"/>
+    <col min="44" max="44" width="35.44140625" customWidth="1"/>
+    <col min="45" max="45" width="27.5546875" customWidth="1"/>
+    <col min="46" max="46" width="31.44140625" customWidth="1"/>
+    <col min="47" max="47" width="56.5546875" customWidth="1"/>
+    <col min="48" max="48" width="29.44140625" customWidth="1"/>
     <col min="49" max="49" width="27" customWidth="1"/>
-    <col min="50" max="50" width="30.453125" customWidth="1"/>
-    <col min="51" max="51" width="32.453125" customWidth="1"/>
+    <col min="50" max="50" width="30.44140625" customWidth="1"/>
+    <col min="51" max="51" width="32.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:54" ht="32.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="O3" s="336" t="s">
+    <row r="3" spans="3:54" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="356" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="336"/>
-      <c r="Q3" s="336"/>
-      <c r="R3" s="336"/>
-      <c r="S3" s="336"/>
-      <c r="T3" s="336"/>
-      <c r="U3" s="336"/>
-      <c r="V3" s="336"/>
-      <c r="W3" s="336"/>
-      <c r="X3" s="336"/>
+      <c r="P3" s="356"/>
+      <c r="Q3" s="356"/>
+      <c r="R3" s="356"/>
+      <c r="S3" s="356"/>
+      <c r="T3" s="356"/>
+      <c r="U3" s="356"/>
+      <c r="V3" s="356"/>
+      <c r="W3" s="356"/>
+      <c r="X3" s="356"/>
     </row>
-    <row r="4" spans="3:54" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="336"/>
-      <c r="P4" s="336"/>
-      <c r="Q4" s="336"/>
-      <c r="R4" s="336"/>
-      <c r="S4" s="336"/>
-      <c r="T4" s="336"/>
-      <c r="U4" s="336"/>
-      <c r="V4" s="336"/>
-      <c r="W4" s="336"/>
-      <c r="X4" s="336"/>
+      <c r="O4" s="356"/>
+      <c r="P4" s="356"/>
+      <c r="Q4" s="356"/>
+      <c r="R4" s="356"/>
+      <c r="S4" s="356"/>
+      <c r="T4" s="356"/>
+      <c r="U4" s="356"/>
+      <c r="V4" s="356"/>
+      <c r="W4" s="356"/>
+      <c r="X4" s="356"/>
     </row>
-    <row r="5" spans="3:54" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="3:54" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J6" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="3:54" ht="14.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:54" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -43483,7 +43472,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="77"/>
     </row>
-    <row r="8" spans="3:54" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:54" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -43491,16 +43480,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="337" t="s">
+      <c r="J8" s="347" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="337"/>
-      <c r="N8" s="337"/>
-      <c r="O8" s="337"/>
-      <c r="P8" s="337"/>
-      <c r="Q8" s="337"/>
+      <c r="K8" s="347"/>
+      <c r="L8" s="347"/>
+      <c r="M8" s="347"/>
+      <c r="N8" s="347"/>
+      <c r="O8" s="347"/>
+      <c r="P8" s="347"/>
+      <c r="Q8" s="347"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43511,107 +43500,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="338" t="s">
+      <c r="X8" s="348" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="339"/>
-      <c r="Z8" s="339"/>
-      <c r="AA8" s="340"/>
-      <c r="AB8" s="341" t="s">
+      <c r="Y8" s="349"/>
+      <c r="Z8" s="349"/>
+      <c r="AA8" s="350"/>
+      <c r="AB8" s="357" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="343" t="s">
+      <c r="AC8" s="359" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="344"/>
-      <c r="AE8" s="344"/>
-      <c r="AF8" s="344"/>
-      <c r="AG8" s="344"/>
-      <c r="AH8" s="344"/>
-      <c r="AI8" s="352" t="s">
+      <c r="AD8" s="360"/>
+      <c r="AE8" s="360"/>
+      <c r="AF8" s="360"/>
+      <c r="AG8" s="360"/>
+      <c r="AH8" s="360"/>
+      <c r="AI8" s="351" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="352"/>
-      <c r="AK8" s="352"/>
-      <c r="AL8" s="352"/>
-      <c r="AM8" s="352"/>
-      <c r="AN8" s="352"/>
-      <c r="AO8" s="349" t="s">
+      <c r="AJ8" s="351"/>
+      <c r="AK8" s="351"/>
+      <c r="AL8" s="351"/>
+      <c r="AM8" s="351"/>
+      <c r="AN8" s="351"/>
+      <c r="AO8" s="344" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="349"/>
-      <c r="AR8" s="349"/>
-      <c r="AS8" s="350" t="s">
+      <c r="AP8" s="344"/>
+      <c r="AQ8" s="344"/>
+      <c r="AR8" s="344"/>
+      <c r="AS8" s="345" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="350"/>
-      <c r="AU8" s="350"/>
+      <c r="AT8" s="345"/>
+      <c r="AU8" s="345"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
-    <row r="9" spans="3:54" s="2" customFormat="1" ht="58.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="351" t="s">
+    <row r="9" spans="3:54" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="346" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="351"/>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
-      <c r="G9" s="351"/>
-      <c r="H9" s="351"/>
-      <c r="I9" s="351"/>
-      <c r="J9" s="337" t="s">
+      <c r="D9" s="346"/>
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="G9" s="346"/>
+      <c r="H9" s="346"/>
+      <c r="I9" s="346"/>
+      <c r="J9" s="347" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="337"/>
-      <c r="L9" s="337"/>
-      <c r="M9" s="337"/>
-      <c r="N9" s="337"/>
-      <c r="O9" s="337"/>
-      <c r="P9" s="337"/>
-      <c r="Q9" s="337"/>
+      <c r="K9" s="347"/>
+      <c r="L9" s="347"/>
+      <c r="M9" s="347"/>
+      <c r="N9" s="347"/>
+      <c r="O9" s="347"/>
+      <c r="P9" s="347"/>
+      <c r="Q9" s="347"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="338" t="s">
+      <c r="V9" s="348" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="339"/>
-      <c r="X9" s="339"/>
-      <c r="Y9" s="339"/>
-      <c r="Z9" s="339"/>
-      <c r="AA9" s="340"/>
-      <c r="AB9" s="342"/>
-      <c r="AC9" s="368" t="s">
+      <c r="W9" s="349"/>
+      <c r="X9" s="349"/>
+      <c r="Y9" s="349"/>
+      <c r="Z9" s="349"/>
+      <c r="AA9" s="350"/>
+      <c r="AB9" s="358"/>
+      <c r="AC9" s="369" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="368"/>
-      <c r="AE9" s="368"/>
-      <c r="AF9" s="368"/>
-      <c r="AG9" s="368"/>
-      <c r="AH9" s="368"/>
-      <c r="AI9" s="353" t="s">
+      <c r="AD9" s="369"/>
+      <c r="AE9" s="369"/>
+      <c r="AF9" s="369"/>
+      <c r="AG9" s="369"/>
+      <c r="AH9" s="369"/>
+      <c r="AI9" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="353"/>
-      <c r="AK9" s="353"/>
-      <c r="AL9" s="353"/>
-      <c r="AM9" s="353"/>
-      <c r="AN9" s="353"/>
-      <c r="AO9" s="345" t="s">
+      <c r="AJ9" s="352"/>
+      <c r="AK9" s="352"/>
+      <c r="AL9" s="352"/>
+      <c r="AM9" s="352"/>
+      <c r="AN9" s="352"/>
+      <c r="AO9" s="340" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="345"/>
-      <c r="AQ9" s="345"/>
-      <c r="AR9" s="345"/>
-      <c r="AS9" s="348" t="s">
+      <c r="AP9" s="340"/>
+      <c r="AQ9" s="340"/>
+      <c r="AR9" s="340"/>
+      <c r="AS9" s="343" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="348"/>
-      <c r="AU9" s="348"/>
+      <c r="AT9" s="343"/>
+      <c r="AU9" s="343"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43628,7 +43617,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="3:54" ht="62.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:54" ht="62.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="93" t="s">
         <v>217</v>
       </c>
@@ -43777,7 +43766,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="3:54" ht="51" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C11" s="90" t="s">
         <v>4</v>
       </c>
@@ -43878,7 +43867,7 @@
       </c>
       <c r="AY11" s="12"/>
     </row>
-    <row r="12" spans="3:54" ht="51" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C12" s="90" t="s">
         <v>4</v>
       </c>
@@ -43991,7 +43980,7 @@
       </c>
       <c r="AY12" s="12"/>
     </row>
-    <row r="13" spans="3:54" ht="51" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C13" s="90" t="s">
         <v>4</v>
       </c>
@@ -44092,7 +44081,7 @@
       </c>
       <c r="AY13" s="12"/>
     </row>
-    <row r="14" spans="3:54" ht="51" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C14" s="90" t="s">
         <v>4</v>
       </c>
@@ -44191,7 +44180,7 @@
       </c>
       <c r="AY14" s="12"/>
     </row>
-    <row r="15" spans="3:54" ht="51" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:54" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C15" s="91" t="s">
         <v>10</v>
       </c>
@@ -44292,7 +44281,7 @@
       </c>
       <c r="AY15" s="12"/>
     </row>
-    <row r="16" spans="3:54" ht="85" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:54" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C16" s="91" t="s">
         <v>10</v>
       </c>
@@ -44389,7 +44378,7 @@
       </c>
       <c r="AY16" s="12"/>
     </row>
-    <row r="17" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C17" s="91" t="s">
         <v>10</v>
       </c>
@@ -44476,7 +44465,7 @@
       </c>
       <c r="AY17" s="12"/>
     </row>
-    <row r="18" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C18" s="91" t="s">
         <v>10</v>
       </c>
@@ -44589,7 +44578,7 @@
       </c>
       <c r="AY18" s="12"/>
     </row>
-    <row r="19" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C19" s="91" t="s">
         <v>10</v>
       </c>
@@ -44688,7 +44677,7 @@
       </c>
       <c r="AY19" s="12"/>
     </row>
-    <row r="20" spans="3:51" ht="68" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C20" s="91" t="s">
         <v>10</v>
       </c>
@@ -44787,7 +44776,7 @@
       </c>
       <c r="AY20" s="12"/>
     </row>
-    <row r="21" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C21" s="91" t="s">
         <v>10</v>
       </c>
@@ -44886,7 +44875,7 @@
       </c>
       <c r="AY21" s="12"/>
     </row>
-    <row r="22" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C22" s="91" t="s">
         <v>10</v>
       </c>
@@ -44983,7 +44972,7 @@
       </c>
       <c r="AY22" s="12"/>
     </row>
-    <row r="23" spans="3:51" ht="85" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C23" s="91" t="s">
         <v>10</v>
       </c>
@@ -45098,7 +45087,7 @@
       </c>
       <c r="AY23" s="12"/>
     </row>
-    <row r="24" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C24" s="91" t="s">
         <v>10</v>
       </c>
@@ -45189,7 +45178,7 @@
       </c>
       <c r="AY24" s="12"/>
     </row>
-    <row r="25" spans="3:51" ht="68" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C25" s="91" t="s">
         <v>10</v>
       </c>
@@ -45288,7 +45277,7 @@
       </c>
       <c r="AY25" s="12"/>
     </row>
-    <row r="26" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C26" s="92" t="s">
         <v>7</v>
       </c>
@@ -45391,7 +45380,7 @@
       </c>
       <c r="AY26" s="12"/>
     </row>
-    <row r="27" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C27" s="92" t="s">
         <v>7</v>
       </c>
@@ -45490,7 +45479,7 @@
       </c>
       <c r="AY27" s="12"/>
     </row>
-    <row r="28" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C28" s="92" t="s">
         <v>7</v>
       </c>
@@ -45603,7 +45592,7 @@
       </c>
       <c r="AY28" s="12"/>
     </row>
-    <row r="29" spans="3:51" ht="68" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C29" s="91" t="s">
         <v>10</v>
       </c>
@@ -45718,7 +45707,7 @@
       </c>
       <c r="AY29" s="12"/>
     </row>
-    <row r="30" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C30" s="90" t="s">
         <v>4</v>
       </c>
@@ -45805,7 +45794,7 @@
       </c>
       <c r="AY30" s="12"/>
     </row>
-    <row r="31" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C31" s="90" t="s">
         <v>4</v>
       </c>
@@ -45920,7 +45909,7 @@
       </c>
       <c r="AY31" s="12"/>
     </row>
-    <row r="32" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C32" s="90" t="s">
         <v>4</v>
       </c>
@@ -46035,7 +46024,7 @@
       </c>
       <c r="AY32" s="12"/>
     </row>
-    <row r="33" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C33" s="90" t="s">
         <v>4</v>
       </c>
@@ -46134,7 +46123,7 @@
       </c>
       <c r="AY33" s="12"/>
     </row>
-    <row r="34" spans="3:51" ht="68" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C34" s="91" t="s">
         <v>10</v>
       </c>
@@ -46221,7 +46210,7 @@
       </c>
       <c r="AY34" s="12"/>
     </row>
-    <row r="35" spans="3:51" ht="68" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C35" s="91" t="s">
         <v>10</v>
       </c>
@@ -46320,7 +46309,7 @@
       </c>
       <c r="AY35" s="12"/>
     </row>
-    <row r="36" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C36" s="92" t="s">
         <v>7</v>
       </c>
@@ -46423,7 +46412,7 @@
       </c>
       <c r="AY36" s="12"/>
     </row>
-    <row r="37" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C37" s="92" t="s">
         <v>7</v>
       </c>
@@ -46523,7 +46512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C38" s="92" t="s">
         <v>7</v>
       </c>
@@ -46617,7 +46606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C39" s="92" t="s">
         <v>7</v>
       </c>
@@ -46731,7 +46720,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="3:51" ht="68" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:51" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C40" s="90" t="s">
         <v>4</v>
       </c>
@@ -46845,7 +46834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="3:51" ht="58" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:51" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C41" s="90" t="s">
         <v>4</v>
       </c>
@@ -46945,7 +46934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C42" s="91" t="s">
         <v>10</v>
       </c>
@@ -47043,7 +47032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C43" s="91" t="s">
         <v>10</v>
       </c>
@@ -47157,7 +47146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C44" s="90" t="s">
         <v>4</v>
       </c>
@@ -47257,7 +47246,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C45" s="92" t="s">
         <v>7</v>
       </c>
@@ -47343,7 +47332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C46" s="92" t="s">
         <v>7</v>
       </c>
@@ -47441,7 +47430,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C47" s="92" t="s">
         <v>7</v>
       </c>
@@ -47555,7 +47544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="3:51" ht="51" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:51" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C48" s="92" t="s">
         <v>7</v>
       </c>
@@ -47655,7 +47644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C49" s="90" t="s">
         <v>4</v>
       </c>
@@ -47739,7 +47728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C50" s="90" t="s">
         <v>4</v>
       </c>
@@ -47835,7 +47824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C51" s="92" t="s">
         <v>7</v>
       </c>
@@ -47947,7 +47936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="3:50" ht="68" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C52" s="90" t="s">
         <v>4</v>
       </c>
@@ -48043,7 +48032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="3:50" ht="68" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C53" s="90" t="s">
         <v>4</v>
       </c>
@@ -48139,7 +48128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:50" ht="68" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C54" s="90" t="s">
         <v>4</v>
       </c>
@@ -48245,7 +48234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C55" s="92" t="s">
         <v>7</v>
       </c>
@@ -48329,7 +48318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C56" s="91" t="s">
         <v>10</v>
       </c>
@@ -48423,7 +48412,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="57" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C57" s="91" t="s">
         <v>10</v>
       </c>
@@ -48523,7 +48512,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="3:50" ht="68" x14ac:dyDescent="0.35">
+    <row r="58" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C58" s="91" t="s">
         <v>10</v>
       </c>
@@ -48607,7 +48596,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="59" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C59" s="92" t="s">
         <v>7</v>
       </c>
@@ -48691,7 +48680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="60" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C60" s="92" t="s">
         <v>7</v>
       </c>
@@ -48775,7 +48764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="61" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C61" s="92" t="s">
         <v>7</v>
       </c>
@@ -48871,7 +48860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="62" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C62" s="90" t="s">
         <v>4</v>
       </c>
@@ -48971,7 +48960,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="63" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C63" s="90" t="s">
         <v>4</v>
       </c>
@@ -49055,7 +49044,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="64" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C64" s="90" t="s">
         <v>4</v>
       </c>
@@ -49167,7 +49156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="3:50" ht="68" x14ac:dyDescent="0.35">
+    <row r="65" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C65" s="90" t="s">
         <v>4</v>
       </c>
@@ -49267,7 +49256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="66" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C66" s="92" t="s">
         <v>7</v>
       </c>
@@ -49351,7 +49340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="3:50" ht="68" x14ac:dyDescent="0.35">
+    <row r="67" spans="3:50" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="C67" s="90" t="s">
         <v>4</v>
       </c>
@@ -49433,7 +49422,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C68" s="90" t="s">
         <v>4</v>
       </c>
@@ -49517,7 +49506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="69" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C69" s="90" t="s">
         <v>4</v>
       </c>
@@ -49617,7 +49606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="3:50" ht="51" x14ac:dyDescent="0.35">
+    <row r="70" spans="3:50" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C70" s="90" t="s">
         <v>4</v>
       </c>
@@ -49717,52 +49706,47 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="71" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W71" s="12"/>
     </row>
-    <row r="72" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="72" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W72" s="12"/>
     </row>
-    <row r="73" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="73" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W73" s="12"/>
     </row>
-    <row r="74" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="74" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W74" s="12"/>
     </row>
-    <row r="75" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="75" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W75" s="12"/>
     </row>
-    <row r="76" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="76" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W76" s="12"/>
     </row>
-    <row r="77" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="77" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W77" s="12"/>
     </row>
-    <row r="78" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="78" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W78" s="12"/>
     </row>
-    <row r="79" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="79" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W79" s="12"/>
     </row>
-    <row r="80" spans="3:50" x14ac:dyDescent="0.35">
+    <row r="80" spans="3:50" x14ac:dyDescent="0.3">
       <c r="W80" s="12"/>
     </row>
-    <row r="81" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="81" spans="23:23" x14ac:dyDescent="0.3">
       <c r="W81" s="12"/>
     </row>
-    <row r="82" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="82" spans="23:23" x14ac:dyDescent="0.3">
       <c r="W82" s="12"/>
     </row>
-    <row r="83" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="83" spans="23:23" x14ac:dyDescent="0.3">
       <c r="W83" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49773,6 +49757,11 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -49813,55 +49802,55 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06CB0E3-701B-45AE-AB79-3AAE71B2CA0C}">
   <dimension ref="A2:T31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
-    <col min="6" max="6" width="22.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="18" max="18" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="371" t="s">
+    <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="375" t="s">
         <v>391</v>
       </c>
-      <c r="B2" s="371"/>
-      <c r="C2" s="371"/>
+      <c r="B2" s="375"/>
+      <c r="C2" s="375"/>
       <c r="D2" t="s">
         <v>392</v>
       </c>
-      <c r="E2" s="371" t="s">
+      <c r="E2" s="375" t="s">
         <v>393</v>
       </c>
-      <c r="F2" s="371"/>
+      <c r="F2" s="375"/>
       <c r="G2" s="181" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="370" t="s">
+      <c r="H2" s="374" t="s">
         <v>394</v>
       </c>
-      <c r="I2" s="370"/>
-      <c r="J2" s="370"/>
-      <c r="K2" s="370" t="s">
+      <c r="I2" s="374"/>
+      <c r="J2" s="374"/>
+      <c r="K2" s="374" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="371"/>
-      <c r="M2" s="371"/>
-      <c r="N2" s="370" t="s">
+      <c r="L2" s="375"/>
+      <c r="M2" s="375"/>
+      <c r="N2" s="374" t="s">
         <v>395</v>
       </c>
-      <c r="O2" s="371"/>
-      <c r="P2" s="371"/>
-      <c r="Q2" s="372"/>
-      <c r="R2" s="370" t="s">
+      <c r="O2" s="375"/>
+      <c r="P2" s="375"/>
+      <c r="Q2" s="376"/>
+      <c r="R2" s="374" t="s">
         <v>211</v>
       </c>
-      <c r="S2" s="371"/>
+      <c r="S2" s="375"/>
     </row>
-    <row r="3" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="85" t="s">
         <v>224</v>
       </c>
@@ -49923,22 +49912,22 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="195" t="s">
         <v>391</v>
       </c>
@@ -49946,7 +49935,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="195" t="s">
         <v>391</v>
       </c>
@@ -49954,7 +49943,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="195" t="s">
         <v>391</v>
       </c>
@@ -49962,7 +49951,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="78" t="s">
         <v>392</v>
       </c>
@@ -49970,7 +49959,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="195" t="s">
         <v>393</v>
       </c>
@@ -49978,7 +49967,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="195" t="s">
         <v>393</v>
       </c>
@@ -49986,7 +49975,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="171" t="s">
         <v>199</v>
       </c>
@@ -49994,7 +49983,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="195" t="s">
         <v>394</v>
       </c>
@@ -50002,7 +49991,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="195" t="s">
         <v>394</v>
       </c>
@@ -50010,7 +49999,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="195" t="s">
         <v>394</v>
       </c>
@@ -50018,7 +50007,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="78" t="s">
         <v>23</v>
       </c>
@@ -50026,7 +50015,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="78" t="s">
         <v>23</v>
       </c>
@@ -50034,7 +50023,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="78" t="s">
         <v>23</v>
       </c>
@@ -50042,7 +50031,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="78" t="s">
         <v>395</v>
       </c>
@@ -50050,7 +50039,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="78" t="s">
         <v>395</v>
       </c>
@@ -50058,7 +50047,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="78" t="s">
         <v>395</v>
       </c>
@@ -50066,7 +50055,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="78" t="s">
         <v>395</v>
       </c>
@@ -50074,7 +50063,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>211</v>
       </c>
@@ -50082,7 +50071,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>211</v>
       </c>
@@ -50090,7 +50079,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>211</v>
       </c>
@@ -50113,9 +50102,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50257,26 +50249,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -50300,9 +50281,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Reforma_Curricular/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran.sharepoint.com/sites/PlaneacinyGestinInstitucional-REFORMACURRICULAR/Documentos compartidos/REFORMA CURRICULAR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13476" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1335EB00-23C1-43D4-9807-C9F588968DB8}"/>
+  <xr:revisionPtr revIDLastSave="13725" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3A4017C-D1F8-48C0-8B94-7155FDB6C489}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -20,17 +20,18 @@
     <sheet name="Borrador" sheetId="3" r:id="rId5"/>
     <sheet name="Hoja3" sheetId="15" r:id="rId6"/>
     <sheet name="Hoja2" sheetId="14" r:id="rId7"/>
-    <sheet name="Borrador (2)" sheetId="6" state="hidden" r:id="rId8"/>
-    <sheet name="Hoja1" sheetId="1" state="hidden" r:id="rId9"/>
-    <sheet name="Estructura" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet name="_Listas" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="Criterios de calidad" sheetId="16" r:id="rId8"/>
+    <sheet name="Borrador (2)" sheetId="6" state="hidden" r:id="rId9"/>
+    <sheet name="Hoja1" sheetId="1" state="hidden" r:id="rId10"/>
+    <sheet name="Estructura" sheetId="10" state="hidden" r:id="rId11"/>
+    <sheet name="_Listas" sheetId="11" state="hidden" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Borrador!$C$10:$BM$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Borrador (2)'!$C$8:$AY$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Maestro!$C$10:$BZ$10</definedName>
     <definedName name="TABLA_REV">[1]!Tabla2[#All]</definedName>
   </definedNames>
@@ -508,7 +509,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4412" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4474" uniqueCount="467">
   <si>
     <t>RC</t>
   </si>
@@ -1466,9 +1467,6 @@
     <t>Negocios Internacionales</t>
   </si>
   <si>
-    <t>En visita de pares académicos pero se debe cotejar si todo coincide</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
@@ -1617,9 +1615,6 @@
   </si>
   <si>
     <t>Maestría en Contratación Estatal</t>
-  </si>
-  <si>
-    <t>Con notificación MEN</t>
   </si>
   <si>
     <t>Agosto de 2024</t>
@@ -1808,7 +1803,142 @@
     <t>Finalizado</t>
   </si>
   <si>
-    <t>BOGOTA-Finalizado</t>
+    <t>¿Cuál es el Tipo de trámite de aseguramiento de la calidad?</t>
+  </si>
+  <si>
+    <t>¿El estado del programa desde Aseguramiento está claramente definido?</t>
+  </si>
+  <si>
+    <t>¿Cúel es el Estado del trámite?</t>
+  </si>
+  <si>
+    <t>¿El plan de estudios es único y equivalente (MEN = Reforma)</t>
+  </si>
+  <si>
+    <t>¿El Instrumento de verificación curricular diligenciado de manera correcta?</t>
+  </si>
+  <si>
+    <t>¿El formato banner esta diligenciado de manera correcta?</t>
+  </si>
+  <si>
+    <t>¿Syllabus completos, versionados y consistentes?</t>
+  </si>
+  <si>
+    <t>¿Cuántos Syllabus son?</t>
+  </si>
+  <si>
+    <t>¿La reforma cumple la Política Curricular?</t>
+  </si>
+  <si>
+    <t>¿La vicerrectoría académica aprueba la reforma?</t>
+  </si>
+  <si>
+    <t>¿Requiere informar al MEN previa implementación?</t>
+  </si>
+  <si>
+    <t>¿El formato de proyecciones académicas y financieras esta diligenciado?</t>
+  </si>
+  <si>
+    <t>¿Se cuenta con el visto bueno académico?</t>
+  </si>
+  <si>
+    <t>¿Se cuenta con el visto bueno financiero?</t>
+  </si>
+  <si>
+    <t>¿El plan de virtualización esta aprobado?</t>
+  </si>
+  <si>
+    <t>¿Cuántos módulos deben crearse?</t>
+  </si>
+  <si>
+    <t>¿Cuántos módulos deben actualizarse?</t>
+  </si>
+  <si>
+    <t>¿Cuál es el % de avance de contenidos virtuales?</t>
+  </si>
+  <si>
+    <t>¿Cuántos módulos virtuales tiene el programa?</t>
+  </si>
+  <si>
+    <t>¿Se tiene el plan de estudios?</t>
+  </si>
+  <si>
+    <t>¿Se deben crear o actualizar Aulas Máster?</t>
+  </si>
+  <si>
+    <t>¿Cuántas Aulas Máster se deben crear?</t>
+  </si>
+  <si>
+    <t>¿Cuántas Aulas Máster se deben Actualizar?</t>
+  </si>
+  <si>
+    <t>¿Se tiene Ruta sugerida programa homologación/articulación convenio</t>
+  </si>
+  <si>
+    <t>¿Se tiene el Acta de homologación</t>
+  </si>
+  <si>
+    <t>¿El programa aplica para convenios / Homologación?</t>
+  </si>
+  <si>
+    <t>¿Se tiene el Formato reconocimiento de competencias o resultados de aprendizaje para homologación?</t>
+  </si>
+  <si>
+    <t>¿Se tiene el Formato acta currículo articulación SENA?</t>
+  </si>
+  <si>
+    <t>¿Se tiene el Formato acta currículo homologación/convenios?</t>
+  </si>
+  <si>
+    <t>¿Cuál es el % de avance de parametrización de convenios?</t>
+  </si>
+  <si>
+    <t>¿El Maestro de convenios esta Actualizado?</t>
+  </si>
+  <si>
+    <t>¿El programa se debe parametrizar en Banner?</t>
+  </si>
+  <si>
+    <t>¿La parametrización del programa en Banner esta?</t>
+  </si>
+  <si>
+    <t>¿Cuál es el % de avance de parametrización del programa en Banner?</t>
+  </si>
+  <si>
+    <t>¿El plan de estudios esta en formato PDF?</t>
+  </si>
+  <si>
+    <t>¿El programa cuenta con su actualización comercial?</t>
+  </si>
+  <si>
+    <t>¿El programa esta listo para publicar en página web?</t>
+  </si>
+  <si>
+    <t>Seguramiento de la calidad</t>
+  </si>
+  <si>
+    <t>Dirección de curriculo</t>
+  </si>
+  <si>
+    <t>Secretaría academica y docencia</t>
+  </si>
+  <si>
+    <t>Planeación Financiera</t>
+  </si>
+  <si>
+    <t>Gerencia de Educación Virtual</t>
+  </si>
+  <si>
+    <t>Convenios Institucionales</t>
+  </si>
+  <si>
+    <t>Operaciones académicas</t>
+  </si>
+  <si>
+    <t>Desarrollo de Mercado</t>
+  </si>
+  <si>
+    <t>Aprobado</t>
   </si>
 </sst>
 </file>
@@ -1818,7 +1948,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="82" x14ac:knownFonts="1">
+  <fonts count="83" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2433,8 +2563,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="55">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2741,6 +2877,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC301"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE072BE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="22">
     <border>
@@ -2991,7 +3145,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="377">
+  <cellXfs count="390">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3838,68 +3992,45 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="26" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3919,22 +4050,82 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5290,9 +5481,9 @@
   <colors>
     <mruColors>
       <color rgb="FFE072BE"/>
+      <color rgb="FF53D2FF"/>
+      <color rgb="FFFFC301"/>
       <color rgb="FF552579"/>
-      <color rgb="FFFFC301"/>
-      <color rgb="FF53D2FF"/>
       <color rgb="FF3CE0B5"/>
       <color rgb="FF3292EA"/>
     </mruColors>
@@ -8607,6 +8798,10 @@
 </externalLink>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Francisco Javier Joya Vargas" id="{107E5F63-F4F9-4333-B827-F2411F5B2461}" userId="S::fjoya@poligran.edu.co::8dff1f57-3734-439b-9420-c7b70004bff6" providerId="AD"/>
@@ -9241,11 +9436,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="283"/>
-      <c r="E3" s="361" t="s">
+      <c r="E3" s="354" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="362"/>
-      <c r="G3" s="363"/>
+      <c r="F3" s="355"/>
+      <c r="G3" s="356"/>
       <c r="H3" s="281" t="s">
         <v>8</v>
       </c>
@@ -11721,6 +11916,308 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06CB0E3-701B-45AE-AB79-3AAE71B2CA0C}">
+  <dimension ref="A2:T31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="388" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="388"/>
+      <c r="C2" s="388"/>
+      <c r="D2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" s="388" t="s">
+        <v>391</v>
+      </c>
+      <c r="F2" s="388"/>
+      <c r="G2" s="181" t="s">
+        <v>199</v>
+      </c>
+      <c r="H2" s="387" t="s">
+        <v>392</v>
+      </c>
+      <c r="I2" s="387"/>
+      <c r="J2" s="387"/>
+      <c r="K2" s="387" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="388"/>
+      <c r="M2" s="388"/>
+      <c r="N2" s="387" t="s">
+        <v>393</v>
+      </c>
+      <c r="O2" s="388"/>
+      <c r="P2" s="388"/>
+      <c r="Q2" s="389"/>
+      <c r="R2" s="387" t="s">
+        <v>211</v>
+      </c>
+      <c r="S2" s="388"/>
+    </row>
+    <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="85" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="85" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="85" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="85" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="179" t="s">
+        <v>234</v>
+      </c>
+      <c r="F3" s="179" t="s">
+        <v>235</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="H3" s="87" t="s">
+        <v>231</v>
+      </c>
+      <c r="I3" s="87" t="s">
+        <v>244</v>
+      </c>
+      <c r="J3" s="87" t="s">
+        <v>160</v>
+      </c>
+      <c r="K3" s="88" t="s">
+        <v>159</v>
+      </c>
+      <c r="L3" s="88" t="s">
+        <v>248</v>
+      </c>
+      <c r="M3" s="89" t="s">
+        <v>247</v>
+      </c>
+      <c r="N3" s="89" t="s">
+        <v>253</v>
+      </c>
+      <c r="O3" s="89" t="s">
+        <v>254</v>
+      </c>
+      <c r="P3" s="178" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q3" s="88" t="s">
+        <v>255</v>
+      </c>
+      <c r="R3" s="89" t="s">
+        <v>258</v>
+      </c>
+      <c r="S3" s="89" t="s">
+        <v>246</v>
+      </c>
+      <c r="T3" s="89" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="195" t="s">
+        <v>389</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="195" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="195" t="s">
+        <v>389</v>
+      </c>
+      <c r="B14" s="85" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="78" t="s">
+        <v>390</v>
+      </c>
+      <c r="B15" s="85" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="195" t="s">
+        <v>391</v>
+      </c>
+      <c r="B16" s="179" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="195" t="s">
+        <v>391</v>
+      </c>
+      <c r="B17" s="179" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="171" t="s">
+        <v>199</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="195" t="s">
+        <v>392</v>
+      </c>
+      <c r="B19" s="87" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="195" t="s">
+        <v>392</v>
+      </c>
+      <c r="B20" s="87" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="195" t="s">
+        <v>392</v>
+      </c>
+      <c r="B21" s="87" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="88" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="88" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="89" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="B25" s="89" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="B27" s="178" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="B28" s="88" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>211</v>
+      </c>
+      <c r="B29" s="89" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" s="89" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>211</v>
+      </c>
+      <c r="B31" s="89" t="s">
+        <v>214</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E3B875-7ADC-4741-BE27-E237F70F3A60}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11736,7 +12233,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="196" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B1" s="196" t="s">
         <v>147</v>
@@ -11744,56 +12241,56 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="195" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B2" s="197" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="195" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B3" s="197" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="195" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B4" s="197" t="s">
         <v>205</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="195" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B5" s="197" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="195" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B6" s="197" t="s">
         <v>234</v>
       </c>
       <c r="D6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="195" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B7" s="197" t="s">
         <v>235</v>
@@ -11801,15 +12298,15 @@
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="195" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B8" s="197" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="195" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B9" s="197" t="s">
         <v>231</v>
@@ -11817,15 +12314,15 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="195" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B10" s="197" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="195" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B11" s="197" t="s">
         <v>160</v>
@@ -11833,7 +12330,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="195" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B12" s="197" t="s">
         <v>159</v>
@@ -11841,7 +12338,7 @@
     </row>
     <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="195" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B13" s="197" t="s">
         <v>248</v>
@@ -11849,7 +12346,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="195" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B14" s="197" t="s">
         <v>247</v>
@@ -11857,58 +12354,58 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="195" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B15" s="197" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="195" t="s">
+        <v>408</v>
+      </c>
+      <c r="B16" s="197" t="s">
         <v>410</v>
-      </c>
-      <c r="B16" s="197" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="195" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B17" s="197" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="195" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B18" s="197" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="195" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B19" s="197" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="195" t="s">
+        <v>413</v>
+      </c>
+      <c r="B20" s="197" t="s">
         <v>415</v>
-      </c>
-      <c r="B20" s="197" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="195" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B21" s="197" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -11917,14 +12414,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BABA1AD-5F60-4CF2-9381-F579E93FA4C9}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -12155,11 +12652,11 @@
       </c>
       <c r="C9" s="139">
         <f>COUNTIF(Maestro!U11:U70,"finalizado")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="140">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E9" s="141">
         <f>COUNTIF(Maestro!U11:U70,"en proceso")</f>
@@ -12179,7 +12676,7 @@
       </c>
       <c r="I9" s="145">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J9" s="145">
         <f>COUNTA(Maestro!E11:E70)</f>
@@ -12544,21 +13041,21 @@
       <c r="C20" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="364" t="s">
+      <c r="D20" s="357" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="364"/>
-      <c r="F20" s="364"/>
-      <c r="G20" s="365" t="s">
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
+      <c r="G20" s="358" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="365"/>
-      <c r="I20" s="365"/>
-      <c r="J20" s="366" t="s">
+      <c r="H20" s="358"/>
+      <c r="I20" s="358"/>
+      <c r="J20" s="359" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="366"/>
-      <c r="L20" s="366"/>
+      <c r="K20" s="359"/>
+      <c r="L20" s="359"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C21" s="146"/>
@@ -12652,7 +13149,7 @@
       </c>
       <c r="G23" s="153">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!U11:U70,"finalizado")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="154">
         <f>COUNTIFS(Maestro!F11:F70,"Virtual",Maestro!U11:U70,"en proceso")</f>
@@ -13851,7 +14348,7 @@
       </c>
       <c r="K52" s="138" t="str">
         <f>IF(B52="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B52,Maestro!$I$11:$I$70,Maestro!$BP$11:$BP$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
-        <v>0,22</v>
+        <v>0,35</v>
       </c>
       <c r="L52" s="138" t="str">
         <f t="shared" si="6"/>
@@ -13943,7 +14440,7 @@
       </c>
       <c r="K54" s="138" t="str">
         <f>IF(B54="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B54,Maestro!$I$11:$I$70,Maestro!$BP$11:$BP$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
-        <v>0,22</v>
+        <v>0,35</v>
       </c>
       <c r="L54" s="138" t="str">
         <f t="shared" si="6"/>
@@ -13989,7 +14486,7 @@
       </c>
       <c r="K55" s="158" t="str">
         <f>IF(B55="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B55,Maestro!$I$11:$I$70,Maestro!$BP$11:$BP$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
-        <v>0,22</v>
+        <v>0,35</v>
       </c>
       <c r="L55" s="158" t="str">
         <f t="shared" si="6"/>
@@ -14387,7 +14884,7 @@
       </c>
       <c r="G64" s="137" t="str">
         <f>IF(B64="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B64,Maestro!$I$11:$I$70,Maestro!$U$11:$U$70,"—"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v)))))</f>
-        <v>BOGOTA-Finalizado</v>
+        <v>Finalizado</v>
       </c>
       <c r="H64" s="137" t="str">
         <f>IF(B64="","",_xlfn.LET(_xlpm.v,_xlfn.XLOOKUP(B64,Maestro!$I$11:$I$70,Maestro!$AQ$11:$AQ$70,"—"),IF(ISNUMBER(_xlpm.v),TEXT(_xlpm.v,"0%"),IF(_xlpm.v="","—",IF(LEN(_xlpm.v)&gt;1,UPPER(LEFT(_xlpm.v,1))&amp;MID(_xlpm.v,2,LEN(_xlpm.v)),UPPER(_xlpm.v))))))</f>
@@ -14407,7 +14904,7 @@
       </c>
       <c r="L64" s="138" t="str">
         <f t="shared" si="6"/>
-        <v>⏳ 1/6</v>
+        <v>⏳ 2/6</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.3">
@@ -16001,43 +16498,43 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:78" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="356" t="s">
+      <c r="O3" s="372" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="356"/>
-      <c r="Q3" s="356"/>
-      <c r="R3" s="356"/>
-      <c r="S3" s="356"/>
-      <c r="T3" s="356"/>
-      <c r="U3" s="356"/>
-      <c r="V3" s="356"/>
-      <c r="W3" s="356"/>
-      <c r="X3" s="356"/>
-      <c r="Y3" s="356"/>
-      <c r="Z3" s="356"/>
-      <c r="AA3" s="356"/>
-      <c r="AB3" s="356"/>
-      <c r="AC3" s="356"/>
+      <c r="P3" s="372"/>
+      <c r="Q3" s="372"/>
+      <c r="R3" s="372"/>
+      <c r="S3" s="372"/>
+      <c r="T3" s="372"/>
+      <c r="U3" s="372"/>
+      <c r="V3" s="372"/>
+      <c r="W3" s="372"/>
+      <c r="X3" s="372"/>
+      <c r="Y3" s="372"/>
+      <c r="Z3" s="372"/>
+      <c r="AA3" s="372"/>
+      <c r="AB3" s="372"/>
+      <c r="AC3" s="372"/>
     </row>
     <row r="4" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="356"/>
-      <c r="P4" s="356"/>
-      <c r="Q4" s="356"/>
-      <c r="R4" s="356"/>
-      <c r="S4" s="356"/>
-      <c r="T4" s="356"/>
-      <c r="U4" s="356"/>
-      <c r="V4" s="356"/>
-      <c r="W4" s="356"/>
-      <c r="X4" s="356"/>
-      <c r="Y4" s="356"/>
-      <c r="Z4" s="356"/>
-      <c r="AA4" s="356"/>
-      <c r="AB4" s="356"/>
-      <c r="AC4" s="356"/>
+      <c r="O4" s="372"/>
+      <c r="P4" s="372"/>
+      <c r="Q4" s="372"/>
+      <c r="R4" s="372"/>
+      <c r="S4" s="372"/>
+      <c r="T4" s="372"/>
+      <c r="U4" s="372"/>
+      <c r="V4" s="372"/>
+      <c r="W4" s="372"/>
+      <c r="X4" s="372"/>
+      <c r="Y4" s="372"/>
+      <c r="Z4" s="372"/>
+      <c r="AA4" s="372"/>
+      <c r="AB4" s="372"/>
+      <c r="AC4" s="372"/>
     </row>
     <row r="5" spans="3:78" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -16066,17 +16563,17 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="347" t="s">
+      <c r="J8" s="368" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="347"/>
-      <c r="L8" s="347"/>
-      <c r="M8" s="347"/>
-      <c r="N8" s="347"/>
-      <c r="O8" s="347"/>
-      <c r="P8" s="347"/>
-      <c r="Q8" s="347"/>
-      <c r="R8" s="347"/>
+      <c r="K8" s="368"/>
+      <c r="L8" s="368"/>
+      <c r="M8" s="368"/>
+      <c r="N8" s="368"/>
+      <c r="O8" s="368"/>
+      <c r="P8" s="368"/>
+      <c r="Q8" s="368"/>
+      <c r="R8" s="368"/>
       <c r="S8" s="5" t="s">
         <v>196</v>
       </c>
@@ -16091,168 +16588,168 @@
       <c r="Z8" s="75"/>
       <c r="AA8" s="75"/>
       <c r="AB8" s="75"/>
-      <c r="AC8" s="348" t="s">
+      <c r="AC8" s="373" t="s">
         <v>198</v>
       </c>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="350"/>
-      <c r="AI8" s="357" t="s">
+      <c r="AD8" s="374"/>
+      <c r="AE8" s="374"/>
+      <c r="AF8" s="374"/>
+      <c r="AG8" s="374"/>
+      <c r="AH8" s="375"/>
+      <c r="AI8" s="376" t="s">
         <v>199</v>
       </c>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
-      <c r="AL8" s="359" t="s">
+      <c r="AL8" s="378" t="s">
         <v>200</v>
       </c>
-      <c r="AM8" s="360"/>
-      <c r="AN8" s="360"/>
-      <c r="AO8" s="360"/>
-      <c r="AP8" s="360"/>
-      <c r="AQ8" s="360"/>
-      <c r="AR8" s="351" t="s">
+      <c r="AM8" s="379"/>
+      <c r="AN8" s="379"/>
+      <c r="AO8" s="379"/>
+      <c r="AP8" s="379"/>
+      <c r="AQ8" s="379"/>
+      <c r="AR8" s="366" t="s">
         <v>201</v>
       </c>
-      <c r="AS8" s="351"/>
-      <c r="AT8" s="351"/>
-      <c r="AU8" s="351"/>
-      <c r="AV8" s="351"/>
-      <c r="AW8" s="351"/>
-      <c r="AX8" s="351"/>
-      <c r="AY8" s="351"/>
-      <c r="AZ8" s="351"/>
+      <c r="AS8" s="366"/>
+      <c r="AT8" s="366"/>
+      <c r="AU8" s="366"/>
+      <c r="AV8" s="366"/>
+      <c r="AW8" s="366"/>
+      <c r="AX8" s="366"/>
+      <c r="AY8" s="366"/>
+      <c r="AZ8" s="366"/>
       <c r="BA8" s="174"/>
       <c r="BB8" s="174"/>
       <c r="BC8" s="174"/>
-      <c r="BD8" s="344" t="s">
+      <c r="BD8" s="362" t="s">
         <v>202</v>
       </c>
-      <c r="BE8" s="344"/>
-      <c r="BF8" s="344"/>
-      <c r="BG8" s="344"/>
-      <c r="BH8" s="344"/>
-      <c r="BI8" s="344"/>
-      <c r="BJ8" s="344"/>
-      <c r="BK8" s="344"/>
-      <c r="BL8" s="344"/>
-      <c r="BM8" s="344"/>
-      <c r="BN8" s="344"/>
-      <c r="BO8" s="344"/>
-      <c r="BP8" s="344"/>
-      <c r="BQ8" s="345" t="s">
+      <c r="BE8" s="362"/>
+      <c r="BF8" s="362"/>
+      <c r="BG8" s="362"/>
+      <c r="BH8" s="362"/>
+      <c r="BI8" s="362"/>
+      <c r="BJ8" s="362"/>
+      <c r="BK8" s="362"/>
+      <c r="BL8" s="362"/>
+      <c r="BM8" s="362"/>
+      <c r="BN8" s="362"/>
+      <c r="BO8" s="362"/>
+      <c r="BP8" s="362"/>
+      <c r="BQ8" s="363" t="s">
         <v>203</v>
       </c>
-      <c r="BR8" s="345"/>
-      <c r="BS8" s="345"/>
+      <c r="BR8" s="363"/>
+      <c r="BS8" s="363"/>
       <c r="BT8" s="14"/>
       <c r="BU8" s="14"/>
       <c r="BV8" s="14"/>
       <c r="BW8" s="14"/>
     </row>
     <row r="9" spans="3:78" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="346" t="s">
+      <c r="C9" s="349" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="346"/>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
-      <c r="G9" s="346"/>
-      <c r="H9" s="346"/>
-      <c r="I9" s="346"/>
-      <c r="J9" s="347" t="s">
+      <c r="D9" s="349"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
+      <c r="G9" s="349"/>
+      <c r="H9" s="349"/>
+      <c r="I9" s="349"/>
+      <c r="J9" s="368" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="347"/>
-      <c r="L9" s="347"/>
-      <c r="M9" s="347"/>
-      <c r="N9" s="347"/>
-      <c r="O9" s="347"/>
-      <c r="P9" s="347"/>
-      <c r="Q9" s="347"/>
-      <c r="R9" s="347"/>
-      <c r="S9" s="370" t="s">
+      <c r="K9" s="368"/>
+      <c r="L9" s="368"/>
+      <c r="M9" s="368"/>
+      <c r="N9" s="368"/>
+      <c r="O9" s="368"/>
+      <c r="P9" s="368"/>
+      <c r="Q9" s="368"/>
+      <c r="R9" s="368"/>
+      <c r="S9" s="369" t="s">
         <v>205</v>
       </c>
-      <c r="T9" s="367" t="s">
+      <c r="T9" s="370" t="s">
         <v>206</v>
       </c>
-      <c r="U9" s="367" t="s">
+      <c r="U9" s="370" t="s">
         <v>158</v>
       </c>
-      <c r="V9" s="367" t="s">
+      <c r="V9" s="370" t="s">
         <v>207</v>
       </c>
       <c r="W9" s="198"/>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
       <c r="Z9" s="198"/>
-      <c r="AA9" s="348" t="s">
+      <c r="AA9" s="373" t="s">
         <v>208</v>
       </c>
-      <c r="AB9" s="349"/>
-      <c r="AC9" s="349"/>
-      <c r="AD9" s="349"/>
-      <c r="AE9" s="349"/>
-      <c r="AF9" s="349"/>
-      <c r="AG9" s="349"/>
-      <c r="AH9" s="350"/>
-      <c r="AI9" s="358"/>
+      <c r="AB9" s="374"/>
+      <c r="AC9" s="374"/>
+      <c r="AD9" s="374"/>
+      <c r="AE9" s="374"/>
+      <c r="AF9" s="374"/>
+      <c r="AG9" s="374"/>
+      <c r="AH9" s="375"/>
+      <c r="AI9" s="377"/>
       <c r="AJ9" s="172"/>
       <c r="AK9" s="172"/>
-      <c r="AL9" s="369" t="s">
+      <c r="AL9" s="380" t="s">
         <v>209</v>
       </c>
-      <c r="AM9" s="369"/>
-      <c r="AN9" s="369"/>
-      <c r="AO9" s="369"/>
-      <c r="AP9" s="369"/>
-      <c r="AQ9" s="369"/>
-      <c r="AR9" s="352" t="s">
+      <c r="AM9" s="380"/>
+      <c r="AN9" s="380"/>
+      <c r="AO9" s="380"/>
+      <c r="AP9" s="380"/>
+      <c r="AQ9" s="380"/>
+      <c r="AR9" s="367" t="s">
         <v>201</v>
       </c>
-      <c r="AS9" s="352"/>
-      <c r="AT9" s="352"/>
-      <c r="AU9" s="352"/>
-      <c r="AV9" s="352"/>
-      <c r="AW9" s="352"/>
-      <c r="AX9" s="352"/>
-      <c r="AY9" s="352"/>
-      <c r="AZ9" s="352"/>
+      <c r="AS9" s="367"/>
+      <c r="AT9" s="367"/>
+      <c r="AU9" s="367"/>
+      <c r="AV9" s="367"/>
+      <c r="AW9" s="367"/>
+      <c r="AX9" s="367"/>
+      <c r="AY9" s="367"/>
+      <c r="AZ9" s="367"/>
       <c r="BA9" s="175"/>
       <c r="BB9" s="175"/>
       <c r="BC9" s="175"/>
-      <c r="BD9" s="340" t="s">
+      <c r="BD9" s="364" t="s">
         <v>210</v>
       </c>
-      <c r="BE9" s="340"/>
-      <c r="BF9" s="340"/>
-      <c r="BG9" s="340"/>
-      <c r="BH9" s="340"/>
-      <c r="BI9" s="340"/>
-      <c r="BJ9" s="340"/>
-      <c r="BK9" s="340"/>
-      <c r="BL9" s="340"/>
-      <c r="BM9" s="340"/>
-      <c r="BN9" s="340"/>
-      <c r="BO9" s="340"/>
-      <c r="BP9" s="340"/>
-      <c r="BQ9" s="343" t="s">
+      <c r="BE9" s="364"/>
+      <c r="BF9" s="364"/>
+      <c r="BG9" s="364"/>
+      <c r="BH9" s="364"/>
+      <c r="BI9" s="364"/>
+      <c r="BJ9" s="364"/>
+      <c r="BK9" s="364"/>
+      <c r="BL9" s="364"/>
+      <c r="BM9" s="364"/>
+      <c r="BN9" s="364"/>
+      <c r="BO9" s="364"/>
+      <c r="BP9" s="364"/>
+      <c r="BQ9" s="365" t="s">
         <v>211</v>
       </c>
-      <c r="BR9" s="343"/>
-      <c r="BS9" s="343"/>
-      <c r="BT9" s="371" t="s">
+      <c r="BR9" s="365"/>
+      <c r="BS9" s="365"/>
+      <c r="BT9" s="360" t="s">
         <v>212</v>
       </c>
-      <c r="BU9" s="371" t="s">
+      <c r="BU9" s="360" t="s">
         <v>213</v>
       </c>
-      <c r="BV9" s="371" t="s">
+      <c r="BV9" s="360" t="s">
         <v>214</v>
       </c>
-      <c r="BW9" s="372" t="s">
+      <c r="BW9" s="361" t="s">
         <v>215</v>
       </c>
       <c r="BZ9" s="2" t="s">
@@ -16308,10 +16805,10 @@
       <c r="R10" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="S10" s="370"/>
-      <c r="T10" s="368"/>
-      <c r="U10" s="368"/>
-      <c r="V10" s="368"/>
+      <c r="S10" s="369"/>
+      <c r="T10" s="371"/>
+      <c r="U10" s="371"/>
+      <c r="V10" s="371"/>
       <c r="W10" s="173" t="s">
         <v>205</v>
       </c>
@@ -16437,10 +16934,10 @@
       <c r="BS10" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="BT10" s="371"/>
-      <c r="BU10" s="371"/>
-      <c r="BV10" s="371"/>
-      <c r="BW10" s="372"/>
+      <c r="BT10" s="360"/>
+      <c r="BU10" s="360"/>
+      <c r="BV10" s="360"/>
+      <c r="BW10" s="361"/>
     </row>
     <row r="11" spans="3:78" ht="52.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="str">
@@ -16711,7 +17208,7 @@
       </c>
       <c r="BT11" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU11" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -16719,7 +17216,7 @@
       </c>
       <c r="BV11" s="34" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,Borrador!$BK$11:$BK$70,""),"")</f>
-        <v>2026-2</v>
+        <v>2027-1</v>
       </c>
       <c r="BW11" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I11,Borrador!$I$11:$I$70,Borrador!$BL$11:$BL$70,""),"")</f>
@@ -16995,7 +17492,7 @@
       </c>
       <c r="BT12" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU12" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I12,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -21089,7 +21586,7 @@
       </c>
       <c r="AB27" s="12" t="str" cm="1">
         <f t="array" ref="AB27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AB$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>En visita de pares académicos pero se debe cotejar si todo coincide</v>
+        <v>Aprobado por el MEN</v>
       </c>
       <c r="AC27" s="54" t="str" cm="1">
         <f t="array" ref="AC27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AC$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21110,7 +21607,7 @@
       </c>
       <c r="AH27" s="12" t="str" cm="1">
         <f t="array" ref="AH27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AH$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Pendiente</v>
+        <v>Aprobado</v>
       </c>
       <c r="AI27" s="12" t="str" cm="1">
         <f t="array" ref="AI27">IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AI$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21264,7 +21761,7 @@
       </c>
       <c r="BV27" s="34" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,Borrador!$BK$11:$BK$70,""),"")</f>
-        <v>2027-1</v>
+        <v>2026-2</v>
       </c>
       <c r="BW27" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I27,Borrador!$I$11:$I$70,Borrador!$BL$11:$BL$70,""),"")</f>
@@ -21496,7 +21993,7 @@
       </c>
       <c r="BI28" s="12" cm="1">
         <f t="array" ref="BI28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BI$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="BJ28" s="12" cm="1">
         <f t="array" ref="BJ28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -21524,7 +22021,7 @@
       </c>
       <c r="BP28" s="12" cm="1">
         <f t="array" ref="BP28">IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="BQ28" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,Borrador!$BC$11:$BC$70,""),"")</f>
@@ -21540,7 +22037,7 @@
       </c>
       <c r="BT28" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU28" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -21548,7 +22045,7 @@
       </c>
       <c r="BV28" s="34" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,Borrador!$BK$11:$BK$70,""),"")</f>
-        <v>2026-2</v>
+        <v>2027-1</v>
       </c>
       <c r="BW28" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I28,Borrador!$I$11:$I$70,Borrador!$BL$11:$BL$70,""),"")</f>
@@ -22064,7 +22561,7 @@
       </c>
       <c r="BI30" s="12" cm="1">
         <f t="array" ref="BI30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BI$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="BJ30" s="12" cm="1">
         <f t="array" ref="BJ30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22092,7 +22589,7 @@
       </c>
       <c r="BP30" s="12" cm="1">
         <f t="array" ref="BP30">IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="BQ30" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,Borrador!$BC$11:$BC$70,""),"")</f>
@@ -22108,7 +22605,7 @@
       </c>
       <c r="BT30" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU30" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I30,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -22349,7 +22846,7 @@
       </c>
       <c r="BI31" s="12" cm="1">
         <f t="array" ref="BI31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BI$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="BJ31" s="12" cm="1">
         <f t="array" ref="BJ31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BJ$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -22377,7 +22874,7 @@
       </c>
       <c r="BP31" s="12" cm="1">
         <f t="array" ref="BP31">IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(BP$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="BQ31" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,Borrador!$BC$11:$BC$70,""),"")</f>
@@ -22393,7 +22890,7 @@
       </c>
       <c r="BT31" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU31" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I31,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -24103,7 +24600,7 @@
       </c>
       <c r="BT37" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU37" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I37,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -24506,7 +25003,7 @@
       </c>
       <c r="AB39" s="12" t="str" cm="1">
         <f t="array" ref="AB39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AB$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>En elaboración de documentación</v>
+        <v>Aprobado por el MEN</v>
       </c>
       <c r="AC39" s="54" t="str" cm="1">
         <f t="array" ref="AC39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AC$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24527,7 +25024,7 @@
       </c>
       <c r="AH39" s="12" t="str" cm="1">
         <f t="array" ref="AH39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AH$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>No aplica</v>
+        <v>Aprobado</v>
       </c>
       <c r="AI39" s="12" t="str" cm="1">
         <f t="array" ref="AI39">IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AI$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -24673,7 +25170,7 @@
       </c>
       <c r="BT39" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU39" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I39,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -24762,7 +25259,7 @@
       </c>
       <c r="U40" s="12" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,Borrador!$T$11:$T$70,""),"")</f>
-        <v>BOGOTA-Finalizado</v>
+        <v>Finalizado</v>
       </c>
       <c r="V40" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,Borrador!$U$11:$U$70,""),"")</f>
@@ -24778,7 +25275,7 @@
       </c>
       <c r="Y40" s="76" t="str" cm="1">
         <f t="array" ref="Y40">IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(Y$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>BOGOTA-Finalizado</v>
+        <v>Finalizado</v>
       </c>
       <c r="Z40" s="76" t="str" cm="1">
         <f t="array" ref="Z40">IFERROR(_xlfn.XLOOKUP($I40,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(Z$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -25527,7 +26024,7 @@
       </c>
       <c r="BT42" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU42" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -25535,7 +26032,7 @@
       </c>
       <c r="BV42" s="34" t="str">
         <f>IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,Borrador!$BK$11:$BK$70,""),"")</f>
-        <v>2026-2</v>
+        <v>2027-1</v>
       </c>
       <c r="BW42" s="12">
         <f>IFERROR(_xlfn.XLOOKUP($I42,Borrador!$I$11:$I$70,Borrador!$BL$11:$BL$70,""),"")</f>
@@ -26380,7 +26877,7 @@
       </c>
       <c r="BT45" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU45" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I45,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -26664,7 +27161,7 @@
       </c>
       <c r="BT46" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,Borrador!$BI$11:$BI$70,""),"")</f>
-        <v>0</v>
+        <v>46199</v>
       </c>
       <c r="BU46" s="11">
         <f>IFERROR(_xlfn.XLOOKUP($I46,Borrador!$I$11:$I$70,Borrador!$BJ$11:$BJ$70,""),"")</f>
@@ -31041,7 +31538,7 @@
       </c>
       <c r="AB62" s="12" t="str" cm="1">
         <f t="array" ref="AB62">IFERROR(_xlfn.XLOOKUP($I62,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AB$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
-        <v>Con notificación MEN</v>
+        <v>Notificado al MEN</v>
       </c>
       <c r="AC62" s="54" t="str" cm="1">
         <f t="array" ref="AC62">IFERROR(_xlfn.XLOOKUP($I62,Borrador!$I$11:$I$70,_xlfn.XLOOKUP(AC$10,Borrador!$C$10:$BL$10,Borrador!$C$11:$BL$70,"",0,1),""),"")</f>
@@ -33480,6 +33977,21 @@
   </sheetData>
   <autoFilter ref="C10:BZ10" xr:uid="{0DE7F4C8-C4D9-4718-9A45-DE15ED66A68A}"/>
   <mergeCells count="23">
+    <mergeCell ref="O3:AC4"/>
+    <mergeCell ref="J8:R8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AL8:AQ8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="AA9:AH9"/>
+    <mergeCell ref="AL9:AQ9"/>
+    <mergeCell ref="AR8:AZ8"/>
+    <mergeCell ref="AR9:AZ9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
     <mergeCell ref="BU9:BU10"/>
     <mergeCell ref="BV9:BV10"/>
     <mergeCell ref="BW9:BW10"/>
@@ -33488,21 +34000,6 @@
     <mergeCell ref="BD9:BP9"/>
     <mergeCell ref="BQ9:BS9"/>
     <mergeCell ref="BT9:BT10"/>
-    <mergeCell ref="AR8:AZ8"/>
-    <mergeCell ref="AR9:AZ9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="O3:AC4"/>
-    <mergeCell ref="J8:R8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AL8:AQ8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="AA9:AH9"/>
-    <mergeCell ref="AL9:AQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M69 M70:N70">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="En Proceso">
@@ -33634,34 +34131,34 @@
       <c r="AS2" s="316"/>
     </row>
     <row r="3" spans="3:65" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="356" t="s">
+      <c r="O3" s="372" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="356"/>
-      <c r="Q3" s="356"/>
-      <c r="R3" s="356"/>
-      <c r="S3" s="356"/>
-      <c r="T3" s="356"/>
-      <c r="U3" s="356"/>
-      <c r="V3" s="356"/>
-      <c r="W3" s="356"/>
-      <c r="X3" s="356"/>
+      <c r="P3" s="372"/>
+      <c r="Q3" s="372"/>
+      <c r="R3" s="372"/>
+      <c r="S3" s="372"/>
+      <c r="T3" s="372"/>
+      <c r="U3" s="372"/>
+      <c r="V3" s="372"/>
+      <c r="W3" s="372"/>
+      <c r="X3" s="372"/>
       <c r="AS3" s="316"/>
     </row>
     <row r="4" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J4" s="318" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="356"/>
-      <c r="P4" s="356"/>
-      <c r="Q4" s="356"/>
-      <c r="R4" s="356"/>
-      <c r="S4" s="356"/>
-      <c r="T4" s="356"/>
-      <c r="U4" s="356"/>
-      <c r="V4" s="356"/>
-      <c r="W4" s="356"/>
-      <c r="X4" s="356"/>
+      <c r="O4" s="372"/>
+      <c r="P4" s="372"/>
+      <c r="Q4" s="372"/>
+      <c r="R4" s="372"/>
+      <c r="S4" s="372"/>
+      <c r="T4" s="372"/>
+      <c r="U4" s="372"/>
+      <c r="V4" s="372"/>
+      <c r="W4" s="372"/>
+      <c r="X4" s="372"/>
       <c r="AS4" s="316"/>
     </row>
     <row r="5" spans="3:65" ht="14.4" x14ac:dyDescent="0.3">
@@ -33694,16 +34191,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="347" t="s">
+      <c r="J8" s="368" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="347"/>
-      <c r="L8" s="347"/>
-      <c r="M8" s="347"/>
-      <c r="N8" s="347"/>
-      <c r="O8" s="347"/>
-      <c r="P8" s="347"/>
-      <c r="Q8" s="347"/>
+      <c r="K8" s="368"/>
+      <c r="L8" s="368"/>
+      <c r="M8" s="368"/>
+      <c r="N8" s="368"/>
+      <c r="O8" s="368"/>
+      <c r="P8" s="368"/>
+      <c r="Q8" s="368"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -33714,133 +34211,133 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="348" t="s">
+      <c r="X8" s="373" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="349"/>
-      <c r="Z8" s="349"/>
-      <c r="AA8" s="349"/>
-      <c r="AB8" s="350"/>
-      <c r="AC8" s="357" t="s">
+      <c r="Y8" s="374"/>
+      <c r="Z8" s="374"/>
+      <c r="AA8" s="374"/>
+      <c r="AB8" s="375"/>
+      <c r="AC8" s="376" t="s">
         <v>199</v>
       </c>
       <c r="AD8" s="170"/>
       <c r="AE8" s="170"/>
-      <c r="AF8" s="359" t="s">
+      <c r="AF8" s="378" t="s">
         <v>200</v>
       </c>
-      <c r="AG8" s="360"/>
-      <c r="AH8" s="360"/>
-      <c r="AI8" s="360"/>
-      <c r="AJ8" s="360"/>
-      <c r="AK8" s="360"/>
-      <c r="AL8" s="351" t="s">
+      <c r="AG8" s="379"/>
+      <c r="AH8" s="379"/>
+      <c r="AI8" s="379"/>
+      <c r="AJ8" s="379"/>
+      <c r="AK8" s="379"/>
+      <c r="AL8" s="366" t="s">
         <v>201</v>
       </c>
-      <c r="AM8" s="351"/>
-      <c r="AN8" s="351"/>
-      <c r="AO8" s="351"/>
-      <c r="AP8" s="351"/>
-      <c r="AQ8" s="351"/>
-      <c r="AR8" s="351"/>
-      <c r="AS8" s="351"/>
-      <c r="AT8" s="344" t="s">
+      <c r="AM8" s="366"/>
+      <c r="AN8" s="366"/>
+      <c r="AO8" s="366"/>
+      <c r="AP8" s="366"/>
+      <c r="AQ8" s="366"/>
+      <c r="AR8" s="366"/>
+      <c r="AS8" s="366"/>
+      <c r="AT8" s="362" t="s">
         <v>202</v>
       </c>
-      <c r="AU8" s="344"/>
-      <c r="AV8" s="344"/>
-      <c r="AW8" s="344"/>
-      <c r="AX8" s="344"/>
-      <c r="AY8" s="344"/>
-      <c r="AZ8" s="344"/>
-      <c r="BA8" s="344"/>
-      <c r="BB8" s="344"/>
-      <c r="BC8" s="345" t="s">
+      <c r="AU8" s="362"/>
+      <c r="AV8" s="362"/>
+      <c r="AW8" s="362"/>
+      <c r="AX8" s="362"/>
+      <c r="AY8" s="362"/>
+      <c r="AZ8" s="362"/>
+      <c r="BA8" s="362"/>
+      <c r="BB8" s="362"/>
+      <c r="BC8" s="363" t="s">
         <v>203</v>
       </c>
-      <c r="BD8" s="345"/>
-      <c r="BE8" s="345"/>
-      <c r="BF8" s="345"/>
-      <c r="BG8" s="345"/>
-      <c r="BH8" s="345"/>
+      <c r="BD8" s="363"/>
+      <c r="BE8" s="363"/>
+      <c r="BF8" s="363"/>
+      <c r="BG8" s="363"/>
+      <c r="BH8" s="363"/>
       <c r="BI8" s="14"/>
       <c r="BJ8" s="14"/>
       <c r="BK8" s="14"/>
       <c r="BL8" s="14"/>
     </row>
     <row r="9" spans="3:65" s="319" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="346" t="s">
+      <c r="C9" s="349" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="346"/>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
-      <c r="G9" s="346"/>
-      <c r="H9" s="346"/>
-      <c r="I9" s="346"/>
-      <c r="J9" s="347" t="s">
+      <c r="D9" s="349"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
+      <c r="G9" s="349"/>
+      <c r="H9" s="349"/>
+      <c r="I9" s="349"/>
+      <c r="J9" s="368" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="347"/>
-      <c r="L9" s="347"/>
-      <c r="M9" s="347"/>
-      <c r="N9" s="347"/>
-      <c r="O9" s="347"/>
-      <c r="P9" s="347"/>
-      <c r="Q9" s="347"/>
+      <c r="K9" s="368"/>
+      <c r="L9" s="368"/>
+      <c r="M9" s="368"/>
+      <c r="N9" s="368"/>
+      <c r="O9" s="368"/>
+      <c r="P9" s="368"/>
+      <c r="Q9" s="368"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="348" t="s">
+      <c r="V9" s="373" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="349"/>
-      <c r="X9" s="349"/>
-      <c r="Y9" s="349"/>
-      <c r="Z9" s="349"/>
-      <c r="AA9" s="349"/>
-      <c r="AB9" s="350"/>
-      <c r="AC9" s="358"/>
-      <c r="AD9" s="353" t="s">
+      <c r="W9" s="374"/>
+      <c r="X9" s="374"/>
+      <c r="Y9" s="374"/>
+      <c r="Z9" s="374"/>
+      <c r="AA9" s="374"/>
+      <c r="AB9" s="375"/>
+      <c r="AC9" s="377"/>
+      <c r="AD9" s="383" t="s">
         <v>209</v>
       </c>
-      <c r="AE9" s="354"/>
-      <c r="AF9" s="354"/>
-      <c r="AG9" s="354"/>
-      <c r="AH9" s="354"/>
-      <c r="AI9" s="354"/>
-      <c r="AJ9" s="354"/>
-      <c r="AK9" s="355"/>
-      <c r="AL9" s="352" t="s">
+      <c r="AE9" s="384"/>
+      <c r="AF9" s="384"/>
+      <c r="AG9" s="384"/>
+      <c r="AH9" s="384"/>
+      <c r="AI9" s="384"/>
+      <c r="AJ9" s="384"/>
+      <c r="AK9" s="385"/>
+      <c r="AL9" s="367" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="352"/>
-      <c r="AN9" s="352"/>
-      <c r="AO9" s="352"/>
-      <c r="AP9" s="352"/>
-      <c r="AQ9" s="352"/>
-      <c r="AR9" s="352"/>
-      <c r="AS9" s="352"/>
-      <c r="AT9" s="340" t="s">
+      <c r="AM9" s="367"/>
+      <c r="AN9" s="367"/>
+      <c r="AO9" s="367"/>
+      <c r="AP9" s="367"/>
+      <c r="AQ9" s="367"/>
+      <c r="AR9" s="367"/>
+      <c r="AS9" s="367"/>
+      <c r="AT9" s="364" t="s">
         <v>210</v>
       </c>
-      <c r="AU9" s="340"/>
-      <c r="AV9" s="340"/>
-      <c r="AW9" s="340"/>
-      <c r="AX9" s="340"/>
-      <c r="AY9" s="341"/>
-      <c r="AZ9" s="341"/>
-      <c r="BA9" s="341"/>
-      <c r="BB9" s="341"/>
-      <c r="BC9" s="342" t="s">
+      <c r="AU9" s="364"/>
+      <c r="AV9" s="364"/>
+      <c r="AW9" s="364"/>
+      <c r="AX9" s="364"/>
+      <c r="AY9" s="381"/>
+      <c r="AZ9" s="381"/>
+      <c r="BA9" s="381"/>
+      <c r="BB9" s="381"/>
+      <c r="BC9" s="382" t="s">
         <v>211</v>
       </c>
-      <c r="BD9" s="343"/>
-      <c r="BE9" s="343"/>
-      <c r="BF9" s="343"/>
-      <c r="BG9" s="343"/>
-      <c r="BH9" s="343"/>
+      <c r="BD9" s="365"/>
+      <c r="BE9" s="365"/>
+      <c r="BF9" s="365"/>
+      <c r="BG9" s="365"/>
+      <c r="BH9" s="365"/>
       <c r="BI9" s="83" t="s">
         <v>212</v>
       </c>
@@ -34343,10 +34840,12 @@
       <c r="BF12" s="177"/>
       <c r="BG12" s="177"/>
       <c r="BH12" s="12"/>
-      <c r="BI12" s="11"/>
+      <c r="BI12" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ12" s="11"/>
       <c r="BK12" s="34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BL12" s="12"/>
     </row>
@@ -34399,7 +34898,7 @@
       </c>
       <c r="S13" s="12"/>
       <c r="T13" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U13" s="12"/>
       <c r="V13" s="186" t="s">
@@ -34504,7 +35003,9 @@
       <c r="BF13" s="177"/>
       <c r="BG13" s="177"/>
       <c r="BH13" s="12"/>
-      <c r="BI13" s="11"/>
+      <c r="BI13" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ13" s="11"/>
       <c r="BK13" s="34" t="s">
         <v>14</v>
@@ -34563,7 +35064,7 @@
         <v>269</v>
       </c>
       <c r="W14" s="187" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="X14" s="188" t="s">
         <v>286</v>
@@ -34841,7 +35342,7 @@
       </c>
       <c r="S16" s="12"/>
       <c r="T16" s="337" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U16" s="12"/>
       <c r="V16" s="186" t="s">
@@ -34991,7 +35492,7 @@
       </c>
       <c r="S17" s="12"/>
       <c r="T17" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U17" s="12"/>
       <c r="V17" s="186" t="s">
@@ -35147,7 +35648,7 @@
       </c>
       <c r="S18" s="12"/>
       <c r="T18" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U18" s="12"/>
       <c r="V18" s="186" t="s">
@@ -35303,7 +35804,7 @@
       </c>
       <c r="S19" s="12"/>
       <c r="T19" s="337" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U19" s="12"/>
       <c r="V19" s="186" t="s">
@@ -35451,7 +35952,7 @@
       </c>
       <c r="S20" s="12"/>
       <c r="T20" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U20" s="12"/>
       <c r="V20" s="186" t="s">
@@ -35599,7 +36100,7 @@
       </c>
       <c r="S21" s="12"/>
       <c r="T21" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U21" s="12"/>
       <c r="V21" s="186" t="s">
@@ -35747,7 +36248,7 @@
       </c>
       <c r="S22" s="12"/>
       <c r="T22" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U22" s="12"/>
       <c r="V22" s="186" t="s">
@@ -35897,14 +36398,14 @@
       </c>
       <c r="S23" s="12"/>
       <c r="T23" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U23" s="12"/>
       <c r="V23" s="186" t="s">
         <v>269</v>
       </c>
       <c r="W23" s="187" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="X23" s="192" t="s">
         <v>295</v>
@@ -36047,7 +36548,7 @@
       </c>
       <c r="S24" s="12"/>
       <c r="T24" s="337" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U24" s="12"/>
       <c r="V24" s="186" t="s">
@@ -36194,7 +36695,7 @@
       </c>
       <c r="S25" s="12"/>
       <c r="T25" s="337" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U25" s="12"/>
       <c r="V25" s="186" t="s">
@@ -36340,7 +36841,7 @@
       </c>
       <c r="S26" s="12"/>
       <c r="T26" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U26" s="12"/>
       <c r="V26" s="186" t="s">
@@ -36584,7 +37085,7 @@
       </c>
       <c r="BL27" s="12"/>
     </row>
-    <row r="28" spans="3:64" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>7</v>
       </c>
@@ -36640,7 +37141,7 @@
         <v>269</v>
       </c>
       <c r="W28" s="187" t="s">
-        <v>316</v>
+        <v>359</v>
       </c>
       <c r="X28" s="189" t="s">
         <v>300</v>
@@ -36655,7 +37156,7 @@
         <v>273</v>
       </c>
       <c r="AB28" s="189" t="s">
-        <v>274</v>
+        <v>466</v>
       </c>
       <c r="AC28" s="12" t="s">
         <v>275</v>
@@ -36734,7 +37235,7 @@
       <c r="BI28" s="11"/>
       <c r="BJ28" s="11"/>
       <c r="BK28" s="34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BL28" s="12"/>
     </row>
@@ -36787,7 +37288,7 @@
       </c>
       <c r="S29" s="12"/>
       <c r="T29" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="186" t="s">
@@ -36815,7 +37316,7 @@
         <v>275</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AE29" s="12">
         <v>6</v>
@@ -36870,7 +37371,7 @@
         <v>194</v>
       </c>
       <c r="AY29" s="336">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="AZ29" s="12"/>
       <c r="BA29" s="12"/>
@@ -36884,10 +37385,12 @@
       <c r="BF29" s="177"/>
       <c r="BG29" s="177"/>
       <c r="BH29" s="12"/>
-      <c r="BI29" s="11"/>
+      <c r="BI29" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ29" s="11"/>
       <c r="BK29" s="34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BL29" s="12"/>
     </row>
@@ -36899,7 +37402,7 @@
         <v>265</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>100</v>
@@ -37051,10 +37554,10 @@
         <v>4</v>
       </c>
       <c r="D31" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="E31" s="29" t="s">
         <v>319</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>320</v>
       </c>
       <c r="F31" s="34" t="s">
         <v>88</v>
@@ -37182,7 +37685,7 @@
         <v>194</v>
       </c>
       <c r="AY31" s="336">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="AZ31" s="12"/>
       <c r="BA31" s="12"/>
@@ -37196,7 +37699,9 @@
       <c r="BF31" s="177"/>
       <c r="BG31" s="177"/>
       <c r="BH31" s="12"/>
-      <c r="BI31" s="11"/>
+      <c r="BI31" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ31" s="11"/>
       <c r="BK31" s="34" t="s">
         <v>14</v>
@@ -37208,10 +37713,10 @@
         <v>4</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F32" s="34" t="s">
         <v>88</v>
@@ -37238,7 +37743,7 @@
         <v>45960</v>
       </c>
       <c r="N32" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O32" s="12"/>
       <c r="P32" s="12" t="s">
@@ -37340,7 +37845,7 @@
         <v>194</v>
       </c>
       <c r="AY32" s="336">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="AZ32" s="12"/>
       <c r="BA32" s="12"/>
@@ -37354,7 +37859,9 @@
       <c r="BF32" s="177"/>
       <c r="BG32" s="177"/>
       <c r="BH32" s="12"/>
-      <c r="BI32" s="11"/>
+      <c r="BI32" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ32" s="11"/>
       <c r="BK32" s="34" t="s">
         <v>14</v>
@@ -37396,7 +37903,7 @@
         <v>45960</v>
       </c>
       <c r="N33" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
@@ -37408,7 +37915,7 @@
       </c>
       <c r="S33" s="12"/>
       <c r="T33" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U33" s="12"/>
       <c r="V33" s="186" t="s">
@@ -37517,7 +38024,7 @@
         <v>302</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>100</v>
@@ -37544,7 +38051,7 @@
         <v>45960</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
@@ -37556,7 +38063,7 @@
       </c>
       <c r="S34" s="12"/>
       <c r="T34" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="186" t="s">
@@ -37699,7 +38206,7 @@
         <v>45960</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
@@ -37711,7 +38218,7 @@
       </c>
       <c r="S35" s="12"/>
       <c r="T35" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U35" s="12"/>
       <c r="V35" s="186" t="s">
@@ -37817,10 +38324,10 @@
         <v>7</v>
       </c>
       <c r="D36" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="E36" s="21" t="s">
         <v>324</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>325</v>
       </c>
       <c r="F36" s="21" t="s">
         <v>88</v>
@@ -37847,7 +38354,7 @@
         <v>45960</v>
       </c>
       <c r="N36" s="46" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O36" s="12"/>
       <c r="P36" s="12" t="s">
@@ -37861,7 +38368,7 @@
       </c>
       <c r="S36" s="12"/>
       <c r="T36" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U36" s="12"/>
       <c r="V36" s="186" t="s">
@@ -37871,10 +38378,10 @@
         <v>279</v>
       </c>
       <c r="X36" s="192" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y36" s="189" t="s">
         <v>327</v>
-      </c>
-      <c r="Y36" s="189" t="s">
-        <v>328</v>
       </c>
       <c r="Z36" s="189" t="s">
         <v>273</v>
@@ -37889,7 +38396,7 @@
         <v>275</v>
       </c>
       <c r="AD36" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AE36" s="12">
         <v>1</v>
@@ -37975,10 +38482,10 @@
         <v>7</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F37" s="35" t="s">
         <v>6</v>
@@ -38005,7 +38512,7 @@
         <v>45960</v>
       </c>
       <c r="N37" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O37" s="12"/>
       <c r="P37" s="12"/>
@@ -38015,7 +38522,7 @@
       </c>
       <c r="S37" s="12"/>
       <c r="T37" s="337" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="186" t="s">
@@ -38043,7 +38550,7 @@
         <v>275</v>
       </c>
       <c r="AD37" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AE37" s="12"/>
       <c r="AF37" s="79"/>
@@ -38115,10 +38622,10 @@
         <v>7</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F38" s="21" t="s">
         <v>100</v>
@@ -38145,7 +38652,7 @@
         <v>45960</v>
       </c>
       <c r="N38" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O38" s="12"/>
       <c r="P38" s="12"/>
@@ -38157,7 +38664,7 @@
       </c>
       <c r="S38" s="12"/>
       <c r="T38" s="337" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="186" t="s">
@@ -38251,7 +38758,9 @@
       <c r="BF38" s="177"/>
       <c r="BG38" s="177"/>
       <c r="BH38" s="12"/>
-      <c r="BI38" s="11"/>
+      <c r="BI38" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ38" s="11"/>
       <c r="BK38" s="34" t="s">
         <v>14</v>
@@ -38262,7 +38771,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>118</v>
@@ -38292,7 +38801,7 @@
         <v>45960</v>
       </c>
       <c r="N39" s="46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O39" s="12"/>
       <c r="P39" s="12" t="s">
@@ -38306,7 +38815,7 @@
       </c>
       <c r="S39" s="12"/>
       <c r="T39" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="186" t="s">
@@ -38316,10 +38825,10 @@
         <v>279</v>
       </c>
       <c r="X39" s="192" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y39" s="189" t="s">
         <v>327</v>
-      </c>
-      <c r="Y39" s="189" t="s">
-        <v>328</v>
       </c>
       <c r="Z39" s="189" t="s">
         <v>273</v>
@@ -38415,10 +38924,10 @@
         <v>4</v>
       </c>
       <c r="D40" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="E40" s="26" t="s">
         <v>331</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>332</v>
       </c>
       <c r="F40" s="34" t="s">
         <v>88</v>
@@ -38445,7 +38954,7 @@
         <v>45960</v>
       </c>
       <c r="N40" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O40" s="12"/>
       <c r="P40" s="12" t="s">
@@ -38466,7 +38975,7 @@
         <v>278</v>
       </c>
       <c r="W40" s="187" t="s">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="X40" s="191" t="s">
         <v>280</v>
@@ -38481,7 +38990,7 @@
         <v>282</v>
       </c>
       <c r="AB40" s="189" t="s">
-        <v>268</v>
+        <v>466</v>
       </c>
       <c r="AC40" s="12" t="s">
         <v>275</v>
@@ -38556,7 +39065,9 @@
       <c r="BF40" s="177"/>
       <c r="BG40" s="177"/>
       <c r="BH40" s="12"/>
-      <c r="BI40" s="11"/>
+      <c r="BI40" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ40" s="11"/>
       <c r="BK40" s="34" t="s">
         <v>14</v>
@@ -38570,7 +39081,7 @@
         <v>260</v>
       </c>
       <c r="E41" s="30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F41" s="34" t="s">
         <v>88</v>
@@ -38611,7 +39122,7 @@
       </c>
       <c r="S41" s="12"/>
       <c r="T41" s="337" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="U41" s="12"/>
       <c r="V41" s="186" t="s">
@@ -38729,7 +39240,7 @@
         <v>123</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F42" s="20" t="s">
         <v>100</v>
@@ -38756,7 +39267,7 @@
         <v>45960</v>
       </c>
       <c r="N42" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O42" s="12"/>
       <c r="P42" s="12"/>
@@ -38768,7 +39279,7 @@
       </c>
       <c r="S42" s="12"/>
       <c r="T42" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U42" s="12"/>
       <c r="V42" s="186" t="s">
@@ -38903,11 +39414,11 @@
         <v>45960</v>
       </c>
       <c r="N43" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O43" s="12"/>
       <c r="P43" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q43" s="12" t="s">
         <v>193</v>
@@ -38917,7 +39428,7 @@
       </c>
       <c r="S43" s="12"/>
       <c r="T43" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U43" s="12"/>
       <c r="V43" s="186" t="s">
@@ -38945,7 +39456,7 @@
         <v>275</v>
       </c>
       <c r="AD43" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AE43" s="12">
         <v>0</v>
@@ -39014,10 +39525,12 @@
       <c r="BF43" s="177"/>
       <c r="BG43" s="177"/>
       <c r="BH43" s="12"/>
-      <c r="BI43" s="11"/>
+      <c r="BI43" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ43" s="11"/>
       <c r="BK43" s="34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="3:64" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
@@ -39025,10 +39538,10 @@
         <v>4</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F44" s="34" t="s">
         <v>88</v>
@@ -39055,7 +39568,7 @@
         <v>45960</v>
       </c>
       <c r="N44" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O44" s="12"/>
       <c r="P44" s="12" t="s">
@@ -39079,7 +39592,7 @@
         <v>279</v>
       </c>
       <c r="X44" s="192" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Y44" s="192" t="s">
         <v>274</v>
@@ -39185,7 +39698,7 @@
         <v>312</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F45" s="21" t="s">
         <v>100</v>
@@ -39224,7 +39737,7 @@
       </c>
       <c r="S45" s="12"/>
       <c r="T45" s="337" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U45" s="12"/>
       <c r="V45" s="186" t="s">
@@ -39234,10 +39747,10 @@
         <v>279</v>
       </c>
       <c r="X45" s="192" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y45" s="189" t="s">
         <v>327</v>
-      </c>
-      <c r="Y45" s="189" t="s">
-        <v>328</v>
       </c>
       <c r="Z45" s="189" t="s">
         <v>273</v>
@@ -39362,7 +39875,7 @@
         <v>193</v>
       </c>
       <c r="M46" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N46" s="47">
         <v>46111</v>
@@ -39377,7 +39890,7 @@
       </c>
       <c r="S46" s="12"/>
       <c r="T46" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U46" s="12"/>
       <c r="V46" s="186" t="s">
@@ -39473,7 +39986,9 @@
       <c r="BF46" s="177"/>
       <c r="BG46" s="177"/>
       <c r="BH46" s="12"/>
-      <c r="BI46" s="11"/>
+      <c r="BI46" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ46" s="11"/>
       <c r="BK46" s="34" t="s">
         <v>14</v>
@@ -39511,7 +40026,7 @@
         <v>193</v>
       </c>
       <c r="M47" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N47" s="47">
         <v>46111</v>
@@ -39528,7 +40043,7 @@
       </c>
       <c r="S47" s="12"/>
       <c r="T47" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U47" s="12"/>
       <c r="V47" s="186" t="s">
@@ -39625,7 +40140,9 @@
       <c r="BF47" s="177"/>
       <c r="BG47" s="177"/>
       <c r="BH47" s="12"/>
-      <c r="BI47" s="11"/>
+      <c r="BI47" s="340">
+        <v>46199</v>
+      </c>
       <c r="BJ47" s="11"/>
       <c r="BK47" s="34" t="s">
         <v>14</v>
@@ -39639,7 +40156,7 @@
         <v>314</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F48" s="21" t="s">
         <v>88</v>
@@ -39663,7 +40180,7 @@
         <v>193</v>
       </c>
       <c r="M48" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N48" s="47">
         <v>46111</v>
@@ -39680,7 +40197,7 @@
       </c>
       <c r="S48" s="12"/>
       <c r="T48" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U48" s="12"/>
       <c r="V48" s="186" t="s">
@@ -39690,10 +40207,10 @@
         <v>279</v>
       </c>
       <c r="X48" s="192" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y48" s="189" t="s">
         <v>340</v>
-      </c>
-      <c r="Y48" s="189" t="s">
-        <v>341</v>
       </c>
       <c r="Z48" s="189" t="s">
         <v>273</v>
@@ -39796,7 +40313,7 @@
         <v>260</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F49" s="34" t="s">
         <v>100</v>
@@ -39820,7 +40337,7 @@
         <v>193</v>
       </c>
       <c r="M49" s="49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N49" s="39">
         <v>46111</v>
@@ -39835,7 +40352,7 @@
       </c>
       <c r="S49" s="12"/>
       <c r="T49" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U49" s="12"/>
       <c r="V49" s="186" t="s">
@@ -39845,10 +40362,10 @@
         <v>279</v>
       </c>
       <c r="X49" s="192" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y49" s="189" t="s">
         <v>340</v>
-      </c>
-      <c r="Y49" s="189" t="s">
-        <v>341</v>
       </c>
       <c r="Z49" s="189" t="s">
         <v>273</v>
@@ -39970,7 +40487,7 @@
         <v>193</v>
       </c>
       <c r="M50" s="49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N50" s="38">
         <v>46111</v>
@@ -39985,7 +40502,7 @@
       </c>
       <c r="S50" s="12"/>
       <c r="T50" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U50" s="12"/>
       <c r="V50" s="186" t="s">
@@ -39995,10 +40512,10 @@
         <v>279</v>
       </c>
       <c r="X50" s="192" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y50" s="189" t="s">
         <v>340</v>
-      </c>
-      <c r="Y50" s="189" t="s">
-        <v>341</v>
       </c>
       <c r="Z50" s="189" t="s">
         <v>273</v>
@@ -40092,10 +40609,10 @@
         <v>7</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F51" s="21" t="s">
         <v>88</v>
@@ -40136,7 +40653,7 @@
       </c>
       <c r="S51" s="12"/>
       <c r="T51" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U51" s="12"/>
       <c r="V51" s="186" t="s">
@@ -40146,10 +40663,10 @@
         <v>279</v>
       </c>
       <c r="X51" s="192" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y51" s="189" t="s">
         <v>340</v>
-      </c>
-      <c r="Y51" s="189" t="s">
-        <v>341</v>
       </c>
       <c r="Z51" s="189" t="s">
         <v>273</v>
@@ -40164,7 +40681,7 @@
         <v>275</v>
       </c>
       <c r="AD51" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AE51" s="12">
         <v>0</v>
@@ -40245,7 +40762,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>94</v>
@@ -40297,10 +40814,10 @@
         <v>279</v>
       </c>
       <c r="X52" s="188" t="s">
+        <v>343</v>
+      </c>
+      <c r="Y52" s="189" t="s">
         <v>344</v>
-      </c>
-      <c r="Y52" s="189" t="s">
-        <v>345</v>
       </c>
       <c r="Z52" s="189" t="s">
         <v>273</v>
@@ -40394,7 +40911,7 @@
         <v>4</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>94</v>
@@ -40443,13 +40960,13 @@
         <v>278</v>
       </c>
       <c r="W53" s="187" t="s">
+        <v>345</v>
+      </c>
+      <c r="X53" s="189" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y53" s="194" t="s">
         <v>346</v>
-      </c>
-      <c r="X53" s="189" t="s">
-        <v>340</v>
-      </c>
-      <c r="Y53" s="194" t="s">
-        <v>347</v>
       </c>
       <c r="Z53" s="189" t="s">
         <v>273</v>
@@ -40543,7 +41060,7 @@
         <v>4</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>94</v>
@@ -40597,10 +41114,10 @@
         <v>279</v>
       </c>
       <c r="X54" s="192" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Y54" s="189" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Z54" s="189" t="s">
         <v>273</v>
@@ -40690,7 +41207,7 @@
         <v>314</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F55" s="21" t="s">
         <v>100</v>
@@ -40729,20 +41246,20 @@
       </c>
       <c r="S55" s="12"/>
       <c r="T55" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U55" s="12"/>
       <c r="V55" s="186" t="s">
         <v>278</v>
       </c>
       <c r="W55" s="187" t="s">
+        <v>345</v>
+      </c>
+      <c r="X55" s="189" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y55" s="194" t="s">
         <v>346</v>
-      </c>
-      <c r="X55" s="189" t="s">
-        <v>340</v>
-      </c>
-      <c r="Y55" s="194" t="s">
-        <v>347</v>
       </c>
       <c r="Z55" s="189" t="s">
         <v>273</v>
@@ -40843,7 +41360,7 @@
         <v>309</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F56" s="20" t="s">
         <v>88</v>
@@ -40867,10 +41384,10 @@
         <v>193</v>
       </c>
       <c r="M56" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N56" s="51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O56" s="12"/>
       <c r="P56" s="12" t="s">
@@ -40884,7 +41401,7 @@
       </c>
       <c r="S56" s="12"/>
       <c r="T56" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U56" s="12"/>
       <c r="V56" s="186" t="s">
@@ -40991,7 +41508,7 @@
         <v>297</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F57" s="20" t="s">
         <v>88</v>
@@ -41015,10 +41532,10 @@
         <v>193</v>
       </c>
       <c r="M57" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N57" s="51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O57" s="12"/>
       <c r="P57" s="12" t="s">
@@ -41032,20 +41549,20 @@
       </c>
       <c r="S57" s="12"/>
       <c r="T57" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U57" s="12"/>
       <c r="V57" s="186" t="s">
         <v>269</v>
       </c>
       <c r="W57" s="187" t="s">
+        <v>352</v>
+      </c>
+      <c r="X57" s="190" t="s">
         <v>353</v>
       </c>
-      <c r="X57" s="190" t="s">
+      <c r="Y57" s="189" t="s">
         <v>354</v>
-      </c>
-      <c r="Y57" s="189" t="s">
-        <v>355</v>
       </c>
       <c r="Z57" s="189" t="s">
         <v>273</v>
@@ -41148,7 +41665,7 @@
         <v>297</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F58" s="20" t="s">
         <v>100</v>
@@ -41172,10 +41689,10 @@
         <v>193</v>
       </c>
       <c r="M58" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N58" s="51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O58" s="12"/>
       <c r="P58" s="12"/>
@@ -41187,7 +41704,7 @@
       </c>
       <c r="S58" s="12"/>
       <c r="T58" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U58" s="12"/>
       <c r="V58" s="186" t="s">
@@ -41197,10 +41714,10 @@
         <v>270</v>
       </c>
       <c r="X58" s="190" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y58" s="189" t="s">
         <v>357</v>
-      </c>
-      <c r="Y58" s="189" t="s">
-        <v>358</v>
       </c>
       <c r="Z58" s="189" t="s">
         <v>273</v>
@@ -41301,7 +41818,7 @@
         <v>312</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F59" s="21" t="s">
         <v>100</v>
@@ -41325,10 +41842,10 @@
         <v>193</v>
       </c>
       <c r="M59" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N59" s="52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O59" s="12"/>
       <c r="P59" s="12"/>
@@ -41347,7 +41864,7 @@
         <v>269</v>
       </c>
       <c r="W59" s="187" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="X59" s="189" t="s">
         <v>300</v>
@@ -41454,7 +41971,7 @@
         <v>314</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F60" s="21" t="s">
         <v>100</v>
@@ -41478,10 +41995,10 @@
         <v>193</v>
       </c>
       <c r="M60" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N60" s="52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O60" s="12"/>
       <c r="P60" s="12"/>
@@ -41631,10 +42148,10 @@
         <v>193</v>
       </c>
       <c r="M61" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N61" s="52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O61" s="12"/>
       <c r="P61" s="12"/>
@@ -41656,10 +42173,10 @@
         <v>285</v>
       </c>
       <c r="X61" s="189" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y61" s="189" t="s">
         <v>362</v>
-      </c>
-      <c r="Y61" s="189" t="s">
-        <v>363</v>
       </c>
       <c r="Z61" s="189" t="s">
         <v>273</v>
@@ -41780,10 +42297,10 @@
         <v>193</v>
       </c>
       <c r="M62" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N62" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O62" s="12"/>
       <c r="P62" s="12" t="s">
@@ -41797,14 +42314,14 @@
       </c>
       <c r="S62" s="12"/>
       <c r="T62" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U62" s="12"/>
       <c r="V62" s="186" t="s">
         <v>269</v>
       </c>
       <c r="W62" s="187" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="X62" s="188" t="s">
         <v>286</v>
@@ -41913,7 +42430,7 @@
         <v>276</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F63" s="34" t="s">
         <v>100</v>
@@ -41937,10 +42454,10 @@
         <v>193</v>
       </c>
       <c r="M63" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N63" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O63" s="12"/>
       <c r="P63" s="12"/>
@@ -41959,13 +42476,13 @@
         <v>278</v>
       </c>
       <c r="W63" s="187" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="X63" s="190" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Y63" s="190" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Z63" s="189" t="s">
         <v>273</v>
@@ -42063,10 +42580,10 @@
         <v>4</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F64" s="34" t="s">
         <v>88</v>
@@ -42090,10 +42607,10 @@
         <v>193</v>
       </c>
       <c r="M64" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N64" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O64" s="322"/>
       <c r="P64" s="322" t="s">
@@ -42107,7 +42624,7 @@
       </c>
       <c r="S64" s="322"/>
       <c r="T64" s="338" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U64" s="322"/>
       <c r="V64" s="186" t="s">
@@ -42117,10 +42634,10 @@
         <v>270</v>
       </c>
       <c r="X64" s="188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Y64" s="189" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z64" s="189" t="s">
         <v>273</v>
@@ -42219,10 +42736,10 @@
         <v>4</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F65" s="34" t="s">
         <v>88</v>
@@ -42246,10 +42763,10 @@
         <v>193</v>
       </c>
       <c r="M65" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N65" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O65" s="12"/>
       <c r="P65" s="12" t="s">
@@ -42263,7 +42780,7 @@
       </c>
       <c r="S65" s="12"/>
       <c r="T65" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U65" s="12"/>
       <c r="V65" s="186" t="s">
@@ -42379,7 +42896,7 @@
         <v>312</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F66" s="21" t="s">
         <v>100</v>
@@ -42533,7 +43050,7 @@
         <v>276</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F67" s="34" t="s">
         <v>100</v>
@@ -42572,20 +43089,20 @@
       </c>
       <c r="S67" s="12"/>
       <c r="T67" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U67" s="12"/>
       <c r="V67" s="186" t="s">
         <v>278</v>
       </c>
       <c r="W67" s="187" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="X67" s="190" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Y67" s="189" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Z67" s="189" t="s">
         <v>273</v>
@@ -42727,7 +43244,7 @@
       </c>
       <c r="S68" s="12"/>
       <c r="T68" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U68" s="12"/>
       <c r="V68" s="186" t="s">
@@ -42737,10 +43254,10 @@
         <v>279</v>
       </c>
       <c r="X68" s="192" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y68" s="189" t="s">
         <v>327</v>
-      </c>
-      <c r="Y68" s="189" t="s">
-        <v>328</v>
       </c>
       <c r="Z68" s="189" t="s">
         <v>273</v>
@@ -42840,10 +43357,10 @@
         <v>4</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F69" s="34" t="s">
         <v>88</v>
@@ -42870,7 +43387,7 @@
         <v>45960</v>
       </c>
       <c r="N69" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O69" s="12"/>
       <c r="P69" s="12" t="s">
@@ -42894,10 +43411,10 @@
         <v>279</v>
       </c>
       <c r="X69" s="189" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Y69" s="189" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Z69" s="189" t="s">
         <v>273</v>
@@ -43045,7 +43562,7 @@
       </c>
       <c r="S70" s="12"/>
       <c r="T70" s="337" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="U70" s="12"/>
       <c r="V70" s="186" t="s">
@@ -43055,10 +43572,10 @@
         <v>279</v>
       </c>
       <c r="X70" s="189" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Y70" s="189" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Z70" s="189" t="s">
         <v>273</v>
@@ -43073,7 +43590,7 @@
         <v>275</v>
       </c>
       <c r="AD70" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AE70" s="12">
         <v>0</v>
@@ -43174,11 +43691,6 @@
     <row r="83" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AF8:AK8"/>
     <mergeCell ref="AT9:BB9"/>
     <mergeCell ref="BC9:BH9"/>
     <mergeCell ref="AT8:BB8"/>
@@ -43189,6 +43701,11 @@
     <mergeCell ref="AL8:AS8"/>
     <mergeCell ref="AL9:AS9"/>
     <mergeCell ref="AD9:AK9"/>
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AF8:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="En Proceso">
@@ -43229,22 +43746,22 @@
   </cols>
   <sheetData>
     <row r="10" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D10" s="373" t="s">
+      <c r="D10" s="386" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="373"/>
+      <c r="E10" s="386"/>
     </row>
     <row r="11" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D11" s="328" t="s">
         <v>182</v>
       </c>
       <c r="E11" s="328" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D12" s="11" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>88</v>
@@ -43252,7 +43769,7 @@
     </row>
     <row r="13" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D13" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>88</v>
@@ -43260,7 +43777,7 @@
     </row>
     <row r="14" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D14" s="11" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>88</v>
@@ -43268,7 +43785,7 @@
     </row>
     <row r="15" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D15" s="11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>100</v>
@@ -43276,7 +43793,7 @@
     </row>
     <row r="16" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D16" s="11" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>100</v>
@@ -43284,7 +43801,7 @@
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17" s="329" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E17" s="329" t="s">
         <v>88</v>
@@ -43292,7 +43809,7 @@
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D18" s="330" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>88</v>
@@ -43300,7 +43817,7 @@
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D19" s="330" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>88</v>
@@ -43308,7 +43825,7 @@
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D20" s="330" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -43343,7 +43860,7 @@
         <v>124</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C2" s="70">
         <v>0.11</v>
@@ -43354,10 +43871,10 @@
     </row>
     <row r="3" spans="1:4" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C3" s="70">
         <v>0.3</v>
@@ -43372,6 +43889,324 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD07AE4-227B-42C1-96DB-C74849E41428}">
+  <dimension ref="B4:CH6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="19.77734375" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+    <col min="13" max="13" width="18.109375" customWidth="1"/>
+    <col min="15" max="15" width="16.77734375" customWidth="1"/>
+    <col min="22" max="22" width="22.88671875" customWidth="1"/>
+    <col min="23" max="23" width="12.77734375" customWidth="1"/>
+    <col min="25" max="25" width="18.88671875" customWidth="1"/>
+    <col min="32" max="32" width="21.33203125" customWidth="1"/>
+    <col min="33" max="37" width="21.21875" customWidth="1"/>
+    <col min="43" max="43" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:86" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="349" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="350" t="s">
+        <v>458</v>
+      </c>
+      <c r="J4" s="351"/>
+      <c r="K4" s="351"/>
+      <c r="L4" s="351"/>
+      <c r="M4" s="352" t="s">
+        <v>459</v>
+      </c>
+      <c r="N4" s="352"/>
+      <c r="O4" s="352"/>
+      <c r="P4" s="352"/>
+      <c r="Q4" s="352"/>
+      <c r="R4" s="352"/>
+      <c r="T4" s="348" t="s">
+        <v>458</v>
+      </c>
+      <c r="U4" s="348"/>
+      <c r="V4" s="344" t="s">
+        <v>459</v>
+      </c>
+      <c r="W4" s="345" t="s">
+        <v>460</v>
+      </c>
+      <c r="X4" s="343" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y4" s="353" t="s">
+        <v>462</v>
+      </c>
+      <c r="Z4" s="353"/>
+      <c r="AA4" s="353"/>
+      <c r="AB4" s="353"/>
+      <c r="AC4" s="353"/>
+      <c r="AD4" s="346" t="s">
+        <v>463</v>
+      </c>
+      <c r="AE4" s="346"/>
+      <c r="AF4" s="346"/>
+      <c r="AG4" s="346"/>
+      <c r="AH4" s="346"/>
+      <c r="AI4" s="346"/>
+      <c r="AJ4" s="346"/>
+      <c r="AK4" s="346"/>
+      <c r="AL4" s="347" t="s">
+        <v>464</v>
+      </c>
+      <c r="AM4" s="347"/>
+      <c r="AN4" s="347"/>
+      <c r="AO4" s="347"/>
+      <c r="AP4" s="347"/>
+      <c r="AQ4" s="347"/>
+      <c r="AR4" s="348" t="s">
+        <v>465</v>
+      </c>
+      <c r="AS4" s="348"/>
+      <c r="AT4" s="348"/>
+    </row>
+    <row r="5" spans="2:86" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H5" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="I5" s="341" t="s">
+        <v>422</v>
+      </c>
+      <c r="J5" s="341" t="s">
+        <v>421</v>
+      </c>
+      <c r="K5" s="341" t="s">
+        <v>423</v>
+      </c>
+      <c r="L5" s="341" t="s">
+        <v>424</v>
+      </c>
+      <c r="M5" s="341" t="s">
+        <v>425</v>
+      </c>
+      <c r="N5" s="341" t="s">
+        <v>426</v>
+      </c>
+      <c r="O5" s="341" t="s">
+        <v>428</v>
+      </c>
+      <c r="P5" s="341" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q5" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="R5" s="341" t="s">
+        <v>429</v>
+      </c>
+      <c r="S5" s="341" t="s">
+        <v>430</v>
+      </c>
+      <c r="T5" s="341" t="s">
+        <v>431</v>
+      </c>
+      <c r="U5" s="341" t="s">
+        <v>239</v>
+      </c>
+      <c r="V5" s="341" t="s">
+        <v>432</v>
+      </c>
+      <c r="W5" s="341" t="s">
+        <v>433</v>
+      </c>
+      <c r="X5" s="341" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y5" s="341" t="s">
+        <v>435</v>
+      </c>
+      <c r="Z5" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="AA5" s="341" t="s">
+        <v>436</v>
+      </c>
+      <c r="AB5" s="341" t="s">
+        <v>437</v>
+      </c>
+      <c r="AC5" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="AD5" s="341" t="s">
+        <v>446</v>
+      </c>
+      <c r="AE5" s="341" t="s">
+        <v>445</v>
+      </c>
+      <c r="AF5" s="341" t="s">
+        <v>444</v>
+      </c>
+      <c r="AG5" s="341" t="s">
+        <v>447</v>
+      </c>
+      <c r="AH5" s="341" t="s">
+        <v>448</v>
+      </c>
+      <c r="AI5" s="341" t="s">
+        <v>449</v>
+      </c>
+      <c r="AJ5" s="341" t="s">
+        <v>450</v>
+      </c>
+      <c r="AK5" s="341" t="s">
+        <v>451</v>
+      </c>
+      <c r="AL5" s="341" t="s">
+        <v>452</v>
+      </c>
+      <c r="AM5" s="341" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN5" s="341" t="s">
+        <v>441</v>
+      </c>
+      <c r="AO5" s="341" t="s">
+        <v>442</v>
+      </c>
+      <c r="AP5" s="341" t="s">
+        <v>443</v>
+      </c>
+      <c r="AQ5" s="341" t="s">
+        <v>454</v>
+      </c>
+      <c r="AR5" s="341" t="s">
+        <v>455</v>
+      </c>
+      <c r="AS5" s="341" t="s">
+        <v>456</v>
+      </c>
+      <c r="AT5" s="341" t="s">
+        <v>457</v>
+      </c>
+      <c r="AU5" s="342"/>
+      <c r="AV5" s="342"/>
+      <c r="AW5" s="342"/>
+      <c r="AX5" s="342"/>
+      <c r="AY5" s="342"/>
+      <c r="AZ5" s="342"/>
+      <c r="BA5" s="342"/>
+      <c r="BB5" s="342"/>
+      <c r="BC5" s="342"/>
+      <c r="BD5" s="342"/>
+      <c r="BE5" s="342"/>
+      <c r="BF5" s="342"/>
+      <c r="BG5" s="342"/>
+      <c r="BH5" s="342"/>
+      <c r="BI5" s="342"/>
+      <c r="BJ5" s="342"/>
+      <c r="BK5" s="342"/>
+      <c r="BL5" s="342"/>
+      <c r="BM5" s="342"/>
+      <c r="BN5" s="342"/>
+      <c r="BO5" s="342"/>
+      <c r="BP5" s="342"/>
+      <c r="BQ5" s="342"/>
+      <c r="BR5" s="342"/>
+      <c r="BS5" s="342"/>
+      <c r="BT5" s="342"/>
+      <c r="BU5" s="342"/>
+      <c r="BV5" s="342"/>
+      <c r="BW5" s="342"/>
+      <c r="BX5" s="342"/>
+      <c r="BY5" s="342"/>
+      <c r="BZ5" s="342"/>
+      <c r="CA5" s="342"/>
+      <c r="CB5" s="342"/>
+      <c r="CC5" s="342"/>
+      <c r="CD5" s="342"/>
+      <c r="CE5" s="342"/>
+      <c r="CF5" s="342"/>
+      <c r="CG5" s="342"/>
+      <c r="CH5" s="342"/>
+    </row>
+    <row r="6" spans="2:86" ht="69.599999999999994" x14ac:dyDescent="0.3">
+      <c r="B6" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="H6" s="79">
+        <v>108274</v>
+      </c>
+      <c r="P6" s="341"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="AD4:AK4"/>
+    <mergeCell ref="AL4:AQ4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="Y4:AC4"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{B461DC4B-E108-4E2E-9DBF-59B5A9F8BCAA}">
+      <formula1>INDIRECT($B6)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6" xr:uid="{88ECAE0E-CF04-40BD-BD00-258B95033316}">
+      <formula1>"Presencial,Virtual,Híbrido"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6" xr:uid="{04A0A963-D81E-47DD-AE05-70089CDAD228}">
+      <formula1>"Técnico,Tecnológico,Profesional,Especialización,Maestría,Doctorado"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6" xr:uid="{62760F0D-74AF-40FE-83E6-20D598F1243C}">
+      <formula1>"Bogotá,Medellín,Nacional"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E45BE9-C0E2-407D-BCEF-D4C7A244596E}">
   <dimension ref="C3:BB83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -43425,33 +44260,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:54" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O3" s="356" t="s">
+      <c r="O3" s="372" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="356"/>
-      <c r="Q3" s="356"/>
-      <c r="R3" s="356"/>
-      <c r="S3" s="356"/>
-      <c r="T3" s="356"/>
-      <c r="U3" s="356"/>
-      <c r="V3" s="356"/>
-      <c r="W3" s="356"/>
-      <c r="X3" s="356"/>
+      <c r="P3" s="372"/>
+      <c r="Q3" s="372"/>
+      <c r="R3" s="372"/>
+      <c r="S3" s="372"/>
+      <c r="T3" s="372"/>
+      <c r="U3" s="372"/>
+      <c r="V3" s="372"/>
+      <c r="W3" s="372"/>
+      <c r="X3" s="372"/>
     </row>
     <row r="4" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O4" s="356"/>
-      <c r="P4" s="356"/>
-      <c r="Q4" s="356"/>
-      <c r="R4" s="356"/>
-      <c r="S4" s="356"/>
-      <c r="T4" s="356"/>
-      <c r="U4" s="356"/>
-      <c r="V4" s="356"/>
-      <c r="W4" s="356"/>
-      <c r="X4" s="356"/>
+      <c r="O4" s="372"/>
+      <c r="P4" s="372"/>
+      <c r="Q4" s="372"/>
+      <c r="R4" s="372"/>
+      <c r="S4" s="372"/>
+      <c r="T4" s="372"/>
+      <c r="U4" s="372"/>
+      <c r="V4" s="372"/>
+      <c r="W4" s="372"/>
+      <c r="X4" s="372"/>
     </row>
     <row r="5" spans="3:54" x14ac:dyDescent="0.3">
       <c r="J5" s="3" t="s">
@@ -43480,16 +44315,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="77"/>
-      <c r="J8" s="347" t="s">
+      <c r="J8" s="368" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="347"/>
-      <c r="L8" s="347"/>
-      <c r="M8" s="347"/>
-      <c r="N8" s="347"/>
-      <c r="O8" s="347"/>
-      <c r="P8" s="347"/>
-      <c r="Q8" s="347"/>
+      <c r="K8" s="368"/>
+      <c r="L8" s="368"/>
+      <c r="M8" s="368"/>
+      <c r="N8" s="368"/>
+      <c r="O8" s="368"/>
+      <c r="P8" s="368"/>
+      <c r="Q8" s="368"/>
       <c r="R8" s="5" t="s">
         <v>196</v>
       </c>
@@ -43500,107 +44335,107 @@
       </c>
       <c r="V8" s="75"/>
       <c r="W8" s="75"/>
-      <c r="X8" s="348" t="s">
+      <c r="X8" s="373" t="s">
         <v>198</v>
       </c>
-      <c r="Y8" s="349"/>
-      <c r="Z8" s="349"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="357" t="s">
+      <c r="Y8" s="374"/>
+      <c r="Z8" s="374"/>
+      <c r="AA8" s="375"/>
+      <c r="AB8" s="376" t="s">
         <v>199</v>
       </c>
-      <c r="AC8" s="359" t="s">
+      <c r="AC8" s="378" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="360"/>
-      <c r="AE8" s="360"/>
-      <c r="AF8" s="360"/>
-      <c r="AG8" s="360"/>
-      <c r="AH8" s="360"/>
-      <c r="AI8" s="351" t="s">
+      <c r="AD8" s="379"/>
+      <c r="AE8" s="379"/>
+      <c r="AF8" s="379"/>
+      <c r="AG8" s="379"/>
+      <c r="AH8" s="379"/>
+      <c r="AI8" s="366" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="351"/>
-      <c r="AK8" s="351"/>
-      <c r="AL8" s="351"/>
-      <c r="AM8" s="351"/>
-      <c r="AN8" s="351"/>
-      <c r="AO8" s="344" t="s">
+      <c r="AJ8" s="366"/>
+      <c r="AK8" s="366"/>
+      <c r="AL8" s="366"/>
+      <c r="AM8" s="366"/>
+      <c r="AN8" s="366"/>
+      <c r="AO8" s="362" t="s">
         <v>202</v>
       </c>
-      <c r="AP8" s="344"/>
-      <c r="AQ8" s="344"/>
-      <c r="AR8" s="344"/>
-      <c r="AS8" s="345" t="s">
+      <c r="AP8" s="362"/>
+      <c r="AQ8" s="362"/>
+      <c r="AR8" s="362"/>
+      <c r="AS8" s="363" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="345"/>
-      <c r="AU8" s="345"/>
+      <c r="AT8" s="363"/>
+      <c r="AU8" s="363"/>
       <c r="AV8" s="14"/>
       <c r="AW8" s="14"/>
       <c r="AX8" s="14"/>
       <c r="AY8" s="14"/>
     </row>
     <row r="9" spans="3:54" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="346" t="s">
+      <c r="C9" s="349" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="346"/>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
-      <c r="G9" s="346"/>
-      <c r="H9" s="346"/>
-      <c r="I9" s="346"/>
-      <c r="J9" s="347" t="s">
+      <c r="D9" s="349"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
+      <c r="G9" s="349"/>
+      <c r="H9" s="349"/>
+      <c r="I9" s="349"/>
+      <c r="J9" s="368" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="347"/>
-      <c r="L9" s="347"/>
-      <c r="M9" s="347"/>
-      <c r="N9" s="347"/>
-      <c r="O9" s="347"/>
-      <c r="P9" s="347"/>
-      <c r="Q9" s="347"/>
+      <c r="K9" s="368"/>
+      <c r="L9" s="368"/>
+      <c r="M9" s="368"/>
+      <c r="N9" s="368"/>
+      <c r="O9" s="368"/>
+      <c r="P9" s="368"/>
+      <c r="Q9" s="368"/>
       <c r="R9" s="81"/>
       <c r="S9" s="82"/>
       <c r="T9" s="82"/>
       <c r="U9" s="82"/>
-      <c r="V9" s="348" t="s">
+      <c r="V9" s="373" t="s">
         <v>208</v>
       </c>
-      <c r="W9" s="349"/>
-      <c r="X9" s="349"/>
-      <c r="Y9" s="349"/>
-      <c r="Z9" s="349"/>
-      <c r="AA9" s="350"/>
-      <c r="AB9" s="358"/>
-      <c r="AC9" s="369" t="s">
+      <c r="W9" s="374"/>
+      <c r="X9" s="374"/>
+      <c r="Y9" s="374"/>
+      <c r="Z9" s="374"/>
+      <c r="AA9" s="375"/>
+      <c r="AB9" s="377"/>
+      <c r="AC9" s="380" t="s">
         <v>209</v>
       </c>
-      <c r="AD9" s="369"/>
-      <c r="AE9" s="369"/>
-      <c r="AF9" s="369"/>
-      <c r="AG9" s="369"/>
-      <c r="AH9" s="369"/>
-      <c r="AI9" s="352" t="s">
+      <c r="AD9" s="380"/>
+      <c r="AE9" s="380"/>
+      <c r="AF9" s="380"/>
+      <c r="AG9" s="380"/>
+      <c r="AH9" s="380"/>
+      <c r="AI9" s="367" t="s">
         <v>201</v>
       </c>
-      <c r="AJ9" s="352"/>
-      <c r="AK9" s="352"/>
-      <c r="AL9" s="352"/>
-      <c r="AM9" s="352"/>
-      <c r="AN9" s="352"/>
-      <c r="AO9" s="340" t="s">
+      <c r="AJ9" s="367"/>
+      <c r="AK9" s="367"/>
+      <c r="AL9" s="367"/>
+      <c r="AM9" s="367"/>
+      <c r="AN9" s="367"/>
+      <c r="AO9" s="364" t="s">
         <v>210</v>
       </c>
-      <c r="AP9" s="340"/>
-      <c r="AQ9" s="340"/>
-      <c r="AR9" s="340"/>
-      <c r="AS9" s="343" t="s">
+      <c r="AP9" s="364"/>
+      <c r="AQ9" s="364"/>
+      <c r="AR9" s="364"/>
+      <c r="AS9" s="365" t="s">
         <v>211</v>
       </c>
-      <c r="AT9" s="343"/>
-      <c r="AU9" s="343"/>
+      <c r="AT9" s="365"/>
+      <c r="AU9" s="365"/>
       <c r="AV9" s="83" t="s">
         <v>212</v>
       </c>
@@ -43922,7 +44757,7 @@
       <c r="V12" s="76"/>
       <c r="W12" s="12"/>
       <c r="X12" s="54" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
@@ -44231,7 +45066,7 @@
       <c r="V15" s="76"/>
       <c r="W15" s="12"/>
       <c r="X15" s="55" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Y15" s="12"/>
       <c r="Z15" s="12"/>
@@ -44429,7 +45264,7 @@
       <c r="V17" s="76"/>
       <c r="W17" s="12"/>
       <c r="X17" s="57" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y17" s="12"/>
       <c r="Z17" s="12"/>
@@ -44629,7 +45464,7 @@
       <c r="V19" s="76"/>
       <c r="W19" s="12"/>
       <c r="X19" s="55" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y19" s="12"/>
       <c r="Z19" s="12"/>
@@ -44728,7 +45563,7 @@
       <c r="V20" s="76"/>
       <c r="W20" s="12"/>
       <c r="X20" s="58" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y20" s="12"/>
       <c r="Z20" s="12"/>
@@ -44827,7 +45662,7 @@
       <c r="V21" s="76"/>
       <c r="W21" s="12"/>
       <c r="X21" s="57" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y21" s="12"/>
       <c r="Z21" s="12"/>
@@ -45138,7 +45973,7 @@
       <c r="V24" s="76"/>
       <c r="W24" s="12"/>
       <c r="X24" s="59" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y24" s="12"/>
       <c r="Z24" s="12"/>
@@ -45229,7 +46064,7 @@
       <c r="V25" s="76"/>
       <c r="W25" s="12"/>
       <c r="X25" s="57" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y25" s="12"/>
       <c r="Z25" s="12"/>
@@ -45328,7 +46163,7 @@
       <c r="V26" s="76"/>
       <c r="W26" s="12"/>
       <c r="X26" s="60" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y26" s="12"/>
       <c r="Z26" s="12"/>
@@ -45431,7 +46266,7 @@
       <c r="V27" s="76"/>
       <c r="W27" s="12"/>
       <c r="X27" s="60" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y27" s="12"/>
       <c r="Z27" s="12"/>
@@ -45647,7 +46482,7 @@
       <c r="V29" s="76"/>
       <c r="W29" s="12"/>
       <c r="X29" s="61" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y29" s="12"/>
       <c r="Z29" s="12"/>
@@ -45715,7 +46550,7 @@
         <v>265</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>100</v>
@@ -45758,7 +46593,7 @@
       <c r="V30" s="76"/>
       <c r="W30" s="12"/>
       <c r="X30" s="59" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12"/>
@@ -45799,10 +46634,10 @@
         <v>4</v>
       </c>
       <c r="D31" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="E31" s="29" t="s">
         <v>319</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>320</v>
       </c>
       <c r="F31" s="34" t="s">
         <v>88</v>
@@ -45849,7 +46684,7 @@
       <c r="V31" s="76"/>
       <c r="W31" s="12"/>
       <c r="X31" s="54" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y31" s="12"/>
       <c r="Z31" s="12"/>
@@ -45914,10 +46749,10 @@
         <v>4</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F32" s="34" t="s">
         <v>88</v>
@@ -45944,7 +46779,7 @@
         <v>45960</v>
       </c>
       <c r="N32" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O32" s="12"/>
       <c r="P32" s="12" t="s">
@@ -45964,7 +46799,7 @@
       <c r="V32" s="76"/>
       <c r="W32" s="12"/>
       <c r="X32" s="62" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y32" s="12"/>
       <c r="Z32" s="12"/>
@@ -46059,7 +46894,7 @@
         <v>45960</v>
       </c>
       <c r="N33" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
@@ -46075,7 +46910,7 @@
       <c r="V33" s="76"/>
       <c r="W33" s="12"/>
       <c r="X33" s="62" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y33" s="12"/>
       <c r="Z33" s="12"/>
@@ -46131,7 +46966,7 @@
         <v>302</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>100</v>
@@ -46158,7 +46993,7 @@
         <v>45960</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
@@ -46174,7 +47009,7 @@
       <c r="V34" s="76"/>
       <c r="W34" s="12"/>
       <c r="X34" s="56" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Y34" s="12"/>
       <c r="Z34" s="12"/>
@@ -46245,7 +47080,7 @@
         <v>45960</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
@@ -46261,7 +47096,7 @@
       <c r="V35" s="76"/>
       <c r="W35" s="12"/>
       <c r="X35" s="56" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
@@ -46314,10 +47149,10 @@
         <v>7</v>
       </c>
       <c r="D36" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="E36" s="21" t="s">
         <v>324</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>325</v>
       </c>
       <c r="F36" s="21" t="s">
         <v>88</v>
@@ -46344,7 +47179,7 @@
         <v>45960</v>
       </c>
       <c r="N36" s="46" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O36" s="12"/>
       <c r="P36" s="12" t="s">
@@ -46364,7 +47199,7 @@
       <c r="V36" s="76"/>
       <c r="W36" s="12"/>
       <c r="X36" s="63" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Y36" s="12"/>
       <c r="Z36" s="12"/>
@@ -46417,10 +47252,10 @@
         <v>7</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F37" s="35" t="s">
         <v>6</v>
@@ -46447,7 +47282,7 @@
         <v>45960</v>
       </c>
       <c r="N37" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O37" s="12"/>
       <c r="P37" s="12"/>
@@ -46463,7 +47298,7 @@
       <c r="V37" s="76"/>
       <c r="W37" s="12"/>
       <c r="X37" s="63" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y37" s="12"/>
       <c r="Z37" s="12"/>
@@ -46517,10 +47352,10 @@
         <v>7</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F38" s="21" t="s">
         <v>100</v>
@@ -46547,7 +47382,7 @@
         <v>45960</v>
       </c>
       <c r="N38" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O38" s="12"/>
       <c r="P38" s="12"/>
@@ -46611,7 +47446,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>118</v>
@@ -46641,7 +47476,7 @@
         <v>45960</v>
       </c>
       <c r="N39" s="46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O39" s="12"/>
       <c r="P39" s="12" t="s">
@@ -46661,7 +47496,7 @@
       <c r="V39" s="76"/>
       <c r="W39" s="12"/>
       <c r="X39" s="63" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Y39" s="12"/>
       <c r="Z39" s="12"/>
@@ -46725,10 +47560,10 @@
         <v>4</v>
       </c>
       <c r="D40" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="E40" s="26" t="s">
         <v>331</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>332</v>
       </c>
       <c r="F40" s="34" t="s">
         <v>88</v>
@@ -46755,7 +47590,7 @@
         <v>45960</v>
       </c>
       <c r="N40" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O40" s="12"/>
       <c r="P40" s="12" t="s">
@@ -46775,7 +47610,7 @@
       <c r="V40" s="76"/>
       <c r="W40" s="12"/>
       <c r="X40" s="62" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y40" s="12"/>
       <c r="Z40" s="12"/>
@@ -46842,7 +47677,7 @@
         <v>260</v>
       </c>
       <c r="E41" s="30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F41" s="34" t="s">
         <v>88</v>
@@ -46854,7 +47689,7 @@
         <v>262</v>
       </c>
       <c r="I41" s="80" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>193</v>
@@ -46889,7 +47724,7 @@
       <c r="V41" s="76"/>
       <c r="W41" s="12"/>
       <c r="X41" s="62" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Y41" s="12"/>
       <c r="Z41" s="12"/>
@@ -46942,7 +47777,7 @@
         <v>123</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F42" s="20" t="s">
         <v>100</v>
@@ -46969,7 +47804,7 @@
         <v>45960</v>
       </c>
       <c r="N42" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O42" s="12"/>
       <c r="P42" s="12"/>
@@ -46985,7 +47820,7 @@
       <c r="V42" s="76"/>
       <c r="W42" s="12"/>
       <c r="X42" s="56" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y42" s="12"/>
       <c r="Z42" s="12"/>
@@ -47067,11 +47902,11 @@
         <v>45960</v>
       </c>
       <c r="N43" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O43" s="12"/>
       <c r="P43" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q43" s="12" t="s">
         <v>193</v>
@@ -47087,7 +47922,7 @@
       <c r="V43" s="76"/>
       <c r="W43" s="12"/>
       <c r="X43" s="56" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y43" s="12"/>
       <c r="Z43" s="12"/>
@@ -47151,10 +47986,10 @@
         <v>4</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F44" s="34" t="s">
         <v>88</v>
@@ -47181,7 +48016,7 @@
         <v>45960</v>
       </c>
       <c r="N44" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O44" s="12"/>
       <c r="P44" s="12" t="s">
@@ -47254,7 +48089,7 @@
         <v>312</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F45" s="21" t="s">
         <v>100</v>
@@ -47297,7 +48132,7 @@
       <c r="V45" s="76"/>
       <c r="W45" s="12"/>
       <c r="X45" s="60" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Y45" s="12"/>
       <c r="Z45" s="12"/>
@@ -47364,7 +48199,7 @@
         <v>193</v>
       </c>
       <c r="M46" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N46" s="47">
         <v>46111</v>
@@ -47383,7 +48218,7 @@
       <c r="V46" s="76"/>
       <c r="W46" s="12"/>
       <c r="X46" s="60" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y46" s="12"/>
       <c r="Z46" s="12"/>
@@ -47462,7 +48297,7 @@
         <v>193</v>
       </c>
       <c r="M47" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N47" s="47">
         <v>46111</v>
@@ -47485,7 +48320,7 @@
       <c r="V47" s="76"/>
       <c r="W47" s="12"/>
       <c r="X47" s="60" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y47" s="12"/>
       <c r="Z47" s="12"/>
@@ -47552,7 +48387,7 @@
         <v>314</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F48" s="21" t="s">
         <v>88</v>
@@ -47576,7 +48411,7 @@
         <v>193</v>
       </c>
       <c r="M48" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N48" s="47">
         <v>46111</v>
@@ -47652,7 +48487,7 @@
         <v>260</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F49" s="34" t="s">
         <v>100</v>
@@ -47676,7 +48511,7 @@
         <v>193</v>
       </c>
       <c r="M49" s="49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N49" s="39">
         <v>46111</v>
@@ -47760,7 +48595,7 @@
         <v>193</v>
       </c>
       <c r="M50" s="49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N50" s="38">
         <v>46111</v>
@@ -47829,10 +48664,10 @@
         <v>7</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F51" s="21" t="s">
         <v>88</v>
@@ -47941,7 +48776,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>94</v>
@@ -48037,7 +48872,7 @@
         <v>4</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>94</v>
@@ -48133,7 +48968,7 @@
         <v>4</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>94</v>
@@ -48242,7 +49077,7 @@
         <v>314</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F55" s="21" t="s">
         <v>100</v>
@@ -48326,7 +49161,7 @@
         <v>309</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F56" s="20" t="s">
         <v>88</v>
@@ -48350,10 +49185,10 @@
         <v>193</v>
       </c>
       <c r="M56" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N56" s="51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O56" s="12"/>
       <c r="P56" s="12" t="s">
@@ -48420,7 +49255,7 @@
         <v>297</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F57" s="20" t="s">
         <v>88</v>
@@ -48444,10 +49279,10 @@
         <v>193</v>
       </c>
       <c r="M57" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N57" s="51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O57" s="12"/>
       <c r="P57" s="12" t="s">
@@ -48520,7 +49355,7 @@
         <v>297</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F58" s="20" t="s">
         <v>100</v>
@@ -48544,10 +49379,10 @@
         <v>193</v>
       </c>
       <c r="M58" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N58" s="51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O58" s="12"/>
       <c r="P58" s="12"/>
@@ -48604,7 +49439,7 @@
         <v>312</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F59" s="21" t="s">
         <v>100</v>
@@ -48628,10 +49463,10 @@
         <v>193</v>
       </c>
       <c r="M59" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N59" s="52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O59" s="12"/>
       <c r="P59" s="12"/>
@@ -48688,7 +49523,7 @@
         <v>314</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F60" s="21" t="s">
         <v>100</v>
@@ -48712,10 +49547,10 @@
         <v>193</v>
       </c>
       <c r="M60" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N60" s="52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O60" s="12"/>
       <c r="P60" s="12"/>
@@ -48796,10 +49631,10 @@
         <v>193</v>
       </c>
       <c r="M61" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N61" s="52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O61" s="12"/>
       <c r="P61" s="12"/>
@@ -48892,10 +49727,10 @@
         <v>193</v>
       </c>
       <c r="M62" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N62" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O62" s="12"/>
       <c r="P62" s="12" t="s">
@@ -48968,7 +49803,7 @@
         <v>276</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F63" s="34" t="s">
         <v>100</v>
@@ -48992,10 +49827,10 @@
         <v>193</v>
       </c>
       <c r="M63" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N63" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O63" s="12"/>
       <c r="P63" s="12"/>
@@ -49049,10 +49884,10 @@
         <v>4</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F64" s="34" t="s">
         <v>88</v>
@@ -49076,10 +49911,10 @@
         <v>193</v>
       </c>
       <c r="M64" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N64" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O64" s="12"/>
       <c r="P64" s="12" t="s">
@@ -49161,10 +49996,10 @@
         <v>4</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F65" s="34" t="s">
         <v>88</v>
@@ -49188,10 +50023,10 @@
         <v>193</v>
       </c>
       <c r="M65" s="49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N65" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O65" s="12"/>
       <c r="P65" s="12" t="s">
@@ -49264,7 +50099,7 @@
         <v>312</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F66" s="21" t="s">
         <v>100</v>
@@ -49307,7 +50142,7 @@
       <c r="V66" s="76"/>
       <c r="W66" s="12"/>
       <c r="X66" s="67" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="Y66" s="12"/>
       <c r="Z66" s="12"/>
@@ -49348,7 +50183,7 @@
         <v>276</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F67" s="34" t="s">
         <v>100</v>
@@ -49473,7 +50308,7 @@
       <c r="V68" s="76"/>
       <c r="W68" s="12"/>
       <c r="X68" s="54" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Y68" s="12"/>
       <c r="Z68" s="12"/>
@@ -49511,10 +50346,10 @@
         <v>4</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F69" s="34" t="s">
         <v>88</v>
@@ -49541,7 +50376,7 @@
         <v>45960</v>
       </c>
       <c r="N69" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O69" s="12"/>
       <c r="P69" s="12" t="s">
@@ -49747,6 +50582,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O3:X4"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AH8"/>
     <mergeCell ref="AO8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
     <mergeCell ref="C9:I9"/>
@@ -49757,11 +50597,6 @@
     <mergeCell ref="AO9:AR9"/>
     <mergeCell ref="AS9:AU9"/>
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="O3:X4"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AH8"/>
   </mergeCells>
   <conditionalFormatting sqref="M11:M67 M69 M70:N70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="En Proceso">
@@ -49799,308 +50634,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06CB0E3-701B-45AE-AB79-3AAE71B2CA0C}">
-  <dimension ref="A2:T31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:20" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="375" t="s">
-        <v>391</v>
-      </c>
-      <c r="B2" s="375"/>
-      <c r="C2" s="375"/>
-      <c r="D2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E2" s="375" t="s">
-        <v>393</v>
-      </c>
-      <c r="F2" s="375"/>
-      <c r="G2" s="181" t="s">
-        <v>199</v>
-      </c>
-      <c r="H2" s="374" t="s">
-        <v>394</v>
-      </c>
-      <c r="I2" s="374"/>
-      <c r="J2" s="374"/>
-      <c r="K2" s="374" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="375"/>
-      <c r="M2" s="375"/>
-      <c r="N2" s="374" t="s">
-        <v>395</v>
-      </c>
-      <c r="O2" s="375"/>
-      <c r="P2" s="375"/>
-      <c r="Q2" s="376"/>
-      <c r="R2" s="374" t="s">
-        <v>211</v>
-      </c>
-      <c r="S2" s="375"/>
-    </row>
-    <row r="3" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="85" t="s">
-        <v>224</v>
-      </c>
-      <c r="B3" s="85" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="85" t="s">
-        <v>205</v>
-      </c>
-      <c r="D3" s="85" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" s="179" t="s">
-        <v>234</v>
-      </c>
-      <c r="F3" s="179" t="s">
-        <v>235</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>241</v>
-      </c>
-      <c r="H3" s="87" t="s">
-        <v>231</v>
-      </c>
-      <c r="I3" s="87" t="s">
-        <v>244</v>
-      </c>
-      <c r="J3" s="87" t="s">
-        <v>160</v>
-      </c>
-      <c r="K3" s="88" t="s">
-        <v>159</v>
-      </c>
-      <c r="L3" s="88" t="s">
-        <v>248</v>
-      </c>
-      <c r="M3" s="89" t="s">
-        <v>247</v>
-      </c>
-      <c r="N3" s="89" t="s">
-        <v>253</v>
-      </c>
-      <c r="O3" s="89" t="s">
-        <v>254</v>
-      </c>
-      <c r="P3" s="178" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q3" s="88" t="s">
-        <v>255</v>
-      </c>
-      <c r="R3" s="89" t="s">
-        <v>258</v>
-      </c>
-      <c r="S3" s="89" t="s">
-        <v>246</v>
-      </c>
-      <c r="T3" s="89" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="195" t="s">
-        <v>391</v>
-      </c>
-      <c r="B12" s="85" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="195" t="s">
-        <v>391</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="195" t="s">
-        <v>391</v>
-      </c>
-      <c r="B14" s="85" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="78" t="s">
-        <v>392</v>
-      </c>
-      <c r="B15" s="85" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="195" t="s">
-        <v>393</v>
-      </c>
-      <c r="B16" s="179" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="195" t="s">
-        <v>393</v>
-      </c>
-      <c r="B17" s="179" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="171" t="s">
-        <v>199</v>
-      </c>
-      <c r="B18" s="74" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="195" t="s">
-        <v>394</v>
-      </c>
-      <c r="B19" s="87" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="195" t="s">
-        <v>394</v>
-      </c>
-      <c r="B20" s="87" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="195" t="s">
-        <v>394</v>
-      </c>
-      <c r="B21" s="87" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="88" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="88" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="89" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="78" t="s">
-        <v>395</v>
-      </c>
-      <c r="B25" s="89" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="78" t="s">
-        <v>395</v>
-      </c>
-      <c r="B26" s="89" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="78" t="s">
-        <v>395</v>
-      </c>
-      <c r="B27" s="178" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="78" t="s">
-        <v>395</v>
-      </c>
-      <c r="B28" s="88" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>211</v>
-      </c>
-      <c r="B29" s="89" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>211</v>
-      </c>
-      <c r="B30" s="89" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B31" s="89" t="s">
-        <v>214</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:Q2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -50111,6 +50644,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D53C3A3428B1B4A9D164F0D85BEEA57" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="1b756714394f243dc1e59234ebaea7ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fc092c77-77a9-40ad-ae14-39067143678a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47b6ece98d39c8f8132b14d131b38829" ns2:_="">
     <xsd:import namespace="fc092c77-77a9-40ad-ae14-39067143678a"/>
@@ -50248,12 +50787,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62ABF450-D662-42F6-AC20-132C11E15452}">
   <ds:schemaRefs>
@@ -50263,6 +50796,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88112FF-E6D9-4EFB-A2F0-A6CBF29F2F7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50278,20 +50827,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EEA9B3D-0DA4-4009-82C0-0694809F88AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fc092c77-77a9-40ad-ae14-39067143678a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
+++ b/data/raw/CONTROL MAESTRO DE REFORMA CURRICULAR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran.sharepoint.com/sites/PlaneacinyGestinInstitucional-REFORMACURRICULAR/Documentos compartidos/REFORMA CURRICULAR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Reforma_Curricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13725" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3A4017C-D1F8-48C0-8B94-7155FDB6C489}"/>
+  <xr:revisionPtr revIDLastSave="13726" documentId="8_{3BAA4E05-85DC-4689-9347-38426449B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB3A83D9-0ED8-4965-B608-CFDF66E9DCC0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{5D2AA78B-CF8F-4F04-8CED-873384612ABA}"/>
   </bookViews>
@@ -73,7 +73,7 @@
     <comment ref="J9" authorId="0" shapeId="0" xr:uid="{4909E1DA-D04D-459F-A755-C874E2A2376C}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Maria Isabel</t>
       </text>
@@ -81,7 +81,7 @@
     <comment ref="S9" authorId="1" shapeId="0" xr:uid="{C5EACC81-0278-4BD6-BE1C-328BE6CEF044}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -89,7 +89,7 @@
     <comment ref="T9" authorId="2" shapeId="0" xr:uid="{07A9C90F-C4AF-4058-8369-82DC7D82B304}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Lina Giraldo</t>
       </text>
@@ -97,7 +97,7 @@
     <comment ref="U9" authorId="3" shapeId="0" xr:uid="{33379761-7408-47CA-A73F-96920D166F6F}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero
 </t>
@@ -106,7 +106,7 @@
     <comment ref="AA9" authorId="4" shapeId="0" xr:uid="{DA888406-B3C3-47EB-94C0-AD38A44E0A0E}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Hector</t>
       </text>
@@ -114,7 +114,7 @@
     <comment ref="AL9" authorId="5" shapeId="0" xr:uid="{AB292E73-2881-46CA-A2EC-13F131DCF115}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Luis Martín / Jonathan Camilo</t>
       </text>
@@ -122,7 +122,7 @@
     <comment ref="AR9" authorId="6" shapeId="0" xr:uid="{469532B5-891A-4F4C-925C-AFAB7020C3BF}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Yady fernanda
 </t>
@@ -131,7 +131,7 @@
     <comment ref="BD9" authorId="7" shapeId="0" xr:uid="{4F4D565E-CBAD-4B43-8202-B4F4327A7F61}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Ivonne</t>
       </text>
@@ -139,7 +139,7 @@
     <comment ref="BQ9" authorId="8" shapeId="0" xr:uid="{7492BF5A-A8EA-4806-BFAF-95DE22CE85C5}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Laura Barrera</t>
       </text>
@@ -147,7 +147,7 @@
     <comment ref="AD10" authorId="9" shapeId="0" xr:uid="{EBC3B04C-562F-4E8D-B1E3-F992E17EAF0F}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Aprobación interna </t>
       </text>
@@ -180,7 +180,7 @@
     <comment ref="J9" authorId="0" shapeId="0" xr:uid="{80B52061-08F6-47ED-A848-F47BBBD771FF}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Maria Isabel</t>
       </text>
@@ -188,7 +188,7 @@
     <comment ref="R9" authorId="1" shapeId="0" xr:uid="{D8DA1F30-A300-40F4-B476-925996CD8443}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -196,7 +196,7 @@
     <comment ref="S9" authorId="2" shapeId="0" xr:uid="{7505DC0C-967B-426C-BC16-554113003C7D}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Lina Giraldo</t>
       </text>
@@ -204,7 +204,7 @@
     <comment ref="T9" authorId="3" shapeId="0" xr:uid="{E461B7D9-0641-45C6-B1E3-DC5A9AAB3A7F}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero
 </t>
@@ -213,7 +213,7 @@
     <comment ref="V9" authorId="4" shapeId="0" xr:uid="{3C05002E-BD16-4D38-A66E-AF06581FFA22}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Hector</t>
       </text>
@@ -221,7 +221,7 @@
     <comment ref="AD9" authorId="5" shapeId="0" xr:uid="{3AD9E8E6-50E3-4D5D-95F5-5ADA3E45292E}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Luis Martín / Jonathan Camilo</t>
       </text>
@@ -229,7 +229,7 @@
     <comment ref="AL9" authorId="6" shapeId="0" xr:uid="{A8DE3515-C1E1-49EA-AFBF-F0B22E7FF84F}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Yady fernanda
 </t>
@@ -238,7 +238,7 @@
     <comment ref="AT9" authorId="7" shapeId="0" xr:uid="{08ACDCC1-6649-4D0D-A86B-69B7D4B48783}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Ivonne</t>
       </text>
@@ -246,7 +246,7 @@
     <comment ref="BC9" authorId="8" shapeId="0" xr:uid="{A8FB029E-3F6A-4304-877C-1A3D4AB675EB}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Laura Barrera</t>
       </text>
@@ -254,7 +254,7 @@
     <comment ref="R10" authorId="9" shapeId="0" xr:uid="{411F6E4D-EB04-444D-97BB-743F5F223921}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -262,7 +262,7 @@
     <comment ref="S10" authorId="10" shapeId="0" xr:uid="{9429D19F-F6E1-4D65-96A4-BBC6C65BA555}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Lina Giraldo</t>
       </text>
@@ -270,7 +270,7 @@
     <comment ref="T10" authorId="11" shapeId="0" xr:uid="{229B08B3-705D-48B7-A5B3-05517A327727}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero
 </t>
@@ -279,7 +279,7 @@
     <comment ref="Y10" authorId="12" shapeId="0" xr:uid="{98402C78-9325-4277-98CE-1DE573CC177E}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Aprobación interna </t>
       </text>
@@ -287,7 +287,7 @@
     <comment ref="AY13" authorId="13" shapeId="0" xr:uid="{FB111D15-BC54-46A2-9B42-764A52E23BFF}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Pendiente acto administrativo, para confirmar periodo de inicio</t>
       </text>
@@ -295,7 +295,7 @@
     <comment ref="AK54" authorId="14" shapeId="0" xr:uid="{60A29768-0473-460C-80A7-6B195BBBC9AA}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Módulos que se hicieron antes de establecer el cronograma de la reforma.</t>
       </text>
@@ -303,7 +303,7 @@
     <comment ref="AK56" authorId="15" shapeId="0" xr:uid="{D36016F3-8B56-4D59-B47D-9F6A1EA5603E}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Módulos que se hicieron antes de establecer el cronograma de la reforma.</t>
       </text>
@@ -333,7 +333,7 @@
     <comment ref="J9" authorId="0" shapeId="0" xr:uid="{AB1486C7-AA92-4748-891B-886743035FDC}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Maria Isabel</t>
       </text>
@@ -341,7 +341,7 @@
     <comment ref="R9" authorId="1" shapeId="0" xr:uid="{5E2A0871-3C6A-43AF-B856-9A20F44C0E24}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -349,7 +349,7 @@
     <comment ref="S9" authorId="2" shapeId="0" xr:uid="{D2E187A2-AF3B-4B43-AD8A-5A22A99E567B}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Lina Giraldo</t>
       </text>
@@ -357,7 +357,7 @@
     <comment ref="T9" authorId="3" shapeId="0" xr:uid="{ED914BC0-A9AD-4460-B4AD-64B21C38754F}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero
 </t>
@@ -366,7 +366,7 @@
     <comment ref="V9" authorId="4" shapeId="0" xr:uid="{AC196D12-BAF7-4D77-BB76-8DDDB1D1AAED}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Hector</t>
       </text>
@@ -374,7 +374,7 @@
     <comment ref="AC9" authorId="5" shapeId="0" xr:uid="{B5416B51-2416-4442-87A8-60557435D0C6}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Luis Martín / Jonathan Camilo</t>
       </text>
@@ -382,7 +382,7 @@
     <comment ref="AI9" authorId="6" shapeId="0" xr:uid="{AF20519C-A4E1-4A0C-9814-C243E278D15B}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Yady fernanda
 </t>
@@ -391,7 +391,7 @@
     <comment ref="AO9" authorId="7" shapeId="0" xr:uid="{6A140D46-EDD4-4F6C-AA4F-2CBC120DF7BC}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Ivonne</t>
       </text>
@@ -399,7 +399,7 @@
     <comment ref="AS9" authorId="8" shapeId="0" xr:uid="{1D6AE7E6-0283-49B1-9DFE-C7D5B111CED2}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Laura Barrera</t>
       </text>
@@ -407,7 +407,7 @@
     <comment ref="R10" authorId="9" shapeId="0" xr:uid="{E74F1B1E-CE79-46D3-807A-5DC12A7AF859}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -415,7 +415,7 @@
     <comment ref="S10" authorId="10" shapeId="0" xr:uid="{AA67B0D4-AF29-4510-BBF9-3D69C706909F}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Lina Giraldo</t>
       </text>
@@ -423,7 +423,7 @@
     <comment ref="T10" authorId="11" shapeId="0" xr:uid="{E23E8F9A-23D4-451D-B6DF-68EA924C4E68}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero
 </t>
@@ -432,7 +432,7 @@
     <comment ref="Y10" authorId="12" shapeId="0" xr:uid="{0C99F784-E3FA-43BC-809B-1404E6FC59EA}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Aprobación interna </t>
       </text>
@@ -451,7 +451,7 @@
     <comment ref="C3" authorId="0" shapeId="0" xr:uid="{3D8D95EC-E3AE-4A32-8BE6-752AA4DE3B2A}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -459,7 +459,7 @@
     <comment ref="B14" authorId="1" shapeId="0" xr:uid="{6CD20443-83D8-4BD3-A822-701BF3EC7215}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -477,7 +477,7 @@
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{243354BE-D8F0-45DF-A6E5-F55CAC4D8EC2}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Diligencia Diana Baquero</t>
       </text>
@@ -4008,29 +4008,68 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="53" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="52" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFo